--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rd8eb4e032ada44af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R25815d70cabc45c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1363,7 +1363,7 @@
         <x:v>collection.staff-doubao.story</x:v>
       </x:c>
       <x:c r="C98" s="8" t="str">
-        <x:v>豆包会把每枚零钱朝同一个方向码好。客流再急，他也能一边报数一边守住收银台，最怕的是下班前少算一枚硬币。</x:v>
+        <x:v>豆包会把每枚金币朝同一个方向码好。客流再急，他也能一边报数一边守住收银台，最怕的是下班前少算一枚硬币。</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1484,7 +1484,7 @@
         <x:v>collection.enemy-jelly.traits</x:v>
       </x:c>
       <x:c r="C109" s="8" t="str">
-        <x:v>耐久中等、速度适中，零钱奖励较多。与快客混行时不要忽略它。</x:v>
+        <x:v>耐久中等、速度适中，金币奖励较多。与快客混行时不要忽略它。</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -1913,7 +1913,7 @@
         <x:v>ui.CollectionData.001</x:v>
       </x:c>
       <x:c r="C148" s="8" t="str">
-        <x:v>基础耐久</x:v>
+        <x:v>血量</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -1924,7 +1924,7 @@
         <x:v>ui.CollectionData.002</x:v>
       </x:c>
       <x:c r="C149" s="8" t="str">
-        <x:v>基础移速</x:v>
+        <x:v>移速</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -1935,7 +1935,7 @@
         <x:v>ui.CollectionData.003</x:v>
       </x:c>
       <x:c r="C150" s="8" t="str">
-        <x:v>零钱奖励</x:v>
+        <x:v>金币奖励</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -1946,7 +1946,7 @@
         <x:v>ui.CollectionData.004</x:v>
       </x:c>
       <x:c r="C151" s="8" t="str">
-        <x:v>漏怪扣耐久</x:v>
+        <x:v>伤害值</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -1957,7 +1957,7 @@
         <x:v>ui.CollectionData.005</x:v>
       </x:c>
       <x:c r="C152" s="8" t="str">
-        <x:v>上岗费用</x:v>
+        <x:v>建造费用</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -1968,7 +1968,7 @@
         <x:v>ui.CollectionData.006</x:v>
       </x:c>
       <x:c r="C153" s="8" t="str">
-        <x:v>一级伤害</x:v>
+        <x:v>伤害</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -1979,7 +1979,7 @@
         <x:v>ui.CollectionData.007</x:v>
       </x:c>
       <x:c r="C154" s="8" t="str">
-        <x:v>攻击间隔</x:v>
+        <x:v>攻速</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -1990,7 +1990,7 @@
         <x:v>ui.CollectionData.008</x:v>
       </x:c>
       <x:c r="C155" s="8" t="str">
-        <x:v>{p0} 秒</x:v>
+        <x:v>{p0}次/秒</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2001,7 +2001,7 @@
         <x:v>ui.CollectionData.009</x:v>
       </x:c>
       <x:c r="C156" s="8" t="str">
-        <x:v>基础射程</x:v>
+        <x:v>射程</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2067,8 +2067,8 @@
         <x:v>ui.CollectionData.015</x:v>
       </x:c>
       <x:c r="C162" s="8" t="str">
-        <x:v>耐久随关卡和波次变化
-移速受关卡影响</x:v>
+        <x:v>显示基础血量，实战随关卡和波次变化
+基础移速固定，仍受技能影响</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2079,7 +2079,7 @@
         <x:v>ui.CollectionData.016</x:v>
       </x:c>
       <x:c r="C163" s="8" t="str">
-        <x:v>在冒险模式中遇见后解锁</x:v>
+        <x:v>未遭遇</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2145,7 +2145,7 @@
         <x:v>ui.GameMenuView.006</x:v>
       </x:c>
       <x:c r="C169" s="8" t="str">
-        <x:v>暂未开放</x:v>
+        <x:v>固定体验关 · 限定4名店员</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2563,7 +2563,7 @@
         <x:v>ui.GameRoot.008</x:v>
       </x:c>
       <x:c r="C207" s="8" t="str">
-        <x:v>{p0}关{p1}</x:v>
+        <x:v>第{p0}关{p1}</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -2629,7 +2629,7 @@
         <x:v>ui.GameRoot.014</x:v>
       </x:c>
       <x:c r="C213" s="8" t="str">
-        <x:v>下一波 {p0}/{p1}</x:v>
+        <x:v>下一波</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
@@ -2651,7 +2651,7 @@
         <x:v>ui.GameRoot.016</x:v>
       </x:c>
       <x:c r="C215" s="8" t="str">
-        <x:v>返回首页</x:v>
+        <x:v>返回选关</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
@@ -2718,7 +2718,7 @@
       </x:c>
       <x:c r="C221" s="8" t="str">
         <x:v>赶走 {p0} 只夜间精怪
-本局收入 {p1}</x:v>
+金币 {p1}</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="15" hidden="0" customHeight="1">
@@ -2839,7 +2839,7 @@
         <x:v>ui.GameRoot.033</x:v>
       </x:c>
       <x:c r="C232" s="8" t="str">
-        <x:v>零钱</x:v>
+        <x:v>金币</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="15" hidden="0" customHeight="1">
@@ -2949,7 +2949,7 @@
         <x:v>ui.GameRoot.043</x:v>
       </x:c>
       <x:c r="C242" s="8" t="str">
-        <x:v>夜班零钱不够，先赶走一些精怪吧</x:v>
+        <x:v>夜班金币不够，先赶走一些精怪吧</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="15" hidden="0" customHeight="1">
@@ -2993,7 +2993,7 @@
         <x:v>ui.GameRoot.047</x:v>
       </x:c>
       <x:c r="C246" s="8" t="str">
-        <x:v>升级所需零钱不足</x:v>
+        <x:v>升级所需金币不足</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="15" hidden="0" customHeight="1">
@@ -3037,7 +3037,7 @@
         <x:v>ui.GameRoot.051</x:v>
       </x:c>
       <x:c r="C250" s="8" t="str">
-        <x:v>紧急零钱 +{p0}</x:v>
+        <x:v>紧急金币 +{p0}</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="15" hidden="0" customHeight="1">
@@ -3070,7 +3070,7 @@
         <x:v>ui.GameRoot.054</x:v>
       </x:c>
       <x:c r="C253" s="8" t="str">
-        <x:v>广告未完整观看，暂未补充道具</x:v>
+        <x:v>广告未完成或暂不可用，道具未使用</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="15" hidden="0" customHeight="1">
@@ -3092,7 +3092,7 @@
         <x:v>ui.GameRoot.056</x:v>
       </x:c>
       <x:c r="C255" s="8" t="str">
-        <x:v>广告未完整观看，暂未复活</x:v>
+        <x:v>广告未完成或暂不可用，未复活</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="15" hidden="0" customHeight="1">
@@ -3114,7 +3114,7 @@
         <x:v>ui.GameRoot.058</x:v>
       </x:c>
       <x:c r="C257" s="8" t="str">
-        <x:v>暂无广告，本次已继续营业</x:v>
+        <x:v>广告暂不可用，请稍后重试</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3269,6 +3269,149 @@
       </x:c>
       <x:c r="C271" s="8" t="str">
         <x:v>BOSS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" t="n">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B272" t="str">
+        <x:v>ui.opt.upgradeCost</x:v>
+      </x:c>
+      <x:c r="C272" t="str">
+        <x:v>升级费用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" t="n">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B273" t="str">
+        <x:v>ui.opt.staffLevel1</x:v>
+      </x:c>
+      <x:c r="C273" t="str">
+        <x:v>1级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" t="n">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B274" t="str">
+        <x:v>ui.opt.staffLevel2</x:v>
+      </x:c>
+      <x:c r="C274" t="str">
+        <x:v>2级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B275" t="str">
+        <x:v>ui.opt.staffLevel3</x:v>
+      </x:c>
+      <x:c r="C275" t="str">
+        <x:v>3级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" t="n">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B276" t="str">
+        <x:v>ui.opt.gold</x:v>
+      </x:c>
+      <x:c r="C276" t="str">
+        <x:v>{p0}金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" t="n">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B277" t="str">
+        <x:v>challenge.title</x:v>
+      </x:c>
+      <x:c r="C277" t="str">
+        <x:v>夜班极限挑战</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="n">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B278" t="str">
+        <x:v>challenge.goal</x:v>
+      </x:c>
+      <x:c r="C278" t="str">
+        <x:v>限定店员搭配，守住最后一班</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="n">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B279" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="C279" t="str">
+        <x:v>首领来袭，准备集中火力！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="n">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B280" t="str">
+        <x:v>challenge.hud</x:v>
+      </x:c>
+      <x:c r="C280" t="str">
+        <x:v>挑战体验关</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="n">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B281" t="str">
+        <x:v>challenge.win</x:v>
+      </x:c>
+      <x:c r="C281" t="str">
+        <x:v>挑战守护完成！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B282" t="str">
+        <x:v>challenge.return</x:v>
+      </x:c>
+      <x:c r="C282" t="str">
+        <x:v>返回首页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="n">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B283" t="str">
+        <x:v>challenge.enter</x:v>
+      </x:c>
+      <x:c r="C283" t="str">
+        <x:v>固定挑战：棉棉、布丁、咕咕、薄荷</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="n">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B284" t="str">
+        <x:v>ui.opt.startWave</x:v>
+      </x:c>
+      <x:c r="C284" t="str">
+        <x:v>开始下一波</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R25815d70cabc45c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R7f812aba51624234"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2266,7 +2266,7 @@
         <x:v>ui.GameMenuView.017</x:v>
       </x:c>
       <x:c r="C180" s="8" t="str">
-        <x:v>{p0} · {p1} 波</x:v>
+        <x:v>共{p0}波</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R7f812aba51624234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R7166bc7fb3b84619"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2519,7 +2519,7 @@
         <x:v>ui.GameRoot.004</x:v>
       </x:c>
       <x:c r="C203" s="8" t="str">
-        <x:v>GM 关卡选择</x:v>
+        <x:v>GM 调试</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>ui.GameRoot.005</x:v>
       </x:c>
       <x:c r="C204" s="8" t="str">
-        <x:v>测试选关，不改变正式解锁</x:v>
+        <x:v>图鉴预览仅本次生效，不改正式存档</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3412,6 +3412,61 @@
       </x:c>
       <x:c r="C284" t="str">
         <x:v>开始下一波</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B285" t="str">
+        <x:v>ui.gm.enemies</x:v>
+      </x:c>
+      <x:c r="C285" t="str">
+        <x:v>解锁怪物</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" t="n">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B286" t="str">
+        <x:v>ui.gm.bosses</x:v>
+      </x:c>
+      <x:c r="C286" t="str">
+        <x:v>解锁 BOSS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" t="n">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B287" t="str">
+        <x:v>ui.gm.staff</x:v>
+      </x:c>
+      <x:c r="C287" t="str">
+        <x:v>解锁店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" t="n">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B288" t="str">
+        <x:v>ui.gm.all</x:v>
+      </x:c>
+      <x:c r="C288" t="str">
+        <x:v>解锁全部图鉴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" t="n">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B289" t="str">
+        <x:v>ui.gm.restore</x:v>
+      </x:c>
+      <x:c r="C289" t="str">
+        <x:v>恢复正式图鉴</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R7166bc7fb3b84619"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R719bf97fc88f4cef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3469,6 +3469,204 @@
         <x:v>恢复正式图鉴</x:v>
       </x:c>
     </x:row>
+    <x:row r="290">
+      <x:c r="A290" t="n">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B290" t="str">
+        <x:v>guide.place</x:v>
+      </x:c>
+      <x:c r="C290" t="str">
+        <x:v>点空位，安排{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B291" t="str">
+        <x:v>guide.choose</x:v>
+      </x:c>
+      <x:c r="C291" t="str">
+        <x:v>选择{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" t="n">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B292" t="str">
+        <x:v>guide.coins</x:v>
+      </x:c>
+      <x:c r="C292" t="str">
+        <x:v>金币够了再安排{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" t="n">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B293" t="str">
+        <x:v>guide.build.select</x:v>
+      </x:c>
+      <x:c r="C293" t="str">
+        <x:v>点空位，安排豆包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B294" t="str">
+        <x:v>guide.build.action</x:v>
+      </x:c>
+      <x:c r="C294" t="str">
+        <x:v>选择豆包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" t="n">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B295" t="str">
+        <x:v>guide.build.wait</x:v>
+      </x:c>
+      <x:c r="C295" t="str">
+        <x:v>豆包会自动攻击</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" t="n">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B296" t="str">
+        <x:v>guide.upgrade.select</x:v>
+      </x:c>
+      <x:c r="C296" t="str">
+        <x:v>点豆包，看看升级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" t="n">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B297" t="str">
+        <x:v>guide.upgrade.action</x:v>
+      </x:c>
+      <x:c r="C297" t="str">
+        <x:v>升级豆包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B298" t="str">
+        <x:v>guide.upgrade.wait</x:v>
+      </x:c>
+      <x:c r="C298" t="str">
+        <x:v>攒够金币再升级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" t="n">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B299" t="str">
+        <x:v>guide.combo.select</x:v>
+      </x:c>
+      <x:c r="C299" t="str">
+        <x:v>把棉棉放在豆包旁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B300" t="str">
+        <x:v>guide.combo.action</x:v>
+      </x:c>
+      <x:c r="C300" t="str">
+        <x:v>选择棉棉</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B301" t="str">
+        <x:v>guide.combo.wait</x:v>
+      </x:c>
+      <x:c r="C301" t="str">
+        <x:v>棉棉减速，豆包接着打</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B302" t="str">
+        <x:v>guide.area.select</x:v>
+      </x:c>
+      <x:c r="C302" t="str">
+        <x:v>安排布丁对付成群精怪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303" t="n">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B303" t="str">
+        <x:v>guide.area.action</x:v>
+      </x:c>
+      <x:c r="C303" t="str">
+        <x:v>选择布丁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B304" t="str">
+        <x:v>guide.area.wait</x:v>
+      </x:c>
+      <x:c r="C304" t="str">
+        <x:v>布丁能一次打到多只精怪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B305" t="str">
+        <x:v>guide.clear.select</x:v>
+      </x:c>
+      <x:c r="C305" t="str">
+        <x:v>点店员旁的杂物</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B306" t="str">
+        <x:v>guide.clear.action</x:v>
+      </x:c>
+      <x:c r="C306" t="str">
+        <x:v>点杂物，清理后获得金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B307" t="str">
+        <x:v>guide.clear.wait</x:v>
+      </x:c>
+      <x:c r="C307" t="str">
+        <x:v>店员空闲时会清理杂物</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R719bf97fc88f4cef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rb3c94ccc51a44c6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3667,6 +3667,28 @@
         <x:v>店员空闲时会清理杂物</x:v>
       </x:c>
     </x:row>
+    <x:row r="308">
+      <x:c r="A308" t="n">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B308" t="str">
+        <x:v>ui.gm.reset</x:v>
+      </x:c>
+      <x:c r="C308" t="str">
+        <x:v>重置进度</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B309" t="str">
+        <x:v>ui.gm.resetConfirm</x:v>
+      </x:c>
+      <x:c r="C309" t="str">
+        <x:v>再次点击确认</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rb3c94ccc51a44c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R0784a41ce0dc4e81"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3689,6 +3689,161 @@
         <x:v>再次点击确认</x:v>
       </x:c>
     </x:row>
+    <x:row r="310">
+      <x:c r="A310" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B310" t="str">
+        <x:v>feedback.boss.mini</x:v>
+      </x:c>
+      <x:c r="C310" t="str">
+        <x:v>小首领来袭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B311" t="str">
+        <x:v>feedback.boss.major</x:v>
+      </x:c>
+      <x:c r="C311" t="str">
+        <x:v>大首领来袭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B312" t="str">
+        <x:v>feedback.boss.defeated</x:v>
+      </x:c>
+      <x:c r="C312" t="str">
+        <x:v>首领已击退</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313" t="n">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B313" t="str">
+        <x:v>feedback.boss.health</x:v>
+      </x:c>
+      <x:c r="C313" t="str">
+        <x:v>{p0} / {p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" t="n">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B314" t="str">
+        <x:v>result.stats</x:v>
+      </x:c>
+      <x:c r="C314" t="str">
+        <x:v>剩余耐久 {p0}/{p1}  ·  清障 {p2}/{p3}
+击退 {p4}  ·  获得金币 {p5}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B315" t="str">
+        <x:v>result.next</x:v>
+      </x:c>
+      <x:c r="C315" t="str">
+        <x:v>下一关 · 第{p0}关</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316" t="n">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B316" t="str">
+        <x:v>result.open</x:v>
+      </x:c>
+      <x:c r="C316" t="str">
+        <x:v>第{p0}关已解锁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317" t="n">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B317" t="str">
+        <x:v>result.staff</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>新店员 {p0} 名</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B318" t="str">
+        <x:v>result.collection</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>图鉴新增 {p0} 项</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B319" t="str">
+        <x:v>result.complete</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>二十关全部完成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B320" t="str">
+        <x:v>result.progress</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>完成 {p0}/{p1} 波</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" t="n">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B321" t="str">
+        <x:v>result.unlockTitle</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>新解锁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322">
+      <x:c r="A322" t="n">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B322" t="str">
+        <x:v>result.noUnlock</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>本局记录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B323" t="str">
+        <x:v>result.more</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>另有 {p0} 项新图鉴</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R0784a41ce0dc4e81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R9d6edc9301f746fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3844,6 +3844,525 @@
         <x:v>另有 {p0} 项新图鉴</x:v>
       </x:c>
     </x:row>
+    <x:row r="324">
+      <x:c r="A324" t="n">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B324" t="str">
+        <x:v>branch.sprout_heavy.name</x:v>
+      </x:c>
+      <x:c r="C324" t="str">
+        <x:v>重投</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325">
+      <x:c r="A325" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B325" t="str">
+        <x:v>branch.sprout_heavy.summary</x:v>
+      </x:c>
+      <x:c r="C325" t="str">
+        <x:v>单发伤害高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326">
+      <x:c r="A326" t="n">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B326" t="str">
+        <x:v>branch.sprout_heavy.tradeoff</x:v>
+      </x:c>
+      <x:c r="C326" t="str">
+        <x:v>攻击间隔长</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327" t="n">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B327" t="str">
+        <x:v>evolution.sprout_heavy.story</x:v>
+      </x:c>
+      <x:c r="C327" t="str">
+        <x:v>豆包把收银台旁的投掷器换大了一号。每次出手前，他仍要先把腰包里的硬币码整齐。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328" t="n">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B328" t="str">
+        <x:v>branch.sprout_burst.name</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>连投</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329" t="n">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B329" t="str">
+        <x:v>branch.sprout_burst.summary</x:v>
+      </x:c>
+      <x:c r="C329" t="str">
+        <x:v>两连发，可接续补刀</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330" t="n">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B330" t="str">
+        <x:v>branch.sprout_burst.tradeoff</x:v>
+      </x:c>
+      <x:c r="C330" t="str">
+        <x:v>单发伤害低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331">
+      <x:c r="A331" t="n">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B331" t="str">
+        <x:v>evolution.sprout_burst.story</x:v>
+      </x:c>
+      <x:c r="C331" t="str">
+        <x:v>晚高峰时，豆包学会了两手交替接零钱。现在守门也用上了这套本领。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332" t="n">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B332" t="str">
+        <x:v>branch.frost_deep.name</x:v>
+      </x:c>
+      <x:c r="C332" t="str">
+        <x:v>深冷</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333" t="n">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B333" t="str">
+        <x:v>branch.frost_deep.summary</x:v>
+      </x:c>
+      <x:c r="C333" t="str">
+        <x:v>单目标减速更强</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334" t="n">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B334" t="str">
+        <x:v>branch.frost_deep.tradeoff</x:v>
+      </x:c>
+      <x:c r="C334" t="str">
+        <x:v>射程较短</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B335" t="str">
+        <x:v>evolution.frost_deep.story</x:v>
+      </x:c>
+      <x:c r="C335" t="str">
+        <x:v>棉棉给冷风器添了一层保温套。来客走慢些，她就有时间把散落的商品放回原位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336">
+      <x:c r="A336" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B336" t="str">
+        <x:v>branch.frost_dual.name</x:v>
+      </x:c>
+      <x:c r="C336" t="str">
+        <x:v>双向冷风</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337" t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B337" t="str">
+        <x:v>branch.frost_dual.summary</x:v>
+      </x:c>
+      <x:c r="C337" t="str">
+        <x:v>同时减速两个目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338">
+      <x:c r="A338" t="n">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B338" t="str">
+        <x:v>branch.frost_dual.tradeoff</x:v>
+      </x:c>
+      <x:c r="C338" t="str">
+        <x:v>每个目标减速较弱</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339">
+      <x:c r="A339" t="n">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B339" t="str">
+        <x:v>evolution.frost_dual.story</x:v>
+      </x:c>
+      <x:c r="C339" t="str">
+        <x:v>通道两头都有人赶来，棉棉便把风口分成两路。哪边的货架乱了，她都看得见。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340">
+      <x:c r="A340" t="n">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B340" t="str">
+        <x:v>branch.bloom_focus.name</x:v>
+      </x:c>
+      <x:c r="C340" t="str">
+        <x:v>集中爆破</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341">
+      <x:c r="A341" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B341" t="str">
+        <x:v>branch.bloom_focus.summary</x:v>
+      </x:c>
+      <x:c r="C341" t="str">
+        <x:v>主目标伤害高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342" t="n">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B342" t="str">
+        <x:v>branch.bloom_focus.tradeoff</x:v>
+      </x:c>
+      <x:c r="C342" t="str">
+        <x:v>范围小，旁伤低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343" t="n">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B343" t="str">
+        <x:v>evolution.bloom_focus.story</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>布丁把烤锅换成了深口的。火候集中以后，最厚的那份热食也能按时出炉。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344">
+      <x:c r="A344" t="n">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B344" t="str">
+        <x:v>branch.bloom_wide.name</x:v>
+      </x:c>
+      <x:c r="C344" t="str">
+        <x:v>广域爆破</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B345" t="str">
+        <x:v>branch.bloom_wide.summary</x:v>
+      </x:c>
+      <x:c r="C345" t="str">
+        <x:v>爆炸覆盖更广</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346">
+      <x:c r="A346" t="n">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B346" t="str">
+        <x:v>branch.bloom_wide.tradeoff</x:v>
+      </x:c>
+      <x:c r="C346" t="str">
+        <x:v>单个目标伤害低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B347" t="str">
+        <x:v>evolution.bloom_wide.story</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>排队的人越来越多，布丁找来一只宽烤盘。一炉多做几份，夜班同伴也能早点吃上。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348" t="n">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B348" t="str">
+        <x:v>ui.evolution.action</x:v>
+      </x:c>
+      <x:c r="C348" t="str">
+        <x:v>进化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349">
+      <x:c r="A349" t="n">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B349" t="str">
+        <x:v>ui.evolution.choose</x:v>
+      </x:c>
+      <x:c r="C349" t="str">
+        <x:v>选择进化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B350" t="str">
+        <x:v>ui.evolution.base</x:v>
+      </x:c>
+      <x:c r="C350" t="str">
+        <x:v>基础形态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351">
+      <x:c r="A351" t="n">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B351" t="str">
+        <x:v>ui.evolution.locked</x:v>
+      </x:c>
+      <x:c r="C351" t="str">
+        <x:v>???</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352" t="n">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B352" t="str">
+        <x:v>ui.evolution.unlock</x:v>
+      </x:c>
+      <x:c r="C352" t="str">
+        <x:v>首次进化后收录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353" t="n">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B353" t="str">
+        <x:v>ui.evolution.new</x:v>
+      </x:c>
+      <x:c r="C353" t="str">
+        <x:v>新形态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354">
+      <x:c r="A354" t="n">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B354" t="str">
+        <x:v>ui.evolution.collection</x:v>
+      </x:c>
+      <x:c r="C354" t="str">
+        <x:v>进化形态 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B355" t="str">
+        <x:v>ui.evolution.cost</x:v>
+      </x:c>
+      <x:c r="C355" t="str">
+        <x:v>进化费用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356">
+      <x:c r="A356" t="n">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B356" t="str">
+        <x:v>ui.evolution.complete</x:v>
+      </x:c>
+      <x:c r="C356" t="str">
+        <x:v>已进化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357">
+      <x:c r="A357" t="n">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B357" t="str">
+        <x:v>ui.evolution.button</x:v>
+      </x:c>
+      <x:c r="C357" t="str">
+        <x:v>进化
+●{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358" t="n">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B358" t="str">
+        <x:v>ui.evolution.name</x:v>
+      </x:c>
+      <x:c r="C358" t="str">
+        <x:v>{p0}·{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359">
+      <x:c r="A359" t="n">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B359" t="str">
+        <x:v>ui.evolution.rate</x:v>
+      </x:c>
+      <x:c r="C359" t="str">
+        <x:v>{p1}秒/轮</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360" t="n">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B360" t="str">
+        <x:v>ui.evolution.slow</x:v>
+      </x:c>
+      <x:c r="C360" t="str">
+        <x:v>移速降至{p0}% · {p1}秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361" t="n">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B361" t="str">
+        <x:v>ui.evolution.splash</x:v>
+      </x:c>
+      <x:c r="C361" t="str">
+        <x:v>范围{p0} · 旁伤{p1}%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362" t="n">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B362" t="str">
+        <x:v>ui.evolution.targets</x:v>
+      </x:c>
+      <x:c r="C362" t="str">
+        <x:v>每轮至多{p0}个目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363">
+      <x:c r="A363" t="n">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B363" t="str">
+        <x:v>ui.evolution.stats</x:v>
+      </x:c>
+      <x:c r="C363" t="str">
+        <x:v>伤害{p0} · 周期{p1}秒
+射程{p2}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364">
+      <x:c r="A364" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B364" t="str">
+        <x:v>ui.evolution.lockedHint</x:v>
+      </x:c>
+      <x:c r="C364" t="str">
+        <x:v>战斗中完成此形态的进化后收录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365">
+      <x:c r="A365" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B365" t="str">
+        <x:v>ui.evolution.shapeCount</x:v>
+      </x:c>
+      <x:c r="C365" t="str">
+        <x:v>形态 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366">
+      <x:c r="A366" t="n">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B366" t="str">
+        <x:v>ui.evolution.base1</x:v>
+      </x:c>
+      <x:c r="C366" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367">
+      <x:c r="A367" t="n">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B367" t="str">
+        <x:v>ui.evolution.base2</x:v>
+      </x:c>
+      <x:c r="C367" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368">
+      <x:c r="A368" t="n">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B368" t="str">
+        <x:v>ui.evolution.profile</x:v>
+      </x:c>
+      <x:c r="C368" t="str">
+        <x:v>进化形态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369">
+      <x:c r="A369" t="n">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B369" t="str">
+        <x:v>ui.evolution.result</x:v>
+      </x:c>
+      <x:c r="C369" t="str">
+        <x:v>新形态 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370">
+      <x:c r="A370" t="n">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B370" t="str">
+        <x:v>ui.evolution.costValue</x:v>
+      </x:c>
+      <x:c r="C370" t="str">
+        <x:v>●{p0}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R9d6edc9301f746fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R64fa2c451e1a46f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4363,6 +4363,303 @@
         <x:v>●{p0}</x:v>
       </x:c>
     </x:row>
+    <x:row r="371">
+      <x:c r="A371" t="n">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B371" t="str">
+        <x:v>ui.loadout.title</x:v>
+      </x:c>
+      <x:c r="C371" t="str">
+        <x:v>出战准备</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372">
+      <x:c r="A372" t="n">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B372" t="str">
+        <x:v>ui.loadout.selected</x:v>
+      </x:c>
+      <x:c r="C372" t="str">
+        <x:v>出战店员 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373">
+      <x:c r="A373" t="n">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B373" t="str">
+        <x:v>ui.loadout.start</x:v>
+      </x:c>
+      <x:c r="C373" t="str">
+        <x:v>开始关卡</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374">
+      <x:c r="A374" t="n">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B374" t="str">
+        <x:v>ui.loadout.choose</x:v>
+      </x:c>
+      <x:c r="C374" t="str">
+        <x:v>选择出战店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375">
+      <x:c r="A375" t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B375" t="str">
+        <x:v>ui.loadout.replace</x:v>
+      </x:c>
+      <x:c r="C375" t="str">
+        <x:v>选择要替换的出战位</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376">
+      <x:c r="A376" t="n">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B376" t="str">
+        <x:v>ui.loadout.empty</x:v>
+      </x:c>
+      <x:c r="C376" t="str">
+        <x:v>空位</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377">
+      <x:c r="A377" t="n">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B377" t="str">
+        <x:v>ui.loadout.ready</x:v>
+      </x:c>
+      <x:c r="C377" t="str">
+        <x:v>出战店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378">
+      <x:c r="A378" t="n">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="B378" t="str">
+        <x:v>ui.loadout.info</x:v>
+      </x:c>
+      <x:c r="C378" t="str">
+        <x:v>详情</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379">
+      <x:c r="A379" t="n">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B379" t="str">
+        <x:v>ui.loadout.stats</x:v>
+      </x:c>
+      <x:c r="C379" t="str">
+        <x:v>初始金币 {p0} · {p1} 波</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380">
+      <x:c r="A380" t="n">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B380" t="str">
+        <x:v>ui.loadout.boss</x:v>
+      </x:c>
+      <x:c r="C380" t="str">
+        <x:v>第{p0}波 · {p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381">
+      <x:c r="A381" t="n">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B381" t="str">
+        <x:v>ui.loadout.enemies</x:v>
+      </x:c>
+      <x:c r="C381" t="str">
+        <x:v>本关来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382">
+      <x:c r="A382" t="n">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B382" t="str">
+        <x:v>ui.loadout.default</x:v>
+      </x:c>
+      <x:c r="C382" t="str">
+        <x:v>默认阵容</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383">
+      <x:c r="A383" t="n">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B383" t="str">
+        <x:v>ui.loadout.need</x:v>
+      </x:c>
+      <x:c r="C383" t="str">
+        <x:v>还需选择 {p0} 名店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384">
+      <x:c r="A384" t="n">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B384" t="str">
+        <x:v>ui.preview.title</x:v>
+      </x:c>
+      <x:c r="C384" t="str">
+        <x:v>第{p0}波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385">
+      <x:c r="A385" t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B385" t="str">
+        <x:v>ui.preview.last</x:v>
+      </x:c>
+      <x:c r="C385" t="str">
+        <x:v>最后一波</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386">
+      <x:c r="A386" t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B386" t="str">
+        <x:v>ui.preview.open</x:v>
+      </x:c>
+      <x:c r="C386" t="str">
+        <x:v>波次预告</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B387" t="str">
+        <x:v>ui.preview.count</x:v>
+      </x:c>
+      <x:c r="C387" t="str">
+        <x:v>×{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388" t="n">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B388" t="str">
+        <x:v>ui.preview.mini</x:v>
+      </x:c>
+      <x:c r="C388" t="str">
+        <x:v>小首领</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B389" t="str">
+        <x:v>ui.preview.major</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>大首领</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390" t="n">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B390" t="str">
+        <x:v>staff.role.sprout</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>单体连投</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391" t="n">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B391" t="str">
+        <x:v>staff.role.frost</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>减速控制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392" t="n">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="B392" t="str">
+        <x:v>staff.role.bloom</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>范围爆破</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B393" t="str">
+        <x:v>staff.role.scope</x:v>
+      </x:c>
+      <x:c r="C393" t="str">
+        <x:v>远程穿透</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394">
+      <x:c r="A394" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B394" t="str">
+        <x:v>staff.role.spark</x:v>
+      </x:c>
+      <x:c r="C394" t="str">
+        <x:v>连锁电击</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B395" t="str">
+        <x:v>staff.role.ember</x:v>
+      </x:c>
+      <x:c r="C395" t="str">
+        <x:v>持续灼烧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396">
+      <x:c r="A396" t="n">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B396" t="str">
+        <x:v>staff.role.mint</x:v>
+      </x:c>
+      <x:c r="C396" t="str">
+        <x:v>标记增伤</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397">
+      <x:c r="A397" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B397" t="str">
+        <x:v>staff.role.fan</x:v>
+      </x:c>
+      <x:c r="C397" t="str">
+        <x:v>多目标散射</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R64fa2c451e1a46f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R61c263b81a4743f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +32,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +60,11 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -57,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -80,6 +95,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -343,4321 +378,4860 @@
         <x:v>zhCN</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="7" t="n">
+    <x:row r="6" ht="58" hidden="0" customHeight="1">
+      <x:c r="A6" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="13" t="str">
         <x:v>game.name</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="13" t="str">
         <x:v>叮咚夜班开始</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="7" t="n">
+    <x:row r="7" ht="58" hidden="0" customHeight="1">
+      <x:c r="A7" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="13" t="str">
         <x:v>staff.sprout.name</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="13" t="str">
         <x:v>豆包</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="7" t="n">
+    <x:row r="8" ht="58" hidden="0" customHeight="1">
+      <x:c r="A8" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="13" t="str">
         <x:v>staff.frost.name</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="13" t="str">
         <x:v>棉棉</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="7" t="n">
+    <x:row r="9" ht="58" hidden="0" customHeight="1">
+      <x:c r="A9" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B9" s="13" t="str">
         <x:v>staff.bloom.name</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="13" t="str">
         <x:v>布丁</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="7" t="n">
+    <x:row r="10" ht="58" hidden="0" customHeight="1">
+      <x:c r="A10" s="15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
+      <x:c r="B10" s="13" t="str">
         <x:v>staff.scope.name</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="C10" s="13" t="str">
         <x:v>咕咕</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="7" t="n">
+    <x:row r="11" ht="58" hidden="0" customHeight="1">
+      <x:c r="A11" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
+      <x:c r="B11" s="13" t="str">
         <x:v>staff.spark.name</x:v>
       </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="C11" s="13" t="str">
         <x:v>栗栗</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="7" t="n">
+    <x:row r="12" ht="58" hidden="0" customHeight="1">
+      <x:c r="A12" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="8" t="str">
+      <x:c r="B12" s="13" t="str">
         <x:v>staff.ember.name</x:v>
       </x:c>
-      <x:c r="C12" s="8" t="str">
+      <x:c r="C12" s="13" t="str">
         <x:v>烘烘</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="7" t="n">
+    <x:row r="13" ht="58" hidden="0" customHeight="1">
+      <x:c r="A13" s="15" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="8" t="str">
+      <x:c r="B13" s="13" t="str">
         <x:v>staff.mint.name</x:v>
       </x:c>
-      <x:c r="C13" s="8" t="str">
+      <x:c r="C13" s="13" t="str">
         <x:v>薄荷</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="7" t="n">
+    <x:row r="14" ht="58" hidden="0" customHeight="1">
+      <x:c r="A14" s="15" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B14" s="8" t="str">
+      <x:c r="B14" s="13" t="str">
         <x:v>staff.fan.name</x:v>
       </x:c>
-      <x:c r="C14" s="8" t="str">
+      <x:c r="C14" s="13" t="str">
         <x:v>啾啾</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="7" t="n">
+    <x:row r="15" ht="58" hidden="0" customHeight="1">
+      <x:c r="A15" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B15" s="8" t="str">
+      <x:c r="B15" s="13" t="str">
         <x:v>enemy.normal.name</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="str">
+      <x:c r="C15" s="13" t="str">
         <x:v>小纸袋怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="7" t="n">
+    <x:row r="16" ht="58" hidden="0" customHeight="1">
+      <x:c r="A16" s="15" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B16" s="8" t="str">
+      <x:c r="B16" s="13" t="str">
         <x:v>enemy.swift.name</x:v>
       </x:c>
-      <x:c r="C16" s="8" t="str">
+      <x:c r="C16" s="13" t="str">
         <x:v>红汽水罐</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="7" t="n">
+    <x:row r="17" ht="58" hidden="0" customHeight="1">
+      <x:c r="A17" s="15" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="8" t="str">
+      <x:c r="B17" s="13" t="str">
         <x:v>enemy.tank.name</x:v>
       </x:c>
-      <x:c r="C17" s="8" t="str">
+      <x:c r="C17" s="13" t="str">
         <x:v>快递纸箱怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="7" t="n">
+    <x:row r="18" ht="58" hidden="0" customHeight="1">
+      <x:c r="A18" s="15" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B18" s="8" t="str">
+      <x:c r="B18" s="13" t="str">
         <x:v>enemy.shield.name</x:v>
       </x:c>
-      <x:c r="C18" s="8" t="str">
+      <x:c r="C18" s="13" t="str">
         <x:v>铁罐卫士</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="7" t="n">
+    <x:row r="19" ht="58" hidden="0" customHeight="1">
+      <x:c r="A19" s="15" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B19" s="8" t="str">
+      <x:c r="B19" s="13" t="str">
         <x:v>enemy.jelly.name</x:v>
       </x:c>
-      <x:c r="C19" s="8" t="str">
+      <x:c r="C19" s="13" t="str">
         <x:v>果冻夜游者</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="7" t="n">
+    <x:row r="20" ht="58" hidden="0" customHeight="1">
+      <x:c r="A20" s="15" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B20" s="8" t="str">
+      <x:c r="B20" s="13" t="str">
         <x:v>enemy.runner.name</x:v>
       </x:c>
-      <x:c r="C20" s="8" t="str">
+      <x:c r="C20" s="13" t="str">
         <x:v>冲刺牛奶盒</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="7" t="n">
+    <x:row r="21" ht="58" hidden="0" customHeight="1">
+      <x:c r="A21" s="15" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B21" s="8" t="str">
+      <x:c r="B21" s="13" t="str">
         <x:v>enemy.postmaster.name</x:v>
       </x:c>
-      <x:c r="C21" s="8" t="str">
+      <x:c r="C21" s="13" t="str">
         <x:v>包裹队长</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="7" t="n">
+    <x:row r="22" ht="58" hidden="0" customHeight="1">
+      <x:c r="A22" s="15" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B22" s="8" t="str">
+      <x:c r="B22" s="13" t="str">
         <x:v>enemy.lantern.name</x:v>
       </x:c>
-      <x:c r="C22" s="8" t="str">
+      <x:c r="C22" s="13" t="str">
         <x:v>雾灯旅客</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="7" t="n">
+    <x:row r="23" ht="58" hidden="0" customHeight="1">
+      <x:c r="A23" s="15" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B23" s="8" t="str">
+      <x:c r="B23" s="13" t="str">
         <x:v>enemy.chef.name</x:v>
       </x:c>
-      <x:c r="C23" s="8" t="str">
+      <x:c r="C23" s="13" t="str">
         <x:v>夜宵团长</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="7" t="n">
+    <x:row r="24" ht="58" hidden="0" customHeight="1">
+      <x:c r="A24" s="15" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B24" s="8" t="str">
+      <x:c r="B24" s="13" t="str">
         <x:v>enemy.clock.name</x:v>
       </x:c>
-      <x:c r="C24" s="8" t="str">
+      <x:c r="C24" s="13" t="str">
         <x:v>午夜钟守</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="7" t="n">
+    <x:row r="25" ht="58" hidden="0" customHeight="1">
+      <x:c r="A25" s="15" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B25" s="8" t="str">
+      <x:c r="B25" s="13" t="str">
         <x:v>theme.courtyard.name</x:v>
       </x:c>
-      <x:c r="C25" s="8" t="str">
+      <x:c r="C25" s="13" t="str">
         <x:v>暖灯庭院</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="7" t="n">
+    <x:row r="26" ht="58" hidden="0" customHeight="1">
+      <x:c r="A26" s="15" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B26" s="8" t="str">
+      <x:c r="B26" s="13" t="str">
         <x:v>theme.rain.name</x:v>
       </x:c>
-      <x:c r="C26" s="8" t="str">
+      <x:c r="C26" s="13" t="str">
         <x:v>雨巷站台</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="7" t="n">
+    <x:row r="27" ht="58" hidden="0" customHeight="1">
+      <x:c r="A27" s="15" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B27" s="8" t="str">
+      <x:c r="B27" s="13" t="str">
         <x:v>theme.market.name</x:v>
       </x:c>
-      <x:c r="C27" s="8" t="str">
+      <x:c r="C27" s="13" t="str">
         <x:v>秋日夜市</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="7" t="n">
+    <x:row r="28" ht="58" hidden="0" customHeight="1">
+      <x:c r="A28" s="15" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B28" s="8" t="str">
+      <x:c r="B28" s="13" t="str">
         <x:v>theme.midnight.name</x:v>
       </x:c>
-      <x:c r="C28" s="8" t="str">
+      <x:c r="C28" s="13" t="str">
         <x:v>月下钟街</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="7" t="n">
+    <x:row r="29" ht="58" hidden="0" customHeight="1">
+      <x:c r="A29" s="15" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B29" s="8" t="str">
+      <x:c r="B29" s="13" t="str">
         <x:v>level.1.title</x:v>
       </x:c>
-      <x:c r="C29" s="8" t="str">
+      <x:c r="C29" s="13" t="str">
         <x:v>第一次夜班</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="7" t="n">
+    <x:row r="30" ht="58" hidden="0" customHeight="1">
+      <x:c r="A30" s="15" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B30" s="8" t="str">
+      <x:c r="B30" s="13" t="str">
         <x:v>level.2.title</x:v>
       </x:c>
-      <x:c r="C30" s="8" t="str">
+      <x:c r="C30" s="13" t="str">
         <x:v>跑得太快啦</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="7" t="n">
+    <x:row r="31" ht="58" hidden="0" customHeight="1">
+      <x:c r="A31" s="15" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B31" s="8" t="str">
+      <x:c r="B31" s="13" t="str">
         <x:v>level.3.title</x:v>
       </x:c>
-      <x:c r="C31" s="8" t="str">
+      <x:c r="C31" s="13" t="str">
         <x:v>热食出炉</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="7" t="n">
+    <x:row r="32" ht="58" hidden="0" customHeight="1">
+      <x:c r="A32" s="15" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B32" s="8" t="str">
+      <x:c r="B32" s="13" t="str">
         <x:v>level.4.title</x:v>
       </x:c>
-      <x:c r="C32" s="8" t="str">
+      <x:c r="C32" s="13" t="str">
         <x:v>重重的纸袋</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="7" t="n">
+    <x:row r="33" ht="58" hidden="0" customHeight="1">
+      <x:c r="A33" s="15" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B33" s="8" t="str">
+      <x:c r="B33" s="13" t="str">
         <x:v>level.5.title</x:v>
       </x:c>
-      <x:c r="C33" s="8" t="str">
+      <x:c r="C33" s="13" t="str">
         <x:v>包裹队长</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="7" t="n">
+    <x:row r="34" ht="58" hidden="0" customHeight="1">
+      <x:c r="A34" s="15" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B34" s="8" t="str">
+      <x:c r="B34" s="13" t="str">
         <x:v>level.5.goal</x:v>
       </x:c>
-      <x:c r="C34" s="8" t="str">
+      <x:c r="C34" s="13" t="str">
         <x:v>击退首领，守住便利店</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="15" hidden="0" customHeight="1">
-      <x:c r="A35" s="7" t="n">
+    <x:row r="35" ht="58" hidden="0" customHeight="1">
+      <x:c r="A35" s="15" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B35" s="8" t="str">
+      <x:c r="B35" s="13" t="str">
         <x:v>level.6.title</x:v>
       </x:c>
-      <x:c r="C35" s="8" t="str">
+      <x:c r="C35" s="13" t="str">
         <x:v>雨夜来客</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="15" hidden="0" customHeight="1">
-      <x:c r="A36" s="7" t="n">
+    <x:row r="36" ht="58" hidden="0" customHeight="1">
+      <x:c r="A36" s="15" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B36" s="8" t="str">
+      <x:c r="B36" s="13" t="str">
         <x:v>level.6.goal</x:v>
       </x:c>
-      <x:c r="C36" s="8" t="str">
+      <x:c r="C36" s="13" t="str">
         <x:v>咕咕远射，贯穿排队来客</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="15" hidden="0" customHeight="1">
-      <x:c r="A37" s="7" t="n">
+    <x:row r="37" ht="58" hidden="0" customHeight="1">
+      <x:c r="A37" s="15" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B37" s="8" t="str">
+      <x:c r="B37" s="13" t="str">
         <x:v>level.7.title</x:v>
       </x:c>
-      <x:c r="C37" s="8" t="str">
+      <x:c r="C37" s="13" t="str">
         <x:v>仓库告急</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="15" hidden="0" customHeight="1">
-      <x:c r="A38" s="7" t="n">
+    <x:row r="38" ht="58" hidden="0" customHeight="1">
+      <x:c r="A38" s="15" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B38" s="8" t="str">
+      <x:c r="B38" s="13" t="str">
         <x:v>level.7.goal</x:v>
       </x:c>
-      <x:c r="C38" s="8" t="str">
+      <x:c r="C38" s="13" t="str">
         <x:v>咕咕远射，贯穿排队来客</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="7" t="n">
+    <x:row r="39" ht="58" hidden="0" customHeight="1">
+      <x:c r="A39" s="15" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B39" s="8" t="str">
+      <x:c r="B39" s="13" t="str">
         <x:v>level.8.title</x:v>
       </x:c>
-      <x:c r="C39" s="8" t="str">
+      <x:c r="C39" s="13" t="str">
         <x:v>深夜加急单</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="15" hidden="0" customHeight="1">
-      <x:c r="A40" s="7" t="n">
+    <x:row r="40" ht="58" hidden="0" customHeight="1">
+      <x:c r="A40" s="15" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B40" s="8" t="str">
+      <x:c r="B40" s="13" t="str">
         <x:v>level.8.goal</x:v>
       </x:c>
-      <x:c r="C40" s="8" t="str">
+      <x:c r="C40" s="13" t="str">
+        <x:v>密集来客与快客交替，照顾整条队伍</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="58" hidden="0" customHeight="1">
+      <x:c r="A41" s="15" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B41" s="13" t="str">
+        <x:v>level.9.title</x:v>
+      </x:c>
+      <x:c r="C41" s="13" t="str">
+        <x:v>天亮前一小时</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="58" hidden="0" customHeight="1">
+      <x:c r="A42" s="15" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" s="13" t="str">
+        <x:v>level.9.goal</x:v>
+      </x:c>
+      <x:c r="C42" s="13" t="str">
         <x:v>栗栗连锁，应对密集来客</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="15" hidden="0" customHeight="1">
-      <x:c r="A41" s="7" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B41" s="8" t="str">
-        <x:v>level.9.title</x:v>
-      </x:c>
-      <x:c r="C41" s="8" t="str">
-        <x:v>天亮前一小时</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="15" hidden="0" customHeight="1">
-      <x:c r="A42" s="7" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B42" s="8" t="str">
-        <x:v>level.9.goal</x:v>
-      </x:c>
-      <x:c r="C42" s="8" t="str">
-        <x:v>栗栗连锁，应对密集来客</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="15" hidden="0" customHeight="1">
-      <x:c r="A43" s="7" t="n">
+    <x:row r="43" ht="58" hidden="0" customHeight="1">
+      <x:c r="A43" s="15" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B43" s="8" t="str">
+      <x:c r="B43" s="13" t="str">
         <x:v>level.10.title</x:v>
       </x:c>
-      <x:c r="C43" s="8" t="str">
+      <x:c r="C43" s="13" t="str">
         <x:v>雾灯旅客</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="7" t="n">
+    <x:row r="44" ht="58" hidden="0" customHeight="1">
+      <x:c r="A44" s="15" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B44" s="8" t="str">
+      <x:c r="B44" s="13" t="str">
         <x:v>level.10.goal</x:v>
       </x:c>
-      <x:c r="C44" s="8" t="str">
-        <x:v>击退首领，守住便利店</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="15" hidden="0" customHeight="1">
-      <x:c r="A45" s="7" t="n">
+      <x:c r="C44" s="13" t="str">
+        <x:v>灯笼领队带着厚实护卫经过街口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="58" hidden="0" customHeight="1">
+      <x:c r="A45" s="15" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B45" s="8" t="str">
+      <x:c r="B45" s="13" t="str">
         <x:v>level.11.title</x:v>
       </x:c>
-      <x:c r="C45" s="8" t="str">
+      <x:c r="C45" s="13" t="str">
         <x:v>夜市开张</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="15" hidden="0" customHeight="1">
-      <x:c r="A46" s="7" t="n">
+    <x:row r="46" ht="58" hidden="0" customHeight="1">
+      <x:c r="A46" s="15" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B46" s="8" t="str">
+      <x:c r="B46" s="13" t="str">
         <x:v>level.11.goal</x:v>
       </x:c>
-      <x:c r="C46" s="8" t="str">
+      <x:c r="C46" s="13" t="str">
         <x:v>认识灼烧与厚血来客</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="15" hidden="0" customHeight="1">
-      <x:c r="A47" s="7" t="n">
+    <x:row r="47" ht="58" hidden="0" customHeight="1">
+      <x:c r="A47" s="15" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B47" s="8" t="str">
+      <x:c r="B47" s="13" t="str">
         <x:v>level.12.title</x:v>
       </x:c>
-      <x:c r="C47" s="8" t="str">
+      <x:c r="C47" s="13" t="str">
         <x:v>穿过摊位</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="15" hidden="0" customHeight="1">
-      <x:c r="A48" s="7" t="n">
+    <x:row r="48" ht="58" hidden="0" customHeight="1">
+      <x:c r="A48" s="15" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B48" s="8" t="str">
+      <x:c r="B48" s="13" t="str">
         <x:v>level.12.goal</x:v>
       </x:c>
-      <x:c r="C48" s="8" t="str">
+      <x:c r="C48" s="13" t="str">
         <x:v>交替火力，守住整条路线</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="7" t="n">
+    <x:row r="49" ht="58" hidden="0" customHeight="1">
+      <x:c r="A49" s="15" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B49" s="8" t="str">
+      <x:c r="B49" s="13" t="str">
         <x:v>level.13.title</x:v>
       </x:c>
-      <x:c r="C49" s="8" t="str">
+      <x:c r="C49" s="13" t="str">
         <x:v>清洁时间</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="7" t="n">
+    <x:row r="50" ht="58" hidden="0" customHeight="1">
+      <x:c r="A50" s="15" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B50" s="8" t="str">
+      <x:c r="B50" s="13" t="str">
         <x:v>level.13.goal</x:v>
       </x:c>
-      <x:c r="C50" s="8" t="str">
+      <x:c r="C50" s="13" t="str">
         <x:v>用薄荷标记集中输出</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="15" hidden="0" customHeight="1">
-      <x:c r="A51" s="7" t="n">
+    <x:row r="51" ht="58" hidden="0" customHeight="1">
+      <x:c r="A51" s="15" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B51" s="8" t="str">
+      <x:c r="B51" s="13" t="str">
         <x:v>level.14.title</x:v>
       </x:c>
-      <x:c r="C51" s="8" t="str">
+      <x:c r="C51" s="13" t="str">
         <x:v>转角夜宵</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="15" hidden="0" customHeight="1">
-      <x:c r="A52" s="7" t="n">
+    <x:row r="52" ht="58" hidden="0" customHeight="1">
+      <x:c r="A52" s="15" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B52" s="8" t="str">
+      <x:c r="B52" s="13" t="str">
         <x:v>level.14.goal</x:v>
       </x:c>
-      <x:c r="C52" s="8" t="str">
+      <x:c r="C52" s="13" t="str">
         <x:v>交替火力，守住整条路线</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="15" hidden="0" customHeight="1">
-      <x:c r="A53" s="7" t="n">
+    <x:row r="53" ht="58" hidden="0" customHeight="1">
+      <x:c r="A53" s="15" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B53" s="8" t="str">
+      <x:c r="B53" s="13" t="str">
         <x:v>level.15.title</x:v>
       </x:c>
-      <x:c r="C53" s="8" t="str">
+      <x:c r="C53" s="13" t="str">
         <x:v>夜宵团长</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="7" t="n">
+    <x:row r="54" ht="58" hidden="0" customHeight="1">
+      <x:c r="A54" s="15" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B54" s="8" t="str">
+      <x:c r="B54" s="13" t="str">
         <x:v>level.15.goal</x:v>
       </x:c>
-      <x:c r="C54" s="8" t="str">
-        <x:v>击退首领，守住便利店</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="7" t="n">
+      <x:c r="C54" s="13" t="str">
+        <x:v>先清货物腾出位置，再迎接夜宵师傅</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="58" hidden="0" customHeight="1">
+      <x:c r="A55" s="15" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B55" s="8" t="str">
+      <x:c r="B55" s="13" t="str">
         <x:v>level.16.title</x:v>
       </x:c>
-      <x:c r="C55" s="8" t="str">
+      <x:c r="C55" s="13" t="str">
         <x:v>午夜快递</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="15" hidden="0" customHeight="1">
-      <x:c r="A56" s="7" t="n">
+    <x:row r="56" ht="58" hidden="0" customHeight="1">
+      <x:c r="A56" s="15" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B56" s="8" t="str">
+      <x:c r="B56" s="13" t="str">
         <x:v>level.16.goal</x:v>
       </x:c>
-      <x:c r="C56" s="8" t="str">
+      <x:c r="C56" s="13" t="str">
         <x:v>用啾啾应对密集快客</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="15" hidden="0" customHeight="1">
-      <x:c r="A57" s="7" t="n">
+    <x:row r="57" ht="58" hidden="0" customHeight="1">
+      <x:c r="A57" s="15" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B57" s="8" t="str">
+      <x:c r="B57" s="13" t="str">
         <x:v>level.17.title</x:v>
       </x:c>
-      <x:c r="C57" s="8" t="str">
+      <x:c r="C57" s="13" t="str">
         <x:v>双向赶路</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="15" hidden="0" customHeight="1">
-      <x:c r="A58" s="7" t="n">
+    <x:row r="58" ht="58" hidden="0" customHeight="1">
+      <x:c r="A58" s="15" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B58" s="8" t="str">
+      <x:c r="B58" s="13" t="str">
         <x:v>level.17.goal</x:v>
       </x:c>
-      <x:c r="C58" s="8" t="str">
+      <x:c r="C58" s="13" t="str">
         <x:v>交替火力，守住整条路线</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="15" hidden="0" customHeight="1">
-      <x:c r="A59" s="7" t="n">
+    <x:row r="59" ht="58" hidden="0" customHeight="1">
+      <x:c r="A59" s="15" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B59" s="8" t="str">
+      <x:c r="B59" s="13" t="str">
         <x:v>level.18.title</x:v>
       </x:c>
-      <x:c r="C59" s="8" t="str">
+      <x:c r="C59" s="13" t="str">
         <x:v>钟前折返</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="15" hidden="0" customHeight="1">
-      <x:c r="A60" s="7" t="n">
+    <x:row r="60" ht="58" hidden="0" customHeight="1">
+      <x:c r="A60" s="15" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B60" s="8" t="str">
+      <x:c r="B60" s="13" t="str">
         <x:v>level.18.goal</x:v>
       </x:c>
-      <x:c r="C60" s="8" t="str">
+      <x:c r="C60" s="13" t="str">
         <x:v>交替火力，守住整条路线</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="15" hidden="0" customHeight="1">
-      <x:c r="A61" s="7" t="n">
+    <x:row r="61" ht="58" hidden="0" customHeight="1">
+      <x:c r="A61" s="15" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B61" s="8" t="str">
+      <x:c r="B61" s="13" t="str">
         <x:v>level.19.title</x:v>
       </x:c>
-      <x:c r="C61" s="8" t="str">
+      <x:c r="C61" s="13" t="str">
         <x:v>最后一班</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="15" hidden="0" customHeight="1">
-      <x:c r="A62" s="7" t="n">
+    <x:row r="62" ht="58" hidden="0" customHeight="1">
+      <x:c r="A62" s="15" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B62" s="8" t="str">
+      <x:c r="B62" s="13" t="str">
         <x:v>level.19.goal</x:v>
       </x:c>
-      <x:c r="C62" s="8" t="str">
+      <x:c r="C62" s="13" t="str">
         <x:v>交替火力，守住整条路线</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="15" hidden="0" customHeight="1">
-      <x:c r="A63" s="7" t="n">
+    <x:row r="63" ht="58" hidden="0" customHeight="1">
+      <x:c r="A63" s="15" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B63" s="8" t="str">
+      <x:c r="B63" s="13" t="str">
         <x:v>level.20.title</x:v>
       </x:c>
-      <x:c r="C63" s="8" t="str">
+      <x:c r="C63" s="13" t="str">
         <x:v>守到天亮</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="7" t="n">
+    <x:row r="64" ht="58" hidden="0" customHeight="1">
+      <x:c r="A64" s="15" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B64" s="8" t="str">
+      <x:c r="B64" s="13" t="str">
         <x:v>level.20.goal</x:v>
       </x:c>
-      <x:c r="C64" s="8" t="str">
-        <x:v>击退午夜钟守，完成二十夜</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="15" hidden="0" customHeight="1">
-      <x:c r="A65" s="7" t="n">
+      <x:c r="C64" s="13" t="str">
+        <x:v>群客、快客与午夜钟守接连抵达</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="58" hidden="0" customHeight="1">
+      <x:c r="A65" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B65" s="8" t="str">
+      <x:c r="B65" s="13" t="str">
         <x:v>wave.104.announcement</x:v>
       </x:c>
-      <x:c r="C65" s="8" t="str">
+      <x:c r="C65" s="13" t="str">
         <x:v>最后一波，扩建完整防线！</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="15" hidden="0" customHeight="1">
-      <x:c r="A66" s="7" t="n">
+    <x:row r="66" ht="58" hidden="0" customHeight="1">
+      <x:c r="A66" s="15" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B66" s="8" t="str">
+      <x:c r="B66" s="13" t="str">
         <x:v>wave.204.announcement</x:v>
       </x:c>
-      <x:c r="C66" s="8" t="str">
+      <x:c r="C66" s="13" t="str">
         <x:v>用减速争取清障和扩建时间！</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="15" hidden="0" customHeight="1">
-      <x:c r="A67" s="7" t="n">
+    <x:row r="67" ht="58" hidden="0" customHeight="1">
+      <x:c r="A67" s="15" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B67" s="8" t="str">
+      <x:c r="B67" s="13" t="str">
         <x:v>wave.304.announcement</x:v>
       </x:c>
-      <x:c r="C67" s="8" t="str">
+      <x:c r="C67" s="13" t="str">
         <x:v>布丁适合守住密集路段！</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="15" hidden="0" customHeight="1">
-      <x:c r="A68" s="7" t="n">
+    <x:row r="68" ht="58" hidden="0" customHeight="1">
+      <x:c r="A68" s="15" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B68" s="8" t="str">
+      <x:c r="B68" s="13" t="str">
         <x:v>wave.404.announcement</x:v>
       </x:c>
-      <x:c r="C68" s="8" t="str">
+      <x:c r="C68" s="13" t="str">
         <x:v>重型纸袋怪需要集中火力！</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="15" hidden="0" customHeight="1">
-      <x:c r="A69" s="7" t="n">
+    <x:row r="69" ht="58" hidden="0" customHeight="1">
+      <x:c r="A69" s="15" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B69" s="8" t="str">
+      <x:c r="B69" s="13" t="str">
         <x:v>wave.504.announcement</x:v>
       </x:c>
-      <x:c r="C69" s="8" t="str">
+      <x:c r="C69" s="13" t="str">
         <x:v>包裹队长登场，集中火力！</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="15" hidden="0" customHeight="1">
-      <x:c r="A70" s="7" t="n">
+    <x:row r="70" ht="58" hidden="0" customHeight="1">
+      <x:c r="A70" s="15" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B70" s="8" t="str">
+      <x:c r="B70" s="13" t="str">
         <x:v>wave.604.announcement</x:v>
       </x:c>
-      <x:c r="C70" s="8" t="str">
+      <x:c r="C70" s="13" t="str">
         <x:v>先清出中场空地，再补终点防线！</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="15" hidden="0" customHeight="1">
-      <x:c r="A71" s="7" t="n">
+    <x:row r="71" ht="58" hidden="0" customHeight="1">
+      <x:c r="A71" s="15" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B71" s="8" t="str">
+      <x:c r="B71" s="13" t="str">
         <x:v>wave.704.announcement</x:v>
       </x:c>
-      <x:c r="C71" s="8" t="str">
+      <x:c r="C71" s="13" t="str">
         <x:v>出口在左下，给终点留一份火力！</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="15" hidden="0" customHeight="1">
-      <x:c r="A72" s="7" t="n">
+    <x:row r="72" ht="58" hidden="0" customHeight="1">
+      <x:c r="A72" s="15" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B72" s="8" t="str">
+      <x:c r="B72" s="13" t="str">
         <x:v>wave.804.announcement</x:v>
       </x:c>
-      <x:c r="C72" s="8" t="str">
+      <x:c r="C72" s="13" t="str">
         <x:v>加急订单到达，别只守入口！</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="15" hidden="0" customHeight="1">
-      <x:c r="A73" s="7" t="n">
+    <x:row r="73" ht="58" hidden="0" customHeight="1">
+      <x:c r="A73" s="15" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B73" s="8" t="str">
+      <x:c r="B73" s="13" t="str">
         <x:v>wave.904.announcement</x:v>
       </x:c>
-      <x:c r="C73" s="8" t="str">
+      <x:c r="C73" s="13" t="str">
         <x:v>天亮前的客流最难守！</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="15" hidden="0" customHeight="1">
-      <x:c r="A74" s="7" t="n">
+    <x:row r="74" ht="58" hidden="0" customHeight="1">
+      <x:c r="A74" s="15" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B74" s="8" t="str">
+      <x:c r="B74" s="13" t="str">
         <x:v>wave.1005.announcement</x:v>
       </x:c>
-      <x:c r="C74" s="8" t="str">
-        <x:v>雾灯旅客登场，集中火力！</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="15" hidden="0" customHeight="1">
-      <x:c r="A75" s="7" t="n">
+      <x:c r="C74" s="13" t="str">
+        <x:v>灯笼领队与护卫来了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="58" hidden="0" customHeight="1">
+      <x:c r="A75" s="15" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B75" s="8" t="str">
+      <x:c r="B75" s="13" t="str">
         <x:v>wave.1101.announcement</x:v>
       </x:c>
-      <x:c r="C75" s="8" t="str">
-        <x:v>本关店员：豆包、棉棉、布丁、烘烘</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="15" hidden="0" customHeight="1">
-      <x:c r="A76" s="7" t="n">
+      <x:c r="C75" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="58" hidden="0" customHeight="1">
+      <x:c r="A76" s="15" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B76" s="8" t="str">
+      <x:c r="B76" s="13" t="str">
         <x:v>wave.1201.announcement</x:v>
       </x:c>
-      <x:c r="C76" s="8" t="str">
-        <x:v>本关店员：咕咕、棉棉、布丁、烘烘</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="15" hidden="0" customHeight="1">
-      <x:c r="A77" s="7" t="n">
+      <x:c r="C76" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="58" hidden="0" customHeight="1">
+      <x:c r="A77" s="15" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B77" s="8" t="str">
+      <x:c r="B77" s="13" t="str">
         <x:v>wave.1301.announcement</x:v>
       </x:c>
-      <x:c r="C77" s="8" t="str">
-        <x:v>本关店员：豆包、布丁、薄荷、烘烘</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="15" hidden="0" customHeight="1">
-      <x:c r="A78" s="7" t="n">
+      <x:c r="C77" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="58" hidden="0" customHeight="1">
+      <x:c r="A78" s="15" t="n">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B78" s="8" t="str">
+      <x:c r="B78" s="13" t="str">
         <x:v>wave.1401.announcement</x:v>
       </x:c>
-      <x:c r="C78" s="8" t="str">
-        <x:v>本关店员：咕咕、栗栗、薄荷、棉棉</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="15" hidden="0" customHeight="1">
-      <x:c r="A79" s="7" t="n">
+      <x:c r="C78" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="58" hidden="0" customHeight="1">
+      <x:c r="A79" s="15" t="n">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B79" s="8" t="str">
+      <x:c r="B79" s="13" t="str">
         <x:v>wave.1501.announcement</x:v>
       </x:c>
-      <x:c r="C79" s="8" t="str">
-        <x:v>本关店员：咕咕、布丁、烘烘、薄荷</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="15" hidden="0" customHeight="1">
-      <x:c r="A80" s="7" t="n">
+      <x:c r="C79" s="13" t="str">
+        <x:v>先整理门口的货物</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="58" hidden="0" customHeight="1">
+      <x:c r="A80" s="15" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B80" s="8" t="str">
+      <x:c r="B80" s="13" t="str">
         <x:v>wave.1505.announcement</x:v>
       </x:c>
-      <x:c r="C80" s="8" t="str">
+      <x:c r="C80" s="13" t="str">
         <x:v>夜宵团长登场，集中火力！</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="15" hidden="0" customHeight="1">
-      <x:c r="A81" s="7" t="n">
+    <x:row r="81" ht="58" hidden="0" customHeight="1">
+      <x:c r="A81" s="15" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B81" s="8" t="str">
+      <x:c r="B81" s="13" t="str">
         <x:v>wave.1601.announcement</x:v>
       </x:c>
-      <x:c r="C81" s="8" t="str">
-        <x:v>本关店员：豆包、棉棉、布丁、啾啾</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="15" hidden="0" customHeight="1">
-      <x:c r="A82" s="7" t="n">
+      <x:c r="C81" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="58" hidden="0" customHeight="1">
+      <x:c r="A82" s="15" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B82" s="8" t="str">
+      <x:c r="B82" s="13" t="str">
         <x:v>wave.1701.announcement</x:v>
       </x:c>
-      <x:c r="C82" s="8" t="str">
-        <x:v>本关店员：咕咕、栗栗、棉棉、啾啾</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="15" hidden="0" customHeight="1">
-      <x:c r="A83" s="7" t="n">
+      <x:c r="C82" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="58" hidden="0" customHeight="1">
+      <x:c r="A83" s="15" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B83" s="8" t="str">
+      <x:c r="B83" s="13" t="str">
         <x:v>wave.1801.announcement</x:v>
       </x:c>
-      <x:c r="C83" s="8" t="str">
-        <x:v>本关店员：咕咕、布丁、薄荷、啾啾</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="15" hidden="0" customHeight="1">
-      <x:c r="A84" s="7" t="n">
+      <x:c r="C83" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="58" hidden="0" customHeight="1">
+      <x:c r="A84" s="15" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B84" s="8" t="str">
+      <x:c r="B84" s="13" t="str">
         <x:v>wave.1901.announcement</x:v>
       </x:c>
-      <x:c r="C84" s="8" t="str">
-        <x:v>本关店员：咕咕、棉棉、烘烘、啾啾</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="15" hidden="0" customHeight="1">
-      <x:c r="A85" s="7" t="n">
+      <x:c r="C84" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="58" hidden="0" customHeight="1">
+      <x:c r="A85" s="15" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B85" s="8" t="str">
+      <x:c r="B85" s="13" t="str">
         <x:v>wave.2001.announcement</x:v>
       </x:c>
-      <x:c r="C85" s="8" t="str">
-        <x:v>本关店员：咕咕、棉棉、布丁、薄荷</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="15" hidden="0" customHeight="1">
-      <x:c r="A86" s="7" t="n">
+      <x:c r="C85" s="13" t="str">
+        <x:v>第一波来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="58" hidden="0" customHeight="1">
+      <x:c r="A86" s="15" t="n">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B86" s="8" t="str">
+      <x:c r="B86" s="13" t="str">
         <x:v>wave.2005.announcement</x:v>
       </x:c>
-      <x:c r="C86" s="8" t="str">
-        <x:v>午夜钟守来了，守住最后一班！</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="15" hidden="0" customHeight="1">
-      <x:c r="A87" s="7" t="n">
+      <x:c r="C86" s="13" t="str">
+        <x:v>午夜钟守来了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="58" hidden="0" customHeight="1">
+      <x:c r="A87" s="15" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B87" s="8" t="str">
+      <x:c r="B87" s="13" t="str">
         <x:v>collection.enemy-normal.category</x:v>
       </x:c>
-      <x:c r="C87" s="8" t="str">
+      <x:c r="C87" s="13" t="str">
         <x:v>普通精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A88" s="7" t="n">
+    <x:row r="88" ht="58" hidden="0" customHeight="1">
+      <x:c r="A88" s="15" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B88" s="8" t="str">
+      <x:c r="B88" s="13" t="str">
         <x:v>collection.enemy-normal.traits</x:v>
       </x:c>
-      <x:c r="C88" s="8" t="str">
+      <x:c r="C88" s="13" t="str">
         <x:v>移动稳定，常常结伴出现，适合交给豆包逐个赶走。</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A89" s="7" t="n">
+    <x:row r="89" ht="58" hidden="0" customHeight="1">
+      <x:c r="A89" s="15" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B89" s="8" t="str">
+      <x:c r="B89" s="13" t="str">
         <x:v>collection.enemy-normal.story</x:v>
       </x:c>
-      <x:c r="C89" s="8" t="str">
+      <x:c r="C89" s="13" t="str">
         <x:v>地铁末班车离站后，它才把小短腿伸出纸袋。袋口总朝着便利店的暖光，像在等一份刚装好的夜宵。</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="15" hidden="0" customHeight="1">
-      <x:c r="A90" s="7" t="n">
+    <x:row r="90" ht="58" hidden="0" customHeight="1">
+      <x:c r="A90" s="15" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B90" s="8" t="str">
+      <x:c r="B90" s="13" t="str">
         <x:v>collection.enemy-swift.category</x:v>
       </x:c>
-      <x:c r="C90" s="8" t="str">
+      <x:c r="C90" s="13" t="str">
         <x:v>疾行精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A91" s="7" t="n">
+    <x:row r="91" ht="58" hidden="0" customHeight="1">
+      <x:c r="A91" s="15" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B91" s="8" t="str">
+      <x:c r="B91" s="13" t="str">
         <x:v>collection.enemy-swift.traits</x:v>
       </x:c>
-      <x:c r="C91" s="8" t="str">
+      <x:c r="C91" s="13" t="str">
         <x:v>跑得快，耐久较低。棉棉的减速能让它在防线前多留一会儿。</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A92" s="7" t="n">
+    <x:row r="92" ht="58" hidden="0" customHeight="1">
+      <x:c r="A92" s="15" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B92" s="8" t="str">
+      <x:c r="B92" s="13" t="str">
         <x:v>collection.enemy-swift.story</x:v>
       </x:c>
-      <x:c r="C92" s="8" t="str">
+      <x:c r="C92" s="13" t="str">
         <x:v>它总觉得末班车还没开走，顺着庭院一路小跑。跑到店门前才想起来：自己出门只是想听汽水开罐的声音。</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="15" hidden="0" customHeight="1">
-      <x:c r="A93" s="7" t="n">
+    <x:row r="93" ht="58" hidden="0" customHeight="1">
+      <x:c r="A93" s="15" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B93" s="8" t="str">
+      <x:c r="B93" s="13" t="str">
         <x:v>collection.enemy-tank.category</x:v>
       </x:c>
-      <x:c r="C93" s="8" t="str">
+      <x:c r="C93" s="13" t="str">
         <x:v>重型精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A94" s="7" t="n">
+    <x:row r="94" ht="58" hidden="0" customHeight="1">
+      <x:c r="A94" s="15" t="n">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B94" s="8" t="str">
+      <x:c r="B94" s="13" t="str">
         <x:v>collection.enemy-tank.traits</x:v>
       </x:c>
-      <x:c r="C94" s="8" t="str">
+      <x:c r="C94" s="13" t="str">
         <x:v>移动较慢、耐久较高；漏进店里会扣除更多店铺耐久。</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A95" s="7" t="n">
+    <x:row r="95" ht="58" hidden="0" customHeight="1">
+      <x:c r="A95" s="15" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B95" s="8" t="str">
+      <x:c r="B95" s="13" t="str">
         <x:v>collection.enemy-tank.story</x:v>
       </x:c>
-      <x:c r="C95" s="8" t="str">
+      <x:c r="C95" s="13" t="str">
         <x:v>箱子上没有收件地址，只有一张歪歪扭扭的“夜间送达”。它走得很认真，至今还没发现纸箱里的自己就是那件包裹。</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="15" hidden="0" customHeight="1">
-      <x:c r="A96" s="7" t="n">
+    <x:row r="96" ht="58" hidden="0" customHeight="1">
+      <x:c r="A96" s="15" t="n">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B96" s="8" t="str">
+      <x:c r="B96" s="13" t="str">
         <x:v>collection.staff-doubao.category</x:v>
       </x:c>
-      <x:c r="C96" s="8" t="str">
+      <x:c r="C96" s="13" t="str">
         <x:v>仓鼠 · 收银员</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A97" s="7" t="n">
+    <x:row r="97" ht="58" hidden="0" customHeight="1">
+      <x:c r="A97" s="15" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B97" s="8" t="str">
+      <x:c r="B97" s="13" t="str">
         <x:v>collection.staff-doubao.traits</x:v>
       </x:c>
-      <x:c r="C97" s="8" t="str">
+      <x:c r="C97" s="13" t="str">
         <x:v>快速、稳定的单体驱赶。上岗费用低，方便逐步扩展防线。</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A98" s="7" t="n">
+    <x:row r="98" ht="58" hidden="0" customHeight="1">
+      <x:c r="A98" s="15" t="n">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B98" s="8" t="str">
+      <x:c r="B98" s="13" t="str">
         <x:v>collection.staff-doubao.story</x:v>
       </x:c>
-      <x:c r="C98" s="8" t="str">
+      <x:c r="C98" s="13" t="str">
         <x:v>豆包会把每枚金币朝同一个方向码好。客流再急，他也能一边报数一边守住收银台，最怕的是下班前少算一枚硬币。</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="15" hidden="0" customHeight="1">
-      <x:c r="A99" s="7" t="n">
+    <x:row r="99" ht="58" hidden="0" customHeight="1">
+      <x:c r="A99" s="15" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B99" s="8" t="str">
+      <x:c r="B99" s="13" t="str">
         <x:v>collection.staff-mianmian.category</x:v>
       </x:c>
-      <x:c r="C99" s="8" t="str">
+      <x:c r="C99" s="13" t="str">
         <x:v>垂耳兔 · 理货员</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A100" s="7" t="n">
+    <x:row r="100" ht="58" hidden="0" customHeight="1">
+      <x:c r="A100" s="15" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B100" s="8" t="str">
+      <x:c r="B100" s="13" t="str">
         <x:v>collection.staff-mianmian.traits</x:v>
       </x:c>
-      <x:c r="C100" s="8" t="str">
+      <x:c r="C100" s="13" t="str">
         <x:v>攻击附带减速，为其他店员争取输出时间，适合照看疾行精怪。</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A101" s="7" t="n">
+    <x:row r="101" ht="58" hidden="0" customHeight="1">
+      <x:c r="A101" s="15" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B101" s="8" t="str">
+      <x:c r="B101" s="13" t="str">
         <x:v>collection.staff-mianmian.story</x:v>
       </x:c>
-      <x:c r="C101" s="8" t="str">
+      <x:c r="C101" s="13" t="str">
         <x:v>棉棉能记住每件商品该在的格子。遇到匆忙的来客，她总会轻轻提醒：“慢一点，热食还没凉。”</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="15" hidden="0" customHeight="1">
-      <x:c r="A102" s="7" t="n">
+    <x:row r="102" ht="58" hidden="0" customHeight="1">
+      <x:c r="A102" s="15" t="n">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B102" s="8" t="str">
+      <x:c r="B102" s="13" t="str">
         <x:v>collection.staff-buding.category</x:v>
       </x:c>
-      <x:c r="C102" s="8" t="str">
+      <x:c r="C102" s="13" t="str">
         <x:v>柯基 · 热食员</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A103" s="7" t="n">
+    <x:row r="103" ht="58" hidden="0" customHeight="1">
+      <x:c r="A103" s="15" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B103" s="8" t="str">
+      <x:c r="B103" s="13" t="str">
         <x:v>collection.staff-buding.traits</x:v>
       </x:c>
-      <x:c r="C103" s="8" t="str">
+      <x:c r="C103" s="13" t="str">
         <x:v>对目标及附近精怪造成范围伤害，适合应对密集精怪。</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A104" s="7" t="n">
+    <x:row r="104" ht="58" hidden="0" customHeight="1">
+      <x:c r="A104" s="15" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B104" s="8" t="str">
+      <x:c r="B104" s="13" t="str">
         <x:v>collection.staff-buding.story</x:v>
       </x:c>
-      <x:c r="C104" s="8" t="str">
+      <x:c r="C104" s="13" t="str">
         <x:v>布丁总把“刚出炉”喊得比广播还响。看到门外排起长队，他会先把围裙系紧，再把最后一份热食留给值夜的同伴。</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="15" hidden="0" customHeight="1">
-      <x:c r="A105" s="7" t="n">
+    <x:row r="105" ht="58" hidden="0" customHeight="1">
+      <x:c r="A105" s="15" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B105" s="8" t="str">
+      <x:c r="B105" s="13" t="str">
         <x:v>collection.enemy-shield.category</x:v>
       </x:c>
-      <x:c r="C105" s="8" t="str">
+      <x:c r="C105" s="13" t="str">
         <x:v>夜间精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A106" s="7" t="n">
+    <x:row r="106" ht="58" hidden="0" customHeight="1">
+      <x:c r="A106" s="15" t="n">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B106" s="8" t="str">
+      <x:c r="B106" s="13" t="str">
         <x:v>collection.enemy-shield.traits</x:v>
       </x:c>
-      <x:c r="C106" s="8" t="str">
+      <x:c r="C106" s="13" t="str">
         <x:v>耐久较高，速度适中。适合集中输出，也可以让咕咕利用远射多打几轮。</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A107" s="7" t="n">
+    <x:row r="107" ht="58" hidden="0" customHeight="1">
+      <x:c r="A107" s="15" t="n">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B107" s="8" t="str">
+      <x:c r="B107" s="13" t="str">
         <x:v>collection.enemy-shield.story</x:v>
       </x:c>
-      <x:c r="C107" s="8" t="str">
+      <x:c r="C107" s="13" t="str">
         <x:v>它把茶叶罐擦得锃亮，郑重宣布自己是夜班巡逻员。走到店门口才发现，巡逻路线正好绕回了零食货架。</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="15" hidden="0" customHeight="1">
-      <x:c r="A108" s="7" t="n">
+    <x:row r="108" ht="58" hidden="0" customHeight="1">
+      <x:c r="A108" s="15" t="n">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B108" s="8" t="str">
+      <x:c r="B108" s="13" t="str">
         <x:v>collection.enemy-jelly.category</x:v>
       </x:c>
-      <x:c r="C108" s="8" t="str">
+      <x:c r="C108" s="13" t="str">
         <x:v>夜间精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A109" s="7" t="n">
+    <x:row r="109" ht="58" hidden="0" customHeight="1">
+      <x:c r="A109" s="15" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B109" s="8" t="str">
+      <x:c r="B109" s="13" t="str">
         <x:v>collection.enemy-jelly.traits</x:v>
       </x:c>
-      <x:c r="C109" s="8" t="str">
+      <x:c r="C109" s="13" t="str">
         <x:v>耐久中等、速度适中，金币奖励较多。与快客混行时不要忽略它。</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A110" s="7" t="n">
+    <x:row r="110" ht="58" hidden="0" customHeight="1">
+      <x:c r="A110" s="15" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B110" s="8" t="str">
+      <x:c r="B110" s="13" t="str">
         <x:v>collection.enemy-jelly.story</x:v>
       </x:c>
-      <x:c r="C110" s="8" t="str">
+      <x:c r="C110" s="13" t="str">
         <x:v>白天躲在冷柜里打瞌睡，夜里悄悄出门散步。每走一步都晃一下，却从来没把杯里的月光洒出来。</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="15" hidden="0" customHeight="1">
-      <x:c r="A111" s="7" t="n">
+    <x:row r="111" ht="58" hidden="0" customHeight="1">
+      <x:c r="A111" s="15" t="n">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B111" s="8" t="str">
+      <x:c r="B111" s="13" t="str">
         <x:v>collection.enemy-runner.category</x:v>
       </x:c>
-      <x:c r="C111" s="8" t="str">
+      <x:c r="C111" s="13" t="str">
         <x:v>夜间精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A112" s="7" t="n">
+    <x:row r="112" ht="58" hidden="0" customHeight="1">
+      <x:c r="A112" s="15" t="n">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B112" s="8" t="str">
+      <x:c r="B112" s="13" t="str">
         <x:v>collection.enemy-runner.traits</x:v>
       </x:c>
-      <x:c r="C112" s="8" t="str">
+      <x:c r="C112" s="13" t="str">
         <x:v>移速高于汽水罐，耐久也更高。减速和多目标火力能减少漏怪。</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A113" s="7" t="n">
+    <x:row r="113" ht="58" hidden="0" customHeight="1">
+      <x:c r="A113" s="15" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B113" s="8" t="str">
+      <x:c r="B113" s="13" t="str">
         <x:v>collection.enemy-runner.story</x:v>
       </x:c>
-      <x:c r="C113" s="8" t="str">
+      <x:c r="C113" s="13" t="str">
         <x:v>它把保质期当成了末班车时刻，系上围巾就往前跑。棉棉常常拦住它，提醒它今天其实还早。</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="15" hidden="0" customHeight="1">
-      <x:c r="A114" s="7" t="n">
+    <x:row r="114" ht="58" hidden="0" customHeight="1">
+      <x:c r="A114" s="15" t="n">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B114" s="8" t="str">
+      <x:c r="B114" s="13" t="str">
         <x:v>collection.boss-postmaster.category</x:v>
       </x:c>
-      <x:c r="C114" s="8" t="str">
+      <x:c r="C114" s="13" t="str">
         <x:v>小首领 · 第5关</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A115" s="7" t="n">
+    <x:row r="115" ht="58" hidden="0" customHeight="1">
+      <x:c r="A115" s="15" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B115" s="8" t="str">
+      <x:c r="B115" s="13" t="str">
         <x:v>collection.boss-postmaster.traits</x:v>
       </x:c>
-      <x:c r="C115" s="8" t="str">
+      <x:c r="C115" s="13" t="str">
         <x:v>耐久远高于普通来客，移动较慢；漏进店里扣 {p0} 点耐久，需要持续输出。</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A116" s="7" t="n">
+    <x:row r="116" ht="58" hidden="0" customHeight="1">
+      <x:c r="A116" s="15" t="n">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B116" s="8" t="str">
+      <x:c r="B116" s="13" t="str">
         <x:v>collection.boss-postmaster.story</x:v>
       </x:c>
-      <x:c r="C116" s="8" t="str">
+      <x:c r="C116" s="13" t="str">
         <x:v>它揣着整条街的夜间包裹，坚信便利店是最后一站。红帽子歪了也不肯停，因为清单上还差一枚签收章。</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="15" hidden="0" customHeight="1">
-      <x:c r="A117" s="7" t="n">
+    <x:row r="117" ht="58" hidden="0" customHeight="1">
+      <x:c r="A117" s="15" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B117" s="8" t="str">
+      <x:c r="B117" s="13" t="str">
         <x:v>collection.boss-fog-guest.category</x:v>
       </x:c>
-      <x:c r="C117" s="8" t="str">
+      <x:c r="C117" s="13" t="str">
         <x:v>大首领 · 第10关</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A118" s="7" t="n">
+    <x:row r="118" ht="58" hidden="0" customHeight="1">
+      <x:c r="A118" s="15" t="n">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B118" s="8" t="str">
+      <x:c r="B118" s="13" t="str">
         <x:v>collection.boss-fog-guest.traits</x:v>
       </x:c>
-      <x:c r="C118" s="8" t="str">
+      <x:c r="C118" s="13" t="str">
         <x:v>耐久远高于普通来客，移动较慢；漏进店里扣 {p0} 点耐久，需要持续输出。</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A119" s="7" t="n">
+    <x:row r="119" ht="58" hidden="0" customHeight="1">
+      <x:c r="A119" s="15" t="n">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="B119" s="8" t="str">
+      <x:c r="B119" s="13" t="str">
         <x:v>collection.boss-fog-guest.story</x:v>
       </x:c>
-      <x:c r="C119" s="8" t="str">
+      <x:c r="C119" s="13" t="str">
         <x:v>它提着自己走过潮湿的石板路。灯芯里藏着几封没寄出的信，只愿在便利店的屋檐下等到雾散。</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A120" s="7" t="n">
+    <x:row r="120" ht="58" hidden="0" customHeight="1">
+      <x:c r="A120" s="15" t="n">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B120" s="8" t="str">
+      <x:c r="B120" s="13" t="str">
         <x:v>collection.boss-midnight-leader.category</x:v>
       </x:c>
-      <x:c r="C120" s="8" t="str">
+      <x:c r="C120" s="13" t="str">
         <x:v>小首领 · 第15关</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A121" s="7" t="n">
+    <x:row r="121" ht="58" hidden="0" customHeight="1">
+      <x:c r="A121" s="15" t="n">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B121" s="8" t="str">
+      <x:c r="B121" s="13" t="str">
         <x:v>collection.boss-midnight-leader.traits</x:v>
       </x:c>
-      <x:c r="C121" s="8" t="str">
+      <x:c r="C121" s="13" t="str">
         <x:v>耐久远高于普通来客，移动较慢；漏进店里扣 {p0} 点耐久，需要持续输出。</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A122" s="7" t="n">
+    <x:row r="122" ht="58" hidden="0" customHeight="1">
+      <x:c r="A122" s="15" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B122" s="8" t="str">
+      <x:c r="B122" s="13" t="str">
         <x:v>collection.boss-midnight-leader.story</x:v>
       </x:c>
-      <x:c r="C122" s="8" t="str">
+      <x:c r="C122" s="13" t="str">
         <x:v>它推着装满热食的小车，打算请每位夜班店员吃一口。可惜清单太长，排队的来客把整条夜市都挤满了。</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="15" hidden="0" customHeight="1">
-      <x:c r="A123" s="7" t="n">
+    <x:row r="123" ht="58" hidden="0" customHeight="1">
+      <x:c r="A123" s="15" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B123" s="8" t="str">
+      <x:c r="B123" s="13" t="str">
         <x:v>collection.boss-clock.category</x:v>
       </x:c>
-      <x:c r="C123" s="8" t="str">
+      <x:c r="C123" s="13" t="str">
         <x:v>大首领 · 第20关</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A124" s="7" t="n">
+    <x:row r="124" ht="58" hidden="0" customHeight="1">
+      <x:c r="A124" s="15" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B124" s="8" t="str">
+      <x:c r="B124" s="13" t="str">
         <x:v>collection.boss-clock.traits</x:v>
       </x:c>
-      <x:c r="C124" s="8" t="str">
+      <x:c r="C124" s="13" t="str">
         <x:v>耐久远高于普通来客，移动较慢；漏进店里扣 {p0} 点耐久，需要持续输出。</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A125" s="7" t="n">
+    <x:row r="125" ht="58" hidden="0" customHeight="1">
+      <x:c r="A125" s="15" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B125" s="8" t="str">
+      <x:c r="B125" s="13" t="str">
         <x:v>collection.boss-clock.story</x:v>
       </x:c>
-      <x:c r="C125" s="8" t="str">
+      <x:c r="C125" s="13" t="str">
         <x:v>它每晚巡回一次，确认还有灯为晚归的人亮着。最后一声钟响之后，它也会在便利店门口坐下，等一杯温热的牛奶。</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="15" hidden="0" customHeight="1">
-      <x:c r="A126" s="7" t="n">
+    <x:row r="126" ht="58" hidden="0" customHeight="1">
+      <x:c r="A126" s="15" t="n">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B126" s="8" t="str">
+      <x:c r="B126" s="13" t="str">
         <x:v>collection.staff-scope.category</x:v>
       </x:c>
-      <x:c r="C126" s="8" t="str">
+      <x:c r="C126" s="13" t="str">
         <x:v>猫头鹰 · 盘点员</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A127" s="7" t="n">
+    <x:row r="127" ht="58" hidden="0" customHeight="1">
+      <x:c r="A127" s="15" t="n">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B127" s="8" t="str">
+      <x:c r="B127" s="13" t="str">
         <x:v>collection.staff-scope.traits</x:v>
       </x:c>
-      <x:c r="C127" s="8" t="str">
+      <x:c r="C127" s="13" t="str">
         <x:v>远射贯穿：命中后继续攻击后方 {p0} 范围的同线来客，后续伤害 {p1}%。</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A128" s="7" t="n">
+    <x:row r="128" ht="58" hidden="0" customHeight="1">
+      <x:c r="A128" s="15" t="n">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="B128" s="8" t="str">
+      <x:c r="B128" s="13" t="str">
         <x:v>collection.staff-scope.story</x:v>
       </x:c>
-      <x:c r="C128" s="8" t="str">
+      <x:c r="C128" s="13" t="str">
         <x:v>咕咕隔着一整排货架也能看清价签。那支长长的扫码镜是他的宝贝，只有认真盘点时才舍得擦亮。</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="15" hidden="0" customHeight="1">
-      <x:c r="A129" s="7" t="n">
+    <x:row r="129" ht="58" hidden="0" customHeight="1">
+      <x:c r="A129" s="15" t="n">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B129" s="8" t="str">
+      <x:c r="B129" s="13" t="str">
         <x:v>collection.staff-spark.category</x:v>
       </x:c>
-      <x:c r="C129" s="8" t="str">
+      <x:c r="C129" s="13" t="str">
         <x:v>松鼠 · 电工</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A130" s="7" t="n">
+    <x:row r="130" ht="58" hidden="0" customHeight="1">
+      <x:c r="A130" s="15" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B130" s="8" t="str">
+      <x:c r="B130" s="13" t="str">
         <x:v>collection.staff-spark.traits</x:v>
       </x:c>
-      <x:c r="C130" s="8" t="str">
+      <x:c r="C130" s="13" t="str">
         <x:v>连锁电光：最多命中 {p0} 名来客，每跳保留 {p1}% 伤害。</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A131" s="7" t="n">
+    <x:row r="131" ht="58" hidden="0" customHeight="1">
+      <x:c r="A131" s="15" t="n">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B131" s="8" t="str">
+      <x:c r="B131" s="13" t="str">
         <x:v>collection.staff-spark.story</x:v>
       </x:c>
-      <x:c r="C131" s="8" t="str">
+      <x:c r="C131" s="13" t="str">
         <x:v>栗栗把便利店坏掉的小电器都修好了。口袋里总有一颗备用电池，说是为了应付夜里突然不亮的招牌。</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="15" hidden="0" customHeight="1">
-      <x:c r="A132" s="7" t="n">
+    <x:row r="132" ht="58" hidden="0" customHeight="1">
+      <x:c r="A132" s="15" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B132" s="8" t="str">
+      <x:c r="B132" s="13" t="str">
         <x:v>collection.staff-ember.category</x:v>
       </x:c>
-      <x:c r="C132" s="8" t="str">
+      <x:c r="C132" s="13" t="str">
         <x:v>小熊猫 · 烘焙员</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A133" s="7" t="n">
+    <x:row r="133" ht="58" hidden="0" customHeight="1">
+      <x:c r="A133" s="15" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B133" s="8" t="str">
+      <x:c r="B133" s="13" t="str">
         <x:v>collection.staff-ember.traits</x:v>
       </x:c>
-      <x:c r="C133" s="8" t="str">
+      <x:c r="C133" s="13" t="str">
         <x:v>持续灼烧：命中附加 {p0} 秒灼烧，重复命中刷新时间，不叠层。</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A134" s="7" t="n">
+    <x:row r="134" ht="58" hidden="0" customHeight="1">
+      <x:c r="A134" s="15" t="n">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B134" s="8" t="str">
+      <x:c r="B134" s="13" t="str">
         <x:v>collection.staff-ember.story</x:v>
       </x:c>
-      <x:c r="C134" s="8" t="str">
+      <x:c r="C134" s="13" t="str">
         <x:v>烘烘坚持最后一炉面包也要烤得刚刚好。烤箱的余温总留到收班，谁路过都能闻到一点甜香。</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="15" hidden="0" customHeight="1">
-      <x:c r="A135" s="7" t="n">
+    <x:row r="135" ht="58" hidden="0" customHeight="1">
+      <x:c r="A135" s="15" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B135" s="8" t="str">
+      <x:c r="B135" s="13" t="str">
         <x:v>collection.staff-mint.category</x:v>
       </x:c>
-      <x:c r="C135" s="8" t="str">
+      <x:c r="C135" s="13" t="str">
         <x:v>浣熊 · 保洁员</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A136" s="7" t="n">
+    <x:row r="136" ht="58" hidden="0" customHeight="1">
+      <x:c r="A136" s="15" t="n">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B136" s="8" t="str">
+      <x:c r="B136" s="13" t="str">
         <x:v>collection.staff-mint.traits</x:v>
       </x:c>
-      <x:c r="C136" s="8" t="str">
+      <x:c r="C136" s="13" t="str">
         <x:v>清洁标记：{p0} 秒内受到的店员伤害增加 {p1}%。</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A137" s="7" t="n">
+    <x:row r="137" ht="58" hidden="0" customHeight="1">
+      <x:c r="A137" s="15" t="n">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B137" s="8" t="str">
+      <x:c r="B137" s="13" t="str">
         <x:v>collection.staff-mint.story</x:v>
       </x:c>
-      <x:c r="C137" s="8" t="str">
+      <x:c r="C137" s="13" t="str">
         <x:v>薄荷把雨脚印擦成一道弯弯的光。她的喷瓶上没有刻度，因为每一处污渍她都愿意多照顾一下。</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="15" hidden="0" customHeight="1">
-      <x:c r="A138" s="7" t="n">
+    <x:row r="138" ht="58" hidden="0" customHeight="1">
+      <x:c r="A138" s="15" t="n">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B138" s="8" t="str">
+      <x:c r="B138" s="13" t="str">
         <x:v>collection.staff-fan.category</x:v>
       </x:c>
-      <x:c r="C138" s="8" t="str">
+      <x:c r="C138" s="13" t="str">
         <x:v>小鸭 · 配送员</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A139" s="7" t="n">
+    <x:row r="139" ht="58" hidden="0" customHeight="1">
+      <x:c r="A139" s="15" t="n">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B139" s="8" t="str">
+      <x:c r="B139" s="13" t="str">
         <x:v>collection.staff-fan.traits</x:v>
       </x:c>
-      <x:c r="C139" s="8" t="str">
+      <x:c r="C139" s="13" t="str">
         <x:v>多路风刃：一次最多攻击 {p0} 名不同来客，单个目标只承受一道。</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A140" s="7" t="n">
+    <x:row r="140" ht="58" hidden="0" customHeight="1">
+      <x:c r="A140" s="15" t="n">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B140" s="8" t="str">
+      <x:c r="B140" s="13" t="str">
         <x:v>collection.staff-fan.story</x:v>
       </x:c>
-      <x:c r="C140" s="8" t="str">
+      <x:c r="C140" s="13" t="str">
         <x:v>啾啾担心热食太烫，送餐时总抱着一台小风扇。后来大家发现，它吹走排队烦恼的本领比送餐还熟练。</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="15" hidden="0" customHeight="1">
-      <x:c r="A141" s="7" t="n">
+    <x:row r="141" ht="58" hidden="0" customHeight="1">
+      <x:c r="A141" s="15" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="B141" s="8" t="str">
+      <x:c r="B141" s="13" t="str">
         <x:v>ui.BattleArtView.001</x:v>
       </x:c>
-      <x:c r="C141" s="8" t="str">
+      <x:c r="C141" s="13" t="str">
         <x:v>战斗美术未完整加载，继续使用程序图形。</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="15" hidden="0" customHeight="1">
-      <x:c r="A142" s="7" t="n">
+    <x:row r="142" ht="58" hidden="0" customHeight="1">
+      <x:c r="A142" s="15" t="n">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B142" s="8" t="str">
+      <x:c r="B142" s="13" t="str">
         <x:v>ui.BattleArtView.002</x:v>
       </x:c>
-      <x:c r="C142" s="8" t="str">
+      <x:c r="C142" s="13" t="str">
         <x:v>战斗美术加载失败，继续使用程序图形。</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="15" hidden="0" customHeight="1">
-      <x:c r="A143" s="7" t="n">
+    <x:row r="143" ht="58" hidden="0" customHeight="1">
+      <x:c r="A143" s="15" t="n">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B143" s="8" t="str">
+      <x:c r="B143" s="13" t="str">
         <x:v>ui.BattleSceneryView.001</x:v>
       </x:c>
-      <x:c r="C143" s="8" t="str">
+      <x:c r="C143" s="13" t="str">
         <x:v>场景图集必须为512×512。</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="15" hidden="0" customHeight="1">
-      <x:c r="A144" s="7" t="n">
+    <x:row r="144" ht="58" hidden="0" customHeight="1">
+      <x:c r="A144" s="15" t="n">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B144" s="8" t="str">
+      <x:c r="B144" s="13" t="str">
         <x:v>ui.BattleSceneryView.002</x:v>
       </x:c>
-      <x:c r="C144" s="8" t="str">
+      <x:c r="C144" s="13" t="str">
         <x:v>场景美术加载失败，保留地图和程序地标。</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A145" s="7" t="n">
+    <x:row r="145" ht="58" hidden="0" customHeight="1">
+      <x:c r="A145" s="15" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="B145" s="8" t="str">
+      <x:c r="B145" s="13" t="str">
         <x:v>ui.BattleUiView.001</x:v>
       </x:c>
-      <x:c r="C145" s="8" t="str">
+      <x:c r="C145" s="13" t="str">
         <x:v>战斗UI图标未完整加载，继续使用文字按钮。</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A146" s="7" t="n">
+    <x:row r="146" ht="58" hidden="0" customHeight="1">
+      <x:c r="A146" s="15" t="n">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="B146" s="8" t="str">
+      <x:c r="B146" s="13" t="str">
         <x:v>ui.BattleUiView.002</x:v>
       </x:c>
-      <x:c r="C146" s="8" t="str">
+      <x:c r="C146" s="13" t="str">
         <x:v>战斗UI图集尺寸应为512×512，请核对运行资源导出。</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="15" hidden="0" customHeight="1">
-      <x:c r="A147" s="7" t="n">
+    <x:row r="147" ht="58" hidden="0" customHeight="1">
+      <x:c r="A147" s="15" t="n">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="B147" s="8" t="str">
+      <x:c r="B147" s="13" t="str">
         <x:v>ui.BattleUiView.003</x:v>
       </x:c>
-      <x:c r="C147" s="8" t="str">
+      <x:c r="C147" s="13" t="str">
         <x:v>战斗UI图标加载失败，继续使用文字按钮。</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="15" hidden="0" customHeight="1">
-      <x:c r="A148" s="7" t="n">
+    <x:row r="148" ht="58" hidden="0" customHeight="1">
+      <x:c r="A148" s="15" t="n">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B148" s="8" t="str">
+      <x:c r="B148" s="13" t="str">
         <x:v>ui.CollectionData.001</x:v>
       </x:c>
-      <x:c r="C148" s="8" t="str">
+      <x:c r="C148" s="13" t="str">
         <x:v>血量</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="15" hidden="0" customHeight="1">
-      <x:c r="A149" s="7" t="n">
+    <x:row r="149" ht="58" hidden="0" customHeight="1">
+      <x:c r="A149" s="15" t="n">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="B149" s="8" t="str">
+      <x:c r="B149" s="13" t="str">
         <x:v>ui.CollectionData.002</x:v>
       </x:c>
-      <x:c r="C149" s="8" t="str">
+      <x:c r="C149" s="13" t="str">
         <x:v>移速</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="15" hidden="0" customHeight="1">
-      <x:c r="A150" s="7" t="n">
+    <x:row r="150" ht="58" hidden="0" customHeight="1">
+      <x:c r="A150" s="15" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B150" s="8" t="str">
+      <x:c r="B150" s="13" t="str">
         <x:v>ui.CollectionData.003</x:v>
       </x:c>
-      <x:c r="C150" s="8" t="str">
+      <x:c r="C150" s="13" t="str">
         <x:v>金币奖励</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="15" hidden="0" customHeight="1">
-      <x:c r="A151" s="7" t="n">
+    <x:row r="151" ht="58" hidden="0" customHeight="1">
+      <x:c r="A151" s="15" t="n">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B151" s="8" t="str">
+      <x:c r="B151" s="13" t="str">
         <x:v>ui.CollectionData.004</x:v>
       </x:c>
-      <x:c r="C151" s="8" t="str">
+      <x:c r="C151" s="13" t="str">
         <x:v>伤害值</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="15" hidden="0" customHeight="1">
-      <x:c r="A152" s="7" t="n">
+    <x:row r="152" ht="58" hidden="0" customHeight="1">
+      <x:c r="A152" s="15" t="n">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B152" s="8" t="str">
+      <x:c r="B152" s="13" t="str">
         <x:v>ui.CollectionData.005</x:v>
       </x:c>
-      <x:c r="C152" s="8" t="str">
+      <x:c r="C152" s="13" t="str">
         <x:v>建造费用</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="15" hidden="0" customHeight="1">
-      <x:c r="A153" s="7" t="n">
+    <x:row r="153" ht="58" hidden="0" customHeight="1">
+      <x:c r="A153" s="15" t="n">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="B153" s="8" t="str">
+      <x:c r="B153" s="13" t="str">
         <x:v>ui.CollectionData.006</x:v>
       </x:c>
-      <x:c r="C153" s="8" t="str">
+      <x:c r="C153" s="13" t="str">
         <x:v>伤害</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="15" hidden="0" customHeight="1">
-      <x:c r="A154" s="7" t="n">
+    <x:row r="154" ht="58" hidden="0" customHeight="1">
+      <x:c r="A154" s="15" t="n">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="B154" s="8" t="str">
+      <x:c r="B154" s="13" t="str">
         <x:v>ui.CollectionData.007</x:v>
       </x:c>
-      <x:c r="C154" s="8" t="str">
+      <x:c r="C154" s="13" t="str">
         <x:v>攻速</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="15" hidden="0" customHeight="1">
-      <x:c r="A155" s="7" t="n">
+    <x:row r="155" ht="58" hidden="0" customHeight="1">
+      <x:c r="A155" s="15" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B155" s="8" t="str">
+      <x:c r="B155" s="13" t="str">
         <x:v>ui.CollectionData.008</x:v>
       </x:c>
-      <x:c r="C155" s="8" t="str">
+      <x:c r="C155" s="13" t="str">
         <x:v>{p0}次/秒</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="15" hidden="0" customHeight="1">
-      <x:c r="A156" s="7" t="n">
+    <x:row r="156" ht="58" hidden="0" customHeight="1">
+      <x:c r="A156" s="15" t="n">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B156" s="8" t="str">
+      <x:c r="B156" s="13" t="str">
         <x:v>ui.CollectionData.009</x:v>
       </x:c>
-      <x:c r="C156" s="8" t="str">
+      <x:c r="C156" s="13" t="str">
         <x:v>射程</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="15" hidden="0" customHeight="1">
-      <x:c r="A157" s="7" t="n">
+    <x:row r="157" ht="58" hidden="0" customHeight="1">
+      <x:c r="A157" s="15" t="n">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B157" s="8" t="str">
+      <x:c r="B157" s="13" t="str">
         <x:v>ui.CollectionData.010</x:v>
       </x:c>
-      <x:c r="C157" s="8" t="str">
+      <x:c r="C157" s="13" t="str">
         <x:v>解锁第 {p0} 关后上岗</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="15" hidden="0" customHeight="1">
-      <x:c r="A158" s="7" t="n">
+    <x:row r="158" ht="58" hidden="0" customHeight="1">
+      <x:c r="A158" s="15" t="n">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B158" s="8" t="str">
+      <x:c r="B158" s="13" t="str">
         <x:v>ui.CollectionData.011</x:v>
       </x:c>
-      <x:c r="C158" s="8" t="str">
+      <x:c r="C158" s="13" t="str">
         <x:v>后续开放</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="15" hidden="0" customHeight="1">
-      <x:c r="A159" s="7" t="n">
+    <x:row r="159" ht="58" hidden="0" customHeight="1">
+      <x:c r="A159" s="15" t="n">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B159" s="8" t="str">
+      <x:c r="B159" s="13" t="str">
         <x:v>ui.CollectionData.012</x:v>
       </x:c>
-      <x:c r="C159" s="8" t="str">
+      <x:c r="C159" s="13" t="str">
         <x:v>怪物</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="15" hidden="0" customHeight="1">
-      <x:c r="A160" s="7" t="n">
+    <x:row r="160" ht="58" hidden="0" customHeight="1">
+      <x:c r="A160" s="15" t="n">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B160" s="8" t="str">
+      <x:c r="B160" s="13" t="str">
         <x:v>ui.CollectionData.013</x:v>
       </x:c>
-      <x:c r="C160" s="8" t="str">
+      <x:c r="C160" s="13" t="str">
         <x:v>店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="15" hidden="0" customHeight="1">
-      <x:c r="A161" s="7" t="n">
+    <x:row r="161" ht="58" hidden="0" customHeight="1">
+      <x:c r="A161" s="15" t="n">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="B161" s="8" t="str">
+      <x:c r="B161" s="13" t="str">
         <x:v>ui.CollectionData.014</x:v>
       </x:c>
-      <x:c r="C161" s="8" t="str">
+      <x:c r="C161" s="13" t="str">
         <x:v>升级提高伤害与射程，缩短攻击间隔</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A162" s="7" t="n">
+    <x:row r="162" ht="58" hidden="0" customHeight="1">
+      <x:c r="A162" s="15" t="n">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="B162" s="8" t="str">
+      <x:c r="B162" s="13" t="str">
         <x:v>ui.CollectionData.015</x:v>
       </x:c>
-      <x:c r="C162" s="8" t="str">
+      <x:c r="C162" s="13" t="str">
         <x:v>显示基础血量，实战随关卡和波次变化
 基础移速固定，仍受技能影响</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="15" hidden="0" customHeight="1">
-      <x:c r="A163" s="7" t="n">
+    <x:row r="163" ht="58" hidden="0" customHeight="1">
+      <x:c r="A163" s="15" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B163" s="8" t="str">
+      <x:c r="B163" s="13" t="str">
         <x:v>ui.CollectionData.016</x:v>
       </x:c>
-      <x:c r="C163" s="8" t="str">
+      <x:c r="C163" s="13" t="str">
         <x:v>未遭遇</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="15" hidden="0" customHeight="1">
-      <x:c r="A164" s="7" t="n">
+    <x:row r="164" ht="58" hidden="0" customHeight="1">
+      <x:c r="A164" s="15" t="n">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="B164" s="8" t="str">
+      <x:c r="B164" s="13" t="str">
         <x:v>ui.GameMenuView.001</x:v>
       </x:c>
-      <x:c r="C164" s="8" t="str">
+      <x:c r="C164" s="13" t="str">
         <x:v>森林便利店</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="15" hidden="0" customHeight="1">
-      <x:c r="A165" s="7" t="n">
+    <x:row r="165" ht="58" hidden="0" customHeight="1">
+      <x:c r="A165" s="15" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B165" s="8" t="str">
+      <x:c r="B165" s="13" t="str">
         <x:v>ui.GameMenuView.002</x:v>
       </x:c>
-      <x:c r="C165" s="8" t="str">
+      <x:c r="C165" s="13" t="str">
         <x:v>灯亮着，夜班就开始了</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="15" hidden="0" customHeight="1">
-      <x:c r="A166" s="7" t="n">
+    <x:row r="166" ht="58" hidden="0" customHeight="1">
+      <x:c r="A166" s="15" t="n">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B166" s="8" t="str">
+      <x:c r="B166" s="13" t="str">
         <x:v>ui.GameMenuView.003</x:v>
       </x:c>
-      <x:c r="C166" s="8" t="str">
+      <x:c r="C166" s="13" t="str">
         <x:v>冒险模式</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="15" hidden="0" customHeight="1">
-      <x:c r="A167" s="7" t="n">
+    <x:row r="167" ht="58" hidden="0" customHeight="1">
+      <x:c r="A167" s="15" t="n">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B167" s="8" t="str">
+      <x:c r="B167" s="13" t="str">
         <x:v>ui.GameMenuView.004</x:v>
       </x:c>
-      <x:c r="C167" s="8" t="str">
+      <x:c r="C167" s="13" t="str">
         <x:v>已解锁 {p0} / {p1} 关</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="15" hidden="0" customHeight="1">
-      <x:c r="A168" s="7" t="n">
+    <x:row r="168" ht="58" hidden="0" customHeight="1">
+      <x:c r="A168" s="15" t="n">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B168" s="8" t="str">
+      <x:c r="B168" s="13" t="str">
         <x:v>ui.GameMenuView.005</x:v>
       </x:c>
-      <x:c r="C168" s="8" t="str">
+      <x:c r="C168" s="13" t="str">
         <x:v>挑战模式</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="15" hidden="0" customHeight="1">
-      <x:c r="A169" s="7" t="n">
+    <x:row r="169" ht="58" hidden="0" customHeight="1">
+      <x:c r="A169" s="15" t="n">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="B169" s="8" t="str">
+      <x:c r="B169" s="13" t="str">
         <x:v>ui.GameMenuView.006</x:v>
       </x:c>
-      <x:c r="C169" s="8" t="str">
+      <x:c r="C169" s="13" t="str">
         <x:v>固定体验关 · 限定4名店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="15" hidden="0" customHeight="1">
-      <x:c r="A170" s="7" t="n">
+    <x:row r="170" ht="58" hidden="0" customHeight="1">
+      <x:c r="A170" s="15" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B170" s="8" t="str">
+      <x:c r="B170" s="13" t="str">
         <x:v>ui.GameMenuView.007</x:v>
       </x:c>
-      <x:c r="C170" s="8" t="str">
+      <x:c r="C170" s="13" t="str">
         <x:v>挑战模式</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="15" hidden="0" customHeight="1">
-      <x:c r="A171" s="7" t="n">
+    <x:row r="171" ht="58" hidden="0" customHeight="1">
+      <x:c r="A171" s="15" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B171" s="8" t="str">
+      <x:c r="B171" s="13" t="str">
         <x:v>ui.GameMenuView.008</x:v>
       </x:c>
-      <x:c r="C171" s="8" t="str">
+      <x:c r="C171" s="13" t="str">
         <x:v>挑战模式暂未开放。</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="15" hidden="0" customHeight="1">
-      <x:c r="A172" s="7" t="n">
+    <x:row r="172" ht="58" hidden="0" customHeight="1">
+      <x:c r="A172" s="15" t="n">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B172" s="8" t="str">
+      <x:c r="B172" s="13" t="str">
         <x:v>ui.GameMenuView.009</x:v>
       </x:c>
-      <x:c r="C172" s="8" t="str">
+      <x:c r="C172" s="13" t="str">
         <x:v>游戏图鉴</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="15" hidden="0" customHeight="1">
-      <x:c r="A173" s="7" t="n">
+    <x:row r="173" ht="58" hidden="0" customHeight="1">
+      <x:c r="A173" s="15" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B173" s="8" t="str">
+      <x:c r="B173" s="13" t="str">
         <x:v>ui.GameMenuView.010</x:v>
       </x:c>
-      <x:c r="C173" s="8" t="str">
+      <x:c r="C173" s="13" t="str">
         <x:v>怪物 · BOSS · 店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="15" hidden="0" customHeight="1">
-      <x:c r="A174" s="7" t="n">
+    <x:row r="174" ht="58" hidden="0" customHeight="1">
+      <x:c r="A174" s="15" t="n">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="B174" s="8" t="str">
+      <x:c r="B174" s="13" t="str">
         <x:v>ui.GameMenuView.011</x:v>
       </x:c>
-      <x:c r="C174" s="8" t="str">
+      <x:c r="C174" s="13" t="str">
         <x:v>侧边栏再玩</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="15" hidden="0" customHeight="1">
-      <x:c r="A175" s="7" t="n">
+    <x:row r="175" ht="58" hidden="0" customHeight="1">
+      <x:c r="A175" s="15" t="n">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B175" s="8" t="str">
+      <x:c r="B175" s="13" t="str">
         <x:v>ui.GameMenuView.012</x:v>
       </x:c>
-      <x:c r="C175" s="8" t="str">
+      <x:c r="C175" s="13" t="str">
         <x:v>侧边栏再玩</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="15" hidden="0" customHeight="1">
-      <x:c r="A176" s="7" t="n">
+    <x:row r="176" ht="58" hidden="0" customHeight="1">
+      <x:c r="A176" s="15" t="n">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="B176" s="8" t="str">
+      <x:c r="B176" s="13" t="str">
         <x:v>ui.GameMenuView.013</x:v>
       </x:c>
-      <x:c r="C176" s="8" t="str">
+      <x:c r="C176" s="13" t="str">
         <x:v>欢迎回来，店长</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="15" hidden="0" customHeight="1">
-      <x:c r="A177" s="7" t="n">
+    <x:row r="177" ht="58" hidden="0" customHeight="1">
+      <x:c r="A177" s="15" t="n">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B177" s="8" t="str">
+      <x:c r="B177" s="13" t="str">
         <x:v>ui.GameMenuView.014</x:v>
       </x:c>
-      <x:c r="C177" s="8" t="str">
+      <x:c r="C177" s="13" t="str">
         <x:v>返回</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="15" hidden="0" customHeight="1">
-      <x:c r="A178" s="7" t="n">
+    <x:row r="178" ht="58" hidden="0" customHeight="1">
+      <x:c r="A178" s="15" t="n">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="B178" s="8" t="str">
+      <x:c r="B178" s="13" t="str">
         <x:v>ui.GameMenuView.015</x:v>
       </x:c>
-      <x:c r="C178" s="8" t="str">
+      <x:c r="C178" s="13" t="str">
         <x:v>冒险模式</x:v>
       </x:c>
     </x:row>
-    <x:row r="179" ht="15" hidden="0" customHeight="1">
-      <x:c r="A179" s="7" t="n">
+    <x:row r="179" ht="58" hidden="0" customHeight="1">
+      <x:c r="A179" s="15" t="n">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="B179" s="8" t="str">
+      <x:c r="B179" s="13" t="str">
         <x:v>ui.GameMenuView.016</x:v>
       </x:c>
-      <x:c r="C179" s="8" t="str">
+      <x:c r="C179" s="13" t="str">
         <x:v>已解锁 {p0} / {p1} 关 · 通关开启下一班</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="15" hidden="0" customHeight="1">
-      <x:c r="A180" s="7" t="n">
+    <x:row r="180" ht="58" hidden="0" customHeight="1">
+      <x:c r="A180" s="15" t="n">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B180" s="8" t="str">
+      <x:c r="B180" s="13" t="str">
         <x:v>ui.GameMenuView.017</x:v>
       </x:c>
-      <x:c r="C180" s="8" t="str">
+      <x:c r="C180" s="13" t="str">
         <x:v>共{p0}波</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="15" hidden="0" customHeight="1">
-      <x:c r="A181" s="7" t="n">
+    <x:row r="181" ht="58" hidden="0" customHeight="1">
+      <x:c r="A181" s="15" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="B181" s="8" t="str">
+      <x:c r="B181" s="13" t="str">
         <x:v>ui.GameMenuView.018</x:v>
       </x:c>
-      <x:c r="C181" s="8" t="str">
+      <x:c r="C181" s="13" t="str">
         <x:v>通关第 {p0} 关解锁</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="15" hidden="0" customHeight="1">
-      <x:c r="A182" s="7" t="n">
+    <x:row r="182" ht="58" hidden="0" customHeight="1">
+      <x:c r="A182" s="15" t="n">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="B182" s="8" t="str">
+      <x:c r="B182" s="13" t="str">
         <x:v>ui.GameMenuView.019</x:v>
       </x:c>
-      <x:c r="C182" s="8" t="str">
+      <x:c r="C182" s="13" t="str">
         <x:v>关卡未解锁</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="15" hidden="0" customHeight="1">
-      <x:c r="A183" s="7" t="n">
+    <x:row r="183" ht="58" hidden="0" customHeight="1">
+      <x:c r="A183" s="15" t="n">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="B183" s="8" t="str">
+      <x:c r="B183" s="13" t="str">
         <x:v>ui.GameMenuView.020</x:v>
       </x:c>
-      <x:c r="C183" s="8" t="str">
+      <x:c r="C183" s="13" t="str">
         <x:v>通关第 {p0} 关后解锁。</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="15" hidden="0" customHeight="1">
-      <x:c r="A184" s="7" t="n">
+    <x:row r="184" ht="58" hidden="0" customHeight="1">
+      <x:c r="A184" s="15" t="n">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="B184" s="8" t="str">
+      <x:c r="B184" s="13" t="str">
         <x:v>ui.GameMenuView.021</x:v>
       </x:c>
-      <x:c r="C184" s="8" t="str">
+      <x:c r="C184" s="13" t="str">
         <x:v>上一页</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="15" hidden="0" customHeight="1">
-      <x:c r="A185" s="7" t="n">
+    <x:row r="185" ht="58" hidden="0" customHeight="1">
+      <x:c r="A185" s="15" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="B185" s="8" t="str">
+      <x:c r="B185" s="13" t="str">
         <x:v>ui.GameMenuView.022</x:v>
       </x:c>
-      <x:c r="C185" s="8" t="str">
+      <x:c r="C185" s="13" t="str">
         <x:v>下一页</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="15" hidden="0" customHeight="1">
-      <x:c r="A186" s="7" t="n">
+    <x:row r="186" ht="58" hidden="0" customHeight="1">
+      <x:c r="A186" s="15" t="n">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="B186" s="8" t="str">
+      <x:c r="B186" s="13" t="str">
         <x:v>ui.GameMenuView.023</x:v>
       </x:c>
-      <x:c r="C186" s="8" t="str">
+      <x:c r="C186" s="13" t="str">
         <x:v>点击关卡图片，从开局开始挑战</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="15" hidden="0" customHeight="1">
-      <x:c r="A187" s="7" t="n">
+    <x:row r="187" ht="58" hidden="0" customHeight="1">
+      <x:c r="A187" s="15" t="n">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="B187" s="8" t="str">
+      <x:c r="B187" s="13" t="str">
         <x:v>ui.GameMenuView.024</x:v>
       </x:c>
-      <x:c r="C187" s="8" t="str">
+      <x:c r="C187" s="13" t="str">
         <x:v>游戏图鉴</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="15" hidden="0" customHeight="1">
-      <x:c r="A188" s="7" t="n">
+    <x:row r="188" ht="58" hidden="0" customHeight="1">
+      <x:c r="A188" s="15" t="n">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="B188" s="8" t="str">
+      <x:c r="B188" s="13" t="str">
         <x:v>ui.GameMenuView.025</x:v>
       </x:c>
-      <x:c r="C188" s="8" t="str">
+      <x:c r="C188" s="13" t="str">
         <x:v>{p0}图鉴</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" ht="15" hidden="0" customHeight="1">
-      <x:c r="A189" s="7" t="n">
+    <x:row r="189" ht="58" hidden="0" customHeight="1">
+      <x:c r="A189" s="15" t="n">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="B189" s="8" t="str">
+      <x:c r="B189" s="13" t="str">
         <x:v>ui.GameMenuView.026</x:v>
       </x:c>
-      <x:c r="C189" s="8" t="str">
+      <x:c r="C189" s="13" t="str">
         <x:v>{p0} / {p1} 已收录</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="15" hidden="0" customHeight="1">
-      <x:c r="A190" s="7" t="n">
+    <x:row r="190" ht="58" hidden="0" customHeight="1">
+      <x:c r="A190" s="15" t="n">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="B190" s="8" t="str">
+      <x:c r="B190" s="13" t="str">
         <x:v>ui.GameMenuView.027</x:v>
       </x:c>
-      <x:c r="C190" s="8" t="str">
+      <x:c r="C190" s="13" t="str">
         <x:v>上一页</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="15" hidden="0" customHeight="1">
-      <x:c r="A191" s="7" t="n">
+    <x:row r="191" ht="58" hidden="0" customHeight="1">
+      <x:c r="A191" s="15" t="n">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="B191" s="8" t="str">
+      <x:c r="B191" s="13" t="str">
         <x:v>ui.GameMenuView.028</x:v>
       </x:c>
-      <x:c r="C191" s="8" t="str">
+      <x:c r="C191" s="13" t="str">
         <x:v>下一页</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="15" hidden="0" customHeight="1">
-      <x:c r="A192" s="7" t="n">
+    <x:row r="192" ht="58" hidden="0" customHeight="1">
+      <x:c r="A192" s="15" t="n">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="B192" s="8" t="str">
+      <x:c r="B192" s="13" t="str">
         <x:v>ui.GameMenuView.029</x:v>
       </x:c>
-      <x:c r="C192" s="8" t="str">
+      <x:c r="C192" s="13" t="str">
         <x:v>点击图片，查看特点与夜班故事</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="15" hidden="0" customHeight="1">
-      <x:c r="A193" s="7" t="n">
+    <x:row r="193" ht="58" hidden="0" customHeight="1">
+      <x:c r="A193" s="15" t="n">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="B193" s="8" t="str">
+      <x:c r="B193" s="13" t="str">
         <x:v>ui.GameMenuView.030</x:v>
       </x:c>
-      <x:c r="C193" s="8" t="str">
+      <x:c r="C193" s="13" t="str">
         <x:v>设置</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="15" hidden="0" customHeight="1">
-      <x:c r="A194" s="7" t="n">
+    <x:row r="194" ht="58" hidden="0" customHeight="1">
+      <x:c r="A194" s="15" t="n">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="B194" s="8" t="str">
+      <x:c r="B194" s="13" t="str">
         <x:v>ui.GameMenuView.031</x:v>
       </x:c>
-      <x:c r="C194" s="8" t="str">
+      <x:c r="C194" s="13" t="str">
         <x:v>音乐</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="15" hidden="0" customHeight="1">
-      <x:c r="A195" s="7" t="n">
+    <x:row r="195" ht="58" hidden="0" customHeight="1">
+      <x:c r="A195" s="15" t="n">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="B195" s="8" t="str">
+      <x:c r="B195" s="13" t="str">
         <x:v>ui.GameMenuView.032</x:v>
       </x:c>
-      <x:c r="C195" s="8" t="str">
+      <x:c r="C195" s="13" t="str">
         <x:v>音效</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="15" hidden="0" customHeight="1">
-      <x:c r="A196" s="7" t="n">
+    <x:row r="196" ht="58" hidden="0" customHeight="1">
+      <x:c r="A196" s="15" t="n">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="B196" s="8" t="str">
+      <x:c r="B196" s="13" t="str">
         <x:v>ui.GameMenuView.033</x:v>
       </x:c>
-      <x:c r="C196" s="8" t="str">
+      <x:c r="C196" s="13" t="str">
         <x:v>{p0}  ·  v{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="15" hidden="0" customHeight="1">
-      <x:c r="A197" s="7" t="n">
+    <x:row r="197" ht="58" hidden="0" customHeight="1">
+      <x:c r="A197" s="15" t="n">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="B197" s="8" t="str">
+      <x:c r="B197" s="13" t="str">
         <x:v>ui.GameMenuView.034</x:v>
       </x:c>
-      <x:c r="C197" s="8" t="str">
+      <x:c r="C197" s="13" t="str">
         <x:v>开</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" ht="15" hidden="0" customHeight="1">
-      <x:c r="A198" s="7" t="n">
+    <x:row r="198" ht="58" hidden="0" customHeight="1">
+      <x:c r="A198" s="15" t="n">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="B198" s="8" t="str">
+      <x:c r="B198" s="13" t="str">
         <x:v>ui.GameMenuView.035</x:v>
       </x:c>
-      <x:c r="C198" s="8" t="str">
+      <x:c r="C198" s="13" t="str">
         <x:v>关</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="15" hidden="0" customHeight="1">
-      <x:c r="A199" s="7" t="n">
+    <x:row r="199" ht="58" hidden="0" customHeight="1">
+      <x:c r="A199" s="15" t="n">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="B199" s="8" t="str">
+      <x:c r="B199" s="13" t="str">
         <x:v>ui.GameMenuView.036</x:v>
       </x:c>
-      <x:c r="C199" s="8" t="str">
+      <x:c r="C199" s="13" t="str">
         <x:v>未知档案</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="15" hidden="0" customHeight="1">
-      <x:c r="A200" s="7" t="n">
+    <x:row r="200" ht="58" hidden="0" customHeight="1">
+      <x:c r="A200" s="15" t="n">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="B200" s="8" t="str">
+      <x:c r="B200" s="13" t="str">
         <x:v>ui.GameRoot.001</x:v>
       </x:c>
-      <x:c r="C200" s="8" t="str">
+      <x:c r="C200" s="13" t="str">
         <x:v>地铁口</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="15" hidden="0" customHeight="1">
-      <x:c r="A201" s="7" t="n">
+    <x:row r="201" ht="58" hidden="0" customHeight="1">
+      <x:c r="A201" s="15" t="n">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="B201" s="8" t="str">
+      <x:c r="B201" s="13" t="str">
         <x:v>ui.GameRoot.002</x:v>
       </x:c>
-      <x:c r="C201" s="8" t="str">
+      <x:c r="C201" s="13" t="str">
         <x:v>便利店</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="15" hidden="0" customHeight="1">
-      <x:c r="A202" s="7" t="n">
+    <x:row r="202" ht="58" hidden="0" customHeight="1">
+      <x:c r="A202" s="15" t="n">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B202" s="8" t="str">
+      <x:c r="B202" s="13" t="str">
         <x:v>ui.GameRoot.003</x:v>
       </x:c>
-      <x:c r="C202" s="8" t="str">
+      <x:c r="C202" s="13" t="str">
         <x:v>返回首页</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="15" hidden="0" customHeight="1">
-      <x:c r="A203" s="7" t="n">
+    <x:row r="203" ht="58" hidden="0" customHeight="1">
+      <x:c r="A203" s="15" t="n">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="B203" s="8" t="str">
+      <x:c r="B203" s="13" t="str">
         <x:v>ui.GameRoot.004</x:v>
       </x:c>
-      <x:c r="C203" s="8" t="str">
+      <x:c r="C203" s="13" t="str">
         <x:v>GM 调试</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="15" hidden="0" customHeight="1">
-      <x:c r="A204" s="7" t="n">
+    <x:row r="204" ht="58" hidden="0" customHeight="1">
+      <x:c r="A204" s="15" t="n">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="B204" s="8" t="str">
+      <x:c r="B204" s="13" t="str">
         <x:v>ui.GameRoot.005</x:v>
       </x:c>
-      <x:c r="C204" s="8" t="str">
+      <x:c r="C204" s="13" t="str">
         <x:v>图鉴预览仅本次生效，不改正式存档</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="15" hidden="0" customHeight="1">
-      <x:c r="A205" s="7" t="n">
+    <x:row r="205" ht="58" hidden="0" customHeight="1">
+      <x:c r="A205" s="15" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="B205" s="8" t="str">
+      <x:c r="B205" s="13" t="str">
         <x:v>ui.GameRoot.006</x:v>
       </x:c>
-      <x:c r="C205" s="8" t="str">
+      <x:c r="C205" s="13" t="str">
         <x:v>关闭</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" ht="15" hidden="0" customHeight="1">
-      <x:c r="A206" s="7" t="n">
+    <x:row r="206" ht="58" hidden="0" customHeight="1">
+      <x:c r="A206" s="15" t="n">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="B206" s="8" t="str">
+      <x:c r="B206" s="13" t="str">
         <x:v>ui.GameRoot.007</x:v>
       </x:c>
-      <x:c r="C206" s="8" t="str">
+      <x:c r="C206" s="13" t="str">
         <x:v>返回正式进度</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" ht="15" hidden="0" customHeight="1">
-      <x:c r="A207" s="7" t="n">
+    <x:row r="207" ht="58" hidden="0" customHeight="1">
+      <x:c r="A207" s="15" t="n">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="B207" s="8" t="str">
+      <x:c r="B207" s="13" t="str">
         <x:v>ui.GameRoot.008</x:v>
       </x:c>
-      <x:c r="C207" s="8" t="str">
+      <x:c r="C207" s="13" t="str">
         <x:v>第{p0}关{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="208" ht="15" hidden="0" customHeight="1">
-      <x:c r="A208" s="7" t="n">
+    <x:row r="208" ht="58" hidden="0" customHeight="1">
+      <x:c r="A208" s="15" t="n">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="B208" s="8" t="str">
+      <x:c r="B208" s="13" t="str">
         <x:v>ui.GameRoot.009</x:v>
       </x:c>
-      <x:c r="C208" s="8" t="str">
+      <x:c r="C208" s="13" t="str">
         <x:v>{p0}/{p1} 波</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" ht="15" hidden="0" customHeight="1">
-      <x:c r="A209" s="7" t="n">
+    <x:row r="209" ht="58" hidden="0" customHeight="1">
+      <x:c r="A209" s="15" t="n">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="B209" s="8" t="str">
+      <x:c r="B209" s="13" t="str">
         <x:v>ui.GameRoot.010</x:v>
       </x:c>
-      <x:c r="C209" s="8" t="str">
+      <x:c r="C209" s="13" t="str">
         <x:v>已满级</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" ht="15" hidden="0" customHeight="1">
-      <x:c r="A210" s="7" t="n">
+    <x:row r="210" ht="58" hidden="0" customHeight="1">
+      <x:c r="A210" s="15" t="n">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="B210" s="8" t="str">
+      <x:c r="B210" s="13" t="str">
         <x:v>ui.GameRoot.011</x:v>
       </x:c>
-      <x:c r="C210" s="8" t="str">
+      <x:c r="C210" s="13" t="str">
         <x:v>升级 ●{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="211" ht="15" hidden="0" customHeight="1">
-      <x:c r="A211" s="7" t="n">
+    <x:row r="211" ht="58" hidden="0" customHeight="1">
+      <x:c r="A211" s="15" t="n">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="B211" s="8" t="str">
+      <x:c r="B211" s="13" t="str">
         <x:v>ui.GameRoot.012</x:v>
       </x:c>
-      <x:c r="C211" s="8" t="str">
+      <x:c r="C211" s="13" t="str">
         <x:v>出售 +{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="212" ht="15" hidden="0" customHeight="1">
-      <x:c r="A212" s="7" t="n">
+    <x:row r="212" ht="58" hidden="0" customHeight="1">
+      <x:c r="A212" s="15" t="n">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="B212" s="8" t="str">
+      <x:c r="B212" s="13" t="str">
         <x:v>ui.GameRoot.013</x:v>
       </x:c>
-      <x:c r="C212" s="8" t="str">
+      <x:c r="C212" s="13" t="str">
         <x:v>清理 ♥{p0}  +{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="213" ht="15" hidden="0" customHeight="1">
-      <x:c r="A213" s="7" t="n">
+    <x:row r="213" ht="58" hidden="0" customHeight="1">
+      <x:c r="A213" s="15" t="n">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="B213" s="8" t="str">
+      <x:c r="B213" s="13" t="str">
         <x:v>ui.GameRoot.014</x:v>
       </x:c>
-      <x:c r="C213" s="8" t="str">
+      <x:c r="C213" s="13" t="str">
         <x:v>下一波</x:v>
       </x:c>
     </x:row>
-    <x:row r="214" ht="15" hidden="0" customHeight="1">
-      <x:c r="A214" s="7" t="n">
+    <x:row r="214" ht="58" hidden="0" customHeight="1">
+      <x:c r="A214" s="15" t="n">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="B214" s="8" t="str">
+      <x:c r="B214" s="13" t="str">
         <x:v>ui.GameRoot.015</x:v>
       </x:c>
-      <x:c r="C214" s="8" t="str">
+      <x:c r="C214" s="13" t="str">
         <x:v>结束本局并返回</x:v>
       </x:c>
     </x:row>
-    <x:row r="215" ht="15" hidden="0" customHeight="1">
-      <x:c r="A215" s="7" t="n">
+    <x:row r="215" ht="58" hidden="0" customHeight="1">
+      <x:c r="A215" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="B215" s="8" t="str">
+      <x:c r="B215" s="13" t="str">
         <x:v>ui.GameRoot.016</x:v>
       </x:c>
-      <x:c r="C215" s="8" t="str">
+      <x:c r="C215" s="13" t="str">
         <x:v>返回选关</x:v>
       </x:c>
     </x:row>
-    <x:row r="216" ht="15" hidden="0" customHeight="1">
-      <x:c r="A216" s="7" t="n">
+    <x:row r="216" ht="58" hidden="0" customHeight="1">
+      <x:c r="A216" s="15" t="n">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="B216" s="8" t="str">
+      <x:c r="B216" s="13" t="str">
         <x:v>ui.GameRoot.017</x:v>
       </x:c>
-      <x:c r="C216" s="8" t="str">
+      <x:c r="C216" s="13" t="str">
         <x:v>暂停营业</x:v>
       </x:c>
     </x:row>
-    <x:row r="217" ht="15" hidden="0" customHeight="1">
-      <x:c r="A217" s="7" t="n">
+    <x:row r="217" ht="58" hidden="0" customHeight="1">
+      <x:c r="A217" s="15" t="n">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="B217" s="8" t="str">
+      <x:c r="B217" s="13" t="str">
         <x:v>ui.GameRoot.018</x:v>
       </x:c>
-      <x:c r="C217" s="8" t="str">
+      <x:c r="C217" s="13" t="str">
         <x:v>继续营业</x:v>
       </x:c>
     </x:row>
-    <x:row r="218" ht="15" hidden="0" customHeight="1">
-      <x:c r="A218" s="7" t="n">
+    <x:row r="218" ht="58" hidden="0" customHeight="1">
+      <x:c r="A218" s="15" t="n">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="B218" s="8" t="str">
+      <x:c r="B218" s="13" t="str">
         <x:v>ui.GameRoot.019</x:v>
       </x:c>
-      <x:c r="C218" s="8" t="str">
+      <x:c r="C218" s="13" t="str">
         <x:v>二十夜守护完成！</x:v>
       </x:c>
     </x:row>
-    <x:row r="219" ht="15" hidden="0" customHeight="1">
-      <x:c r="A219" s="7" t="n">
+    <x:row r="219" ht="58" hidden="0" customHeight="1">
+      <x:c r="A219" s="15" t="n">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="B219" s="8" t="str">
+      <x:c r="B219" s="13" t="str">
         <x:v>ui.GameRoot.020</x:v>
       </x:c>
-      <x:c r="C219" s="8" t="str">
+      <x:c r="C219" s="13" t="str">
         <x:v>顺利打烊！</x:v>
       </x:c>
     </x:row>
-    <x:row r="220" ht="15" hidden="0" customHeight="1">
-      <x:c r="A220" s="7" t="n">
+    <x:row r="220" ht="58" hidden="0" customHeight="1">
+      <x:c r="A220" s="15" t="n">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="B220" s="8" t="str">
+      <x:c r="B220" s="13" t="str">
         <x:v>ui.GameRoot.021</x:v>
       </x:c>
-      <x:c r="C220" s="8" t="str">
+      <x:c r="C220" s="13" t="str">
         <x:v>便利店失守了</x:v>
       </x:c>
     </x:row>
-    <x:row r="221" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A221" s="7" t="n">
+    <x:row r="221" ht="58" hidden="0" customHeight="1">
+      <x:c r="A221" s="15" t="n">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="B221" s="8" t="str">
+      <x:c r="B221" s="13" t="str">
         <x:v>ui.GameRoot.022</x:v>
       </x:c>
-      <x:c r="C221" s="8" t="str">
+      <x:c r="C221" s="13" t="str">
         <x:v>赶走 {p0} 只夜间精怪
 金币 {p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="222" ht="15" hidden="0" customHeight="1">
-      <x:c r="A222" s="7" t="n">
+    <x:row r="222" ht="58" hidden="0" customHeight="1">
+      <x:c r="A222" s="15" t="n">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="B222" s="8" t="str">
+      <x:c r="B222" s="13" t="str">
         <x:v>ui.GameRoot.023</x:v>
       </x:c>
-      <x:c r="C222" s="8" t="str">
+      <x:c r="C222" s="13" t="str">
         <x:v>下一关</x:v>
       </x:c>
     </x:row>
-    <x:row r="223" ht="15" hidden="0" customHeight="1">
-      <x:c r="A223" s="7" t="n">
+    <x:row r="223" ht="58" hidden="0" customHeight="1">
+      <x:c r="A223" s="15" t="n">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="B223" s="8" t="str">
+      <x:c r="B223" s="13" t="str">
         <x:v>ui.GameRoot.024</x:v>
       </x:c>
-      <x:c r="C223" s="8" t="str">
+      <x:c r="C223" s="13" t="str">
         <x:v>再次挑战</x:v>
       </x:c>
     </x:row>
-    <x:row r="224" ht="15" hidden="0" customHeight="1">
-      <x:c r="A224" s="7" t="n">
+    <x:row r="224" ht="58" hidden="0" customHeight="1">
+      <x:c r="A224" s="15" t="n">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="B224" s="8" t="str">
+      <x:c r="B224" s="13" t="str">
         <x:v>ui.GameRoot.025</x:v>
       </x:c>
-      <x:c r="C224" s="8" t="str">
+      <x:c r="C224" s="13" t="str">
         <x:v>看广告继续营业</x:v>
       </x:c>
     </x:row>
-    <x:row r="225" ht="15" hidden="0" customHeight="1">
-      <x:c r="A225" s="7" t="n">
+    <x:row r="225" ht="58" hidden="0" customHeight="1">
+      <x:c r="A225" s="15" t="n">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="B225" s="8" t="str">
+      <x:c r="B225" s="13" t="str">
         <x:v>ui.GameRoot.026</x:v>
       </x:c>
-      <x:c r="C225" s="8" t="str">
+      <x:c r="C225" s="13" t="str">
         <x:v>重新挑战</x:v>
       </x:c>
     </x:row>
-    <x:row r="226" ht="15" hidden="0" customHeight="1">
-      <x:c r="A226" s="7" t="n">
+    <x:row r="226" ht="58" hidden="0" customHeight="1">
+      <x:c r="A226" s="15" t="n">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="B226" s="8" t="str">
+      <x:c r="B226" s="13" t="str">
         <x:v>ui.GameRoot.027</x:v>
       </x:c>
-      <x:c r="C226" s="8" t="str">
+      <x:c r="C226" s="13" t="str">
         <x:v>保留店员，重打当前波次</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" ht="15" hidden="0" customHeight="1">
-      <x:c r="A227" s="7" t="n">
+    <x:row r="227" ht="58" hidden="0" customHeight="1">
+      <x:c r="A227" s="15" t="n">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="B227" s="8" t="str">
+      <x:c r="B227" s="13" t="str">
         <x:v>ui.GameRoot.028</x:v>
       </x:c>
-      <x:c r="C227" s="8" t="str">
+      <x:c r="C227" s="13" t="str">
         <x:v>重新开始</x:v>
       </x:c>
     </x:row>
-    <x:row r="228" ht="15" hidden="0" customHeight="1">
-      <x:c r="A228" s="7" t="n">
+    <x:row r="228" ht="58" hidden="0" customHeight="1">
+      <x:c r="A228" s="15" t="n">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="B228" s="8" t="str">
+      <x:c r="B228" s="13" t="str">
         <x:v>ui.GameRoot.029</x:v>
       </x:c>
-      <x:c r="C228" s="8" t="str">
+      <x:c r="C228" s="13" t="str">
         <x:v>当前：第 {p0} 关{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="229" ht="15" hidden="0" customHeight="1">
-      <x:c r="A229" s="7" t="n">
+    <x:row r="229" ht="58" hidden="0" customHeight="1">
+      <x:c r="A229" s="15" t="n">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="B229" s="8" t="str">
+      <x:c r="B229" s="13" t="str">
         <x:v>ui.GameRoot.030</x:v>
       </x:c>
-      <x:c r="C229" s="8" t="str">
+      <x:c r="C229" s="13" t="str">
         <x:v>第 {p0} 关{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="230" ht="15" hidden="0" customHeight="1">
-      <x:c r="A230" s="7" t="n">
+    <x:row r="230" ht="58" hidden="0" customHeight="1">
+      <x:c r="A230" s="15" t="n">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="B230" s="8" t="str">
+      <x:c r="B230" s="13" t="str">
         <x:v>ui.GameRoot.031</x:v>
       </x:c>
-      <x:c r="C230" s="8" t="str">
+      <x:c r="C230" s="13" t="str">
         <x:v>冷气</x:v>
       </x:c>
     </x:row>
-    <x:row r="231" ht="15" hidden="0" customHeight="1">
-      <x:c r="A231" s="7" t="n">
+    <x:row r="231" ht="58" hidden="0" customHeight="1">
+      <x:c r="A231" s="15" t="n">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="B231" s="8" t="str">
+      <x:c r="B231" s="13" t="str">
         <x:v>ui.GameRoot.032</x:v>
       </x:c>
-      <x:c r="C231" s="8" t="str">
+      <x:c r="C231" s="13" t="str">
         <x:v>清场</x:v>
       </x:c>
     </x:row>
-    <x:row r="232" ht="15" hidden="0" customHeight="1">
-      <x:c r="A232" s="7" t="n">
+    <x:row r="232" ht="58" hidden="0" customHeight="1">
+      <x:c r="A232" s="15" t="n">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="B232" s="8" t="str">
+      <x:c r="B232" s="13" t="str">
         <x:v>ui.GameRoot.033</x:v>
       </x:c>
-      <x:c r="C232" s="8" t="str">
+      <x:c r="C232" s="13" t="str">
         <x:v>金币</x:v>
       </x:c>
     </x:row>
-    <x:row r="233" ht="15" hidden="0" customHeight="1">
-      <x:c r="A233" s="7" t="n">
+    <x:row r="233" ht="58" hidden="0" customHeight="1">
+      <x:c r="A233" s="15" t="n">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="B233" s="8" t="str">
+      <x:c r="B233" s="13" t="str">
         <x:v>ui.GameRoot.034</x:v>
       </x:c>
-      <x:c r="C233" s="8" t="str">
+      <x:c r="C233" s="13" t="str">
         <x:v>{p0}·用完</x:v>
       </x:c>
     </x:row>
-    <x:row r="234" ht="15" hidden="0" customHeight="1">
-      <x:c r="A234" s="7" t="n">
+    <x:row r="234" ht="58" hidden="0" customHeight="1">
+      <x:c r="A234" s="15" t="n">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="B234" s="8" t="str">
+      <x:c r="B234" s="13" t="str">
         <x:v>ui.GameRoot.035</x:v>
       </x:c>
-      <x:c r="C234" s="8" t="str">
+      <x:c r="C234" s="13" t="str">
         <x:v>{p0}·广告</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="15" hidden="0" customHeight="1">
-      <x:c r="A235" s="7" t="n">
+    <x:row r="235" ht="58" hidden="0" customHeight="1">
+      <x:c r="A235" s="15" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="B235" s="8" t="str">
+      <x:c r="B235" s="13" t="str">
         <x:v>ui.GameRoot.036</x:v>
       </x:c>
-      <x:c r="C235" s="8" t="str">
+      <x:c r="C235" s="13" t="str">
         <x:v>点空地建造；空闲时点货箱清理</x:v>
       </x:c>
     </x:row>
-    <x:row r="236" ht="15" hidden="0" customHeight="1">
-      <x:c r="A236" s="7" t="n">
+    <x:row r="236" ht="58" hidden="0" customHeight="1">
+      <x:c r="A236" s="15" t="n">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B236" s="8" t="str">
+      <x:c r="B236" s="13" t="str">
         <x:v>ui.GameRoot.037</x:v>
       </x:c>
-      <x:c r="C236" s="8" t="str">
+      <x:c r="C236" s="13" t="str">
         <x:v>第 {p0} 关：{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="237" ht="15" hidden="0" customHeight="1">
-      <x:c r="A237" s="7" t="n">
+    <x:row r="237" ht="58" hidden="0" customHeight="1">
+      <x:c r="A237" s="15" t="n">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="B237" s="8" t="str">
+      <x:c r="B237" s="13" t="str">
         <x:v>ui.GameRoot.038</x:v>
       </x:c>
-      <x:c r="C237" s="8" t="str">
+      <x:c r="C237" s="13" t="str">
         <x:v>便利店耐久 -{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="238" ht="15" hidden="0" customHeight="1">
-      <x:c r="A238" s="7" t="n">
+    <x:row r="238" ht="58" hidden="0" customHeight="1">
+      <x:c r="A238" s="15" t="n">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="B238" s="8" t="str">
+      <x:c r="B238" s="13" t="str">
         <x:v>ui.GameRoot.039</x:v>
       </x:c>
-      <x:c r="C238" s="8" t="str">
+      <x:c r="C238" s="13" t="str">
         <x:v>守住了！夜班收入 +{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" ht="15" hidden="0" customHeight="1">
-      <x:c r="A239" s="7" t="n">
+    <x:row r="239" ht="58" hidden="0" customHeight="1">
+      <x:c r="A239" s="15" t="n">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="B239" s="8" t="str">
+      <x:c r="B239" s="13" t="str">
         <x:v>ui.GameRoot.040</x:v>
       </x:c>
-      <x:c r="C239" s="8" t="str">
+      <x:c r="C239" s="13" t="str">
         <x:v>第 {p0} 波来袭！</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="15" hidden="0" customHeight="1">
-      <x:c r="A240" s="7" t="n">
+    <x:row r="240" ht="58" hidden="0" customHeight="1">
+      <x:c r="A240" s="15" t="n">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="B240" s="8" t="str">
+      <x:c r="B240" s="13" t="str">
         <x:v>ui.GameRoot.041</x:v>
       </x:c>
-      <x:c r="C240" s="8" t="str">
+      <x:c r="C240" s="13" t="str">
         <x:v>清出空地 +{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="241" ht="15" hidden="0" customHeight="1">
-      <x:c r="A241" s="7" t="n">
+    <x:row r="241" ht="58" hidden="0" customHeight="1">
+      <x:c r="A241" s="15" t="n">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="B241" s="8" t="str">
+      <x:c r="B241" s="13" t="str">
         <x:v>ui.GameRoot.042</x:v>
       </x:c>
-      <x:c r="C241" s="8" t="str">
+      <x:c r="C241" s="13" t="str">
         <x:v>这名店员还没有加入夜班</x:v>
       </x:c>
     </x:row>
-    <x:row r="242" ht="15" hidden="0" customHeight="1">
-      <x:c r="A242" s="7" t="n">
+    <x:row r="242" ht="58" hidden="0" customHeight="1">
+      <x:c r="A242" s="15" t="n">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="B242" s="8" t="str">
+      <x:c r="B242" s="13" t="str">
         <x:v>ui.GameRoot.043</x:v>
       </x:c>
-      <x:c r="C242" s="8" t="str">
+      <x:c r="C242" s="13" t="str">
         <x:v>夜班金币不够，先赶走一些精怪吧</x:v>
       </x:c>
     </x:row>
-    <x:row r="243" ht="15" hidden="0" customHeight="1">
-      <x:c r="A243" s="7" t="n">
+    <x:row r="243" ht="58" hidden="0" customHeight="1">
+      <x:c r="A243" s="15" t="n">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="B243" s="8" t="str">
+      <x:c r="B243" s="13" t="str">
         <x:v>ui.GameRoot.044</x:v>
       </x:c>
-      <x:c r="C243" s="8" t="str">
+      <x:c r="C243" s="13" t="str">
         <x:v>{p0}上岗！</x:v>
       </x:c>
     </x:row>
-    <x:row r="244" ht="15" hidden="0" customHeight="1">
-      <x:c r="A244" s="7" t="n">
+    <x:row r="244" ht="58" hidden="0" customHeight="1">
+      <x:c r="A244" s="15" t="n">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="B244" s="8" t="str">
+      <x:c r="B244" s="13" t="str">
         <x:v>ui.GameRoot.045</x:v>
       </x:c>
-      <x:c r="C244" s="8" t="str">
+      <x:c r="C244" s="13" t="str">
         <x:v>先点击一名场上店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="245" ht="15" hidden="0" customHeight="1">
-      <x:c r="A245" s="7" t="n">
+    <x:row r="245" ht="58" hidden="0" customHeight="1">
+      <x:c r="A245" s="15" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="B245" s="8" t="str">
+      <x:c r="B245" s="13" t="str">
         <x:v>ui.GameRoot.046</x:v>
       </x:c>
-      <x:c r="C245" s="8" t="str">
+      <x:c r="C245" s="13" t="str">
         <x:v>{p0}已经满级</x:v>
       </x:c>
     </x:row>
-    <x:row r="246" ht="15" hidden="0" customHeight="1">
-      <x:c r="A246" s="7" t="n">
+    <x:row r="246" ht="58" hidden="0" customHeight="1">
+      <x:c r="A246" s="15" t="n">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="B246" s="8" t="str">
+      <x:c r="B246" s="13" t="str">
         <x:v>ui.GameRoot.047</x:v>
       </x:c>
-      <x:c r="C246" s="8" t="str">
+      <x:c r="C246" s="13" t="str">
         <x:v>升级所需金币不足</x:v>
       </x:c>
     </x:row>
-    <x:row r="247" ht="15" hidden="0" customHeight="1">
-      <x:c r="A247" s="7" t="n">
+    <x:row r="247" ht="58" hidden="0" customHeight="1">
+      <x:c r="A247" s="15" t="n">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="B247" s="8" t="str">
+      <x:c r="B247" s="13" t="str">
         <x:v>ui.GameRoot.048</x:v>
       </x:c>
-      <x:c r="C247" s="8" t="str">
+      <x:c r="C247" s="13" t="str">
         <x:v>调岗返还 +{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="248" ht="15" hidden="0" customHeight="1">
-      <x:c r="A248" s="7" t="n">
+    <x:row r="248" ht="58" hidden="0" customHeight="1">
+      <x:c r="A248" s="15" t="n">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="B248" s="8" t="str">
+      <x:c r="B248" s="13" t="str">
         <x:v>ui.GameRoot.049</x:v>
       </x:c>
-      <x:c r="C248" s="8" t="str">
+      <x:c r="C248" s="13" t="str">
         <x:v>本关这个道具已经用完了</x:v>
       </x:c>
     </x:row>
-    <x:row r="249" ht="15" hidden="0" customHeight="1">
-      <x:c r="A249" s="7" t="n">
+    <x:row r="249" ht="58" hidden="0" customHeight="1">
+      <x:c r="A249" s="15" t="n">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="B249" s="8" t="str">
+      <x:c r="B249" s="13" t="str">
         <x:v>ui.GameRoot.050</x:v>
       </x:c>
-      <x:c r="C249" s="8" t="str">
+      <x:c r="C249" s="13" t="str">
         <x:v>冰柜冷气：全场冻结 {p0} 秒</x:v>
       </x:c>
     </x:row>
-    <x:row r="250" ht="15" hidden="0" customHeight="1">
-      <x:c r="A250" s="7" t="n">
+    <x:row r="250" ht="58" hidden="0" customHeight="1">
+      <x:c r="A250" s="15" t="n">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="B250" s="8" t="str">
+      <x:c r="B250" s="13" t="str">
         <x:v>ui.GameRoot.051</x:v>
       </x:c>
-      <x:c r="C250" s="8" t="str">
+      <x:c r="C250" s="13" t="str">
         <x:v>紧急金币 +{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="251" ht="15" hidden="0" customHeight="1">
-      <x:c r="A251" s="7" t="n">
+    <x:row r="251" ht="58" hidden="0" customHeight="1">
+      <x:c r="A251" s="15" t="n">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="B251" s="8" t="str">
+      <x:c r="B251" s="13" t="str">
         <x:v>ui.GameRoot.052</x:v>
       </x:c>
-      <x:c r="C251" s="8" t="str">
+      <x:c r="C251" s="13" t="str">
         <x:v>闭店清场：赶走小怪，削弱重型与首领</x:v>
       </x:c>
     </x:row>
-    <x:row r="252" ht="15" hidden="0" customHeight="1">
-      <x:c r="A252" s="7" t="n">
+    <x:row r="252" ht="58" hidden="0" customHeight="1">
+      <x:c r="A252" s="15" t="n">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="B252" s="8" t="str">
+      <x:c r="B252" s="13" t="str">
         <x:v>ui.GameRoot.053</x:v>
       </x:c>
-      <x:c r="C252" s="8" t="str">
+      <x:c r="C252" s="13" t="str">
         <x:v>正在请求道具广告…</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" ht="15" hidden="0" customHeight="1">
-      <x:c r="A253" s="7" t="n">
+    <x:row r="253" ht="58" hidden="0" customHeight="1">
+      <x:c r="A253" s="15" t="n">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="B253" s="8" t="str">
+      <x:c r="B253" s="13" t="str">
         <x:v>ui.GameRoot.054</x:v>
       </x:c>
-      <x:c r="C253" s="8" t="str">
+      <x:c r="C253" s="13" t="str">
         <x:v>广告未完成或暂不可用，道具未使用</x:v>
       </x:c>
     </x:row>
-    <x:row r="254" ht="15" hidden="0" customHeight="1">
-      <x:c r="A254" s="7" t="n">
+    <x:row r="254" ht="58" hidden="0" customHeight="1">
+      <x:c r="A254" s="15" t="n">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="B254" s="8" t="str">
+      <x:c r="B254" s="13" t="str">
         <x:v>ui.GameRoot.055</x:v>
       </x:c>
-      <x:c r="C254" s="8" t="str">
+      <x:c r="C254" s="13" t="str">
         <x:v>正在请求继续营业广告…</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" ht="15" hidden="0" customHeight="1">
-      <x:c r="A255" s="7" t="n">
+    <x:row r="255" ht="58" hidden="0" customHeight="1">
+      <x:c r="A255" s="15" t="n">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="B255" s="8" t="str">
+      <x:c r="B255" s="13" t="str">
         <x:v>ui.GameRoot.056</x:v>
       </x:c>
-      <x:c r="C255" s="8" t="str">
+      <x:c r="C255" s="13" t="str">
         <x:v>广告未完成或暂不可用，未复活</x:v>
       </x:c>
     </x:row>
-    <x:row r="256" ht="15" hidden="0" customHeight="1">
-      <x:c r="A256" s="7" t="n">
+    <x:row r="256" ht="58" hidden="0" customHeight="1">
+      <x:c r="A256" s="15" t="n">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="B256" s="8" t="str">
+      <x:c r="B256" s="13" t="str">
         <x:v>ui.GameRoot.057</x:v>
       </x:c>
-      <x:c r="C256" s="8" t="str">
+      <x:c r="C256" s="13" t="str">
         <x:v>继续营业！当前波次即将重来</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" ht="15" hidden="0" customHeight="1">
-      <x:c r="A257" s="7" t="n">
+    <x:row r="257" ht="58" hidden="0" customHeight="1">
+      <x:c r="A257" s="15" t="n">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="B257" s="8" t="str">
+      <x:c r="B257" s="13" t="str">
         <x:v>ui.GameRoot.058</x:v>
       </x:c>
-      <x:c r="C257" s="8" t="str">
+      <x:c r="C257" s="13" t="str">
         <x:v>广告暂不可用，请稍后重试</x:v>
       </x:c>
     </x:row>
-    <x:row r="258" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A258" s="7" t="n">
+    <x:row r="258" ht="58" hidden="0" customHeight="1">
+      <x:c r="A258" s="15" t="n">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="B258" s="8" t="str">
+      <x:c r="B258" s="13" t="str">
         <x:v>ui.MenuArtView.001</x:v>
       </x:c>
-      <x:c r="C258" s="8" t="str">
+      <x:c r="C258" s="13" t="str">
         <x:v>主界面图标未完整加载，继续使用文字按钮。</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A259" s="7" t="n">
+    <x:row r="259" ht="58" hidden="0" customHeight="1">
+      <x:c r="A259" s="15" t="n">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="B259" s="8" t="str">
+      <x:c r="B259" s="13" t="str">
         <x:v>ui.MenuArtView.002</x:v>
       </x:c>
-      <x:c r="C259" s="8" t="str">
+      <x:c r="C259" s="13" t="str">
         <x:v>主界面图集尺寸应为512×512，请核对运行资源导出。</x:v>
       </x:c>
     </x:row>
-    <x:row r="260" ht="15" hidden="0" customHeight="1">
-      <x:c r="A260" s="7" t="n">
+    <x:row r="260" ht="58" hidden="0" customHeight="1">
+      <x:c r="A260" s="15" t="n">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="B260" s="8" t="str">
+      <x:c r="B260" s="13" t="str">
         <x:v>ui.MenuArtView.003</x:v>
       </x:c>
-      <x:c r="C260" s="8" t="str">
+      <x:c r="C260" s="13" t="str">
         <x:v>主界面图标加载失败，继续使用文字按钮。</x:v>
       </x:c>
     </x:row>
-    <x:row r="261" ht="15" hidden="0" customHeight="1">
-      <x:c r="A261" s="7" t="n">
+    <x:row r="261" ht="58" hidden="0" customHeight="1">
+      <x:c r="A261" s="15" t="n">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="B261" s="8" t="str">
+      <x:c r="B261" s="13" t="str">
         <x:v>ui.GameRoot.extra0</x:v>
       </x:c>
-      <x:c r="C261" s="8" t="str">
+      <x:c r="C261" s="13" t="str">
         <x:v>（GM 测试）</x:v>
       </x:c>
     </x:row>
-    <x:row r="262" ht="15" hidden="0" customHeight="1">
-      <x:c r="A262" s="7" t="n">
+    <x:row r="262" ht="58" hidden="0" customHeight="1">
+      <x:c r="A262" s="15" t="n">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="B262" s="8" t="str">
+      <x:c r="B262" s="13" t="str">
         <x:v>ui.GameRoot.extra1</x:v>
       </x:c>
-      <x:c r="C262" s="8" t="str">
+      <x:c r="C262" s="13" t="str">
         <x:v>（正式进度）</x:v>
       </x:c>
     </x:row>
-    <x:row r="263" ht="15" hidden="0" customHeight="1">
-      <x:c r="A263" s="7" t="n">
+    <x:row r="263" ht="58" hidden="0" customHeight="1">
+      <x:c r="A263" s="15" t="n">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="B263" s="8" t="str">
+      <x:c r="B263" s="13" t="str">
         <x:v>ui.GameRoot.extra2</x:v>
       </x:c>
-      <x:c r="C263" s="8" t="str">
+      <x:c r="C263" s="13" t="str">
         <x:v>  当前</x:v>
       </x:c>
     </x:row>
-    <x:row r="264" ht="15" hidden="0" customHeight="1">
-      <x:c r="A264" s="7" t="n">
+    <x:row r="264" ht="58" hidden="0" customHeight="1">
+      <x:c r="A264" s="15" t="n">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="B264" s="8" t="str">
+      <x:c r="B264" s="13" t="str">
         <x:v>ui.GameMenuView.extra0</x:v>
       </x:c>
-      <x:c r="C264" s="8" t="str">
+      <x:c r="C264" s="13" t="str">
         <x:v>大BOSS</x:v>
       </x:c>
     </x:row>
-    <x:row r="265" ht="15" hidden="0" customHeight="1">
-      <x:c r="A265" s="7" t="n">
+    <x:row r="265" ht="58" hidden="0" customHeight="1">
+      <x:c r="A265" s="15" t="n">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="B265" s="8" t="str">
+      <x:c r="B265" s="13" t="str">
         <x:v>ui.GameMenuView.extra1</x:v>
       </x:c>
-      <x:c r="C265" s="8" t="str">
+      <x:c r="C265" s="13" t="str">
         <x:v>小BOSS</x:v>
       </x:c>
     </x:row>
-    <x:row r="266" ht="15" hidden="0" customHeight="1">
-      <x:c r="A266" s="7" t="n">
+    <x:row r="266" ht="58" hidden="0" customHeight="1">
+      <x:c r="A266" s="15" t="n">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="B266" s="8" t="str">
+      <x:c r="B266" s="13" t="str">
         <x:v>ui.GameMenuView.extra2</x:v>
       </x:c>
-      <x:c r="C266" s="8" t="str">
+      <x:c r="C266" s="13" t="str">
         <x:v>可挑战</x:v>
       </x:c>
     </x:row>
-    <x:row r="267" ht="15" hidden="0" customHeight="1">
-      <x:c r="A267" s="7" t="n">
+    <x:row r="267" ht="58" hidden="0" customHeight="1">
+      <x:c r="A267" s="15" t="n">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="B267" s="8" t="str">
+      <x:c r="B267" s="13" t="str">
         <x:v>ui.PlatformSettings.0</x:v>
       </x:c>
-      <x:c r="C267" s="8" t="str">
+      <x:c r="C267" s="13" t="str">
         <x:v>当前环境暂不支持侧边栏入口。</x:v>
       </x:c>
     </x:row>
-    <x:row r="268" ht="15" hidden="0" customHeight="1">
-      <x:c r="A268" s="7" t="n">
+    <x:row r="268" ht="58" hidden="0" customHeight="1">
+      <x:c r="A268" s="15" t="n">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="B268" s="8" t="str">
+      <x:c r="B268" s="13" t="str">
         <x:v>ui.PlatformSettings.1</x:v>
       </x:c>
-      <x:c r="C268" s="8" t="str">
+      <x:c r="C268" s="13" t="str">
         <x:v>暂时无法打开侧边栏，请稍后重试。</x:v>
       </x:c>
     </x:row>
-    <x:row r="269" ht="15" hidden="0" customHeight="1">
-      <x:c r="A269" s="7" t="n">
+    <x:row r="269" ht="58" hidden="0" customHeight="1">
+      <x:c r="A269" s="15" t="n">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="B269" s="8" t="str">
+      <x:c r="B269" s="13" t="str">
         <x:v>ui.PlatformSettings.2</x:v>
       </x:c>
-      <x:c r="C269" s="8" t="str">
+      <x:c r="C269" s="13" t="str">
         <x:v>已打开侧边栏，可从这里再次进入游戏。</x:v>
       </x:c>
     </x:row>
-    <x:row r="270" ht="15" hidden="0" customHeight="1">
-      <x:c r="A270" s="7" t="n">
+    <x:row r="270" ht="58" hidden="0" customHeight="1">
+      <x:c r="A270" s="15" t="n">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="B270" s="8" t="str">
+      <x:c r="B270" s="13" t="str">
         <x:v>ui.unknown</x:v>
       </x:c>
-      <x:c r="C270" s="8" t="str">
+      <x:c r="C270" s="13" t="str">
         <x:v>???</x:v>
       </x:c>
     </x:row>
-    <x:row r="271" ht="15" hidden="0" customHeight="1">
-      <x:c r="A271" s="7" t="n">
+    <x:row r="271" ht="58" hidden="0" customHeight="1">
+      <x:c r="A271" s="15" t="n">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="B271" s="8" t="str">
+      <x:c r="B271" s="13" t="str">
         <x:v>ui.boss</x:v>
       </x:c>
-      <x:c r="C271" s="8" t="str">
+      <x:c r="C271" s="13" t="str">
         <x:v>BOSS</x:v>
       </x:c>
     </x:row>
-    <x:row r="272">
-      <x:c r="A272" t="n">
+    <x:row r="272" ht="58" customHeight="1">
+      <x:c r="A272" s="16" t="n">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B272" t="str">
+      <x:c r="B272" s="16" t="str">
         <x:v>ui.opt.upgradeCost</x:v>
       </x:c>
-      <x:c r="C272" t="str">
+      <x:c r="C272" s="16" t="str">
         <x:v>升级费用</x:v>
       </x:c>
     </x:row>
-    <x:row r="273">
-      <x:c r="A273" t="n">
+    <x:row r="273" ht="58" customHeight="1">
+      <x:c r="A273" s="16" t="n">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="B273" t="str">
+      <x:c r="B273" s="16" t="str">
         <x:v>ui.opt.staffLevel1</x:v>
       </x:c>
-      <x:c r="C273" t="str">
+      <x:c r="C273" s="16" t="str">
         <x:v>1级</x:v>
       </x:c>
     </x:row>
-    <x:row r="274">
-      <x:c r="A274" t="n">
+    <x:row r="274" ht="58" customHeight="1">
+      <x:c r="A274" s="16" t="n">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="B274" t="str">
+      <x:c r="B274" s="16" t="str">
         <x:v>ui.opt.staffLevel2</x:v>
       </x:c>
-      <x:c r="C274" t="str">
+      <x:c r="C274" s="16" t="str">
         <x:v>2级</x:v>
       </x:c>
     </x:row>
-    <x:row r="275">
-      <x:c r="A275" t="n">
+    <x:row r="275" ht="58" customHeight="1">
+      <x:c r="A275" s="16" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="B275" t="str">
+      <x:c r="B275" s="16" t="str">
         <x:v>ui.opt.staffLevel3</x:v>
       </x:c>
-      <x:c r="C275" t="str">
+      <x:c r="C275" s="16" t="str">
         <x:v>3级</x:v>
       </x:c>
     </x:row>
-    <x:row r="276">
-      <x:c r="A276" t="n">
+    <x:row r="276" ht="58" customHeight="1">
+      <x:c r="A276" s="16" t="n">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="B276" t="str">
+      <x:c r="B276" s="16" t="str">
         <x:v>ui.opt.gold</x:v>
       </x:c>
-      <x:c r="C276" t="str">
+      <x:c r="C276" s="16" t="str">
         <x:v>{p0}金币</x:v>
       </x:c>
     </x:row>
-    <x:row r="277">
-      <x:c r="A277" t="n">
+    <x:row r="277" ht="58" customHeight="1">
+      <x:c r="A277" s="16" t="n">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="B277" t="str">
+      <x:c r="B277" s="16" t="str">
         <x:v>challenge.title</x:v>
       </x:c>
-      <x:c r="C277" t="str">
+      <x:c r="C277" s="16" t="str">
         <x:v>夜班极限挑战</x:v>
       </x:c>
     </x:row>
-    <x:row r="278">
-      <x:c r="A278" t="n">
+    <x:row r="278" ht="58" customHeight="1">
+      <x:c r="A278" s="16" t="n">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="B278" t="str">
+      <x:c r="B278" s="16" t="str">
         <x:v>challenge.goal</x:v>
       </x:c>
-      <x:c r="C278" t="str">
+      <x:c r="C278" s="16" t="str">
         <x:v>限定店员搭配，守住最后一班</x:v>
       </x:c>
     </x:row>
-    <x:row r="279">
-      <x:c r="A279" t="n">
+    <x:row r="279" ht="58" customHeight="1">
+      <x:c r="A279" s="16" t="n">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="B279" t="str">
+      <x:c r="B279" s="16" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
-      <x:c r="C279" t="str">
+      <x:c r="C279" s="16" t="str">
         <x:v>首领来袭，准备集中火力！</x:v>
       </x:c>
     </x:row>
-    <x:row r="280">
-      <x:c r="A280" t="n">
+    <x:row r="280" ht="58" customHeight="1">
+      <x:c r="A280" s="16" t="n">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="B280" t="str">
+      <x:c r="B280" s="16" t="str">
         <x:v>challenge.hud</x:v>
       </x:c>
-      <x:c r="C280" t="str">
+      <x:c r="C280" s="16" t="str">
         <x:v>挑战体验关</x:v>
       </x:c>
     </x:row>
-    <x:row r="281">
-      <x:c r="A281" t="n">
+    <x:row r="281" ht="58" customHeight="1">
+      <x:c r="A281" s="16" t="n">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="B281" t="str">
+      <x:c r="B281" s="16" t="str">
         <x:v>challenge.win</x:v>
       </x:c>
-      <x:c r="C281" t="str">
+      <x:c r="C281" s="16" t="str">
         <x:v>挑战守护完成！</x:v>
       </x:c>
     </x:row>
-    <x:row r="282">
-      <x:c r="A282" t="n">
+    <x:row r="282" ht="58" customHeight="1">
+      <x:c r="A282" s="16" t="n">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="B282" t="str">
+      <x:c r="B282" s="16" t="str">
         <x:v>challenge.return</x:v>
       </x:c>
-      <x:c r="C282" t="str">
+      <x:c r="C282" s="16" t="str">
         <x:v>返回首页</x:v>
       </x:c>
     </x:row>
-    <x:row r="283">
-      <x:c r="A283" t="n">
+    <x:row r="283" ht="58" customHeight="1">
+      <x:c r="A283" s="16" t="n">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="B283" t="str">
+      <x:c r="B283" s="16" t="str">
         <x:v>challenge.enter</x:v>
       </x:c>
-      <x:c r="C283" t="str">
+      <x:c r="C283" s="16" t="str">
         <x:v>固定挑战：棉棉、布丁、咕咕、薄荷</x:v>
       </x:c>
     </x:row>
-    <x:row r="284">
-      <x:c r="A284" t="n">
+    <x:row r="284" ht="58" customHeight="1">
+      <x:c r="A284" s="16" t="n">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="B284" t="str">
+      <x:c r="B284" s="16" t="str">
         <x:v>ui.opt.startWave</x:v>
       </x:c>
-      <x:c r="C284" t="str">
+      <x:c r="C284" s="16" t="str">
         <x:v>开始下一波</x:v>
       </x:c>
     </x:row>
-    <x:row r="285">
-      <x:c r="A285" t="n">
+    <x:row r="285" ht="58" customHeight="1">
+      <x:c r="A285" s="16" t="n">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="B285" t="str">
+      <x:c r="B285" s="16" t="str">
         <x:v>ui.gm.enemies</x:v>
       </x:c>
-      <x:c r="C285" t="str">
+      <x:c r="C285" s="16" t="str">
         <x:v>解锁怪物</x:v>
       </x:c>
     </x:row>
-    <x:row r="286">
-      <x:c r="A286" t="n">
+    <x:row r="286" ht="58" customHeight="1">
+      <x:c r="A286" s="16" t="n">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="B286" t="str">
+      <x:c r="B286" s="16" t="str">
         <x:v>ui.gm.bosses</x:v>
       </x:c>
-      <x:c r="C286" t="str">
+      <x:c r="C286" s="16" t="str">
         <x:v>解锁 BOSS</x:v>
       </x:c>
     </x:row>
-    <x:row r="287">
-      <x:c r="A287" t="n">
+    <x:row r="287" ht="58" customHeight="1">
+      <x:c r="A287" s="16" t="n">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="B287" t="str">
+      <x:c r="B287" s="16" t="str">
         <x:v>ui.gm.staff</x:v>
       </x:c>
-      <x:c r="C287" t="str">
+      <x:c r="C287" s="16" t="str">
         <x:v>解锁店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="288">
-      <x:c r="A288" t="n">
+    <x:row r="288" ht="58" customHeight="1">
+      <x:c r="A288" s="16" t="n">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="B288" t="str">
+      <x:c r="B288" s="16" t="str">
         <x:v>ui.gm.all</x:v>
       </x:c>
-      <x:c r="C288" t="str">
+      <x:c r="C288" s="16" t="str">
         <x:v>解锁全部图鉴</x:v>
       </x:c>
     </x:row>
-    <x:row r="289">
-      <x:c r="A289" t="n">
+    <x:row r="289" ht="58" customHeight="1">
+      <x:c r="A289" s="16" t="n">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="B289" t="str">
+      <x:c r="B289" s="16" t="str">
         <x:v>ui.gm.restore</x:v>
       </x:c>
-      <x:c r="C289" t="str">
+      <x:c r="C289" s="16" t="str">
         <x:v>恢复正式图鉴</x:v>
       </x:c>
     </x:row>
-    <x:row r="290">
-      <x:c r="A290" t="n">
+    <x:row r="290" ht="58" customHeight="1">
+      <x:c r="A290" s="16" t="n">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="B290" t="str">
+      <x:c r="B290" s="16" t="str">
         <x:v>guide.place</x:v>
       </x:c>
-      <x:c r="C290" t="str">
+      <x:c r="C290" s="16" t="str">
         <x:v>点空位，安排{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="291">
-      <x:c r="A291" t="n">
+    <x:row r="291" ht="58" customHeight="1">
+      <x:c r="A291" s="16" t="n">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="B291" t="str">
+      <x:c r="B291" s="16" t="str">
         <x:v>guide.choose</x:v>
       </x:c>
-      <x:c r="C291" t="str">
+      <x:c r="C291" s="16" t="str">
         <x:v>选择{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="292">
-      <x:c r="A292" t="n">
+    <x:row r="292" ht="58" customHeight="1">
+      <x:c r="A292" s="16" t="n">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B292" t="str">
+      <x:c r="B292" s="16" t="str">
         <x:v>guide.coins</x:v>
       </x:c>
-      <x:c r="C292" t="str">
+      <x:c r="C292" s="16" t="str">
         <x:v>金币够了再安排{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="293">
-      <x:c r="A293" t="n">
+    <x:row r="293" ht="58" customHeight="1">
+      <x:c r="A293" s="16" t="n">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="B293" t="str">
+      <x:c r="B293" s="16" t="str">
         <x:v>guide.build.select</x:v>
       </x:c>
-      <x:c r="C293" t="str">
+      <x:c r="C293" s="16" t="str">
         <x:v>点空位，安排豆包</x:v>
       </x:c>
     </x:row>
-    <x:row r="294">
-      <x:c r="A294" t="n">
+    <x:row r="294" ht="58" customHeight="1">
+      <x:c r="A294" s="16" t="n">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="B294" t="str">
+      <x:c r="B294" s="16" t="str">
         <x:v>guide.build.action</x:v>
       </x:c>
-      <x:c r="C294" t="str">
+      <x:c r="C294" s="16" t="str">
         <x:v>选择豆包</x:v>
       </x:c>
     </x:row>
-    <x:row r="295">
-      <x:c r="A295" t="n">
+    <x:row r="295" ht="58" customHeight="1">
+      <x:c r="A295" s="16" t="n">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="B295" t="str">
+      <x:c r="B295" s="16" t="str">
         <x:v>guide.build.wait</x:v>
       </x:c>
-      <x:c r="C295" t="str">
+      <x:c r="C295" s="16" t="str">
         <x:v>豆包会自动攻击</x:v>
       </x:c>
     </x:row>
-    <x:row r="296">
-      <x:c r="A296" t="n">
+    <x:row r="296" ht="58" customHeight="1">
+      <x:c r="A296" s="16" t="n">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="B296" t="str">
+      <x:c r="B296" s="16" t="str">
         <x:v>guide.upgrade.select</x:v>
       </x:c>
-      <x:c r="C296" t="str">
+      <x:c r="C296" s="16" t="str">
         <x:v>点豆包，看看升级</x:v>
       </x:c>
     </x:row>
-    <x:row r="297">
-      <x:c r="A297" t="n">
+    <x:row r="297" ht="58" customHeight="1">
+      <x:c r="A297" s="16" t="n">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="B297" t="str">
+      <x:c r="B297" s="16" t="str">
         <x:v>guide.upgrade.action</x:v>
       </x:c>
-      <x:c r="C297" t="str">
+      <x:c r="C297" s="16" t="str">
         <x:v>升级豆包</x:v>
       </x:c>
     </x:row>
-    <x:row r="298">
-      <x:c r="A298" t="n">
+    <x:row r="298" ht="58" customHeight="1">
+      <x:c r="A298" s="16" t="n">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="B298" t="str">
+      <x:c r="B298" s="16" t="str">
         <x:v>guide.upgrade.wait</x:v>
       </x:c>
-      <x:c r="C298" t="str">
+      <x:c r="C298" s="16" t="str">
         <x:v>攒够金币再升级</x:v>
       </x:c>
     </x:row>
-    <x:row r="299">
-      <x:c r="A299" t="n">
+    <x:row r="299" ht="58" customHeight="1">
+      <x:c r="A299" s="16" t="n">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="B299" t="str">
+      <x:c r="B299" s="16" t="str">
         <x:v>guide.combo.select</x:v>
       </x:c>
-      <x:c r="C299" t="str">
+      <x:c r="C299" s="16" t="str">
         <x:v>把棉棉放在豆包旁</x:v>
       </x:c>
     </x:row>
-    <x:row r="300">
-      <x:c r="A300" t="n">
+    <x:row r="300" ht="58" customHeight="1">
+      <x:c r="A300" s="16" t="n">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="B300" t="str">
+      <x:c r="B300" s="16" t="str">
         <x:v>guide.combo.action</x:v>
       </x:c>
-      <x:c r="C300" t="str">
+      <x:c r="C300" s="16" t="str">
         <x:v>选择棉棉</x:v>
       </x:c>
     </x:row>
-    <x:row r="301">
-      <x:c r="A301" t="n">
+    <x:row r="301" ht="58" customHeight="1">
+      <x:c r="A301" s="16" t="n">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="B301" t="str">
+      <x:c r="B301" s="16" t="str">
         <x:v>guide.combo.wait</x:v>
       </x:c>
-      <x:c r="C301" t="str">
+      <x:c r="C301" s="16" t="str">
         <x:v>棉棉减速，豆包接着打</x:v>
       </x:c>
     </x:row>
-    <x:row r="302">
-      <x:c r="A302" t="n">
+    <x:row r="302" ht="58" customHeight="1">
+      <x:c r="A302" s="16" t="n">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="B302" t="str">
+      <x:c r="B302" s="16" t="str">
         <x:v>guide.area.select</x:v>
       </x:c>
-      <x:c r="C302" t="str">
+      <x:c r="C302" s="16" t="str">
         <x:v>安排布丁对付成群精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="303">
-      <x:c r="A303" t="n">
+    <x:row r="303" ht="58" customHeight="1">
+      <x:c r="A303" s="16" t="n">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="B303" t="str">
+      <x:c r="B303" s="16" t="str">
         <x:v>guide.area.action</x:v>
       </x:c>
-      <x:c r="C303" t="str">
+      <x:c r="C303" s="16" t="str">
         <x:v>选择布丁</x:v>
       </x:c>
     </x:row>
-    <x:row r="304">
-      <x:c r="A304" t="n">
+    <x:row r="304" ht="58" customHeight="1">
+      <x:c r="A304" s="16" t="n">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="B304" t="str">
+      <x:c r="B304" s="16" t="str">
         <x:v>guide.area.wait</x:v>
       </x:c>
-      <x:c r="C304" t="str">
+      <x:c r="C304" s="16" t="str">
         <x:v>布丁能一次打到多只精怪</x:v>
       </x:c>
     </x:row>
-    <x:row r="305">
-      <x:c r="A305" t="n">
+    <x:row r="305" ht="58" customHeight="1">
+      <x:c r="A305" s="16" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="B305" t="str">
+      <x:c r="B305" s="16" t="str">
         <x:v>guide.clear.select</x:v>
       </x:c>
-      <x:c r="C305" t="str">
+      <x:c r="C305" s="16" t="str">
         <x:v>点店员旁的杂物</x:v>
       </x:c>
     </x:row>
-    <x:row r="306">
-      <x:c r="A306" t="n">
+    <x:row r="306" ht="58" customHeight="1">
+      <x:c r="A306" s="16" t="n">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B306" t="str">
+      <x:c r="B306" s="16" t="str">
         <x:v>guide.clear.action</x:v>
       </x:c>
-      <x:c r="C306" t="str">
+      <x:c r="C306" s="16" t="str">
         <x:v>点杂物，清理后获得金币</x:v>
       </x:c>
     </x:row>
-    <x:row r="307">
-      <x:c r="A307" t="n">
+    <x:row r="307" ht="58" customHeight="1">
+      <x:c r="A307" s="16" t="n">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="B307" t="str">
+      <x:c r="B307" s="16" t="str">
         <x:v>guide.clear.wait</x:v>
       </x:c>
-      <x:c r="C307" t="str">
+      <x:c r="C307" s="16" t="str">
         <x:v>店员空闲时会清理杂物</x:v>
       </x:c>
     </x:row>
-    <x:row r="308">
-      <x:c r="A308" t="n">
+    <x:row r="308" ht="58" customHeight="1">
+      <x:c r="A308" s="16" t="n">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="B308" t="str">
+      <x:c r="B308" s="16" t="str">
         <x:v>ui.gm.reset</x:v>
       </x:c>
-      <x:c r="C308" t="str">
+      <x:c r="C308" s="16" t="str">
         <x:v>重置进度</x:v>
       </x:c>
     </x:row>
-    <x:row r="309">
-      <x:c r="A309" t="n">
+    <x:row r="309" ht="58" customHeight="1">
+      <x:c r="A309" s="16" t="n">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="B309" t="str">
+      <x:c r="B309" s="16" t="str">
         <x:v>ui.gm.resetConfirm</x:v>
       </x:c>
-      <x:c r="C309" t="str">
+      <x:c r="C309" s="16" t="str">
         <x:v>再次点击确认</x:v>
       </x:c>
     </x:row>
-    <x:row r="310">
-      <x:c r="A310" t="n">
+    <x:row r="310" ht="58" customHeight="1">
+      <x:c r="A310" s="16" t="n">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="B310" t="str">
+      <x:c r="B310" s="16" t="str">
         <x:v>feedback.boss.mini</x:v>
       </x:c>
-      <x:c r="C310" t="str">
+      <x:c r="C310" s="16" t="str">
         <x:v>小首领来袭</x:v>
       </x:c>
     </x:row>
-    <x:row r="311">
-      <x:c r="A311" t="n">
+    <x:row r="311" ht="58" customHeight="1">
+      <x:c r="A311" s="16" t="n">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="B311" t="str">
+      <x:c r="B311" s="16" t="str">
         <x:v>feedback.boss.major</x:v>
       </x:c>
-      <x:c r="C311" t="str">
+      <x:c r="C311" s="16" t="str">
         <x:v>大首领来袭</x:v>
       </x:c>
     </x:row>
-    <x:row r="312">
-      <x:c r="A312" t="n">
+    <x:row r="312" ht="58" customHeight="1">
+      <x:c r="A312" s="16" t="n">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="B312" t="str">
+      <x:c r="B312" s="16" t="str">
         <x:v>feedback.boss.defeated</x:v>
       </x:c>
-      <x:c r="C312" t="str">
+      <x:c r="C312" s="16" t="str">
         <x:v>首领已击退</x:v>
       </x:c>
     </x:row>
-    <x:row r="313">
-      <x:c r="A313" t="n">
+    <x:row r="313" ht="58" customHeight="1">
+      <x:c r="A313" s="16" t="n">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="B313" t="str">
+      <x:c r="B313" s="16" t="str">
         <x:v>feedback.boss.health</x:v>
       </x:c>
-      <x:c r="C313" t="str">
+      <x:c r="C313" s="16" t="str">
         <x:v>{p0} / {p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="314">
-      <x:c r="A314" t="n">
+    <x:row r="314" ht="58" customHeight="1">
+      <x:c r="A314" s="16" t="n">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="B314" t="str">
+      <x:c r="B314" s="16" t="str">
         <x:v>result.stats</x:v>
       </x:c>
-      <x:c r="C314" t="str">
+      <x:c r="C314" s="16" t="str">
         <x:v>剩余耐久 {p0}/{p1}  ·  清障 {p2}/{p3}
 击退 {p4}  ·  获得金币 {p5}</x:v>
       </x:c>
     </x:row>
-    <x:row r="315">
-      <x:c r="A315" t="n">
+    <x:row r="315" ht="58" customHeight="1">
+      <x:c r="A315" s="16" t="n">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="B315" t="str">
+      <x:c r="B315" s="16" t="str">
         <x:v>result.next</x:v>
       </x:c>
-      <x:c r="C315" t="str">
+      <x:c r="C315" s="16" t="str">
         <x:v>下一关 · 第{p0}关</x:v>
       </x:c>
     </x:row>
-    <x:row r="316">
-      <x:c r="A316" t="n">
+    <x:row r="316" ht="58" customHeight="1">
+      <x:c r="A316" s="16" t="n">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="B316" t="str">
+      <x:c r="B316" s="16" t="str">
         <x:v>result.open</x:v>
       </x:c>
-      <x:c r="C316" t="str">
+      <x:c r="C316" s="16" t="str">
         <x:v>第{p0}关已解锁</x:v>
       </x:c>
     </x:row>
-    <x:row r="317">
-      <x:c r="A317" t="n">
+    <x:row r="317" ht="58" customHeight="1">
+      <x:c r="A317" s="16" t="n">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="B317" t="str">
+      <x:c r="B317" s="16" t="str">
         <x:v>result.staff</x:v>
       </x:c>
-      <x:c r="C317" t="str">
+      <x:c r="C317" s="16" t="str">
         <x:v>新店员 {p0} 名</x:v>
       </x:c>
     </x:row>
-    <x:row r="318">
-      <x:c r="A318" t="n">
+    <x:row r="318" ht="58" customHeight="1">
+      <x:c r="A318" s="16" t="n">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="B318" t="str">
+      <x:c r="B318" s="16" t="str">
         <x:v>result.collection</x:v>
       </x:c>
-      <x:c r="C318" t="str">
+      <x:c r="C318" s="16" t="str">
         <x:v>图鉴新增 {p0} 项</x:v>
       </x:c>
     </x:row>
-    <x:row r="319">
-      <x:c r="A319" t="n">
+    <x:row r="319" ht="58" customHeight="1">
+      <x:c r="A319" s="16" t="n">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="B319" t="str">
+      <x:c r="B319" s="16" t="str">
         <x:v>result.complete</x:v>
       </x:c>
-      <x:c r="C319" t="str">
+      <x:c r="C319" s="16" t="str">
         <x:v>二十关全部完成</x:v>
       </x:c>
     </x:row>
-    <x:row r="320">
-      <x:c r="A320" t="n">
+    <x:row r="320" ht="58" customHeight="1">
+      <x:c r="A320" s="16" t="n">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="B320" t="str">
+      <x:c r="B320" s="16" t="str">
         <x:v>result.progress</x:v>
       </x:c>
-      <x:c r="C320" t="str">
+      <x:c r="C320" s="16" t="str">
         <x:v>完成 {p0}/{p1} 波</x:v>
       </x:c>
     </x:row>
-    <x:row r="321">
-      <x:c r="A321" t="n">
+    <x:row r="321" ht="58" customHeight="1">
+      <x:c r="A321" s="16" t="n">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="B321" t="str">
+      <x:c r="B321" s="16" t="str">
         <x:v>result.unlockTitle</x:v>
       </x:c>
-      <x:c r="C321" t="str">
+      <x:c r="C321" s="16" t="str">
         <x:v>新解锁</x:v>
       </x:c>
     </x:row>
-    <x:row r="322">
-      <x:c r="A322" t="n">
+    <x:row r="322" ht="58" customHeight="1">
+      <x:c r="A322" s="16" t="n">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="B322" t="str">
+      <x:c r="B322" s="16" t="str">
         <x:v>result.noUnlock</x:v>
       </x:c>
-      <x:c r="C322" t="str">
+      <x:c r="C322" s="16" t="str">
         <x:v>本局记录</x:v>
       </x:c>
     </x:row>
-    <x:row r="323">
-      <x:c r="A323" t="n">
+    <x:row r="323" ht="58" customHeight="1">
+      <x:c r="A323" s="16" t="n">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="B323" t="str">
+      <x:c r="B323" s="16" t="str">
         <x:v>result.more</x:v>
       </x:c>
-      <x:c r="C323" t="str">
+      <x:c r="C323" s="16" t="str">
         <x:v>另有 {p0} 项新图鉴</x:v>
       </x:c>
     </x:row>
-    <x:row r="324">
-      <x:c r="A324" t="n">
+    <x:row r="324" ht="58" customHeight="1">
+      <x:c r="A324" s="16" t="n">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="B324" t="str">
+      <x:c r="B324" s="16" t="str">
         <x:v>branch.sprout_heavy.name</x:v>
       </x:c>
-      <x:c r="C324" t="str">
+      <x:c r="C324" s="16" t="str">
         <x:v>重投</x:v>
       </x:c>
     </x:row>
-    <x:row r="325">
-      <x:c r="A325" t="n">
+    <x:row r="325" ht="58" customHeight="1">
+      <x:c r="A325" s="16" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="B325" t="str">
+      <x:c r="B325" s="16" t="str">
         <x:v>branch.sprout_heavy.summary</x:v>
       </x:c>
-      <x:c r="C325" t="str">
+      <x:c r="C325" s="16" t="str">
         <x:v>单发伤害高</x:v>
       </x:c>
     </x:row>
-    <x:row r="326">
-      <x:c r="A326" t="n">
+    <x:row r="326" ht="58" customHeight="1">
+      <x:c r="A326" s="16" t="n">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="B326" t="str">
+      <x:c r="B326" s="16" t="str">
         <x:v>branch.sprout_heavy.tradeoff</x:v>
       </x:c>
-      <x:c r="C326" t="str">
+      <x:c r="C326" s="16" t="str">
         <x:v>攻击间隔长</x:v>
       </x:c>
     </x:row>
-    <x:row r="327">
-      <x:c r="A327" t="n">
+    <x:row r="327" ht="58" customHeight="1">
+      <x:c r="A327" s="16" t="n">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="B327" t="str">
+      <x:c r="B327" s="16" t="str">
         <x:v>evolution.sprout_heavy.story</x:v>
       </x:c>
-      <x:c r="C327" t="str">
+      <x:c r="C327" s="16" t="str">
         <x:v>豆包把收银台旁的投掷器换大了一号。每次出手前，他仍要先把腰包里的硬币码整齐。</x:v>
       </x:c>
     </x:row>
-    <x:row r="328">
-      <x:c r="A328" t="n">
+    <x:row r="328" ht="58" customHeight="1">
+      <x:c r="A328" s="16" t="n">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="B328" t="str">
+      <x:c r="B328" s="16" t="str">
         <x:v>branch.sprout_burst.name</x:v>
       </x:c>
-      <x:c r="C328" t="str">
+      <x:c r="C328" s="16" t="str">
         <x:v>连投</x:v>
       </x:c>
     </x:row>
-    <x:row r="329">
-      <x:c r="A329" t="n">
+    <x:row r="329" ht="58" customHeight="1">
+      <x:c r="A329" s="16" t="n">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="B329" t="str">
+      <x:c r="B329" s="16" t="str">
         <x:v>branch.sprout_burst.summary</x:v>
       </x:c>
-      <x:c r="C329" t="str">
+      <x:c r="C329" s="16" t="str">
         <x:v>两连发，可接续补刀</x:v>
       </x:c>
     </x:row>
-    <x:row r="330">
-      <x:c r="A330" t="n">
+    <x:row r="330" ht="58" customHeight="1">
+      <x:c r="A330" s="16" t="n">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="B330" t="str">
+      <x:c r="B330" s="16" t="str">
         <x:v>branch.sprout_burst.tradeoff</x:v>
       </x:c>
-      <x:c r="C330" t="str">
+      <x:c r="C330" s="16" t="str">
         <x:v>单发伤害低</x:v>
       </x:c>
     </x:row>
-    <x:row r="331">
-      <x:c r="A331" t="n">
+    <x:row r="331" ht="58" customHeight="1">
+      <x:c r="A331" s="16" t="n">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B331" t="str">
+      <x:c r="B331" s="16" t="str">
         <x:v>evolution.sprout_burst.story</x:v>
       </x:c>
-      <x:c r="C331" t="str">
+      <x:c r="C331" s="16" t="str">
         <x:v>晚高峰时，豆包学会了两手交替接零钱。现在守门也用上了这套本领。</x:v>
       </x:c>
     </x:row>
-    <x:row r="332">
-      <x:c r="A332" t="n">
+    <x:row r="332" ht="58" customHeight="1">
+      <x:c r="A332" s="16" t="n">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="B332" t="str">
+      <x:c r="B332" s="16" t="str">
         <x:v>branch.frost_deep.name</x:v>
       </x:c>
-      <x:c r="C332" t="str">
+      <x:c r="C332" s="16" t="str">
         <x:v>深冷</x:v>
       </x:c>
     </x:row>
-    <x:row r="333">
-      <x:c r="A333" t="n">
+    <x:row r="333" ht="58" customHeight="1">
+      <x:c r="A333" s="16" t="n">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="B333" t="str">
+      <x:c r="B333" s="16" t="str">
         <x:v>branch.frost_deep.summary</x:v>
       </x:c>
-      <x:c r="C333" t="str">
+      <x:c r="C333" s="16" t="str">
         <x:v>单目标减速更强</x:v>
       </x:c>
     </x:row>
-    <x:row r="334">
-      <x:c r="A334" t="n">
+    <x:row r="334" ht="58" customHeight="1">
+      <x:c r="A334" s="16" t="n">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="B334" t="str">
+      <x:c r="B334" s="16" t="str">
         <x:v>branch.frost_deep.tradeoff</x:v>
       </x:c>
-      <x:c r="C334" t="str">
+      <x:c r="C334" s="16" t="str">
         <x:v>射程较短</x:v>
       </x:c>
     </x:row>
-    <x:row r="335">
-      <x:c r="A335" t="n">
+    <x:row r="335" ht="58" customHeight="1">
+      <x:c r="A335" s="16" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="B335" t="str">
+      <x:c r="B335" s="16" t="str">
         <x:v>evolution.frost_deep.story</x:v>
       </x:c>
-      <x:c r="C335" t="str">
+      <x:c r="C335" s="16" t="str">
         <x:v>棉棉给冷风器添了一层保温套。来客走慢些，她就有时间把散落的商品放回原位。</x:v>
       </x:c>
     </x:row>
-    <x:row r="336">
-      <x:c r="A336" t="n">
+    <x:row r="336" ht="58" customHeight="1">
+      <x:c r="A336" s="16" t="n">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="B336" t="str">
+      <x:c r="B336" s="16" t="str">
         <x:v>branch.frost_dual.name</x:v>
       </x:c>
-      <x:c r="C336" t="str">
+      <x:c r="C336" s="16" t="str">
         <x:v>双向冷风</x:v>
       </x:c>
     </x:row>
-    <x:row r="337">
-      <x:c r="A337" t="n">
+    <x:row r="337" ht="58" customHeight="1">
+      <x:c r="A337" s="16" t="n">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="B337" t="str">
+      <x:c r="B337" s="16" t="str">
         <x:v>branch.frost_dual.summary</x:v>
       </x:c>
-      <x:c r="C337" t="str">
+      <x:c r="C337" s="16" t="str">
         <x:v>同时减速两个目标</x:v>
       </x:c>
     </x:row>
-    <x:row r="338">
-      <x:c r="A338" t="n">
+    <x:row r="338" ht="58" customHeight="1">
+      <x:c r="A338" s="16" t="n">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="B338" t="str">
+      <x:c r="B338" s="16" t="str">
         <x:v>branch.frost_dual.tradeoff</x:v>
       </x:c>
-      <x:c r="C338" t="str">
+      <x:c r="C338" s="16" t="str">
         <x:v>每个目标减速较弱</x:v>
       </x:c>
     </x:row>
-    <x:row r="339">
-      <x:c r="A339" t="n">
+    <x:row r="339" ht="58" customHeight="1">
+      <x:c r="A339" s="16" t="n">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="B339" t="str">
+      <x:c r="B339" s="16" t="str">
         <x:v>evolution.frost_dual.story</x:v>
       </x:c>
-      <x:c r="C339" t="str">
+      <x:c r="C339" s="16" t="str">
         <x:v>通道两头都有人赶来，棉棉便把风口分成两路。哪边的货架乱了，她都看得见。</x:v>
       </x:c>
     </x:row>
-    <x:row r="340">
-      <x:c r="A340" t="n">
+    <x:row r="340" ht="58" customHeight="1">
+      <x:c r="A340" s="16" t="n">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="B340" t="str">
+      <x:c r="B340" s="16" t="str">
         <x:v>branch.bloom_focus.name</x:v>
       </x:c>
-      <x:c r="C340" t="str">
+      <x:c r="C340" s="16" t="str">
         <x:v>集中爆破</x:v>
       </x:c>
     </x:row>
-    <x:row r="341">
-      <x:c r="A341" t="n">
+    <x:row r="341" ht="58" customHeight="1">
+      <x:c r="A341" s="16" t="n">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="B341" t="str">
+      <x:c r="B341" s="16" t="str">
         <x:v>branch.bloom_focus.summary</x:v>
       </x:c>
-      <x:c r="C341" t="str">
+      <x:c r="C341" s="16" t="str">
         <x:v>主目标伤害高</x:v>
       </x:c>
     </x:row>
-    <x:row r="342">
-      <x:c r="A342" t="n">
+    <x:row r="342" ht="58" customHeight="1">
+      <x:c r="A342" s="16" t="n">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="B342" t="str">
+      <x:c r="B342" s="16" t="str">
         <x:v>branch.bloom_focus.tradeoff</x:v>
       </x:c>
-      <x:c r="C342" t="str">
+      <x:c r="C342" s="16" t="str">
         <x:v>范围小，旁伤低</x:v>
       </x:c>
     </x:row>
-    <x:row r="343">
-      <x:c r="A343" t="n">
+    <x:row r="343" ht="58" customHeight="1">
+      <x:c r="A343" s="16" t="n">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="B343" t="str">
+      <x:c r="B343" s="16" t="str">
         <x:v>evolution.bloom_focus.story</x:v>
       </x:c>
-      <x:c r="C343" t="str">
+      <x:c r="C343" s="16" t="str">
         <x:v>布丁把烤锅换成了深口的。火候集中以后，最厚的那份热食也能按时出炉。</x:v>
       </x:c>
     </x:row>
-    <x:row r="344">
-      <x:c r="A344" t="n">
+    <x:row r="344" ht="58" customHeight="1">
+      <x:c r="A344" s="16" t="n">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="B344" t="str">
+      <x:c r="B344" s="16" t="str">
         <x:v>branch.bloom_wide.name</x:v>
       </x:c>
-      <x:c r="C344" t="str">
+      <x:c r="C344" s="16" t="str">
         <x:v>广域爆破</x:v>
       </x:c>
     </x:row>
-    <x:row r="345">
-      <x:c r="A345" t="n">
+    <x:row r="345" ht="58" customHeight="1">
+      <x:c r="A345" s="16" t="n">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="B345" t="str">
+      <x:c r="B345" s="16" t="str">
         <x:v>branch.bloom_wide.summary</x:v>
       </x:c>
-      <x:c r="C345" t="str">
+      <x:c r="C345" s="16" t="str">
         <x:v>爆炸覆盖更广</x:v>
       </x:c>
     </x:row>
-    <x:row r="346">
-      <x:c r="A346" t="n">
+    <x:row r="346" ht="58" customHeight="1">
+      <x:c r="A346" s="16" t="n">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="B346" t="str">
+      <x:c r="B346" s="16" t="str">
         <x:v>branch.bloom_wide.tradeoff</x:v>
       </x:c>
-      <x:c r="C346" t="str">
+      <x:c r="C346" s="16" t="str">
         <x:v>单个目标伤害低</x:v>
       </x:c>
     </x:row>
-    <x:row r="347">
-      <x:c r="A347" t="n">
+    <x:row r="347" ht="58" customHeight="1">
+      <x:c r="A347" s="16" t="n">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="B347" t="str">
+      <x:c r="B347" s="16" t="str">
         <x:v>evolution.bloom_wide.story</x:v>
       </x:c>
-      <x:c r="C347" t="str">
+      <x:c r="C347" s="16" t="str">
         <x:v>排队的人越来越多，布丁找来一只宽烤盘。一炉多做几份，夜班同伴也能早点吃上。</x:v>
       </x:c>
     </x:row>
-    <x:row r="348">
-      <x:c r="A348" t="n">
+    <x:row r="348" ht="58" customHeight="1">
+      <x:c r="A348" s="16" t="n">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="B348" t="str">
+      <x:c r="B348" s="16" t="str">
         <x:v>ui.evolution.action</x:v>
       </x:c>
-      <x:c r="C348" t="str">
+      <x:c r="C348" s="16" t="str">
         <x:v>进化</x:v>
       </x:c>
     </x:row>
-    <x:row r="349">
-      <x:c r="A349" t="n">
+    <x:row r="349" ht="58" customHeight="1">
+      <x:c r="A349" s="16" t="n">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B349" t="str">
+      <x:c r="B349" s="16" t="str">
         <x:v>ui.evolution.choose</x:v>
       </x:c>
-      <x:c r="C349" t="str">
+      <x:c r="C349" s="16" t="str">
         <x:v>选择进化</x:v>
       </x:c>
     </x:row>
-    <x:row r="350">
-      <x:c r="A350" t="n">
+    <x:row r="350" ht="58" customHeight="1">
+      <x:c r="A350" s="16" t="n">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="B350" t="str">
+      <x:c r="B350" s="16" t="str">
         <x:v>ui.evolution.base</x:v>
       </x:c>
-      <x:c r="C350" t="str">
+      <x:c r="C350" s="16" t="str">
         <x:v>基础形态</x:v>
       </x:c>
     </x:row>
-    <x:row r="351">
-      <x:c r="A351" t="n">
+    <x:row r="351" ht="58" customHeight="1">
+      <x:c r="A351" s="16" t="n">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="B351" t="str">
+      <x:c r="B351" s="16" t="str">
         <x:v>ui.evolution.locked</x:v>
       </x:c>
-      <x:c r="C351" t="str">
+      <x:c r="C351" s="16" t="str">
         <x:v>???</x:v>
       </x:c>
     </x:row>
-    <x:row r="352">
-      <x:c r="A352" t="n">
+    <x:row r="352" ht="58" customHeight="1">
+      <x:c r="A352" s="16" t="n">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B352" t="str">
+      <x:c r="B352" s="16" t="str">
         <x:v>ui.evolution.unlock</x:v>
       </x:c>
-      <x:c r="C352" t="str">
+      <x:c r="C352" s="16" t="str">
         <x:v>首次进化后收录</x:v>
       </x:c>
     </x:row>
-    <x:row r="353">
-      <x:c r="A353" t="n">
+    <x:row r="353" ht="58" customHeight="1">
+      <x:c r="A353" s="16" t="n">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="B353" t="str">
+      <x:c r="B353" s="16" t="str">
         <x:v>ui.evolution.new</x:v>
       </x:c>
-      <x:c r="C353" t="str">
+      <x:c r="C353" s="16" t="str">
         <x:v>新形态</x:v>
       </x:c>
     </x:row>
-    <x:row r="354">
-      <x:c r="A354" t="n">
+    <x:row r="354" ht="58" customHeight="1">
+      <x:c r="A354" s="16" t="n">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="B354" t="str">
+      <x:c r="B354" s="16" t="str">
         <x:v>ui.evolution.collection</x:v>
       </x:c>
-      <x:c r="C354" t="str">
+      <x:c r="C354" s="16" t="str">
         <x:v>进化形态 {p0}/{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="355">
-      <x:c r="A355" t="n">
+    <x:row r="355" ht="58" customHeight="1">
+      <x:c r="A355" s="16" t="n">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="B355" t="str">
+      <x:c r="B355" s="16" t="str">
         <x:v>ui.evolution.cost</x:v>
       </x:c>
-      <x:c r="C355" t="str">
+      <x:c r="C355" s="16" t="str">
         <x:v>进化费用</x:v>
       </x:c>
     </x:row>
-    <x:row r="356">
-      <x:c r="A356" t="n">
+    <x:row r="356" ht="58" customHeight="1">
+      <x:c r="A356" s="16" t="n">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="B356" t="str">
+      <x:c r="B356" s="16" t="str">
         <x:v>ui.evolution.complete</x:v>
       </x:c>
-      <x:c r="C356" t="str">
+      <x:c r="C356" s="16" t="str">
         <x:v>已进化</x:v>
       </x:c>
     </x:row>
-    <x:row r="357">
-      <x:c r="A357" t="n">
+    <x:row r="357" ht="58" customHeight="1">
+      <x:c r="A357" s="16" t="n">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="B357" t="str">
+      <x:c r="B357" s="16" t="str">
         <x:v>ui.evolution.button</x:v>
       </x:c>
-      <x:c r="C357" t="str">
+      <x:c r="C357" s="16" t="str">
         <x:v>进化
 ●{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="358">
-      <x:c r="A358" t="n">
+    <x:row r="358" ht="58" customHeight="1">
+      <x:c r="A358" s="16" t="n">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="B358" t="str">
+      <x:c r="B358" s="16" t="str">
         <x:v>ui.evolution.name</x:v>
       </x:c>
-      <x:c r="C358" t="str">
+      <x:c r="C358" s="16" t="str">
         <x:v>{p0}·{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="359">
-      <x:c r="A359" t="n">
+    <x:row r="359" ht="58" customHeight="1">
+      <x:c r="A359" s="16" t="n">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="B359" t="str">
+      <x:c r="B359" s="16" t="str">
         <x:v>ui.evolution.rate</x:v>
       </x:c>
-      <x:c r="C359" t="str">
+      <x:c r="C359" s="16" t="str">
         <x:v>{p1}秒/轮</x:v>
       </x:c>
     </x:row>
-    <x:row r="360">
-      <x:c r="A360" t="n">
+    <x:row r="360" ht="58" customHeight="1">
+      <x:c r="A360" s="16" t="n">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="B360" t="str">
+      <x:c r="B360" s="16" t="str">
         <x:v>ui.evolution.slow</x:v>
       </x:c>
-      <x:c r="C360" t="str">
+      <x:c r="C360" s="16" t="str">
         <x:v>移速降至{p0}% · {p1}秒</x:v>
       </x:c>
     </x:row>
-    <x:row r="361">
-      <x:c r="A361" t="n">
+    <x:row r="361" ht="58" customHeight="1">
+      <x:c r="A361" s="16" t="n">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="B361" t="str">
+      <x:c r="B361" s="16" t="str">
         <x:v>ui.evolution.splash</x:v>
       </x:c>
-      <x:c r="C361" t="str">
+      <x:c r="C361" s="16" t="str">
         <x:v>范围{p0} · 旁伤{p1}%</x:v>
       </x:c>
     </x:row>
-    <x:row r="362">
-      <x:c r="A362" t="n">
+    <x:row r="362" ht="58" customHeight="1">
+      <x:c r="A362" s="16" t="n">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="B362" t="str">
+      <x:c r="B362" s="16" t="str">
         <x:v>ui.evolution.targets</x:v>
       </x:c>
-      <x:c r="C362" t="str">
-        <x:v>每轮至多{p0}个目标</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="363">
-      <x:c r="A363" t="n">
+      <x:c r="C362" s="16" t="str">
+        <x:v>每次至多{p0}个目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="58" customHeight="1">
+      <x:c r="A363" s="16" t="n">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="B363" t="str">
+      <x:c r="B363" s="16" t="str">
         <x:v>ui.evolution.stats</x:v>
       </x:c>
-      <x:c r="C363" t="str">
+      <x:c r="C363" s="16" t="str">
         <x:v>伤害{p0} · 周期{p1}秒
 射程{p2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="364">
-      <x:c r="A364" t="n">
+    <x:row r="364" ht="58" customHeight="1">
+      <x:c r="A364" s="16" t="n">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="B364" t="str">
+      <x:c r="B364" s="16" t="str">
         <x:v>ui.evolution.lockedHint</x:v>
       </x:c>
-      <x:c r="C364" t="str">
+      <x:c r="C364" s="16" t="str">
         <x:v>战斗中完成此形态的进化后收录</x:v>
       </x:c>
     </x:row>
-    <x:row r="365">
-      <x:c r="A365" t="n">
+    <x:row r="365" ht="58" customHeight="1">
+      <x:c r="A365" s="16" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="B365" t="str">
+      <x:c r="B365" s="16" t="str">
         <x:v>ui.evolution.shapeCount</x:v>
       </x:c>
-      <x:c r="C365" t="str">
+      <x:c r="C365" s="16" t="str">
         <x:v>形态 {p0}/{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="366">
-      <x:c r="A366" t="n">
+    <x:row r="366" ht="58" customHeight="1">
+      <x:c r="A366" s="16" t="n">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="B366" t="str">
+      <x:c r="B366" s="16" t="str">
         <x:v>ui.evolution.base1</x:v>
       </x:c>
-      <x:c r="C366" t="str">
+      <x:c r="C366" s="16" t="str">
         <x:v>一级</x:v>
       </x:c>
     </x:row>
-    <x:row r="367">
-      <x:c r="A367" t="n">
+    <x:row r="367" ht="58" customHeight="1">
+      <x:c r="A367" s="16" t="n">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="B367" t="str">
+      <x:c r="B367" s="16" t="str">
         <x:v>ui.evolution.base2</x:v>
       </x:c>
-      <x:c r="C367" t="str">
+      <x:c r="C367" s="16" t="str">
         <x:v>二级</x:v>
       </x:c>
     </x:row>
-    <x:row r="368">
-      <x:c r="A368" t="n">
+    <x:row r="368" ht="58" customHeight="1">
+      <x:c r="A368" s="16" t="n">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="B368" t="str">
+      <x:c r="B368" s="16" t="str">
         <x:v>ui.evolution.profile</x:v>
       </x:c>
-      <x:c r="C368" t="str">
+      <x:c r="C368" s="16" t="str">
         <x:v>进化形态</x:v>
       </x:c>
     </x:row>
-    <x:row r="369">
-      <x:c r="A369" t="n">
+    <x:row r="369" ht="58" customHeight="1">
+      <x:c r="A369" s="16" t="n">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="B369" t="str">
+      <x:c r="B369" s="16" t="str">
         <x:v>ui.evolution.result</x:v>
       </x:c>
-      <x:c r="C369" t="str">
+      <x:c r="C369" s="16" t="str">
         <x:v>新形态 {p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="370">
-      <x:c r="A370" t="n">
+    <x:row r="370" ht="58" customHeight="1">
+      <x:c r="A370" s="16" t="n">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="B370" t="str">
+      <x:c r="B370" s="16" t="str">
         <x:v>ui.evolution.costValue</x:v>
       </x:c>
-      <x:c r="C370" t="str">
+      <x:c r="C370" s="16" t="str">
         <x:v>●{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="371">
-      <x:c r="A371" t="n">
+    <x:row r="371" ht="58" customHeight="1">
+      <x:c r="A371" s="16" t="n">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="B371" t="str">
+      <x:c r="B371" s="16" t="str">
         <x:v>ui.loadout.title</x:v>
       </x:c>
-      <x:c r="C371" t="str">
+      <x:c r="C371" s="16" t="str">
         <x:v>出战准备</x:v>
       </x:c>
     </x:row>
-    <x:row r="372">
-      <x:c r="A372" t="n">
+    <x:row r="372" ht="58" customHeight="1">
+      <x:c r="A372" s="16" t="n">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="B372" t="str">
+      <x:c r="B372" s="16" t="str">
         <x:v>ui.loadout.selected</x:v>
       </x:c>
-      <x:c r="C372" t="str">
+      <x:c r="C372" s="16" t="str">
         <x:v>出战店员 {p0}/{p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="373">
-      <x:c r="A373" t="n">
+    <x:row r="373" ht="58" customHeight="1">
+      <x:c r="A373" s="16" t="n">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="B373" t="str">
+      <x:c r="B373" s="16" t="str">
         <x:v>ui.loadout.start</x:v>
       </x:c>
-      <x:c r="C373" t="str">
+      <x:c r="C373" s="16" t="str">
         <x:v>开始关卡</x:v>
       </x:c>
     </x:row>
-    <x:row r="374">
-      <x:c r="A374" t="n">
+    <x:row r="374" ht="58" customHeight="1">
+      <x:c r="A374" s="16" t="n">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="B374" t="str">
+      <x:c r="B374" s="16" t="str">
         <x:v>ui.loadout.choose</x:v>
       </x:c>
-      <x:c r="C374" t="str">
+      <x:c r="C374" s="16" t="str">
         <x:v>选择出战店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="375">
-      <x:c r="A375" t="n">
+    <x:row r="375" ht="58" customHeight="1">
+      <x:c r="A375" s="16" t="n">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="B375" t="str">
+      <x:c r="B375" s="16" t="str">
         <x:v>ui.loadout.replace</x:v>
       </x:c>
-      <x:c r="C375" t="str">
+      <x:c r="C375" s="16" t="str">
         <x:v>选择要替换的出战位</x:v>
       </x:c>
     </x:row>
-    <x:row r="376">
-      <x:c r="A376" t="n">
+    <x:row r="376" ht="58" customHeight="1">
+      <x:c r="A376" s="16" t="n">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B376" t="str">
+      <x:c r="B376" s="16" t="str">
         <x:v>ui.loadout.empty</x:v>
       </x:c>
-      <x:c r="C376" t="str">
+      <x:c r="C376" s="16" t="str">
         <x:v>空位</x:v>
       </x:c>
     </x:row>
-    <x:row r="377">
-      <x:c r="A377" t="n">
+    <x:row r="377" ht="58" customHeight="1">
+      <x:c r="A377" s="16" t="n">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="B377" t="str">
+      <x:c r="B377" s="16" t="str">
         <x:v>ui.loadout.ready</x:v>
       </x:c>
-      <x:c r="C377" t="str">
+      <x:c r="C377" s="16" t="str">
         <x:v>出战店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="378">
-      <x:c r="A378" t="n">
+    <x:row r="378" ht="58" customHeight="1">
+      <x:c r="A378" s="16" t="n">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="B378" t="str">
+      <x:c r="B378" s="16" t="str">
         <x:v>ui.loadout.info</x:v>
       </x:c>
-      <x:c r="C378" t="str">
+      <x:c r="C378" s="16" t="str">
         <x:v>详情</x:v>
       </x:c>
     </x:row>
-    <x:row r="379">
-      <x:c r="A379" t="n">
+    <x:row r="379" ht="58" customHeight="1">
+      <x:c r="A379" s="16" t="n">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="B379" t="str">
+      <x:c r="B379" s="16" t="str">
         <x:v>ui.loadout.stats</x:v>
       </x:c>
-      <x:c r="C379" t="str">
+      <x:c r="C379" s="16" t="str">
         <x:v>初始金币 {p0} · {p1} 波</x:v>
       </x:c>
     </x:row>
-    <x:row r="380">
-      <x:c r="A380" t="n">
+    <x:row r="380" ht="58" customHeight="1">
+      <x:c r="A380" s="16" t="n">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="B380" t="str">
+      <x:c r="B380" s="16" t="str">
         <x:v>ui.loadout.boss</x:v>
       </x:c>
-      <x:c r="C380" t="str">
+      <x:c r="C380" s="16" t="str">
         <x:v>第{p0}波 · {p1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="381">
-      <x:c r="A381" t="n">
+    <x:row r="381" ht="58" customHeight="1">
+      <x:c r="A381" s="16" t="n">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="B381" t="str">
+      <x:c r="B381" s="16" t="str">
         <x:v>ui.loadout.enemies</x:v>
       </x:c>
-      <x:c r="C381" t="str">
+      <x:c r="C381" s="16" t="str">
         <x:v>本关来客</x:v>
       </x:c>
     </x:row>
-    <x:row r="382">
-      <x:c r="A382" t="n">
+    <x:row r="382" ht="58" customHeight="1">
+      <x:c r="A382" s="16" t="n">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="B382" t="str">
+      <x:c r="B382" s="16" t="str">
         <x:v>ui.loadout.default</x:v>
       </x:c>
-      <x:c r="C382" t="str">
+      <x:c r="C382" s="16" t="str">
         <x:v>默认阵容</x:v>
       </x:c>
     </x:row>
-    <x:row r="383">
-      <x:c r="A383" t="n">
+    <x:row r="383" ht="58" customHeight="1">
+      <x:c r="A383" s="16" t="n">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="B383" t="str">
+      <x:c r="B383" s="16" t="str">
         <x:v>ui.loadout.need</x:v>
       </x:c>
-      <x:c r="C383" t="str">
+      <x:c r="C383" s="16" t="str">
         <x:v>还需选择 {p0} 名店员</x:v>
       </x:c>
     </x:row>
-    <x:row r="384">
-      <x:c r="A384" t="n">
+    <x:row r="384" ht="58" customHeight="1">
+      <x:c r="A384" s="16" t="n">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="B384" t="str">
+      <x:c r="B384" s="16" t="str">
         <x:v>ui.preview.title</x:v>
       </x:c>
-      <x:c r="C384" t="str">
+      <x:c r="C384" s="16" t="str">
         <x:v>第{p0}波来客</x:v>
       </x:c>
     </x:row>
-    <x:row r="385">
-      <x:c r="A385" t="n">
+    <x:row r="385" ht="58" customHeight="1">
+      <x:c r="A385" s="16" t="n">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="B385" t="str">
+      <x:c r="B385" s="16" t="str">
         <x:v>ui.preview.last</x:v>
       </x:c>
-      <x:c r="C385" t="str">
+      <x:c r="C385" s="16" t="str">
         <x:v>最后一波</x:v>
       </x:c>
     </x:row>
-    <x:row r="386">
-      <x:c r="A386" t="n">
+    <x:row r="386" ht="58" customHeight="1">
+      <x:c r="A386" s="16" t="n">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="B386" t="str">
+      <x:c r="B386" s="16" t="str">
         <x:v>ui.preview.open</x:v>
       </x:c>
-      <x:c r="C386" t="str">
+      <x:c r="C386" s="16" t="str">
         <x:v>波次预告</x:v>
       </x:c>
     </x:row>
-    <x:row r="387">
-      <x:c r="A387" t="n">
+    <x:row r="387" ht="58" customHeight="1">
+      <x:c r="A387" s="16" t="n">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="B387" t="str">
+      <x:c r="B387" s="16" t="str">
         <x:v>ui.preview.count</x:v>
       </x:c>
-      <x:c r="C387" t="str">
+      <x:c r="C387" s="16" t="str">
         <x:v>×{p0}</x:v>
       </x:c>
     </x:row>
-    <x:row r="388">
-      <x:c r="A388" t="n">
+    <x:row r="388" ht="58" customHeight="1">
+      <x:c r="A388" s="16" t="n">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="B388" t="str">
+      <x:c r="B388" s="16" t="str">
         <x:v>ui.preview.mini</x:v>
       </x:c>
-      <x:c r="C388" t="str">
+      <x:c r="C388" s="16" t="str">
         <x:v>小首领</x:v>
       </x:c>
     </x:row>
-    <x:row r="389">
-      <x:c r="A389" t="n">
+    <x:row r="389" ht="58" customHeight="1">
+      <x:c r="A389" s="16" t="n">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="B389" t="str">
+      <x:c r="B389" s="16" t="str">
         <x:v>ui.preview.major</x:v>
       </x:c>
-      <x:c r="C389" t="str">
+      <x:c r="C389" s="16" t="str">
         <x:v>大首领</x:v>
       </x:c>
     </x:row>
-    <x:row r="390">
-      <x:c r="A390" t="n">
+    <x:row r="390" ht="58" customHeight="1">
+      <x:c r="A390" s="16" t="n">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="B390" t="str">
+      <x:c r="B390" s="16" t="str">
         <x:v>staff.role.sprout</x:v>
       </x:c>
-      <x:c r="C390" t="str">
+      <x:c r="C390" s="16" t="str">
         <x:v>单体连投</x:v>
       </x:c>
     </x:row>
-    <x:row r="391">
-      <x:c r="A391" t="n">
+    <x:row r="391" ht="58" customHeight="1">
+      <x:c r="A391" s="16" t="n">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="B391" t="str">
+      <x:c r="B391" s="16" t="str">
         <x:v>staff.role.frost</x:v>
       </x:c>
-      <x:c r="C391" t="str">
+      <x:c r="C391" s="16" t="str">
         <x:v>减速控制</x:v>
       </x:c>
     </x:row>
-    <x:row r="392">
-      <x:c r="A392" t="n">
+    <x:row r="392" ht="58" customHeight="1">
+      <x:c r="A392" s="16" t="n">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="B392" t="str">
+      <x:c r="B392" s="16" t="str">
         <x:v>staff.role.bloom</x:v>
       </x:c>
-      <x:c r="C392" t="str">
+      <x:c r="C392" s="16" t="str">
         <x:v>范围爆破</x:v>
       </x:c>
     </x:row>
-    <x:row r="393">
-      <x:c r="A393" t="n">
+    <x:row r="393" ht="58" customHeight="1">
+      <x:c r="A393" s="16" t="n">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="B393" t="str">
+      <x:c r="B393" s="16" t="str">
         <x:v>staff.role.scope</x:v>
       </x:c>
-      <x:c r="C393" t="str">
+      <x:c r="C393" s="16" t="str">
         <x:v>远程穿透</x:v>
       </x:c>
     </x:row>
-    <x:row r="394">
-      <x:c r="A394" t="n">
+    <x:row r="394" ht="58" customHeight="1">
+      <x:c r="A394" s="16" t="n">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B394" t="str">
+      <x:c r="B394" s="16" t="str">
         <x:v>staff.role.spark</x:v>
       </x:c>
-      <x:c r="C394" t="str">
+      <x:c r="C394" s="16" t="str">
         <x:v>连锁电击</x:v>
       </x:c>
     </x:row>
-    <x:row r="395">
-      <x:c r="A395" t="n">
+    <x:row r="395" ht="58" customHeight="1">
+      <x:c r="A395" s="16" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="B395" t="str">
+      <x:c r="B395" s="16" t="str">
         <x:v>staff.role.ember</x:v>
       </x:c>
-      <x:c r="C395" t="str">
+      <x:c r="C395" s="16" t="str">
         <x:v>持续灼烧</x:v>
       </x:c>
     </x:row>
-    <x:row r="396">
-      <x:c r="A396" t="n">
+    <x:row r="396" ht="58" customHeight="1">
+      <x:c r="A396" s="16" t="n">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="B396" t="str">
+      <x:c r="B396" s="16" t="str">
         <x:v>staff.role.mint</x:v>
       </x:c>
-      <x:c r="C396" t="str">
+      <x:c r="C396" s="16" t="str">
         <x:v>标记增伤</x:v>
       </x:c>
     </x:row>
-    <x:row r="397">
-      <x:c r="A397" t="n">
+    <x:row r="397" ht="58" customHeight="1">
+      <x:c r="A397" s="16" t="n">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B397" t="str">
+      <x:c r="B397" s="16" t="str">
         <x:v>staff.role.fan</x:v>
       </x:c>
-      <x:c r="C397" t="str">
+      <x:c r="C397" s="16" t="str">
         <x:v>多目标散射</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="58" customHeight="1">
+      <x:c r="A398" s="16" t="n">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B398" s="16" t="str">
+        <x:v>branch.scope_precision.name</x:v>
+      </x:c>
+      <x:c r="C398" s="16" t="str">
+        <x:v>定点观测</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="58" customHeight="1">
+      <x:c r="A399" s="16" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B399" s="16" t="str">
+        <x:v>branch.scope_precision.summary</x:v>
+      </x:c>
+      <x:c r="C399" s="16" t="str">
+        <x:v>集中重击远处单个目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="58" customHeight="1">
+      <x:c r="A400" s="16" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B400" s="16" t="str">
+        <x:v>branch.scope_precision.tradeoff</x:v>
+      </x:c>
+      <x:c r="C400" s="16" t="str">
+        <x:v>不再穿透后排</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="58" customHeight="1">
+      <x:c r="A401" s="16" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B401" s="16" t="str">
+        <x:v>branch.scope_precision.story</x:v>
+      </x:c>
+      <x:c r="C401" s="16" t="str">
+        <x:v>咕咕把镜片擦了又擦。街角最远的一盏灯，也逃不过它的眼睛。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="58" customHeight="1">
+      <x:c r="A402" s="16" t="n">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B402" s="16" t="str">
+        <x:v>branch.scope_pierce.name</x:v>
+      </x:c>
+      <x:c r="C402" s="16" t="str">
+        <x:v>贯线观测</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="58" customHeight="1">
+      <x:c r="A403" s="16" t="n">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B403" s="16" t="str">
+        <x:v>branch.scope_pierce.summary</x:v>
+      </x:c>
+      <x:c r="C403" s="16" t="str">
+        <x:v>沿命中方向贯穿后排</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="58" customHeight="1">
+      <x:c r="A404" s="16" t="n">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B404" s="16" t="str">
+        <x:v>branch.scope_pierce.tradeoff</x:v>
+      </x:c>
+      <x:c r="C404" s="16" t="str">
+        <x:v>单体伤害较低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="58" customHeight="1">
+      <x:c r="A405" s="16" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B405" s="16" t="str">
+        <x:v>branch.scope_pierce.story</x:v>
+      </x:c>
+      <x:c r="C405" s="16" t="str">
+        <x:v>货架间那条笔直的过道，是咕咕每天练习瞄准的地方。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="58" customHeight="1">
+      <x:c r="A406" s="16" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B406" s="16" t="str">
+        <x:v>branch.spark_focus.name</x:v>
+      </x:c>
+      <x:c r="C406" s="16" t="str">
+        <x:v>强电接力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="58" customHeight="1">
+      <x:c r="A407" s="16" t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B407" s="16" t="str">
+        <x:v>branch.spark_focus.summary</x:v>
+      </x:c>
+      <x:c r="C407" s="16" t="str">
+        <x:v>短链高伤，适合并行的重型目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="58" customHeight="1">
+      <x:c r="A408" s="16" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B408" s="16" t="str">
+        <x:v>branch.spark_focus.tradeoff</x:v>
+      </x:c>
+      <x:c r="C408" s="16" t="str">
+        <x:v>最多连接两个目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="58" customHeight="1">
+      <x:c r="A409" s="16" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B409" s="16" t="str">
+        <x:v>branch.spark_focus.story</x:v>
+      </x:c>
+      <x:c r="C409" s="16" t="str">
+        <x:v>栗栗给插头缠上厚厚的绝缘带。这次，它要把电力送得更扎实。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="58" customHeight="1">
+      <x:c r="A410" s="16" t="n">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B410" s="16" t="str">
+        <x:v>branch.spark_chain.name</x:v>
+      </x:c>
+      <x:c r="C410" s="16" t="str">
+        <x:v>长链接力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="58" customHeight="1">
+      <x:c r="A411" s="16" t="n">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B411" s="16" t="str">
+        <x:v>branch.spark_chain.summary</x:v>
+      </x:c>
+      <x:c r="C411" s="16" t="str">
+        <x:v>电流最多连接五个目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="58" customHeight="1">
+      <x:c r="A412" s="16" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B412" s="16" t="str">
+        <x:v>branch.spark_chain.tradeoff</x:v>
+      </x:c>
+      <x:c r="C412" s="16" t="str">
+        <x:v>单体伤害较低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="58" customHeight="1">
+      <x:c r="A413" s="16" t="n">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B413" s="16" t="str">
+        <x:v>branch.spark_chain.story</x:v>
+      </x:c>
+      <x:c r="C413" s="16" t="str">
+        <x:v>栗栗沿街检查每一盏小灯，尾巴后的线轴一路转个不停。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="58" customHeight="1">
+      <x:c r="A414" s="16" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B414" s="16" t="str">
+        <x:v>branch.ember_scorch.name</x:v>
+      </x:c>
+      <x:c r="C414" s="16" t="str">
+        <x:v>慢火烘焙</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="58" customHeight="1">
+      <x:c r="A415" s="16" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B415" s="16" t="str">
+        <x:v>branch.ember_scorch.summary</x:v>
+      </x:c>
+      <x:c r="C415" s="16" t="str">
+        <x:v>单点持续灼烧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="58" customHeight="1">
+      <x:c r="A416" s="16" t="n">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B416" s="16" t="str">
+        <x:v>branch.ember_scorch.tradeoff</x:v>
+      </x:c>
+      <x:c r="C416" s="16" t="str">
+        <x:v>没有范围伤害</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="58" customHeight="1">
+      <x:c r="A417" s="16" t="n">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B417" s="16" t="str">
+        <x:v>branch.ember_scorch.story</x:v>
+      </x:c>
+      <x:c r="C417" s="16" t="str">
+        <x:v>烘烘守着小火，等面包边缘一点点变成金黄。好火候不必着急。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="58" customHeight="1">
+      <x:c r="A418" s="16" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B418" s="16" t="str">
+        <x:v>branch.ember_burst.name</x:v>
+      </x:c>
+      <x:c r="C418" s="16" t="str">
+        <x:v>开炉热浪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="58" customHeight="1">
+      <x:c r="A419" s="16" t="n">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B419" s="16" t="str">
+        <x:v>branch.ember_burst.summary</x:v>
+      </x:c>
+      <x:c r="C419" s="16" t="str">
+        <x:v>范围点燃密集来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="58" customHeight="1">
+      <x:c r="A420" s="16" t="n">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B420" s="16" t="str">
+        <x:v>branch.ember_burst.tradeoff</x:v>
+      </x:c>
+      <x:c r="C420" s="16" t="str">
+        <x:v>灼烧较短，单体输出较低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="58" customHeight="1">
+      <x:c r="A421" s="16" t="n">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B421" s="16" t="str">
+        <x:v>branch.ember_burst.story</x:v>
+      </x:c>
+      <x:c r="C421" s="16" t="str">
+        <x:v>烤箱门一开，暖香就散满了夜班的小店。烘烘总会多留一盘。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="58" customHeight="1">
+      <x:c r="A422" s="16" t="n">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B422" s="16" t="str">
+        <x:v>branch.mint_focus.name</x:v>
+      </x:c>
+      <x:c r="C422" s="16" t="str">
+        <x:v>浓萃标记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="58" customHeight="1">
+      <x:c r="A423" s="16" t="n">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B423" s="16" t="str">
+        <x:v>branch.mint_focus.summary</x:v>
+      </x:c>
+      <x:c r="C423" s="16" t="str">
+        <x:v>单点标记，强化队友直击</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="58" customHeight="1">
+      <x:c r="A424" s="16" t="n">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B424" s="16" t="str">
+        <x:v>branch.mint_focus.tradeoff</x:v>
+      </x:c>
+      <x:c r="C424" s="16" t="str">
+        <x:v>每轮只标记一个目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="58" customHeight="1">
+      <x:c r="A425" s="16" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B425" s="16" t="str">
+        <x:v>branch.mint_focus.story</x:v>
+      </x:c>
+      <x:c r="C425" s="16" t="str">
+        <x:v>薄荷把喷头调细了一格，认真记下今晚最需要大家照看的来客。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="58" customHeight="1">
+      <x:c r="A426" s="16" t="n">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B426" s="16" t="str">
+        <x:v>branch.mint_dual.name</x:v>
+      </x:c>
+      <x:c r="C426" s="16" t="str">
+        <x:v>双瓶巡护</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="58" customHeight="1">
+      <x:c r="A427" s="16" t="n">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B427" s="16" t="str">
+        <x:v>branch.mint_dual.summary</x:v>
+      </x:c>
+      <x:c r="C427" s="16" t="str">
+        <x:v>双瓶同时标记不同来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="58" customHeight="1">
+      <x:c r="A428" s="16" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B428" s="16" t="str">
+        <x:v>branch.mint_dual.tradeoff</x:v>
+      </x:c>
+      <x:c r="C428" s="16" t="str">
+        <x:v>单个标记的增伤较低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="58" customHeight="1">
+      <x:c r="A429" s="16" t="n">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B429" s="16" t="str">
+        <x:v>branch.mint_dual.story</x:v>
+      </x:c>
+      <x:c r="C429" s="16" t="str">
+        <x:v>薄荷一手一瓶，沿着货架慢慢巡过。忙的时候，谁都不会被落下。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="58" customHeight="1">
+      <x:c r="A430" s="16" t="n">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B430" s="16" t="str">
+        <x:v>branch.fan_spread.name</x:v>
+      </x:c>
+      <x:c r="C430" s="16" t="str">
+        <x:v>五叶巡风</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="58" customHeight="1">
+      <x:c r="A431" s="16" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B431" s="16" t="str">
+        <x:v>branch.fan_spread.summary</x:v>
+      </x:c>
+      <x:c r="C431" s="16" t="str">
+        <x:v>风弹扩散，覆盖更多来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="58" customHeight="1">
+      <x:c r="A432" s="16" t="n">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B432" s="16" t="str">
+        <x:v>branch.fan_spread.tradeoff</x:v>
+      </x:c>
+      <x:c r="C432" s="16" t="str">
+        <x:v>目标少时无法集中多枚风弹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="58" customHeight="1">
+      <x:c r="A433" s="16" t="n">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B433" s="16" t="str">
+        <x:v>branch.fan_spread.story</x:v>
+      </x:c>
+      <x:c r="C433" s="16" t="str">
+        <x:v>啾啾换上宽宽的新扇叶，把门口的热气和困意一起扇走。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="58" customHeight="1">
+      <x:c r="A434" s="16" t="n">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B434" s="16" t="str">
+        <x:v>branch.fan_volley.name</x:v>
+      </x:c>
+      <x:c r="C434" s="16" t="str">
+        <x:v>双翼齐射</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="58" customHeight="1">
+      <x:c r="A435" s="16" t="n">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B435" s="16" t="str">
+        <x:v>branch.fan_volley.summary</x:v>
+      </x:c>
+      <x:c r="C435" s="16" t="str">
+        <x:v>每轮连续两次齐射</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="58" customHeight="1">
+      <x:c r="A436" s="16" t="n">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B436" s="16" t="str">
+        <x:v>branch.fan_volley.tradeoff</x:v>
+      </x:c>
+      <x:c r="C436" s="16" t="str">
+        <x:v>覆盖目标较少</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="58" customHeight="1">
+      <x:c r="A437" s="16" t="n">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B437" s="16" t="str">
+        <x:v>branch.fan_volley.story</x:v>
+      </x:c>
+      <x:c r="C437" s="16" t="str">
+        <x:v>啾啾把两只小风机绑在一起。深夜送货时，它喜欢这一前一后的节拍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="58" customHeight="1">
+      <x:c r="A438" s="16" t="n">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B438" s="16" t="str">
+        <x:v>ui.evolution.pierce</x:v>
+      </x:c>
+      <x:c r="C438" s="16" t="str">
+        <x:v>贯穿{p0} · 旁伤{p1}%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="58" customHeight="1">
+      <x:c r="A439" s="16" t="n">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B439" s="16" t="str">
+        <x:v>ui.evolution.chain</x:v>
+      </x:c>
+      <x:c r="C439" s="16" t="str">
+        <x:v>至多{p0}目标 · 每跳保留{p1}%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="58" customHeight="1">
+      <x:c r="A440" s="16" t="n">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B440" s="16" t="str">
+        <x:v>ui.evolution.burn</x:v>
+      </x:c>
+      <x:c r="C440" s="16" t="str">
+        <x:v>灼烧{p0}/秒 · {p1}秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" ht="58" customHeight="1">
+      <x:c r="A441" s="16" t="n">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B441" s="16" t="str">
+        <x:v>ui.evolution.mark</x:v>
+      </x:c>
+      <x:c r="C441" s="16" t="str">
+        <x:v>直击增伤{p0}% · {p1}秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" ht="58" customHeight="1">
+      <x:c r="A442" s="16" t="n">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B442" s="16" t="str">
+        <x:v>wave.801.announcement</x:v>
+      </x:c>
+      <x:c r="C442" s="16" t="str">
+        <x:v>一大队来客到了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" ht="58" customHeight="1">
+      <x:c r="A443" s="16" t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B443" s="16" t="str">
+        <x:v>wave.803.announcement</x:v>
+      </x:c>
+      <x:c r="C443" s="16" t="str">
+        <x:v>队伍更密了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" ht="58" customHeight="1">
+      <x:c r="A444" s="16" t="n">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B444" s="16" t="str">
+        <x:v>wave.1503.announcement</x:v>
+      </x:c>
+      <x:c r="C444" s="16" t="str">
+        <x:v>来客开始增多</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" ht="58" customHeight="1">
+      <x:c r="A445" s="16" t="n">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B445" s="16" t="str">
+        <x:v>wave.2002.announcement</x:v>
+      </x:c>
+      <x:c r="C445" s="16" t="str">
+        <x:v>厚实来客随后赶到</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" ht="58" customHeight="1">
+      <x:c r="A446" s="16" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B446" s="16" t="str">
+        <x:v>wave.2003.announcement</x:v>
+      </x:c>
+      <x:c r="C446" s="16" t="str">
+        <x:v>快客混进了队伍</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R61c263b81a4743f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rbee404a828674add"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2180,7 +2180,7 @@
         <x:v>ui.GameMenuView.006</x:v>
       </x:c>
       <x:c r="C169" s="13" t="str">
-        <x:v>固定体验关 · 限定4名店员</x:v>
+        <x:v>15波夜班 · 自选4名店员</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="58" hidden="0" customHeight="1">
@@ -3369,7 +3369,7 @@
         <x:v>challenge.title</x:v>
       </x:c>
       <x:c r="C277" s="16" t="str">
-        <x:v>夜班极限挑战</x:v>
+        <x:v>夜班加时赛</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="58" customHeight="1">
@@ -3380,7 +3380,7 @@
         <x:v>challenge.goal</x:v>
       </x:c>
       <x:c r="C278" s="16" t="str">
-        <x:v>限定店员搭配，守住最后一班</x:v>
+        <x:v>守住15波来客</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="58" customHeight="1">
@@ -3391,7 +3391,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="C279" s="16" t="str">
-        <x:v>首领来袭，准备集中火力！</x:v>
+        <x:v>首领来访</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="58" customHeight="1">
@@ -3402,7 +3402,7 @@
         <x:v>challenge.hud</x:v>
       </x:c>
       <x:c r="C280" s="16" t="str">
-        <x:v>挑战体验关</x:v>
+        <x:v>夜班加时赛</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="58" customHeight="1">
@@ -3413,7 +3413,7 @@
         <x:v>challenge.win</x:v>
       </x:c>
       <x:c r="C281" s="16" t="str">
-        <x:v>挑战守护完成！</x:v>
+        <x:v>夜班挑战完成！</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="58" customHeight="1">
@@ -3435,7 +3435,7 @@
         <x:v>challenge.enter</x:v>
       </x:c>
       <x:c r="C283" s="16" t="str">
-        <x:v>固定挑战：棉棉、布丁、咕咕、薄荷</x:v>
+        <x:v>夜班加时赛</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="58" customHeight="1">
@@ -5232,6 +5232,875 @@
       </x:c>
       <x:c r="C446" s="16" t="str">
         <x:v>快客混进了队伍</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447" t="n">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B447" t="str">
+        <x:v>challenge.pick</x:v>
+      </x:c>
+      <x:c r="C447" t="str">
+        <x:v>选一份夜班补给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B448" t="str">
+        <x:v>challenge.pickCount</x:v>
+      </x:c>
+      <x:c r="C448" t="str">
+        <x:v>第 {p0} / {p1} 次补给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449" t="n">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B449" t="str">
+        <x:v>challenge.refresh</x:v>
+      </x:c>
+      <x:c r="C449" t="str">
+        <x:v>免费换一批（{p0}）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450" t="n">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B450" t="str">
+        <x:v>challenge.refreshEmpty</x:v>
+      </x:c>
+      <x:c r="C450" t="str">
+        <x:v>本局换卡已用完</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451" t="n">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B451" t="str">
+        <x:v>challenge.inventory</x:v>
+      </x:c>
+      <x:c r="C451" t="str">
+        <x:v>本局强化 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452" t="n">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B452" t="str">
+        <x:v>challenge.close</x:v>
+      </x:c>
+      <x:c r="C452" t="str">
+        <x:v>返回战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453" t="n">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B453" t="str">
+        <x:v>challenge.exit</x:v>
+      </x:c>
+      <x:c r="C453" t="str">
+        <x:v>结束本局</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B454" t="str">
+        <x:v>challenge.empty</x:v>
+      </x:c>
+      <x:c r="C454" t="str">
+        <x:v>本局还没有强化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B455" t="str">
+        <x:v>challenge.result</x:v>
+      </x:c>
+      <x:c r="C455" t="str">
+        <x:v>抵达第 {p0} / {p1} 波 · 获得 {p2} 项强化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" t="n">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B456" t="str">
+        <x:v>challenge.loadout</x:v>
+      </x:c>
+      <x:c r="C456" t="str">
+        <x:v>夜班加时赛 · 选择店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" t="n">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B457" t="str">
+        <x:v>challenge.category.S</x:v>
+      </x:c>
+      <x:c r="C457" t="str">
+        <x:v>店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" t="n">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B458" t="str">
+        <x:v>challenge.category.G</x:v>
+      </x:c>
+      <x:c r="C458" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" t="n">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B459" t="str">
+        <x:v>challenge.category.E</x:v>
+      </x:c>
+      <x:c r="C459" t="str">
+        <x:v>经济</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460" t="n">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B460" t="str">
+        <x:v>challenge.category.X</x:v>
+      </x:c>
+      <x:c r="C460" t="str">
+        <x:v>特殊</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B461" t="str">
+        <x:v>challenge.category.F</x:v>
+      </x:c>
+      <x:c r="C461" t="str">
+        <x:v>趣味</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" t="n">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B462" t="str">
+        <x:v>perk.S01.name</x:v>
+      </x:c>
+      <x:c r="C462" t="str">
+        <x:v>三连发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" t="n">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B463" t="str">
+        <x:v>perk.S01.desc</x:v>
+      </x:c>
+      <x:c r="C463" t="str">
+        <x:v>豆包每第三轮攻击改为三连发，每发造成70%伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" t="n">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B464" t="str">
+        <x:v>perk.S02.name</x:v>
+      </x:c>
+      <x:c r="C464" t="str">
+        <x:v>冷气外送</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" t="n">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B465" t="str">
+        <x:v>perk.S02.desc</x:v>
+      </x:c>
+      <x:c r="C465" t="str">
+        <x:v>被减速的来客被击败时，将当前减速传给80范围内至多2名来客，持续1.5秒。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B466" t="str">
+        <x:v>perk.S03.name</x:v>
+      </x:c>
+      <x:c r="C466" t="str">
+        <x:v>双响礼花</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467">
+      <x:c r="A467" t="n">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B467" t="str">
+        <x:v>perk.S03.desc</x:v>
+      </x:c>
+      <x:c r="C467" t="str">
+        <x:v>布丁每第三轮攻击的爆点会在0.35秒后再爆一次，造成80%伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468" t="n">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B468" t="str">
+        <x:v>perk.S04.name</x:v>
+      </x:c>
+      <x:c r="C468" t="str">
+        <x:v>远处加急</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B469" t="str">
+        <x:v>perk.S04.desc</x:v>
+      </x:c>
+      <x:c r="C469" t="str">
+        <x:v>咕咕离目标越远伤害越高，在原射程边缘达到额外60%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470" t="n">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B470" t="str">
+        <x:v>perk.S05.name</x:v>
+      </x:c>
+      <x:c r="C470" t="str">
+        <x:v>电流返工</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471" t="n">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B471" t="str">
+        <x:v>perk.S05.desc</x:v>
+      </x:c>
+      <x:c r="C471" t="str">
+        <x:v>栗栗每第三轮攻击多放出一条电链，造成60%伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B472" t="str">
+        <x:v>perk.S06.name</x:v>
+      </x:c>
+      <x:c r="C472" t="str">
+        <x:v>余温四散</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473" t="n">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B473" t="str">
+        <x:v>perk.S06.desc</x:v>
+      </x:c>
+      <x:c r="C473" t="str">
+        <x:v>燃烧中的来客被击败时，对65范围内其他来客造成其每秒灼烧伤害200%的伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474" t="n">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B474" t="str">
+        <x:v>perk.S07.name</x:v>
+      </x:c>
+      <x:c r="C474" t="str">
+        <x:v>接班标记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475" t="n">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="B475" t="str">
+        <x:v>perk.S07.desc</x:v>
+      </x:c>
+      <x:c r="C475" t="str">
+        <x:v>被标记的来客被击败后，将标记传给100范围内至多2名来客，持续2秒，最多传递3代。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476" t="n">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B476" t="str">
+        <x:v>perk.S08.name</x:v>
+      </x:c>
+      <x:c r="C476" t="str">
+        <x:v>回旋小风</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477" t="n">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B477" t="str">
+        <x:v>perk.S08.desc</x:v>
+      </x:c>
+      <x:c r="C477" t="str">
+        <x:v>啾啾的每枚风弹命中后，弹向65范围内另一名来客，造成60%伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478" t="n">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="B478" t="str">
+        <x:v>perk.G01.name</x:v>
+      </x:c>
+      <x:c r="C478" t="str">
+        <x:v>开门冲刺</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479">
+      <x:c r="A479" t="n">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B479" t="str">
+        <x:v>perk.G01.desc</x:v>
+      </x:c>
+      <x:c r="C479" t="str">
+        <x:v>每波开始后的6秒内，全体攻击间隔缩短35%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480" t="n">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B480" t="str">
+        <x:v>perk.G02.name</x:v>
+      </x:c>
+      <x:c r="C480" t="str">
+        <x:v>邻柜帮忙</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481" t="n">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B481" t="str">
+        <x:v>perk.G02.desc</x:v>
+      </x:c>
+      <x:c r="C481" t="str">
+        <x:v>90范围内有其他种类店员时，伤害提高25%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482" t="n">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B482" t="str">
+        <x:v>perk.G03.name</x:v>
+      </x:c>
+      <x:c r="C482" t="str">
+        <x:v>独当一面</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483" t="n">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B483" t="str">
+        <x:v>perk.G03.desc</x:v>
+      </x:c>
+      <x:c r="C483" t="str">
+        <x:v>90范围内没有其他店员时，伤害提高50%，射程缩短10%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484" t="n">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="B484" t="str">
+        <x:v>perk.G04.name</x:v>
+      </x:c>
+      <x:c r="C484" t="str">
+        <x:v>满满收银台</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B485" t="str">
+        <x:v>perk.G04.desc</x:v>
+      </x:c>
+      <x:c r="C485" t="str">
+        <x:v>每持有100金币，全体伤害提高10%，最多提高40%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B486" t="str">
+        <x:v>perk.G05.name</x:v>
+      </x:c>
+      <x:c r="C486" t="str">
+        <x:v>整齐交班</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487" t="n">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B487" t="str">
+        <x:v>perk.G05.desc</x:v>
+      </x:c>
+      <x:c r="C487" t="str">
+        <x:v>上一波没有漏客时，本波伤害提高25%，射程提高15%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488" t="n">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B488" t="str">
+        <x:v>perk.G06.name</x:v>
+      </x:c>
+      <x:c r="C488" t="str">
+        <x:v>全员到岗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" t="n">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B489" t="str">
+        <x:v>perk.G06.desc</x:v>
+      </x:c>
+      <x:c r="C489" t="str">
+        <x:v>所选4种店员全部在场时，全体伤害提高35%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490" t="n">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B490" t="str">
+        <x:v>perk.E01.name</x:v>
+      </x:c>
+      <x:c r="C490" t="str">
+        <x:v>备用金</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" t="n">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B491" t="str">
+        <x:v>perk.E01.desc</x:v>
+      </x:c>
+      <x:c r="C491" t="str">
+        <x:v>立即获得200金币。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" t="n">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B492" t="str">
+        <x:v>perk.E02.name</x:v>
+      </x:c>
+      <x:c r="C492" t="str">
+        <x:v>夜班利息</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" t="n">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B493" t="str">
+        <x:v>perk.E02.desc</x:v>
+      </x:c>
+      <x:c r="C493" t="str">
+        <x:v>接下来5次清波，按清波奖金到账前的金币获得15%利息，每次最多75金币。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B494" t="str">
+        <x:v>perk.E03.name</x:v>
+      </x:c>
+      <x:c r="C494" t="str">
+        <x:v>新柜补贴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" t="n">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B495" t="str">
+        <x:v>perk.E03.desc</x:v>
+      </x:c>
+      <x:c r="C495" t="str">
+        <x:v>接下来3次建造免费。免费投入不计入出售返还。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" t="n">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B496" t="str">
+        <x:v>perk.E04.name</x:v>
+      </x:c>
+      <x:c r="C496" t="str">
+        <x:v>进化报销</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" t="n">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B497" t="str">
+        <x:v>perk.E04.desc</x:v>
+      </x:c>
+      <x:c r="C497" t="str">
+        <x:v>接下来2次进化免费。免费投入不计入出售返还。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498" t="n">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B498" t="str">
+        <x:v>perk.E05.name</x:v>
+      </x:c>
+      <x:c r="C498" t="str">
+        <x:v>清仓补贴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499" t="n">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="B499" t="str">
+        <x:v>perk.E05.desc</x:v>
+      </x:c>
+      <x:c r="C499" t="str">
+        <x:v>立即获得60金币，此后每清除一件货物额外获得30金币。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500" t="n">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B500" t="str">
+        <x:v>perk.E06.name</x:v>
+      </x:c>
+      <x:c r="C500" t="str">
+        <x:v>零钱罐</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501">
+      <x:c r="A501" t="n">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B501" t="str">
+        <x:v>perk.E06.desc</x:v>
+      </x:c>
+      <x:c r="C501" t="str">
+        <x:v>普通来客的基础金币奖励增加25%，向下取整。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502">
+      <x:c r="A502" t="n">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B502" t="str">
+        <x:v>perk.X01.name</x:v>
+      </x:c>
+      <x:c r="C502" t="str">
+        <x:v>退货再加工</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503">
+      <x:c r="A503" t="n">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="B503" t="str">
+        <x:v>perk.X01.desc</x:v>
+      </x:c>
+      <x:c r="C503" t="str">
+        <x:v>每波第一名到达店门的普通来客返回路线30%处，保留生命与状态。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504">
+      <x:c r="A504" t="n">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B504" t="str">
+        <x:v>perk.X02.name</x:v>
+      </x:c>
+      <x:c r="C504" t="str">
+        <x:v>加固门帘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505">
+      <x:c r="A505" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B505" t="str">
+        <x:v>perk.X02.desc</x:v>
+      </x:c>
+      <x:c r="C505" t="str">
+        <x:v>每波抵挡2点漏客伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506">
+      <x:c r="A506" t="n">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B506" t="str">
+        <x:v>perk.X03.name</x:v>
+      </x:c>
+      <x:c r="C506" t="str">
+        <x:v>门口慢行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507">
+      <x:c r="A507" t="n">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B507" t="str">
+        <x:v>perk.X03.desc</x:v>
+      </x:c>
+      <x:c r="C507" t="str">
+        <x:v>每波前3名进入最后20%路段的普通来客，移速降低60%，持续2秒。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508">
+      <x:c r="A508" t="n">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B508" t="str">
+        <x:v>perk.X04.name</x:v>
+      </x:c>
+      <x:c r="C508" t="str">
+        <x:v>收银开火</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509">
+      <x:c r="A509" t="n">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B509" t="str">
+        <x:v>perk.X04.desc</x:v>
+      </x:c>
+      <x:c r="C509" t="str">
+        <x:v>每累计收入100金币，全体攻击间隔缩短25%，持续4秒。出售收入不计入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510">
+      <x:c r="A510" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B510" t="str">
+        <x:v>perk.X05.name</x:v>
+      </x:c>
+      <x:c r="C510" t="str">
+        <x:v>货架连拆</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511">
+      <x:c r="A511" t="n">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B511" t="str">
+        <x:v>perk.X05.desc</x:v>
+      </x:c>
+      <x:c r="C511" t="str">
+        <x:v>直接清除货物时，对100范围内其他货物造成其最大生命35%的伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512">
+      <x:c r="A512" t="n">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B512" t="str">
+        <x:v>perk.X06.name</x:v>
+      </x:c>
+      <x:c r="C512" t="str">
+        <x:v>最后一位</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513">
+      <x:c r="A513" t="n">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B513" t="str">
+        <x:v>perk.X06.desc</x:v>
+      </x:c>
+      <x:c r="C513" t="str">
+        <x:v>本波来客全部出现且只剩一名时，店员直击伤害提高80%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514">
+      <x:c r="A514" t="n">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B514" t="str">
+        <x:v>perk.F01.name</x:v>
+      </x:c>
+      <x:c r="C514" t="str">
+        <x:v>大个子值班</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515">
+      <x:c r="A515" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B515" t="str">
+        <x:v>perk.F01.desc</x:v>
+      </x:c>
+      <x:c r="C515" t="str">
+        <x:v>每波随机一名最高等级店员变大，伤害提高80%，射程提高15%，攻击间隔增加20%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516">
+      <x:c r="A516" t="n">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B516" t="str">
+        <x:v>perk.F02.name</x:v>
+      </x:c>
+      <x:c r="C516" t="str">
+        <x:v>迷你夜班</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517">
+      <x:c r="A517" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B517" t="str">
+        <x:v>perk.F02.desc</x:v>
+      </x:c>
+      <x:c r="C517" t="str">
+        <x:v>全体店员变小，攻击间隔缩短25%，伤害降低10%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518">
+      <x:c r="A518" t="n">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="B518" t="str">
+        <x:v>perk.F03.name</x:v>
+      </x:c>
+      <x:c r="C518" t="str">
+        <x:v>惊喜包裹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519">
+      <x:c r="A519" t="n">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B519" t="str">
+        <x:v>perk.F03.desc</x:v>
+      </x:c>
+      <x:c r="C519" t="str">
+        <x:v>每击败12名来客，随机获得20金币、一次100伤害爆炸或2秒减速。每波最多3次，额外攻击不计数。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520">
+      <x:c r="A520" t="n">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B520" t="str">
+        <x:v>perk.F04.name</x:v>
+      </x:c>
+      <x:c r="C520" t="str">
+        <x:v>夜班保龄球</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521">
+      <x:c r="A521" t="n">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="B521" t="str">
+        <x:v>perk.F04.desc</x:v>
+      </x:c>
+      <x:c r="C521" t="str">
+        <x:v>全队每完成24轮攻击，从店门滚出保龄球，沿路造成100伤害，最多命中8名来客，冷却8秒。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522">
+      <x:c r="A522" t="n">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B522" t="str">
+        <x:v>perk.F05.name</x:v>
+      </x:c>
+      <x:c r="C522" t="str">
+        <x:v>天降快递</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523">
+      <x:c r="A523" t="n">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B523" t="str">
+        <x:v>perk.F05.desc</x:v>
+      </x:c>
+      <x:c r="C523" t="str">
+        <x:v>每10秒在最靠近店门的3名来客处落下快递，0.6秒后对40范围造成80伤害。每次快递雨对同一来客只伤害一次。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524">
+      <x:c r="A524" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B524" t="str">
+        <x:v>perk.F06.name</x:v>
+      </x:c>
+      <x:c r="C524" t="str">
+        <x:v>口袋鼓鼓</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525">
+      <x:c r="A525" t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B525" t="str">
+        <x:v>perk.F06.desc</x:v>
+      </x:c>
+      <x:c r="C525" t="str">
+        <x:v>每波随机一名普通来客生命变为2倍，击败奖励变为4倍。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rbee404a828674add"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R902e27fc1da040e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
         <x:v>challenge.refresh</x:v>
       </x:c>
       <x:c r="C449" t="str">
-        <x:v>免费换一批（{p0}）</x:v>
+        <x:v>看广告刷新</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
@@ -5275,7 +5275,7 @@
         <x:v>challenge.refreshEmpty</x:v>
       </x:c>
       <x:c r="C450" t="str">
-        <x:v>本局换卡已用完</x:v>
+        <x:v>本次刷新已用完</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -5301,15 +5301,9 @@
       </x:c>
     </x:row>
     <x:row r="453">
-      <x:c r="A453" t="n">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="B453" t="str">
-        <x:v>challenge.exit</x:v>
-      </x:c>
-      <x:c r="C453" t="str">
-        <x:v>结束本局</x:v>
-      </x:c>
+      <x:c r="A453" t="str"/>
+      <x:c r="B453" t="str"/>
+      <x:c r="C453" t="str"/>
     </x:row>
     <x:row r="454">
       <x:c r="A454" t="n">
@@ -6101,6 +6095,61 @@
       </x:c>
       <x:c r="C525" t="str">
         <x:v>每波随机一名普通来客生命变为2倍，击败奖励变为4倍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526">
+      <x:c r="A526" t="n">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="B526" t="str">
+        <x:v>challenge.refreshCount</x:v>
+      </x:c>
+      <x:c r="C526" t="str">
+        <x:v>本次剩余刷新 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527">
+      <x:c r="A527" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B527" t="str">
+        <x:v>challenge.refreshLoading</x:v>
+      </x:c>
+      <x:c r="C527" t="str">
+        <x:v>广告加载中…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528">
+      <x:c r="A528" t="n">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B528" t="str">
+        <x:v>challenge.refreshUnavailable</x:v>
+      </x:c>
+      <x:c r="C528" t="str">
+        <x:v>广告暂不可用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529">
+      <x:c r="A529" t="n">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B529" t="str">
+        <x:v>challenge.refreshIncomplete</x:v>
+      </x:c>
+      <x:c r="C529" t="str">
+        <x:v>未完整观看，未刷新</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530">
+      <x:c r="A530" t="n">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B530" t="str">
+        <x:v>challenge.enhanceStaff</x:v>
+      </x:c>
+      <x:c r="C530" t="str">
+        <x:v>强化 {p0}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R902e27fc1da040e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rb054a7da3cb24ee3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4428,7 +4428,7 @@
         <x:v>ui.loadout.start</x:v>
       </x:c>
       <x:c r="C373" s="16" t="str">
-        <x:v>开始关卡</x:v>
+        <x:v>确认出战</x:v>
       </x:c>
     </x:row>
     <x:row r="374" ht="58" customHeight="1">
@@ -5242,7 +5242,7 @@
         <x:v>challenge.pick</x:v>
       </x:c>
       <x:c r="C447" t="str">
-        <x:v>选一份夜班补给</x:v>
+        <x:v>夜班补给</x:v>
       </x:c>
     </x:row>
     <x:row r="448">
@@ -5253,7 +5253,7 @@
         <x:v>challenge.pickCount</x:v>
       </x:c>
       <x:c r="C448" t="str">
-        <x:v>第 {p0} / {p1} 次补给</x:v>
+        <x:v>第 {p0}/{p1} 次补给</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -5301,9 +5301,9 @@
       </x:c>
     </x:row>
     <x:row r="453">
-      <x:c r="A453" t="str"/>
-      <x:c r="B453" t="str"/>
-      <x:c r="C453" t="str"/>
+      <x:c r="A453"/>
+      <x:c r="B453"/>
+      <x:c r="C453"/>
     </x:row>
     <x:row r="454">
       <x:c r="A454" t="n">
@@ -5335,7 +5335,7 @@
         <x:v>challenge.loadout</x:v>
       </x:c>
       <x:c r="C456" t="str">
-        <x:v>夜班加时赛 · 选择店员</x:v>
+        <x:v>选择出战店员</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -6150,6 +6150,501 @@
       </x:c>
       <x:c r="C530" t="str">
         <x:v>强化 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531">
+      <x:c r="A531" t="n">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B531" t="str">
+        <x:v>ui.redesign.homeTitle</x:v>
+      </x:c>
+      <x:c r="C531" t="str">
+        <x:v>我的便利店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532">
+      <x:c r="A532" t="n">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B532" t="str">
+        <x:v>ui.redesign.book</x:v>
+      </x:c>
+      <x:c r="C532" t="str">
+        <x:v>图鉴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533">
+      <x:c r="A533" t="n">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B533" t="str">
+        <x:v>ui.redesign.shop</x:v>
+      </x:c>
+      <x:c r="C533" t="str">
+        <x:v>商店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534">
+      <x:c r="A534" t="n">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B534" t="str">
+        <x:v>ui.redesign.rank</x:v>
+      </x:c>
+      <x:c r="C534" t="str">
+        <x:v>排行榜</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535">
+      <x:c r="A535" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B535" t="str">
+        <x:v>ui.redesign.settings</x:v>
+      </x:c>
+      <x:c r="C535" t="str">
+        <x:v>设置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536">
+      <x:c r="A536" t="n">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B536" t="str">
+        <x:v>ui.redesign.unavailable</x:v>
+      </x:c>
+      <x:c r="C536" t="str">
+        <x:v>暂未开放</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537">
+      <x:c r="A537" t="n">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B537" t="str">
+        <x:v>ui.redesign.loading</x:v>
+      </x:c>
+      <x:c r="C537" t="str">
+        <x:v>正在加载 {p0}%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538">
+      <x:c r="A538" t="n">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B538" t="str">
+        <x:v>ui.redesign.loadingFailed</x:v>
+      </x:c>
+      <x:c r="C538" t="str">
+        <x:v>加载失败，点击重试</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539">
+      <x:c r="A539" t="n">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B539" t="str">
+        <x:v>ui.redesign.select</x:v>
+      </x:c>
+      <x:c r="C539" t="str">
+        <x:v>选择</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540">
+      <x:c r="A540" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B540" t="str">
+        <x:v>ui.redesign.staff</x:v>
+      </x:c>
+      <x:c r="C540" t="str">
+        <x:v>店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541">
+      <x:c r="A541" t="n">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B541" t="str">
+        <x:v>ui.redesign.monsters</x:v>
+      </x:c>
+      <x:c r="C541" t="str">
+        <x:v>怪物</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542">
+      <x:c r="A542" t="n">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B542" t="str">
+        <x:v>ui.redesign.goods</x:v>
+      </x:c>
+      <x:c r="C542" t="str">
+        <x:v>商品</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543">
+      <x:c r="A543" t="n">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B543" t="str">
+        <x:v>ui.redesign.progress</x:v>
+      </x:c>
+      <x:c r="C543" t="str">
+        <x:v>{p0}/{p1}关</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544">
+      <x:c r="A544" t="n">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B544" t="str">
+        <x:v>ui.redesign.collection</x:v>
+      </x:c>
+      <x:c r="C544" t="str">
+        <x:v>收录 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545">
+      <x:c r="A545" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B545" t="str">
+        <x:v>ui.redesign.pickHint</x:v>
+      </x:c>
+      <x:c r="C545" t="str">
+        <x:v>点击头像选择或取消</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546">
+      <x:c r="A546" t="n">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B546" t="str">
+        <x:v>ui.redesign.pickFull</x:v>
+      </x:c>
+      <x:c r="C546" t="str">
+        <x:v>请先取消一名店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547">
+      <x:c r="A547" t="n">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B547" t="str">
+        <x:v>ui.redesign.goodsCategory</x:v>
+      </x:c>
+      <x:c r="C547" t="str">
+        <x:v>便利店商品</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548">
+      <x:c r="A548" t="n">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B548" t="str">
+        <x:v>ui.redesign.goodsUnlock</x:v>
+      </x:c>
+      <x:c r="C548" t="str">
+        <x:v>第 {p0} 关解锁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549">
+      <x:c r="A549" t="n">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B549" t="str">
+        <x:v>goods.cola.name</x:v>
+      </x:c>
+      <x:c r="C549" t="str">
+        <x:v>可乐</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550">
+      <x:c r="A550" t="n">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="B550" t="str">
+        <x:v>goods.cola.description</x:v>
+      </x:c>
+      <x:c r="C550" t="str">
+        <x:v>冰凉爽口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551">
+      <x:c r="A551" t="n">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B551" t="str">
+        <x:v>goods.cola.story</x:v>
+      </x:c>
+      <x:c r="C551" t="str">
+        <x:v>一打开罐子，细密的气泡就从杯沿冒出来。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552">
+      <x:c r="A552" t="n">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B552" t="str">
+        <x:v>goods.bread.name</x:v>
+      </x:c>
+      <x:c r="C552" t="str">
+        <x:v>面包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553">
+      <x:c r="A553" t="n">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B553" t="str">
+        <x:v>goods.bread.description</x:v>
+      </x:c>
+      <x:c r="C553" t="str">
+        <x:v>松软香甜</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554">
+      <x:c r="A554" t="n">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B554" t="str">
+        <x:v>goods.bread.story</x:v>
+      </x:c>
+      <x:c r="C554" t="str">
+        <x:v>清晨烤好的面包，在夜班也能带来一点温暖。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555">
+      <x:c r="A555" t="n">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B555" t="str">
+        <x:v>goods.noodles.name</x:v>
+      </x:c>
+      <x:c r="C555" t="str">
+        <x:v>泡面</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556">
+      <x:c r="A556" t="n">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B556" t="str">
+        <x:v>goods.noodles.description</x:v>
+      </x:c>
+      <x:c r="C556" t="str">
+        <x:v>热气腾腾</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557">
+      <x:c r="A557" t="n">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B557" t="str">
+        <x:v>goods.noodles.story</x:v>
+      </x:c>
+      <x:c r="C557" t="str">
+        <x:v>倒上热水，等一会儿，就是一顿夜班小餐。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558">
+      <x:c r="A558" t="n">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B558" t="str">
+        <x:v>goods.milk.name</x:v>
+      </x:c>
+      <x:c r="C558" t="str">
+        <x:v>牛奶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559">
+      <x:c r="A559" t="n">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B559" t="str">
+        <x:v>goods.milk.description</x:v>
+      </x:c>
+      <x:c r="C559" t="str">
+        <x:v>醇香顺滑</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560">
+      <x:c r="A560" t="n">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B560" t="str">
+        <x:v>goods.milk.story</x:v>
+      </x:c>
+      <x:c r="C560" t="str">
+        <x:v>蓝白小盒里装着一份简单的日常。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561">
+      <x:c r="A561" t="n">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B561" t="str">
+        <x:v>goods.chips.name</x:v>
+      </x:c>
+      <x:c r="C561" t="str">
+        <x:v>薯片</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562">
+      <x:c r="A562" t="n">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B562" t="str">
+        <x:v>goods.chips.description</x:v>
+      </x:c>
+      <x:c r="C562" t="str">
+        <x:v>咔嚓酥脆</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563">
+      <x:c r="A563" t="n">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B563" t="str">
+        <x:v>goods.chips.story</x:v>
+      </x:c>
+      <x:c r="C563" t="str">
+        <x:v>袋子里总藏着一片形状特别的薯片。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564">
+      <x:c r="A564" t="n">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B564" t="str">
+        <x:v>goods.cookies.name</x:v>
+      </x:c>
+      <x:c r="C564" t="str">
+        <x:v>饼干</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565">
+      <x:c r="A565" t="n">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B565" t="str">
+        <x:v>goods.cookies.description</x:v>
+      </x:c>
+      <x:c r="C565" t="str">
+        <x:v>香酥可口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566">
+      <x:c r="A566" t="n">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B566" t="str">
+        <x:v>goods.cookies.story</x:v>
+      </x:c>
+      <x:c r="C566" t="str">
+        <x:v>小盒饼干很适合和忙完夜班的朋友分享。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567">
+      <x:c r="A567" t="n">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="B567" t="str">
+        <x:v>goods.jelly.name</x:v>
+      </x:c>
+      <x:c r="C567" t="str">
+        <x:v>果冻</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568">
+      <x:c r="A568" t="n">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B568" t="str">
+        <x:v>goods.jelly.description</x:v>
+      </x:c>
+      <x:c r="C568" t="str">
+        <x:v>清甜弹软</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569">
+      <x:c r="A569" t="n">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B569" t="str">
+        <x:v>goods.jelly.story</x:v>
+      </x:c>
+      <x:c r="C569" t="str">
+        <x:v>红色和绿色的小杯，摆在货架上像两颗宝石。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570">
+      <x:c r="A570" t="n">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="B570" t="str">
+        <x:v>goods.water.name</x:v>
+      </x:c>
+      <x:c r="C570" t="str">
+        <x:v>矿泉水</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571">
+      <x:c r="A571" t="n">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B571" t="str">
+        <x:v>goods.water.description</x:v>
+      </x:c>
+      <x:c r="C571" t="str">
+        <x:v>清澈解渴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572">
+      <x:c r="A572" t="n">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B572" t="str">
+        <x:v>goods.water.story</x:v>
+      </x:c>
+      <x:c r="C572" t="str">
+        <x:v>店员补货时，总会给水瓶排得整整齐齐。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573">
+      <x:c r="A573" t="n">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B573" t="str">
+        <x:v>goods.rice.name</x:v>
+      </x:c>
+      <x:c r="C573" t="str">
+        <x:v>饭团</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574">
+      <x:c r="A574" t="n">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B574" t="str">
+        <x:v>goods.rice.description</x:v>
+      </x:c>
+      <x:c r="C574" t="str">
+        <x:v>一口满足</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" ht="28" customHeight="1">
+      <x:c r="A575" t="n">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B575" t="str">
+        <x:v>goods.rice.story</x:v>
+      </x:c>
+      <x:c r="C575" t="str">
+        <x:v>小小的三角饭团，藏着夜班便当的心意。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rb054a7da3cb24ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R14f84813dad14e93"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4406,7 +4406,7 @@
         <x:v>ui.loadout.title</x:v>
       </x:c>
       <x:c r="C371" s="16" t="str">
-        <x:v>出战准备</x:v>
+        <x:v>选择出战店员</x:v>
       </x:c>
     </x:row>
     <x:row r="372" ht="58" customHeight="1">
@@ -5253,7 +5253,7 @@
         <x:v>challenge.pickCount</x:v>
       </x:c>
       <x:c r="C448" t="str">
-        <x:v>第 {p0}/{p1} 次补给</x:v>
+        <x:v>第 {p0} / {p1} 次补给</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -5301,1350 +5301,1356 @@
       </x:c>
     </x:row>
     <x:row r="453">
-      <x:c r="A453"/>
-      <x:c r="B453"/>
-      <x:c r="C453"/>
+      <x:c r="A453" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B453" t="str">
+        <x:v>challenge.empty</x:v>
+      </x:c>
+      <x:c r="C453" t="str">
+        <x:v>本局还没有强化</x:v>
+      </x:c>
     </x:row>
     <x:row r="454">
       <x:c r="A454" t="n">
-        <x:v>449</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B454" t="str">
-        <x:v>challenge.empty</x:v>
+        <x:v>challenge.result</x:v>
       </x:c>
       <x:c r="C454" t="str">
-        <x:v>本局还没有强化</x:v>
+        <x:v>抵达第 {p0} / {p1} 波 · 获得 {p2} 项强化</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
       <x:c r="A455" t="n">
-        <x:v>450</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B455" t="str">
-        <x:v>challenge.result</x:v>
+        <x:v>challenge.loadout</x:v>
       </x:c>
       <x:c r="C455" t="str">
-        <x:v>抵达第 {p0} / {p1} 波 · 获得 {p2} 项强化</x:v>
+        <x:v>选择出战店员</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
       <x:c r="A456" t="n">
-        <x:v>451</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B456" t="str">
-        <x:v>challenge.loadout</x:v>
+        <x:v>challenge.category.S</x:v>
       </x:c>
       <x:c r="C456" t="str">
-        <x:v>选择出战店员</x:v>
+        <x:v>店员</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
       <x:c r="A457" t="n">
-        <x:v>452</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B457" t="str">
-        <x:v>challenge.category.S</x:v>
+        <x:v>challenge.category.G</x:v>
       </x:c>
       <x:c r="C457" t="str">
-        <x:v>店员</x:v>
+        <x:v>全局</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
       <x:c r="A458" t="n">
-        <x:v>453</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B458" t="str">
-        <x:v>challenge.category.G</x:v>
+        <x:v>challenge.category.E</x:v>
       </x:c>
       <x:c r="C458" t="str">
-        <x:v>全局</x:v>
+        <x:v>经济</x:v>
       </x:c>
     </x:row>
     <x:row r="459">
       <x:c r="A459" t="n">
-        <x:v>454</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B459" t="str">
-        <x:v>challenge.category.E</x:v>
+        <x:v>challenge.category.X</x:v>
       </x:c>
       <x:c r="C459" t="str">
-        <x:v>经济</x:v>
+        <x:v>特殊</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
       <x:c r="A460" t="n">
-        <x:v>455</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B460" t="str">
-        <x:v>challenge.category.X</x:v>
+        <x:v>challenge.category.F</x:v>
       </x:c>
       <x:c r="C460" t="str">
-        <x:v>特殊</x:v>
+        <x:v>趣味</x:v>
       </x:c>
     </x:row>
     <x:row r="461">
       <x:c r="A461" t="n">
-        <x:v>456</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B461" t="str">
-        <x:v>challenge.category.F</x:v>
+        <x:v>perk.S01.name</x:v>
       </x:c>
       <x:c r="C461" t="str">
-        <x:v>趣味</x:v>
+        <x:v>三连发</x:v>
       </x:c>
     </x:row>
     <x:row r="462">
       <x:c r="A462" t="n">
-        <x:v>457</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B462" t="str">
-        <x:v>perk.S01.name</x:v>
+        <x:v>perk.S01.desc</x:v>
       </x:c>
       <x:c r="C462" t="str">
-        <x:v>三连发</x:v>
+        <x:v>豆包每第三轮攻击改为三连发，每发造成70%伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
       <x:c r="A463" t="n">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B463" t="str">
-        <x:v>perk.S01.desc</x:v>
+        <x:v>perk.S02.name</x:v>
       </x:c>
       <x:c r="C463" t="str">
-        <x:v>豆包每第三轮攻击改为三连发，每发造成70%伤害。</x:v>
+        <x:v>冷气外送</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
       <x:c r="A464" t="n">
-        <x:v>459</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B464" t="str">
-        <x:v>perk.S02.name</x:v>
+        <x:v>perk.S02.desc</x:v>
       </x:c>
       <x:c r="C464" t="str">
-        <x:v>冷气外送</x:v>
+        <x:v>被减速的来客被击败时，将当前减速传给80范围内至多2名来客，持续1.5秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
       <x:c r="A465" t="n">
-        <x:v>460</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B465" t="str">
-        <x:v>perk.S02.desc</x:v>
+        <x:v>perk.S03.name</x:v>
       </x:c>
       <x:c r="C465" t="str">
-        <x:v>被减速的来客被击败时，将当前减速传给80范围内至多2名来客，持续1.5秒。</x:v>
+        <x:v>双响礼花</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
       <x:c r="A466" t="n">
-        <x:v>461</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B466" t="str">
-        <x:v>perk.S03.name</x:v>
+        <x:v>perk.S03.desc</x:v>
       </x:c>
       <x:c r="C466" t="str">
-        <x:v>双响礼花</x:v>
+        <x:v>布丁每第三轮攻击的爆点会在0.35秒后再爆一次，造成80%伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
       <x:c r="A467" t="n">
-        <x:v>462</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B467" t="str">
-        <x:v>perk.S03.desc</x:v>
+        <x:v>perk.S04.name</x:v>
       </x:c>
       <x:c r="C467" t="str">
-        <x:v>布丁每第三轮攻击的爆点会在0.35秒后再爆一次，造成80%伤害。</x:v>
+        <x:v>远处加急</x:v>
       </x:c>
     </x:row>
     <x:row r="468">
       <x:c r="A468" t="n">
-        <x:v>463</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B468" t="str">
-        <x:v>perk.S04.name</x:v>
+        <x:v>perk.S04.desc</x:v>
       </x:c>
       <x:c r="C468" t="str">
-        <x:v>远处加急</x:v>
+        <x:v>咕咕离目标越远伤害越高，在原射程边缘达到额外60%。</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
       <x:c r="A469" t="n">
-        <x:v>464</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B469" t="str">
-        <x:v>perk.S04.desc</x:v>
+        <x:v>perk.S05.name</x:v>
       </x:c>
       <x:c r="C469" t="str">
-        <x:v>咕咕离目标越远伤害越高，在原射程边缘达到额外60%。</x:v>
+        <x:v>电流返工</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
       <x:c r="A470" t="n">
-        <x:v>465</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B470" t="str">
-        <x:v>perk.S05.name</x:v>
+        <x:v>perk.S05.desc</x:v>
       </x:c>
       <x:c r="C470" t="str">
-        <x:v>电流返工</x:v>
+        <x:v>栗栗每第三轮攻击多放出一条电链，造成60%伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
       <x:c r="A471" t="n">
-        <x:v>466</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B471" t="str">
-        <x:v>perk.S05.desc</x:v>
+        <x:v>perk.S06.name</x:v>
       </x:c>
       <x:c r="C471" t="str">
-        <x:v>栗栗每第三轮攻击多放出一条电链，造成60%伤害。</x:v>
+        <x:v>余温四散</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
       <x:c r="A472" t="n">
-        <x:v>467</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B472" t="str">
-        <x:v>perk.S06.name</x:v>
+        <x:v>perk.S06.desc</x:v>
       </x:c>
       <x:c r="C472" t="str">
-        <x:v>余温四散</x:v>
+        <x:v>燃烧中的来客被击败时，对65范围内其他来客造成其每秒灼烧伤害200%的伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
       <x:c r="A473" t="n">
-        <x:v>468</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B473" t="str">
-        <x:v>perk.S06.desc</x:v>
+        <x:v>perk.S07.name</x:v>
       </x:c>
       <x:c r="C473" t="str">
-        <x:v>燃烧中的来客被击败时，对65范围内其他来客造成其每秒灼烧伤害200%的伤害。</x:v>
+        <x:v>接班标记</x:v>
       </x:c>
     </x:row>
     <x:row r="474">
       <x:c r="A474" t="n">
-        <x:v>469</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B474" t="str">
-        <x:v>perk.S07.name</x:v>
+        <x:v>perk.S07.desc</x:v>
       </x:c>
       <x:c r="C474" t="str">
-        <x:v>接班标记</x:v>
+        <x:v>被标记的来客被击败后，将标记传给100范围内至多2名来客，持续2秒，最多传递3代。</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
       <x:c r="A475" t="n">
-        <x:v>470</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B475" t="str">
-        <x:v>perk.S07.desc</x:v>
+        <x:v>perk.S08.name</x:v>
       </x:c>
       <x:c r="C475" t="str">
-        <x:v>被标记的来客被击败后，将标记传给100范围内至多2名来客，持续2秒，最多传递3代。</x:v>
+        <x:v>回旋小风</x:v>
       </x:c>
     </x:row>
     <x:row r="476">
       <x:c r="A476" t="n">
-        <x:v>471</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B476" t="str">
-        <x:v>perk.S08.name</x:v>
+        <x:v>perk.S08.desc</x:v>
       </x:c>
       <x:c r="C476" t="str">
-        <x:v>回旋小风</x:v>
+        <x:v>啾啾的每枚风弹命中后，弹向65范围内另一名来客，造成60%伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
       <x:c r="A477" t="n">
-        <x:v>472</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B477" t="str">
-        <x:v>perk.S08.desc</x:v>
+        <x:v>perk.G01.name</x:v>
       </x:c>
       <x:c r="C477" t="str">
-        <x:v>啾啾的每枚风弹命中后，弹向65范围内另一名来客，造成60%伤害。</x:v>
+        <x:v>开门冲刺</x:v>
       </x:c>
     </x:row>
     <x:row r="478">
       <x:c r="A478" t="n">
-        <x:v>473</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B478" t="str">
-        <x:v>perk.G01.name</x:v>
+        <x:v>perk.G01.desc</x:v>
       </x:c>
       <x:c r="C478" t="str">
-        <x:v>开门冲刺</x:v>
+        <x:v>每波开始后的6秒内，全体攻击间隔缩短35%。</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
       <x:c r="A479" t="n">
-        <x:v>474</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B479" t="str">
-        <x:v>perk.G01.desc</x:v>
+        <x:v>perk.G02.name</x:v>
       </x:c>
       <x:c r="C479" t="str">
-        <x:v>每波开始后的6秒内，全体攻击间隔缩短35%。</x:v>
+        <x:v>邻柜帮忙</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
       <x:c r="A480" t="n">
-        <x:v>475</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B480" t="str">
-        <x:v>perk.G02.name</x:v>
+        <x:v>perk.G02.desc</x:v>
       </x:c>
       <x:c r="C480" t="str">
-        <x:v>邻柜帮忙</x:v>
+        <x:v>90范围内有其他种类店员时，伤害提高25%。</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
       <x:c r="A481" t="n">
-        <x:v>476</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B481" t="str">
-        <x:v>perk.G02.desc</x:v>
+        <x:v>perk.G03.name</x:v>
       </x:c>
       <x:c r="C481" t="str">
-        <x:v>90范围内有其他种类店员时，伤害提高25%。</x:v>
+        <x:v>独当一面</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
       <x:c r="A482" t="n">
-        <x:v>477</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B482" t="str">
-        <x:v>perk.G03.name</x:v>
+        <x:v>perk.G03.desc</x:v>
       </x:c>
       <x:c r="C482" t="str">
-        <x:v>独当一面</x:v>
+        <x:v>90范围内没有其他店员时，伤害提高50%，射程缩短10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
       <x:c r="A483" t="n">
-        <x:v>478</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B483" t="str">
-        <x:v>perk.G03.desc</x:v>
+        <x:v>perk.G04.name</x:v>
       </x:c>
       <x:c r="C483" t="str">
-        <x:v>90范围内没有其他店员时，伤害提高50%，射程缩短10%。</x:v>
+        <x:v>满满收银台</x:v>
       </x:c>
     </x:row>
     <x:row r="484">
       <x:c r="A484" t="n">
-        <x:v>479</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B484" t="str">
-        <x:v>perk.G04.name</x:v>
+        <x:v>perk.G04.desc</x:v>
       </x:c>
       <x:c r="C484" t="str">
-        <x:v>满满收银台</x:v>
+        <x:v>每持有100金币，全体伤害提高10%，最多提高40%。</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
       <x:c r="A485" t="n">
-        <x:v>480</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B485" t="str">
-        <x:v>perk.G04.desc</x:v>
+        <x:v>perk.G05.name</x:v>
       </x:c>
       <x:c r="C485" t="str">
-        <x:v>每持有100金币，全体伤害提高10%，最多提高40%。</x:v>
+        <x:v>整齐交班</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
       <x:c r="A486" t="n">
-        <x:v>481</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B486" t="str">
-        <x:v>perk.G05.name</x:v>
+        <x:v>perk.G05.desc</x:v>
       </x:c>
       <x:c r="C486" t="str">
-        <x:v>整齐交班</x:v>
+        <x:v>上一波没有漏客时，本波伤害提高25%，射程提高15%。</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
       <x:c r="A487" t="n">
-        <x:v>482</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B487" t="str">
-        <x:v>perk.G05.desc</x:v>
+        <x:v>perk.G06.name</x:v>
       </x:c>
       <x:c r="C487" t="str">
-        <x:v>上一波没有漏客时，本波伤害提高25%，射程提高15%。</x:v>
+        <x:v>全员到岗</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
       <x:c r="A488" t="n">
-        <x:v>483</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B488" t="str">
-        <x:v>perk.G06.name</x:v>
+        <x:v>perk.G06.desc</x:v>
       </x:c>
       <x:c r="C488" t="str">
-        <x:v>全员到岗</x:v>
+        <x:v>所选4种店员全部在场时，全体伤害提高35%。</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
       <x:c r="A489" t="n">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B489" t="str">
-        <x:v>perk.G06.desc</x:v>
+        <x:v>perk.E01.name</x:v>
       </x:c>
       <x:c r="C489" t="str">
-        <x:v>所选4种店员全部在场时，全体伤害提高35%。</x:v>
+        <x:v>备用金</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
       <x:c r="A490" t="n">
-        <x:v>485</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B490" t="str">
-        <x:v>perk.E01.name</x:v>
+        <x:v>perk.E01.desc</x:v>
       </x:c>
       <x:c r="C490" t="str">
-        <x:v>备用金</x:v>
+        <x:v>立即获得200金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
       <x:c r="A491" t="n">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B491" t="str">
-        <x:v>perk.E01.desc</x:v>
+        <x:v>perk.E02.name</x:v>
       </x:c>
       <x:c r="C491" t="str">
-        <x:v>立即获得200金币。</x:v>
+        <x:v>夜班利息</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
       <x:c r="A492" t="n">
-        <x:v>487</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B492" t="str">
-        <x:v>perk.E02.name</x:v>
+        <x:v>perk.E02.desc</x:v>
       </x:c>
       <x:c r="C492" t="str">
-        <x:v>夜班利息</x:v>
+        <x:v>接下来5次清波，按清波奖金到账前的金币获得15%利息，每次最多75金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
       <x:c r="A493" t="n">
-        <x:v>488</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B493" t="str">
-        <x:v>perk.E02.desc</x:v>
+        <x:v>perk.E03.name</x:v>
       </x:c>
       <x:c r="C493" t="str">
-        <x:v>接下来5次清波，按清波奖金到账前的金币获得15%利息，每次最多75金币。</x:v>
+        <x:v>新柜补贴</x:v>
       </x:c>
     </x:row>
     <x:row r="494">
       <x:c r="A494" t="n">
-        <x:v>489</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B494" t="str">
-        <x:v>perk.E03.name</x:v>
+        <x:v>perk.E03.desc</x:v>
       </x:c>
       <x:c r="C494" t="str">
-        <x:v>新柜补贴</x:v>
+        <x:v>接下来3次建造免费。免费投入不计入出售返还。</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
       <x:c r="A495" t="n">
-        <x:v>490</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B495" t="str">
-        <x:v>perk.E03.desc</x:v>
+        <x:v>perk.E04.name</x:v>
       </x:c>
       <x:c r="C495" t="str">
-        <x:v>接下来3次建造免费。免费投入不计入出售返还。</x:v>
+        <x:v>进化报销</x:v>
       </x:c>
     </x:row>
     <x:row r="496">
       <x:c r="A496" t="n">
-        <x:v>491</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B496" t="str">
-        <x:v>perk.E04.name</x:v>
+        <x:v>perk.E04.desc</x:v>
       </x:c>
       <x:c r="C496" t="str">
-        <x:v>进化报销</x:v>
+        <x:v>接下来2次进化免费。免费投入不计入出售返还。</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
       <x:c r="A497" t="n">
-        <x:v>492</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B497" t="str">
-        <x:v>perk.E04.desc</x:v>
+        <x:v>perk.E05.name</x:v>
       </x:c>
       <x:c r="C497" t="str">
-        <x:v>接下来2次进化免费。免费投入不计入出售返还。</x:v>
+        <x:v>清仓补贴</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
       <x:c r="A498" t="n">
-        <x:v>493</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B498" t="str">
-        <x:v>perk.E05.name</x:v>
+        <x:v>perk.E05.desc</x:v>
       </x:c>
       <x:c r="C498" t="str">
-        <x:v>清仓补贴</x:v>
+        <x:v>立即获得60金币，此后每清除一件货物额外获得30金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
       <x:c r="A499" t="n">
-        <x:v>494</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B499" t="str">
-        <x:v>perk.E05.desc</x:v>
+        <x:v>perk.E06.name</x:v>
       </x:c>
       <x:c r="C499" t="str">
-        <x:v>立即获得60金币，此后每清除一件货物额外获得30金币。</x:v>
+        <x:v>零钱罐</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
       <x:c r="A500" t="n">
-        <x:v>495</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B500" t="str">
-        <x:v>perk.E06.name</x:v>
+        <x:v>perk.E06.desc</x:v>
       </x:c>
       <x:c r="C500" t="str">
-        <x:v>零钱罐</x:v>
+        <x:v>普通来客的基础金币奖励增加25%，向下取整。</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
       <x:c r="A501" t="n">
-        <x:v>496</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B501" t="str">
-        <x:v>perk.E06.desc</x:v>
+        <x:v>perk.X01.name</x:v>
       </x:c>
       <x:c r="C501" t="str">
-        <x:v>普通来客的基础金币奖励增加25%，向下取整。</x:v>
+        <x:v>退货再加工</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
       <x:c r="A502" t="n">
-        <x:v>497</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B502" t="str">
-        <x:v>perk.X01.name</x:v>
+        <x:v>perk.X01.desc</x:v>
       </x:c>
       <x:c r="C502" t="str">
-        <x:v>退货再加工</x:v>
+        <x:v>每波第一名到达店门的普通来客返回路线30%处，保留生命与状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
       <x:c r="A503" t="n">
-        <x:v>498</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B503" t="str">
-        <x:v>perk.X01.desc</x:v>
+        <x:v>perk.X02.name</x:v>
       </x:c>
       <x:c r="C503" t="str">
-        <x:v>每波第一名到达店门的普通来客返回路线30%处，保留生命与状态。</x:v>
+        <x:v>加固门帘</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
       <x:c r="A504" t="n">
-        <x:v>499</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B504" t="str">
-        <x:v>perk.X02.name</x:v>
+        <x:v>perk.X02.desc</x:v>
       </x:c>
       <x:c r="C504" t="str">
-        <x:v>加固门帘</x:v>
+        <x:v>每波抵挡2点漏客伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
       <x:c r="A505" t="n">
-        <x:v>500</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B505" t="str">
-        <x:v>perk.X02.desc</x:v>
+        <x:v>perk.X03.name</x:v>
       </x:c>
       <x:c r="C505" t="str">
-        <x:v>每波抵挡2点漏客伤害。</x:v>
+        <x:v>门口慢行</x:v>
       </x:c>
     </x:row>
     <x:row r="506">
       <x:c r="A506" t="n">
-        <x:v>501</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B506" t="str">
-        <x:v>perk.X03.name</x:v>
+        <x:v>perk.X03.desc</x:v>
       </x:c>
       <x:c r="C506" t="str">
-        <x:v>门口慢行</x:v>
+        <x:v>每波前3名进入最后20%路段的普通来客，移速降低60%，持续2秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
       <x:c r="A507" t="n">
-        <x:v>502</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B507" t="str">
-        <x:v>perk.X03.desc</x:v>
+        <x:v>perk.X04.name</x:v>
       </x:c>
       <x:c r="C507" t="str">
-        <x:v>每波前3名进入最后20%路段的普通来客，移速降低60%，持续2秒。</x:v>
+        <x:v>收银开火</x:v>
       </x:c>
     </x:row>
     <x:row r="508">
       <x:c r="A508" t="n">
-        <x:v>503</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B508" t="str">
-        <x:v>perk.X04.name</x:v>
+        <x:v>perk.X04.desc</x:v>
       </x:c>
       <x:c r="C508" t="str">
-        <x:v>收银开火</x:v>
+        <x:v>每累计收入100金币，全体攻击间隔缩短25%，持续4秒。出售收入不计入。</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
       <x:c r="A509" t="n">
-        <x:v>504</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B509" t="str">
-        <x:v>perk.X04.desc</x:v>
+        <x:v>perk.X05.name</x:v>
       </x:c>
       <x:c r="C509" t="str">
-        <x:v>每累计收入100金币，全体攻击间隔缩短25%，持续4秒。出售收入不计入。</x:v>
+        <x:v>货架连拆</x:v>
       </x:c>
     </x:row>
     <x:row r="510">
       <x:c r="A510" t="n">
-        <x:v>505</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B510" t="str">
-        <x:v>perk.X05.name</x:v>
+        <x:v>perk.X05.desc</x:v>
       </x:c>
       <x:c r="C510" t="str">
-        <x:v>货架连拆</x:v>
+        <x:v>直接清除货物时，对100范围内其他货物造成其最大生命35%的伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
       <x:c r="A511" t="n">
-        <x:v>506</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B511" t="str">
-        <x:v>perk.X05.desc</x:v>
+        <x:v>perk.X06.name</x:v>
       </x:c>
       <x:c r="C511" t="str">
-        <x:v>直接清除货物时，对100范围内其他货物造成其最大生命35%的伤害。</x:v>
+        <x:v>最后一位</x:v>
       </x:c>
     </x:row>
     <x:row r="512">
       <x:c r="A512" t="n">
-        <x:v>507</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B512" t="str">
-        <x:v>perk.X06.name</x:v>
+        <x:v>perk.X06.desc</x:v>
       </x:c>
       <x:c r="C512" t="str">
-        <x:v>最后一位</x:v>
+        <x:v>本波来客全部出现且只剩一名时，店员直击伤害提高80%。</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
       <x:c r="A513" t="n">
-        <x:v>508</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B513" t="str">
-        <x:v>perk.X06.desc</x:v>
+        <x:v>perk.F01.name</x:v>
       </x:c>
       <x:c r="C513" t="str">
-        <x:v>本波来客全部出现且只剩一名时，店员直击伤害提高80%。</x:v>
+        <x:v>大个子值班</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
       <x:c r="A514" t="n">
-        <x:v>509</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B514" t="str">
-        <x:v>perk.F01.name</x:v>
+        <x:v>perk.F01.desc</x:v>
       </x:c>
       <x:c r="C514" t="str">
-        <x:v>大个子值班</x:v>
+        <x:v>每波随机一名最高等级店员变大，伤害提高80%，射程提高15%，攻击间隔增加20%。</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
       <x:c r="A515" t="n">
-        <x:v>510</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B515" t="str">
-        <x:v>perk.F01.desc</x:v>
+        <x:v>perk.F02.name</x:v>
       </x:c>
       <x:c r="C515" t="str">
-        <x:v>每波随机一名最高等级店员变大，伤害提高80%，射程提高15%，攻击间隔增加20%。</x:v>
+        <x:v>迷你夜班</x:v>
       </x:c>
     </x:row>
     <x:row r="516">
       <x:c r="A516" t="n">
-        <x:v>511</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B516" t="str">
-        <x:v>perk.F02.name</x:v>
+        <x:v>perk.F02.desc</x:v>
       </x:c>
       <x:c r="C516" t="str">
-        <x:v>迷你夜班</x:v>
+        <x:v>全体店员变小，攻击间隔缩短25%，伤害降低10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
       <x:c r="A517" t="n">
-        <x:v>512</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B517" t="str">
-        <x:v>perk.F02.desc</x:v>
+        <x:v>perk.F03.name</x:v>
       </x:c>
       <x:c r="C517" t="str">
-        <x:v>全体店员变小，攻击间隔缩短25%，伤害降低10%。</x:v>
+        <x:v>惊喜包裹</x:v>
       </x:c>
     </x:row>
     <x:row r="518">
       <x:c r="A518" t="n">
-        <x:v>513</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B518" t="str">
-        <x:v>perk.F03.name</x:v>
+        <x:v>perk.F03.desc</x:v>
       </x:c>
       <x:c r="C518" t="str">
-        <x:v>惊喜包裹</x:v>
+        <x:v>每击败12名来客，随机获得20金币、一次100伤害爆炸或2秒减速。每波最多3次，额外攻击不计数。</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
       <x:c r="A519" t="n">
-        <x:v>514</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B519" t="str">
-        <x:v>perk.F03.desc</x:v>
+        <x:v>perk.F04.name</x:v>
       </x:c>
       <x:c r="C519" t="str">
-        <x:v>每击败12名来客，随机获得20金币、一次100伤害爆炸或2秒减速。每波最多3次，额外攻击不计数。</x:v>
+        <x:v>夜班保龄球</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
       <x:c r="A520" t="n">
-        <x:v>515</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B520" t="str">
-        <x:v>perk.F04.name</x:v>
+        <x:v>perk.F04.desc</x:v>
       </x:c>
       <x:c r="C520" t="str">
-        <x:v>夜班保龄球</x:v>
+        <x:v>全队每完成24轮攻击，从店门滚出保龄球，沿路造成100伤害，最多命中8名来客，冷却8秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
       <x:c r="A521" t="n">
-        <x:v>516</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B521" t="str">
-        <x:v>perk.F04.desc</x:v>
+        <x:v>perk.F05.name</x:v>
       </x:c>
       <x:c r="C521" t="str">
-        <x:v>全队每完成24轮攻击，从店门滚出保龄球，沿路造成100伤害，最多命中8名来客，冷却8秒。</x:v>
+        <x:v>天降快递</x:v>
       </x:c>
     </x:row>
     <x:row r="522">
       <x:c r="A522" t="n">
-        <x:v>517</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B522" t="str">
-        <x:v>perk.F05.name</x:v>
+        <x:v>perk.F05.desc</x:v>
       </x:c>
       <x:c r="C522" t="str">
-        <x:v>天降快递</x:v>
+        <x:v>每10秒在最靠近店门的3名来客处落下快递，0.6秒后对40范围造成80伤害。每次快递雨对同一来客只伤害一次。</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
       <x:c r="A523" t="n">
-        <x:v>518</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B523" t="str">
-        <x:v>perk.F05.desc</x:v>
+        <x:v>perk.F06.name</x:v>
       </x:c>
       <x:c r="C523" t="str">
-        <x:v>每10秒在最靠近店门的3名来客处落下快递，0.6秒后对40范围造成80伤害。每次快递雨对同一来客只伤害一次。</x:v>
+        <x:v>口袋鼓鼓</x:v>
       </x:c>
     </x:row>
     <x:row r="524">
       <x:c r="A524" t="n">
-        <x:v>519</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B524" t="str">
-        <x:v>perk.F06.name</x:v>
+        <x:v>perk.F06.desc</x:v>
       </x:c>
       <x:c r="C524" t="str">
-        <x:v>口袋鼓鼓</x:v>
+        <x:v>每波随机一名普通来客生命变为2倍，击败奖励变为4倍。</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
       <x:c r="A525" t="n">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B525" t="str">
-        <x:v>perk.F06.desc</x:v>
+        <x:v>challenge.refreshCount</x:v>
       </x:c>
       <x:c r="C525" t="str">
-        <x:v>每波随机一名普通来客生命变为2倍，击败奖励变为4倍。</x:v>
+        <x:v>本次剩余刷新 {p0}/{p1}</x:v>
       </x:c>
     </x:row>
     <x:row r="526">
       <x:c r="A526" t="n">
-        <x:v>521</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B526" t="str">
-        <x:v>challenge.refreshCount</x:v>
+        <x:v>challenge.refreshLoading</x:v>
       </x:c>
       <x:c r="C526" t="str">
-        <x:v>本次剩余刷新 {p0}/{p1}</x:v>
+        <x:v>广告加载中…</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
       <x:c r="A527" t="n">
-        <x:v>522</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B527" t="str">
-        <x:v>challenge.refreshLoading</x:v>
+        <x:v>challenge.refreshUnavailable</x:v>
       </x:c>
       <x:c r="C527" t="str">
-        <x:v>广告加载中…</x:v>
+        <x:v>广告暂不可用</x:v>
       </x:c>
     </x:row>
     <x:row r="528">
       <x:c r="A528" t="n">
-        <x:v>523</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B528" t="str">
-        <x:v>challenge.refreshUnavailable</x:v>
+        <x:v>challenge.refreshIncomplete</x:v>
       </x:c>
       <x:c r="C528" t="str">
-        <x:v>广告暂不可用</x:v>
+        <x:v>未完整观看，未刷新</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
       <x:c r="A529" t="n">
-        <x:v>524</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B529" t="str">
-        <x:v>challenge.refreshIncomplete</x:v>
+        <x:v>challenge.enhanceStaff</x:v>
       </x:c>
       <x:c r="C529" t="str">
-        <x:v>未完整观看，未刷新</x:v>
+        <x:v>强化 {p0}</x:v>
       </x:c>
     </x:row>
     <x:row r="530">
       <x:c r="A530" t="n">
-        <x:v>525</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B530" t="str">
-        <x:v>challenge.enhanceStaff</x:v>
+        <x:v>ui.redesign.homeTitle</x:v>
       </x:c>
       <x:c r="C530" t="str">
-        <x:v>强化 {p0}</x:v>
+        <x:v>我的便利店</x:v>
       </x:c>
     </x:row>
     <x:row r="531">
       <x:c r="A531" t="n">
-        <x:v>526</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B531" t="str">
-        <x:v>ui.redesign.homeTitle</x:v>
+        <x:v>ui.redesign.book</x:v>
       </x:c>
       <x:c r="C531" t="str">
-        <x:v>我的便利店</x:v>
+        <x:v>图鉴</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
       <x:c r="A532" t="n">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B532" t="str">
-        <x:v>ui.redesign.book</x:v>
+        <x:v>ui.redesign.shop</x:v>
       </x:c>
       <x:c r="C532" t="str">
-        <x:v>图鉴</x:v>
+        <x:v>商店</x:v>
       </x:c>
     </x:row>
     <x:row r="533">
       <x:c r="A533" t="n">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B533" t="str">
-        <x:v>ui.redesign.shop</x:v>
+        <x:v>ui.redesign.rank</x:v>
       </x:c>
       <x:c r="C533" t="str">
-        <x:v>商店</x:v>
+        <x:v>排行榜</x:v>
       </x:c>
     </x:row>
     <x:row r="534">
       <x:c r="A534" t="n">
-        <x:v>529</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B534" t="str">
-        <x:v>ui.redesign.rank</x:v>
+        <x:v>ui.redesign.settings</x:v>
       </x:c>
       <x:c r="C534" t="str">
-        <x:v>排行榜</x:v>
+        <x:v>设置</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
       <x:c r="A535" t="n">
-        <x:v>530</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B535" t="str">
-        <x:v>ui.redesign.settings</x:v>
+        <x:v>ui.redesign.unavailable</x:v>
       </x:c>
       <x:c r="C535" t="str">
-        <x:v>设置</x:v>
+        <x:v>暂未开放</x:v>
       </x:c>
     </x:row>
     <x:row r="536">
       <x:c r="A536" t="n">
-        <x:v>531</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B536" t="str">
-        <x:v>ui.redesign.unavailable</x:v>
+        <x:v>ui.redesign.loading</x:v>
       </x:c>
       <x:c r="C536" t="str">
-        <x:v>暂未开放</x:v>
+        <x:v>LOADING...</x:v>
       </x:c>
     </x:row>
     <x:row r="537">
       <x:c r="A537" t="n">
-        <x:v>532</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B537" t="str">
-        <x:v>ui.redesign.loading</x:v>
+        <x:v>ui.redesign.loadingFailed</x:v>
       </x:c>
       <x:c r="C537" t="str">
-        <x:v>正在加载 {p0}%</x:v>
+        <x:v>加载失败，点击重试</x:v>
       </x:c>
     </x:row>
     <x:row r="538">
       <x:c r="A538" t="n">
-        <x:v>533</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B538" t="str">
-        <x:v>ui.redesign.loadingFailed</x:v>
+        <x:v>ui.redesign.select</x:v>
       </x:c>
       <x:c r="C538" t="str">
-        <x:v>加载失败，点击重试</x:v>
+        <x:v>选择</x:v>
       </x:c>
     </x:row>
     <x:row r="539">
       <x:c r="A539" t="n">
-        <x:v>534</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B539" t="str">
-        <x:v>ui.redesign.select</x:v>
+        <x:v>ui.redesign.staff</x:v>
       </x:c>
       <x:c r="C539" t="str">
-        <x:v>选择</x:v>
+        <x:v>店员</x:v>
       </x:c>
     </x:row>
     <x:row r="540">
       <x:c r="A540" t="n">
-        <x:v>535</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B540" t="str">
-        <x:v>ui.redesign.staff</x:v>
+        <x:v>ui.redesign.monsters</x:v>
       </x:c>
       <x:c r="C540" t="str">
-        <x:v>店员</x:v>
+        <x:v>怪物</x:v>
       </x:c>
     </x:row>
     <x:row r="541">
       <x:c r="A541" t="n">
-        <x:v>536</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B541" t="str">
-        <x:v>ui.redesign.monsters</x:v>
+        <x:v>ui.redesign.goods</x:v>
       </x:c>
       <x:c r="C541" t="str">
-        <x:v>怪物</x:v>
+        <x:v>商品</x:v>
       </x:c>
     </x:row>
     <x:row r="542">
       <x:c r="A542" t="n">
-        <x:v>537</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B542" t="str">
-        <x:v>ui.redesign.goods</x:v>
+        <x:v>ui.redesign.progress</x:v>
       </x:c>
       <x:c r="C542" t="str">
-        <x:v>商品</x:v>
+        <x:v>{p0}</x:v>
       </x:c>
     </x:row>
     <x:row r="543">
       <x:c r="A543" t="n">
-        <x:v>538</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B543" t="str">
-        <x:v>ui.redesign.progress</x:v>
+        <x:v>ui.redesign.collection</x:v>
       </x:c>
       <x:c r="C543" t="str">
-        <x:v>{p0}/{p1}关</x:v>
+        <x:v>{p0}</x:v>
       </x:c>
     </x:row>
     <x:row r="544">
       <x:c r="A544" t="n">
-        <x:v>539</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B544" t="str">
-        <x:v>ui.redesign.collection</x:v>
+        <x:v>ui.redesign.pickHint</x:v>
       </x:c>
       <x:c r="C544" t="str">
-        <x:v>收录 {p0}</x:v>
+        <x:v>点击头像选择或取消</x:v>
       </x:c>
     </x:row>
     <x:row r="545">
       <x:c r="A545" t="n">
-        <x:v>540</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B545" t="str">
-        <x:v>ui.redesign.pickHint</x:v>
+        <x:v>ui.redesign.pickFull</x:v>
       </x:c>
       <x:c r="C545" t="str">
-        <x:v>点击头像选择或取消</x:v>
+        <x:v>请先取消一名店员</x:v>
       </x:c>
     </x:row>
     <x:row r="546">
       <x:c r="A546" t="n">
-        <x:v>541</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B546" t="str">
-        <x:v>ui.redesign.pickFull</x:v>
+        <x:v>ui.redesign.goodsCategory</x:v>
       </x:c>
       <x:c r="C546" t="str">
-        <x:v>请先取消一名店员</x:v>
+        <x:v>便利店商品</x:v>
       </x:c>
     </x:row>
     <x:row r="547">
       <x:c r="A547" t="n">
-        <x:v>542</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B547" t="str">
-        <x:v>ui.redesign.goodsCategory</x:v>
+        <x:v>ui.redesign.goodsUnlock</x:v>
       </x:c>
       <x:c r="C547" t="str">
-        <x:v>便利店商品</x:v>
+        <x:v>第 {p0} 关解锁</x:v>
       </x:c>
     </x:row>
     <x:row r="548">
       <x:c r="A548" t="n">
-        <x:v>543</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B548" t="str">
-        <x:v>ui.redesign.goodsUnlock</x:v>
+        <x:v>goods.cola.name</x:v>
       </x:c>
       <x:c r="C548" t="str">
-        <x:v>第 {p0} 关解锁</x:v>
+        <x:v>可乐</x:v>
       </x:c>
     </x:row>
     <x:row r="549">
       <x:c r="A549" t="n">
-        <x:v>544</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B549" t="str">
-        <x:v>goods.cola.name</x:v>
+        <x:v>goods.cola.description</x:v>
       </x:c>
       <x:c r="C549" t="str">
-        <x:v>可乐</x:v>
+        <x:v>冰凉爽口</x:v>
       </x:c>
     </x:row>
     <x:row r="550">
       <x:c r="A550" t="n">
-        <x:v>545</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B550" t="str">
-        <x:v>goods.cola.description</x:v>
+        <x:v>goods.cola.story</x:v>
       </x:c>
       <x:c r="C550" t="str">
-        <x:v>冰凉爽口</x:v>
+        <x:v>一打开罐子，细密的气泡就从杯沿冒出来。</x:v>
       </x:c>
     </x:row>
     <x:row r="551">
       <x:c r="A551" t="n">
-        <x:v>546</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B551" t="str">
-        <x:v>goods.cola.story</x:v>
+        <x:v>goods.bread.name</x:v>
       </x:c>
       <x:c r="C551" t="str">
-        <x:v>一打开罐子，细密的气泡就从杯沿冒出来。</x:v>
+        <x:v>面包</x:v>
       </x:c>
     </x:row>
     <x:row r="552">
       <x:c r="A552" t="n">
-        <x:v>547</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B552" t="str">
-        <x:v>goods.bread.name</x:v>
+        <x:v>goods.bread.description</x:v>
       </x:c>
       <x:c r="C552" t="str">
-        <x:v>面包</x:v>
+        <x:v>松软香甜</x:v>
       </x:c>
     </x:row>
     <x:row r="553">
       <x:c r="A553" t="n">
-        <x:v>548</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B553" t="str">
-        <x:v>goods.bread.description</x:v>
+        <x:v>goods.bread.story</x:v>
       </x:c>
       <x:c r="C553" t="str">
-        <x:v>松软香甜</x:v>
+        <x:v>清晨烤好的面包，在夜班也能带来一点温暖。</x:v>
       </x:c>
     </x:row>
     <x:row r="554">
       <x:c r="A554" t="n">
-        <x:v>549</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B554" t="str">
-        <x:v>goods.bread.story</x:v>
+        <x:v>goods.noodles.name</x:v>
       </x:c>
       <x:c r="C554" t="str">
-        <x:v>清晨烤好的面包，在夜班也能带来一点温暖。</x:v>
+        <x:v>泡面</x:v>
       </x:c>
     </x:row>
     <x:row r="555">
       <x:c r="A555" t="n">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B555" t="str">
-        <x:v>goods.noodles.name</x:v>
+        <x:v>goods.noodles.description</x:v>
       </x:c>
       <x:c r="C555" t="str">
-        <x:v>泡面</x:v>
+        <x:v>热气腾腾</x:v>
       </x:c>
     </x:row>
     <x:row r="556">
       <x:c r="A556" t="n">
-        <x:v>551</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B556" t="str">
-        <x:v>goods.noodles.description</x:v>
+        <x:v>goods.noodles.story</x:v>
       </x:c>
       <x:c r="C556" t="str">
-        <x:v>热气腾腾</x:v>
+        <x:v>倒上热水，等一会儿，就是一顿夜班小餐。</x:v>
       </x:c>
     </x:row>
     <x:row r="557">
       <x:c r="A557" t="n">
-        <x:v>552</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B557" t="str">
-        <x:v>goods.noodles.story</x:v>
+        <x:v>goods.milk.name</x:v>
       </x:c>
       <x:c r="C557" t="str">
-        <x:v>倒上热水，等一会儿，就是一顿夜班小餐。</x:v>
+        <x:v>牛奶</x:v>
       </x:c>
     </x:row>
     <x:row r="558">
       <x:c r="A558" t="n">
-        <x:v>553</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B558" t="str">
-        <x:v>goods.milk.name</x:v>
+        <x:v>goods.milk.description</x:v>
       </x:c>
       <x:c r="C558" t="str">
-        <x:v>牛奶</x:v>
+        <x:v>醇香顺滑</x:v>
       </x:c>
     </x:row>
     <x:row r="559">
       <x:c r="A559" t="n">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B559" t="str">
-        <x:v>goods.milk.description</x:v>
+        <x:v>goods.milk.story</x:v>
       </x:c>
       <x:c r="C559" t="str">
-        <x:v>醇香顺滑</x:v>
+        <x:v>蓝白小盒里装着一份简单的日常。</x:v>
       </x:c>
     </x:row>
     <x:row r="560">
       <x:c r="A560" t="n">
-        <x:v>555</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B560" t="str">
-        <x:v>goods.milk.story</x:v>
+        <x:v>goods.chips.name</x:v>
       </x:c>
       <x:c r="C560" t="str">
-        <x:v>蓝白小盒里装着一份简单的日常。</x:v>
+        <x:v>薯片</x:v>
       </x:c>
     </x:row>
     <x:row r="561">
       <x:c r="A561" t="n">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B561" t="str">
-        <x:v>goods.chips.name</x:v>
+        <x:v>goods.chips.description</x:v>
       </x:c>
       <x:c r="C561" t="str">
-        <x:v>薯片</x:v>
+        <x:v>咔嚓酥脆</x:v>
       </x:c>
     </x:row>
     <x:row r="562">
       <x:c r="A562" t="n">
-        <x:v>557</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B562" t="str">
-        <x:v>goods.chips.description</x:v>
+        <x:v>goods.chips.story</x:v>
       </x:c>
       <x:c r="C562" t="str">
-        <x:v>咔嚓酥脆</x:v>
+        <x:v>袋子里总藏着一片形状特别的薯片。</x:v>
       </x:c>
     </x:row>
     <x:row r="563">
       <x:c r="A563" t="n">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B563" t="str">
-        <x:v>goods.chips.story</x:v>
+        <x:v>goods.cookies.name</x:v>
       </x:c>
       <x:c r="C563" t="str">
-        <x:v>袋子里总藏着一片形状特别的薯片。</x:v>
+        <x:v>饼干</x:v>
       </x:c>
     </x:row>
     <x:row r="564">
       <x:c r="A564" t="n">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B564" t="str">
-        <x:v>goods.cookies.name</x:v>
+        <x:v>goods.cookies.description</x:v>
       </x:c>
       <x:c r="C564" t="str">
-        <x:v>饼干</x:v>
+        <x:v>香酥可口</x:v>
       </x:c>
     </x:row>
     <x:row r="565">
       <x:c r="A565" t="n">
-        <x:v>560</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B565" t="str">
-        <x:v>goods.cookies.description</x:v>
+        <x:v>goods.cookies.story</x:v>
       </x:c>
       <x:c r="C565" t="str">
-        <x:v>香酥可口</x:v>
+        <x:v>小盒饼干很适合和忙完夜班的朋友分享。</x:v>
       </x:c>
     </x:row>
     <x:row r="566">
       <x:c r="A566" t="n">
-        <x:v>561</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B566" t="str">
-        <x:v>goods.cookies.story</x:v>
+        <x:v>goods.jelly.name</x:v>
       </x:c>
       <x:c r="C566" t="str">
-        <x:v>小盒饼干很适合和忙完夜班的朋友分享。</x:v>
+        <x:v>果冻</x:v>
       </x:c>
     </x:row>
     <x:row r="567">
       <x:c r="A567" t="n">
-        <x:v>562</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B567" t="str">
-        <x:v>goods.jelly.name</x:v>
+        <x:v>goods.jelly.description</x:v>
       </x:c>
       <x:c r="C567" t="str">
-        <x:v>果冻</x:v>
+        <x:v>清甜弹软</x:v>
       </x:c>
     </x:row>
     <x:row r="568">
       <x:c r="A568" t="n">
-        <x:v>563</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B568" t="str">
-        <x:v>goods.jelly.description</x:v>
+        <x:v>goods.jelly.story</x:v>
       </x:c>
       <x:c r="C568" t="str">
-        <x:v>清甜弹软</x:v>
+        <x:v>红色和绿色的小杯，摆在货架上像两颗宝石。</x:v>
       </x:c>
     </x:row>
     <x:row r="569">
       <x:c r="A569" t="n">
-        <x:v>564</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B569" t="str">
-        <x:v>goods.jelly.story</x:v>
+        <x:v>goods.water.name</x:v>
       </x:c>
       <x:c r="C569" t="str">
-        <x:v>红色和绿色的小杯，摆在货架上像两颗宝石。</x:v>
+        <x:v>矿泉水</x:v>
       </x:c>
     </x:row>
     <x:row r="570">
       <x:c r="A570" t="n">
-        <x:v>565</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B570" t="str">
-        <x:v>goods.water.name</x:v>
+        <x:v>goods.water.description</x:v>
       </x:c>
       <x:c r="C570" t="str">
-        <x:v>矿泉水</x:v>
+        <x:v>清澈解渴</x:v>
       </x:c>
     </x:row>
     <x:row r="571">
       <x:c r="A571" t="n">
-        <x:v>566</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B571" t="str">
-        <x:v>goods.water.description</x:v>
+        <x:v>goods.water.story</x:v>
       </x:c>
       <x:c r="C571" t="str">
-        <x:v>清澈解渴</x:v>
+        <x:v>店员补货时，总会给水瓶排得整整齐齐。</x:v>
       </x:c>
     </x:row>
     <x:row r="572">
       <x:c r="A572" t="n">
-        <x:v>567</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B572" t="str">
-        <x:v>goods.water.story</x:v>
+        <x:v>goods.rice.name</x:v>
       </x:c>
       <x:c r="C572" t="str">
-        <x:v>店员补货时，总会给水瓶排得整整齐齐。</x:v>
+        <x:v>饭团</x:v>
       </x:c>
     </x:row>
     <x:row r="573">
       <x:c r="A573" t="n">
-        <x:v>568</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B573" t="str">
-        <x:v>goods.rice.name</x:v>
+        <x:v>goods.rice.description</x:v>
       </x:c>
       <x:c r="C573" t="str">
-        <x:v>饭团</x:v>
+        <x:v>一口满足</x:v>
       </x:c>
     </x:row>
     <x:row r="574">
       <x:c r="A574" t="n">
-        <x:v>569</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B574" t="str">
-        <x:v>goods.rice.description</x:v>
+        <x:v>goods.rice.story</x:v>
       </x:c>
       <x:c r="C574" t="str">
-        <x:v>一口满足</x:v>
+        <x:v>小小的三角饭团，藏着夜班便当的心意。</x:v>
       </x:c>
     </x:row>
     <x:row r="575" ht="28" customHeight="1">
       <x:c r="A575" t="n">
-        <x:v>570</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B575" t="str">
-        <x:v>goods.rice.story</x:v>
+        <x:v>ui.redesign.supplyHint</x:v>
       </x:c>
       <x:c r="C575" t="str">
-        <x:v>小小的三角饭团，藏着夜班便当的心意。</x:v>
+        <x:v>请选择一份补给，助你轻松度过夜班！</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R14f84813dad14e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R60f631202af94f89"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6653,6 +6653,17 @@
         <x:v>请选择一份补给，助你轻松度过夜班！</x:v>
       </x:c>
     </x:row>
+    <x:row r="576" ht="36" customHeight="1">
+      <x:c r="A576" t="n">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B576" t="str">
+        <x:v>ui.homeGold</x:v>
+      </x:c>
+      <x:c r="C576" t="str">
+        <x:v>{p0}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R60f631202af94f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R4dbab969fd3a4bce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6664,6 +6664,545 @@
         <x:v>{p0}</x:v>
       </x:c>
     </x:row>
+    <x:row r="577">
+      <x:c r="A577" t="n">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B577" t="str">
+        <x:v>shop.title</x:v>
+      </x:c>
+      <x:c r="C577" t="str">
+        <x:v>我的便利店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578">
+      <x:c r="A578" t="n">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B578" t="str">
+        <x:v>shop.balance</x:v>
+      </x:c>
+      <x:c r="C578" t="str">
+        <x:v>{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579">
+      <x:c r="A579" t="n">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B579" t="str">
+        <x:v>shop.summary</x:v>
+      </x:c>
+      <x:c r="C579" t="str">
+        <x:v>营业中  ·  已接待 {p0} 位顾客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580">
+      <x:c r="A580" t="n">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B580" t="str">
+        <x:v>shop.staffTab</x:v>
+      </x:c>
+      <x:c r="C580" t="str">
+        <x:v>店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581">
+      <x:c r="A581" t="n">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B581" t="str">
+        <x:v>shop.upgradeTab</x:v>
+      </x:c>
+      <x:c r="C581" t="str">
+        <x:v>改进</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582">
+      <x:c r="A582" t="n">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B582" t="str">
+        <x:v>shop.goodsTab</x:v>
+      </x:c>
+      <x:c r="C582" t="str">
+        <x:v>商品</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583">
+      <x:c r="A583" t="n">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B583" t="str">
+        <x:v>shop.hire</x:v>
+      </x:c>
+      <x:c r="C583" t="str">
+        <x:v>雇佣 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584">
+      <x:c r="A584" t="n">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B584" t="str">
+        <x:v>shop.hired</x:v>
+      </x:c>
+      <x:c r="C584" t="str">
+        <x:v>已雇佣</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585">
+      <x:c r="A585" t="n">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B585" t="str">
+        <x:v>shop.locked</x:v>
+      </x:c>
+      <x:c r="C585" t="str">
+        <x:v>第{p0}关解锁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586">
+      <x:c r="A586" t="n">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B586" t="str">
+        <x:v>shop.upgrade</x:v>
+      </x:c>
+      <x:c r="C586" t="str">
+        <x:v>改进 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587">
+      <x:c r="A587" t="n">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B587" t="str">
+        <x:v>shop.max</x:v>
+      </x:c>
+      <x:c r="C587" t="str">
+        <x:v>已满级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588">
+      <x:c r="A588" t="n">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B588" t="str">
+        <x:v>shop.tier</x:v>
+      </x:c>
+      <x:c r="C588" t="str">
+        <x:v>{p0} Lv.{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589">
+      <x:c r="A589" t="n">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B589" t="str">
+        <x:v>shop.product</x:v>
+      </x:c>
+      <x:c r="C589" t="str">
+        <x:v>{p0}  ·  {p1}金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590">
+      <x:c r="A590" t="n">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B590" t="str">
+        <x:v>shop.inventory</x:v>
+      </x:c>
+      <x:c r="C590" t="str">
+        <x:v>库存 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591">
+      <x:c r="A591" t="n">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B591" t="str">
+        <x:v>shop.closedShelf</x:v>
+      </x:c>
+      <x:c r="C591" t="str">
+        <x:v>新增货架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592">
+      <x:c r="A592" t="n">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B592" t="str">
+        <x:v>shop.offline</x:v>
+      </x:c>
+      <x:c r="C592" t="str">
+        <x:v>离线营业 +{p0}金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593">
+      <x:c r="A593" t="n">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B593" t="str">
+        <x:v>shop.insufficient</x:v>
+      </x:c>
+      <x:c r="C593" t="str">
+        <x:v>金币不足</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594">
+      <x:c r="A594" t="n">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B594" t="str">
+        <x:v>shop.welcome</x:v>
+      </x:c>
+      <x:c r="C594" t="str">
+        <x:v>开店礼金 +{p0}金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595">
+      <x:c r="A595" t="n">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B595" t="str">
+        <x:v>shop.sold</x:v>
+      </x:c>
+      <x:c r="C595" t="str">
+        <x:v>成交 +{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596">
+      <x:c r="A596" t="n">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B596" t="str">
+        <x:v>shop.auto</x:v>
+      </x:c>
+      <x:c r="C596" t="str">
+        <x:v>自动营业</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597">
+      <x:c r="A597" t="n">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B597" t="str">
+        <x:v>shop.order</x:v>
+      </x:c>
+      <x:c r="C597" t="str">
+        <x:v>{p0}件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598">
+      <x:c r="A598" t="n">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B598" t="str">
+        <x:v>shop.goodsCount</x:v>
+      </x:c>
+      <x:c r="C598" t="str">
+        <x:v>已解锁商品 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599">
+      <x:c r="A599" t="n">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B599" t="str">
+        <x:v>shop.goodsLocked</x:v>
+      </x:c>
+      <x:c r="C599" t="str">
+        <x:v>通关第{p0}关解锁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600">
+      <x:c r="A600" t="n">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B600" t="str">
+        <x:v>shop.goodsUnlocked</x:v>
+      </x:c>
+      <x:c r="C600" t="str">
+        <x:v>已解锁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601">
+      <x:c r="A601" t="n">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B601" t="str">
+        <x:v>shop.pickGoods</x:v>
+      </x:c>
+      <x:c r="C601" t="str">
+        <x:v>上架商品</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602">
+      <x:c r="A602" t="n">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B602" t="str">
+        <x:v>shop.price</x:v>
+      </x:c>
+      <x:c r="C602" t="str">
+        <x:v>售价 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603">
+      <x:c r="A603" t="n">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B603" t="str">
+        <x:v>shop.purchaseDenied</x:v>
+      </x:c>
+      <x:c r="C603" t="str">
+        <x:v>暂时无法购买</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604">
+      <x:c r="A604" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B604" t="str">
+        <x:v>shop.staff.sprout</x:v>
+      </x:c>
+      <x:c r="C604" t="str">
+        <x:v>自动收银与补货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605">
+      <x:c r="A605" t="n">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B605" t="str">
+        <x:v>shop.staff.frost</x:v>
+      </x:c>
+      <x:c r="C605" t="str">
+        <x:v>冷藏商品售价 +20%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606">
+      <x:c r="A606" t="n">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B606" t="str">
+        <x:v>shop.staff.bloom</x:v>
+      </x:c>
+      <x:c r="C606" t="str">
+        <x:v>双件订单概率 +15%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607">
+      <x:c r="A607" t="n">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B607" t="str">
+        <x:v>shop.staff.scope</x:v>
+      </x:c>
+      <x:c r="C607" t="str">
+        <x:v>小费概率 +25%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608">
+      <x:c r="A608" t="n">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B608" t="str">
+        <x:v>shop.staff.spark</x:v>
+      </x:c>
+      <x:c r="C608" t="str">
+        <x:v>收银效率 +25%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609">
+      <x:c r="A609" t="n">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B609" t="str">
+        <x:v>shop.staff.ember</x:v>
+      </x:c>
+      <x:c r="C609" t="str">
+        <x:v>热食商品售价 +20%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610">
+      <x:c r="A610" t="n">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B610" t="str">
+        <x:v>shop.staff.mint</x:v>
+      </x:c>
+      <x:c r="C610" t="str">
+        <x:v>补货效率 +40%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611">
+      <x:c r="A611" t="n">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B611" t="str">
+        <x:v>shop.staff.fan</x:v>
+      </x:c>
+      <x:c r="C611" t="str">
+        <x:v>来客效率 +25%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612">
+      <x:c r="A612" t="n">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B612" t="str">
+        <x:v>shop.upgrade.checkout</x:v>
+      </x:c>
+      <x:c r="C612" t="str">
+        <x:v>收银提速</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613">
+      <x:c r="A613" t="n">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B613" t="str">
+        <x:v>shop.upgrade.checkout.1</x:v>
+      </x:c>
+      <x:c r="C613" t="str">
+        <x:v>收银效率 +20%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614">
+      <x:c r="A614" t="n">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B614" t="str">
+        <x:v>shop.upgrade.checkout.2</x:v>
+      </x:c>
+      <x:c r="C614" t="str">
+        <x:v>收银效率 +45%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615">
+      <x:c r="A615" t="n">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B615" t="str">
+        <x:v>shop.upgrade.checkout.3</x:v>
+      </x:c>
+      <x:c r="C615" t="str">
+        <x:v>收银效率 +75%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616">
+      <x:c r="A616" t="n">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B616" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="C616" t="str">
+        <x:v>补货提速</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617">
+      <x:c r="A617" t="n">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B617" t="str">
+        <x:v>shop.upgrade.restock.1</x:v>
+      </x:c>
+      <x:c r="C617" t="str">
+        <x:v>补货效率 +30%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618">
+      <x:c r="A618" t="n">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="B618" t="str">
+        <x:v>shop.upgrade.restock.2</x:v>
+      </x:c>
+      <x:c r="C618" t="str">
+        <x:v>补货效率 +65%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619">
+      <x:c r="A619" t="n">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B619" t="str">
+        <x:v>shop.upgrade.restock.3</x:v>
+      </x:c>
+      <x:c r="C619" t="str">
+        <x:v>补货效率 +100%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620">
+      <x:c r="A620" t="n">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="B620" t="str">
+        <x:v>shop.upgrade.shelves</x:v>
+      </x:c>
+      <x:c r="C620" t="str">
+        <x:v>增加货架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621">
+      <x:c r="A621" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B621" t="str">
+        <x:v>shop.upgrade.shelves.1</x:v>
+      </x:c>
+      <x:c r="C621" t="str">
+        <x:v>货架增加至3组</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622">
+      <x:c r="A622" t="n">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B622" t="str">
+        <x:v>shop.upgrade.shelves.2</x:v>
+      </x:c>
+      <x:c r="C622" t="str">
+        <x:v>货架增加至4组</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623">
+      <x:c r="A623" t="n">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="B623" t="str">
+        <x:v>shop.back</x:v>
+      </x:c>
+      <x:c r="C623" t="str">
+        <x:v>返回</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624">
+      <x:c r="A624" t="n">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="B624" t="str">
+        <x:v>shop.previous</x:v>
+      </x:c>
+      <x:c r="C624" t="str">
+        <x:v>‹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625">
+      <x:c r="A625" t="n">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="B625" t="str">
+        <x:v>shop.next</x:v>
+      </x:c>
+      <x:c r="C625" t="str">
+        <x:v>›</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R4dbab969fd3a4bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R63e846f628694493"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7203,6 +7203,83 @@
         <x:v>›</x:v>
       </x:c>
     </x:row>
+    <x:row r="626">
+      <x:c r="A626" t="n">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="B626" t="str">
+        <x:v>shop.manage</x:v>
+      </x:c>
+      <x:c r="C626" t="str">
+        <x:v>管理</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627">
+      <x:c r="A627" t="n">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="B627" t="str">
+        <x:v>shop.staffMenu</x:v>
+      </x:c>
+      <x:c r="C627" t="str">
+        <x:v>雇佣店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628">
+      <x:c r="A628" t="n">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="B628" t="str">
+        <x:v>shop.upgradeMenu</x:v>
+      </x:c>
+      <x:c r="C628" t="str">
+        <x:v>设备改进</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629">
+      <x:c r="A629" t="n">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="B629" t="str">
+        <x:v>shop.goodsMenu</x:v>
+      </x:c>
+      <x:c r="C629" t="str">
+        <x:v>商品上架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630">
+      <x:c r="A630" t="n">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="B630" t="str">
+        <x:v>shop.currentGoods</x:v>
+      </x:c>
+      <x:c r="C630" t="str">
+        <x:v>已上架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631">
+      <x:c r="A631" t="n">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B631" t="str">
+        <x:v>shop.shelfNumber</x:v>
+      </x:c>
+      <x:c r="C631" t="str">
+        <x:v>货架 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632">
+      <x:c r="A632" t="n">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="B632" t="str">
+        <x:v>shop.coins</x:v>
+      </x:c>
+      <x:c r="C632" t="str">
+        <x:v>金币 {p0}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R63e846f628694493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R81c182d3360c45a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3424,7 +3424,7 @@
         <x:v>challenge.return</x:v>
       </x:c>
       <x:c r="C282" s="16" t="str">
-        <x:v>返回首页</x:v>
+        <x:v>返回挑战</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="58" customHeight="1">
@@ -7278,6 +7278,259 @@
       </x:c>
       <x:c r="C632" t="str">
         <x:v>金币 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633">
+      <x:c r="A633" t="n">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="B633" t="str">
+        <x:v>topics.title</x:v>
+      </x:c>
+      <x:c r="C633" t="str">
+        <x:v>挑战夜班</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634">
+      <x:c r="A634" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="B634" t="str">
+        <x:v>topics.summary</x:v>
+      </x:c>
+      <x:c r="C634" t="str">
+        <x:v>15波夜班 · 10次补给 · 自选4名店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635">
+      <x:c r="A635" t="n">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="B635" t="str">
+        <x:v>topics.play</x:v>
+      </x:c>
+      <x:c r="C635" t="str">
+        <x:v>开始夜班</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636">
+      <x:c r="A636" t="n">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="B636" t="str">
+        <x:v>topics.replay</x:v>
+      </x:c>
+      <x:c r="C636" t="str">
+        <x:v>再次挑战</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637">
+      <x:c r="A637" t="n">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="B637" t="str">
+        <x:v>topics.locked</x:v>
+      </x:c>
+      <x:c r="C637" t="str">
+        <x:v>通关「{p0}」解锁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638">
+      <x:c r="A638" t="n">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="B638" t="str">
+        <x:v>topics.number</x:v>
+      </x:c>
+      <x:c r="C638" t="str">
+        <x:v>夜班 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639">
+      <x:c r="A639" t="n">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="B639" t="str">
+        <x:v>topics.next</x:v>
+      </x:c>
+      <x:c r="C639" t="str">
+        <x:v>下个夜班</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640">
+      <x:c r="A640" t="n">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="B640" t="str">
+        <x:v>topics.allClear</x:v>
+      </x:c>
+      <x:c r="C640" t="str">
+        <x:v>全部夜班已完成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641">
+      <x:c r="A641" t="n">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="B641" t="str">
+        <x:v>topics.opened</x:v>
+      </x:c>
+      <x:c r="C641" t="str">
+        <x:v>已解锁：{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642">
+      <x:c r="A642" t="n">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="B642" t="str">
+        <x:v>topics.list</x:v>
+      </x:c>
+      <x:c r="C642" t="str">
+        <x:v>返回挑战</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643">
+      <x:c r="A643" t="n">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="B643" t="str">
+        <x:v>topics.prepare</x:v>
+      </x:c>
+      <x:c r="C643" t="str">
+        <x:v>选择出战店员</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644">
+      <x:c r="A644" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="B644" t="str">
+        <x:v>topics.opening.title</x:v>
+      </x:c>
+      <x:c r="C644" t="str">
+        <x:v>夜班试营业</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645">
+      <x:c r="A645" t="n">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="B645" t="str">
+        <x:v>topics.opening.rule</x:v>
+      </x:c>
+      <x:c r="C645" t="str">
+        <x:v>经典夜班，自选店员与补给。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646">
+      <x:c r="A646" t="n">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="B646" t="str">
+        <x:v>topics.express.title</x:v>
+      </x:c>
+      <x:c r="C646" t="str">
+        <x:v>急件专场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647">
+      <x:c r="A647" t="n">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="B647" t="str">
+        <x:v>topics.express.rule</x:v>
+      </x:c>
+      <x:c r="C647" t="str">
+        <x:v>每波开场6秒，攻速提高35%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648">
+      <x:c r="A648" t="n">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="B648" t="str">
+        <x:v>topics.warehouse.title</x:v>
+      </x:c>
+      <x:c r="C648" t="str">
+        <x:v>仓库清点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649">
+      <x:c r="A649" t="n">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="B649" t="str">
+        <x:v>topics.warehouse.rule</x:v>
+      </x:c>
+      <x:c r="C649" t="str">
+        <x:v>清除障碍时，对附近障碍造成伤害。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650">
+      <x:c r="A650" t="n">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="B650" t="str">
+        <x:v>topics.coins.title</x:v>
+      </x:c>
+      <x:c r="C650" t="str">
+        <x:v>零钱狂欢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651">
+      <x:c r="A651" t="n">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="B651" t="str">
+        <x:v>topics.coins.rule</x:v>
+      </x:c>
+      <x:c r="C651" t="str">
+        <x:v>普通来客的基础金币奖励增加25%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652">
+      <x:c r="A652" t="n">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="B652" t="str">
+        <x:v>topics.mini.title</x:v>
+      </x:c>
+      <x:c r="C652" t="str">
+        <x:v>迷你流水线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653">
+      <x:c r="A653" t="n">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="B653" t="str">
+        <x:v>topics.mini.rule</x:v>
+      </x:c>
+      <x:c r="C653" t="str">
+        <x:v>店员变小，攻速提高25%，伤害降低10%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654">
+      <x:c r="A654" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="B654" t="str">
+        <x:v>topics.midnight.title</x:v>
+      </x:c>
+      <x:c r="C654" t="str">
+        <x:v>午夜压轴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655">
+      <x:c r="A655" t="n">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="B655" t="str">
+        <x:v>topics.midnight.rule</x:v>
+      </x:c>
+      <x:c r="C655" t="str">
+        <x:v>每波一位高等级店员变大，伤害与射程提高。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R81c182d3360c45a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R3657d13e7aa8467f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7533,6 +7533,28 @@
         <x:v>每波一位高等级店员变大，伤害与射程提高。</x:v>
       </x:c>
     </x:row>
+    <x:row r="656">
+      <x:c r="A656" t="n">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="B656" t="str">
+        <x:v>shop.checkingOut</x:v>
+      </x:c>
+      <x:c r="C656" t="str">
+        <x:v>收银中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657">
+      <x:c r="A657" t="n">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="B657" t="str">
+        <x:v>shop.restocking</x:v>
+      </x:c>
+      <x:c r="C657" t="str">
+        <x:v>补货中</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R3657d13e7aa8467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Ra9a8d089c9834e2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7555,6 +7555,611 @@
         <x:v>补货中</x:v>
       </x:c>
     </x:row>
+    <x:row r="658">
+      <x:c r="A658" t="n">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="B658" t="str">
+        <x:v>shop.stage.1</x:v>
+      </x:c>
+      <x:c r="C658" t="str">
+        <x:v>街角小店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659">
+      <x:c r="A659" t="n">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="B659" t="str">
+        <x:v>shop.stage.2</x:v>
+      </x:c>
+      <x:c r="C659" t="str">
+        <x:v>社区便利店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660">
+      <x:c r="A660" t="n">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="B660" t="str">
+        <x:v>shop.stage.3</x:v>
+      </x:c>
+      <x:c r="C660" t="str">
+        <x:v>人气便利店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661">
+      <x:c r="A661" t="n">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="B661" t="str">
+        <x:v>shop.stage.4</x:v>
+      </x:c>
+      <x:c r="C661" t="str">
+        <x:v>热闹便利店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662">
+      <x:c r="A662" t="n">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="B662" t="str">
+        <x:v>shop.stageSummary</x:v>
+      </x:c>
+      <x:c r="C662" t="str">
+        <x:v>{p0} · 已接待 {p1} 位顾客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663">
+      <x:c r="A663" t="n">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="B663" t="str">
+        <x:v>shop.needStage</x:v>
+      </x:c>
+      <x:c r="C663" t="str">
+        <x:v>扩店至{p0}后开放</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664">
+      <x:c r="A664" t="n">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="B664" t="str">
+        <x:v>shop.needSold</x:v>
+      </x:c>
+      <x:c r="C664" t="str">
+        <x:v>接待{p0}/{p1}位顾客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665">
+      <x:c r="A665" t="n">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="B665" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="C665" t="str">
+        <x:v>{p0} → {p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666">
+      <x:c r="A666" t="n">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="B666" t="str">
+        <x:v>shop.upgrade.capacity</x:v>
+      </x:c>
+      <x:c r="C666" t="str">
+        <x:v>货架容量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667">
+      <x:c r="A667" t="n">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="B667" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="C667" t="str">
+        <x:v>街坊口碑</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668">
+      <x:c r="A668" t="n">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="B668" t="str">
+        <x:v>shop.upgrade.service</x:v>
+      </x:c>
+      <x:c r="C668" t="str">
+        <x:v>购物服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669">
+      <x:c r="A669" t="n">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="B669" t="str">
+        <x:v>shop.unit.seconds</x:v>
+      </x:c>
+      <x:c r="C669" t="str">
+        <x:v>{p0}秒/单</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670">
+      <x:c r="A670" t="n">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="B670" t="str">
+        <x:v>shop.unit.restock</x:v>
+      </x:c>
+      <x:c r="C670" t="str">
+        <x:v>{p0}秒 · 每次{p1}件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671">
+      <x:c r="A671" t="n">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="B671" t="str">
+        <x:v>shop.unit.capacity</x:v>
+      </x:c>
+      <x:c r="C671" t="str">
+        <x:v>每架{p0}件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672">
+      <x:c r="A672" t="n">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="B672" t="str">
+        <x:v>shop.unit.arrival</x:v>
+      </x:c>
+      <x:c r="C672" t="str">
+        <x:v>约{p0}秒/客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673">
+      <x:c r="A673" t="n">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="B673" t="str">
+        <x:v>shop.unit.service</x:v>
+      </x:c>
+      <x:c r="C673" t="str">
+        <x:v>加购概率{p0}%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674">
+      <x:c r="A674" t="n">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="B674" t="str">
+        <x:v>shop.unit.shelves</x:v>
+      </x:c>
+      <x:c r="C674" t="str">
+        <x:v>{p0}货架 · {p1}收银台</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675">
+      <x:c r="A675" t="n">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="B675" t="str">
+        <x:v>shop.researchMenu</x:v>
+      </x:c>
+      <x:c r="C675" t="str">
+        <x:v>商品研发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676">
+      <x:c r="A676" t="n">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="B676" t="str">
+        <x:v>shop.uniformMenu</x:v>
+      </x:c>
+      <x:c r="C676" t="str">
+        <x:v>店员制服</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677">
+      <x:c r="A677" t="n">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="B677" t="str">
+        <x:v>shop.research</x:v>
+      </x:c>
+      <x:c r="C677" t="str">
+        <x:v>研发 {p0}金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678">
+      <x:c r="A678" t="n">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="B678" t="str">
+        <x:v>shop.researchInfo</x:v>
+      </x:c>
+      <x:c r="C678" t="str">
+        <x:v>售价 {p0} → {p1} · 累计售出{p2}份</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679">
+      <x:c r="A679" t="n">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="B679" t="str">
+        <x:v>shop.researchLevel</x:v>
+      </x:c>
+      <x:c r="C679" t="str">
+        <x:v>研发 Lv.{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680">
+      <x:c r="A680" t="n">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="B680" t="str">
+        <x:v>shop.soldUnits</x:v>
+      </x:c>
+      <x:c r="C680" t="str">
+        <x:v>累计售出</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681">
+      <x:c r="A681" t="n">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="B681" t="str">
+        <x:v>shop.uniformOwned</x:v>
+      </x:c>
+      <x:c r="C681" t="str">
+        <x:v>制服已收藏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682">
+      <x:c r="A682" t="n">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="B682" t="str">
+        <x:v>shop.uniformBuy</x:v>
+      </x:c>
+      <x:c r="C682" t="str">
+        <x:v>收藏 {p0}金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683">
+      <x:c r="A683" t="n">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="B683" t="str">
+        <x:v>shop.uniformWear</x:v>
+      </x:c>
+      <x:c r="C683" t="str">
+        <x:v>穿上制服</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684">
+      <x:c r="A684" t="n">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="B684" t="str">
+        <x:v>shop.uniformTakeOff</x:v>
+      </x:c>
+      <x:c r="C684" t="str">
+        <x:v>换回原装</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685">
+      <x:c r="A685" t="n">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="B685" t="str">
+        <x:v>shop.uniformDescription</x:v>
+      </x:c>
+      <x:c r="C685" t="str">
+        <x:v>经营专用制服 · 不改变战斗属性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686">
+      <x:c r="A686" t="n">
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="B686" t="str">
+        <x:v>shop.uniformName</x:v>
+      </x:c>
+      <x:c r="C686" t="str">
+        <x:v>{p0}·工作制服</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687">
+      <x:c r="A687" t="n">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="B687" t="str">
+        <x:v>shop.goodsTitle</x:v>
+      </x:c>
+      <x:c r="C687" t="str">
+        <x:v>货架{p0} · 选择商品</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688">
+      <x:c r="A688" t="n">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="B688" t="str">
+        <x:v>shop.shelfPick</x:v>
+      </x:c>
+      <x:c r="C688" t="str">
+        <x:v>货架{p0}：{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689">
+      <x:c r="A689" t="n">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="B689" t="str">
+        <x:v>shop.shelfChoose</x:v>
+      </x:c>
+      <x:c r="C689" t="str">
+        <x:v>调整上架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690">
+      <x:c r="A690" t="n">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="B690" t="str">
+        <x:v>shop.picked</x:v>
+      </x:c>
+      <x:c r="C690" t="str">
+        <x:v>已上架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691">
+      <x:c r="A691" t="n">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="B691" t="str">
+        <x:v>shop.shift</x:v>
+      </x:c>
+      <x:c r="C691" t="str">
+        <x:v>岗位：{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692">
+      <x:c r="A692" t="n">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="B692" t="str">
+        <x:v>shop.role.cashier</x:v>
+      </x:c>
+      <x:c r="C692" t="str">
+        <x:v>收银</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693">
+      <x:c r="A693" t="n">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="B693" t="str">
+        <x:v>shop.role.cold</x:v>
+      </x:c>
+      <x:c r="C693" t="str">
+        <x:v>冷藏补货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694">
+      <x:c r="A694" t="n">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="B694" t="str">
+        <x:v>shop.role.pack</x:v>
+      </x:c>
+      <x:c r="C694" t="str">
+        <x:v>打包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695">
+      <x:c r="A695" t="n">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="B695" t="str">
+        <x:v>shop.role.guide</x:v>
+      </x:c>
+      <x:c r="C695" t="str">
+        <x:v>导购 / 二号收银</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696">
+      <x:c r="A696" t="n">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="B696" t="str">
+        <x:v>shop.role.tidy</x:v>
+      </x:c>
+      <x:c r="C696" t="str">
+        <x:v>理货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697">
+      <x:c r="A697" t="n">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="B697" t="str">
+        <x:v>shop.role.hot</x:v>
+      </x:c>
+      <x:c r="C697" t="str">
+        <x:v>热食补货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698">
+      <x:c r="A698" t="n">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="B698" t="str">
+        <x:v>shop.role.porter</x:v>
+      </x:c>
+      <x:c r="C698" t="str">
+        <x:v>仓库搬运</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699">
+      <x:c r="A699" t="n">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="B699" t="str">
+        <x:v>shop.role.welcome</x:v>
+      </x:c>
+      <x:c r="C699" t="str">
+        <x:v>迎宾</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700">
+      <x:c r="A700" t="n">
+        <x:v>696</x:v>
+      </x:c>
+      <x:c r="B700" t="str">
+        <x:v>shop.job.source</x:v>
+      </x:c>
+      <x:c r="C700" t="str">
+        <x:v>取货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701">
+      <x:c r="A701" t="n">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="B701" t="str">
+        <x:v>shop.job.travel</x:v>
+      </x:c>
+      <x:c r="C701" t="str">
+        <x:v>搬运</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702">
+      <x:c r="A702" t="n">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="B702" t="str">
+        <x:v>shop.job.unload</x:v>
+      </x:c>
+      <x:c r="C702" t="str">
+        <x:v>上架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703">
+      <x:c r="A703" t="n">
+        <x:v>699</x:v>
+      </x:c>
+      <x:c r="B703" t="str">
+        <x:v>shop.job.pack</x:v>
+      </x:c>
+      <x:c r="C703" t="str">
+        <x:v>打包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704">
+      <x:c r="A704" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="B704" t="str">
+        <x:v>shop.job.guide</x:v>
+      </x:c>
+      <x:c r="C704" t="str">
+        <x:v>导购</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705">
+      <x:c r="A705" t="n">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="B705" t="str">
+        <x:v>shop.job.tidy</x:v>
+      </x:c>
+      <x:c r="C705" t="str">
+        <x:v>理货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706">
+      <x:c r="A706" t="n">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="B706" t="str">
+        <x:v>shop.job.welcome</x:v>
+      </x:c>
+      <x:c r="C706" t="str">
+        <x:v>迎宾</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707">
+      <x:c r="A707" t="n">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c r="B707" t="str">
+        <x:v>shop.job.cashier</x:v>
+      </x:c>
+      <x:c r="C707" t="str">
+        <x:v>收银</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708">
+      <x:c r="A708" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="B708" t="str">
+        <x:v>shop.job.ready</x:v>
+      </x:c>
+      <x:c r="C708" t="str">
+        <x:v>待客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="709">
+      <x:c r="A709" t="n">
+        <x:v>705</x:v>
+      </x:c>
+      <x:c r="B709" t="str">
+        <x:v>shop.scroll</x:v>
+      </x:c>
+      <x:c r="C709" t="str">
+        <x:v>上下滑动查看货架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="710">
+      <x:c r="A710" t="n">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="B710" t="str">
+        <x:v>shop.researchDetail</x:v>
+      </x:c>
+      <x:c r="C710" t="str">
+        <x:v>{p0} · 售出{p1}份</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711">
+      <x:c r="A711" t="n">
+        <x:v>707</x:v>
+      </x:c>
+      <x:c r="B711" t="str">
+        <x:v>shop.uniformDetail</x:v>
+      </x:c>
+      <x:c r="C711" t="str">
+        <x:v>经营制服 {p0}/1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712">
+      <x:c r="A712" t="n">
+        <x:v>708</x:v>
+      </x:c>
+      <x:c r="B712" t="str">
+        <x:v>shop.owned</x:v>
+      </x:c>
+      <x:c r="C712" t="str">
+        <x:v>已收藏</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Ra9a8d089c9834e2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R89a2777943c84f9d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6837,7 +6837,7 @@
         <x:v>shop.offline</x:v>
       </x:c>
       <x:c r="C592" t="str">
-        <x:v>离线营业 +{p0}金币</x:v>
+        <x:v>离线收益 +{p0}金币</x:v>
       </x:c>
     </x:row>
     <x:row r="593">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R89a2777943c84f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R7530088bfc88476a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7288,7 +7288,7 @@
         <x:v>topics.title</x:v>
       </x:c>
       <x:c r="C633" t="str">
-        <x:v>挑战夜班</x:v>
+        <x:v>挑战模式</x:v>
       </x:c>
     </x:row>
     <x:row r="634">
@@ -7343,7 +7343,7 @@
         <x:v>topics.number</x:v>
       </x:c>
       <x:c r="C638" t="str">
-        <x:v>夜班 {p0}</x:v>
+        <x:v>{p0}</x:v>
       </x:c>
     </x:row>
     <x:row r="639">
@@ -7607,7 +7607,7 @@
         <x:v>shop.stageSummary</x:v>
       </x:c>
       <x:c r="C662" t="str">
-        <x:v>{p0} · 已接待 {p1} 位顾客</x:v>
+        <x:v>{p0} · 已接待{p1}位顾客</x:v>
       </x:c>
     </x:row>
     <x:row r="663">
@@ -8158,6 +8158,226 @@
       </x:c>
       <x:c r="C712" t="str">
         <x:v>已收藏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713">
+      <x:c r="A713" t="n">
+        <x:v>709</x:v>
+      </x:c>
+      <x:c r="B713" t="str">
+        <x:v>shop.selectShelf</x:v>
+      </x:c>
+      <x:c r="C713" t="str">
+        <x:v>选择上架货架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="714">
+      <x:c r="A714" t="n">
+        <x:v>710</x:v>
+      </x:c>
+      <x:c r="B714" t="str">
+        <x:v>shop.page</x:v>
+      </x:c>
+      <x:c r="C714" t="str">
+        <x:v>{p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="715">
+      <x:c r="A715" t="n">
+        <x:v>711</x:v>
+      </x:c>
+      <x:c r="B715" t="str">
+        <x:v>topics.page</x:v>
+      </x:c>
+      <x:c r="C715" t="str">
+        <x:v>{p0} / {p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716">
+      <x:c r="A716" t="n">
+        <x:v>712</x:v>
+      </x:c>
+      <x:c r="B716" t="str">
+        <x:v>ranking.title</x:v>
+      </x:c>
+      <x:c r="C716" t="str">
+        <x:v>排行榜</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="717">
+      <x:c r="A717" t="n">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="B717" t="str">
+        <x:v>ranking.all</x:v>
+      </x:c>
+      <x:c r="C717" t="str">
+        <x:v>全服榜</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="718">
+      <x:c r="A718" t="n">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="B718" t="str">
+        <x:v>ranking.friends</x:v>
+      </x:c>
+      <x:c r="C718" t="str">
+        <x:v>好友榜</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="719">
+      <x:c r="A719" t="n">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="B719" t="str">
+        <x:v>ranking.demo</x:v>
+      </x:c>
+      <x:c r="C719" t="str">
+        <x:v>演示榜单 · 尚未接入联网排名</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="720">
+      <x:c r="A720" t="n">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="B720" t="str">
+        <x:v>ranking.pending</x:v>
+      </x:c>
+      <x:c r="C720" t="str">
+        <x:v>排行榜暂未联网</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="721">
+      <x:c r="A721" t="n">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="B721" t="str">
+        <x:v>ranking.empty</x:v>
+      </x:c>
+      <x:c r="C721" t="str">
+        <x:v>个人成绩已保留，联网排名将在平台接入后开放。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="722">
+      <x:c r="A722" t="n">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="B722" t="str">
+        <x:v>ranking.mine</x:v>
+      </x:c>
+      <x:c r="C722" t="str">
+        <x:v>我的成绩</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="723">
+      <x:c r="A723" t="n">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="B723" t="str">
+        <x:v>ranking.progress</x:v>
+      </x:c>
+      <x:c r="C723" t="str">
+        <x:v>冒险{p0}/{p1} · 挑战{p2}/{p3}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="724">
+      <x:c r="A724" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="B724" t="str">
+        <x:v>ranking.play</x:v>
+      </x:c>
+      <x:c r="C724" t="str">
+        <x:v>去挑战</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="725">
+      <x:c r="A725" t="n">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="B725" t="str">
+        <x:v>ranking.name.1</x:v>
+      </x:c>
+      <x:c r="C725" t="str">
+        <x:v>团团店长</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="726">
+      <x:c r="A726" t="n">
+        <x:v>722</x:v>
+      </x:c>
+      <x:c r="B726" t="str">
+        <x:v>ranking.name.2</x:v>
+      </x:c>
+      <x:c r="C726" t="str">
+        <x:v>豆包超市</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="727">
+      <x:c r="A727" t="n">
+        <x:v>723</x:v>
+      </x:c>
+      <x:c r="B727" t="str">
+        <x:v>ranking.name.3</x:v>
+      </x:c>
+      <x:c r="C727" t="str">
+        <x:v>棉棉小铺</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="728">
+      <x:c r="A728" t="n">
+        <x:v>724</x:v>
+      </x:c>
+      <x:c r="B728" t="str">
+        <x:v>ranking.name.4</x:v>
+      </x:c>
+      <x:c r="C728" t="str">
+        <x:v>布丁便利屋</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="729">
+      <x:c r="A729" t="n">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="B729" t="str">
+        <x:v>ranking.name.5</x:v>
+      </x:c>
+      <x:c r="C729" t="str">
+        <x:v>小熊百货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="730">
+      <x:c r="A730" t="n">
+        <x:v>726</x:v>
+      </x:c>
+      <x:c r="B730" t="str">
+        <x:v>ranking.name.6</x:v>
+      </x:c>
+      <x:c r="C730" t="str">
+        <x:v>夜灯小店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="731">
+      <x:c r="A731" t="n">
+        <x:v>727</x:v>
+      </x:c>
+      <x:c r="B731" t="str">
+        <x:v>ranking.name.7</x:v>
+      </x:c>
+      <x:c r="C731" t="str">
+        <x:v>柚子补给站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="732">
+      <x:c r="A732" t="n">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="B732" t="str">
+        <x:v>ranking.name.8</x:v>
+      </x:c>
+      <x:c r="C732" t="str">
+        <x:v>元气杂货铺</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R7530088bfc88476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rf2b03a02a4494b51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7332,7 +7332,8 @@
         <x:v>topics.locked</x:v>
       </x:c>
       <x:c r="C637" t="str">
-        <x:v>通关「{p0}」解锁</x:v>
+        <x:v>通关「{p0}」
+解锁</x:v>
       </x:c>
     </x:row>
     <x:row r="638">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rf2b03a02a4494b51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rf70167afbf5c4d85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8381,6 +8381,94 @@
         <x:v>元气杂货铺</x:v>
       </x:c>
     </x:row>
+    <x:row r="733">
+      <x:c r="A733" t="n">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="B733" t="str">
+        <x:v>shop.goodsSlotTitle</x:v>
+      </x:c>
+      <x:c r="C733" t="str">
+        <x:v>货架{p0} · 商品位{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="734">
+      <x:c r="A734" t="n">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="B734" t="str">
+        <x:v>shop.goodsSlotCaption</x:v>
+      </x:c>
+      <x:c r="C734" t="str">
+        <x:v>{p0} · {p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="735">
+      <x:c r="A735" t="n">
+        <x:v>731</x:v>
+      </x:c>
+      <x:c r="B735" t="str">
+        <x:v>shop.emptySlot</x:v>
+      </x:c>
+      <x:c r="C735" t="str">
+        <x:v>未上架</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="736">
+      <x:c r="A736" t="n">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="B736" t="str">
+        <x:v>shop.slotUsed</x:v>
+      </x:c>
+      <x:c r="C736" t="str">
+        <x:v>已在商品位{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="737">
+      <x:c r="A737" t="n">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="B737" t="str">
+        <x:v>shop.clearSlot</x:v>
+      </x:c>
+      <x:c r="C737" t="str">
+        <x:v>清空此商品位</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="738">
+      <x:c r="A738" t="n">
+        <x:v>734</x:v>
+      </x:c>
+      <x:c r="B738" t="str">
+        <x:v>shop.keepFirstSlot</x:v>
+      </x:c>
+      <x:c r="C738" t="str">
+        <x:v>首位需保留商品</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="739">
+      <x:c r="A739" t="n">
+        <x:v>735</x:v>
+      </x:c>
+      <x:c r="B739" t="str">
+        <x:v>shop.goodsSeparator</x:v>
+      </x:c>
+      <x:c r="C739" t="str">
+        <x:v>·</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="740">
+      <x:c r="A740" t="n">
+        <x:v>736</x:v>
+      </x:c>
+      <x:c r="B740" t="str">
+        <x:v>shop.mixedInventory</x:v>
+      </x:c>
+      <x:c r="C740" t="str">
+        <x:v>库存 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rf70167afbf5c4d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R097bacd0e5ad4136"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2180,7 +2180,7 @@
         <x:v>ui.GameMenuView.006</x:v>
       </x:c>
       <x:c r="C169" s="13" t="str">
-        <x:v>15波夜班 · 自选4名店员</x:v>
+        <x:v>15波长夜 · 3倍速约15分钟</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="58" hidden="0" customHeight="1">
@@ -3380,7 +3380,7 @@
         <x:v>challenge.goal</x:v>
       </x:c>
       <x:c r="C278" s="16" t="str">
-        <x:v>守住15波来客</x:v>
+        <x:v>守住15波怪潮</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="58" customHeight="1">
@@ -5473,7 +5473,7 @@
         <x:v>perk.S04.desc</x:v>
       </x:c>
       <x:c r="C468" t="str">
-        <x:v>咕咕离目标越远伤害越高，在原射程边缘达到额外60%。</x:v>
+        <x:v>咕咕离目标越远伤害越高，在原射程边缘达到额外35%。</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -5517,7 +5517,7 @@
         <x:v>perk.S06.desc</x:v>
       </x:c>
       <x:c r="C472" t="str">
-        <x:v>燃烧中的来客被击败时，对65范围内其他来客造成其每秒灼烧伤害200%的伤害。</x:v>
+        <x:v>燃烧中的来客被击败时，对56范围内最多6名其他来客造成其每秒灼烧伤害120%的伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -5649,7 +5649,7 @@
         <x:v>perk.G04.desc</x:v>
       </x:c>
       <x:c r="C484" t="str">
-        <x:v>每持有100金币，全体伤害提高10%，最多提高40%。</x:v>
+        <x:v>每持有100金币，全体伤害提高2%，最多提高20%。</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -5957,7 +5957,7 @@
         <x:v>perk.X06.desc</x:v>
       </x:c>
       <x:c r="C512" t="str">
-        <x:v>本波来客全部出现且只剩一名时，店员直击伤害提高80%。</x:v>
+        <x:v>本波来客全部出现且只剩一名时，店员直击伤害提高40%。</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
@@ -7299,7 +7299,7 @@
         <x:v>topics.summary</x:v>
       </x:c>
       <x:c r="C634" t="str">
-        <x:v>15波夜班 · 10次补给 · 自选4名店员</x:v>
+        <x:v>3倍速约15分钟 · 10次补给</x:v>
       </x:c>
     </x:row>
     <x:row r="635">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R097bacd0e5ad4136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R48479aa8aded4e8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2180,7 +2180,7 @@
         <x:v>ui.GameMenuView.006</x:v>
       </x:c>
       <x:c r="C169" s="13" t="str">
-        <x:v>15波长夜 · 3倍速约15分钟</x:v>
+        <x:v>共15波</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="58" hidden="0" customHeight="1">
@@ -7299,7 +7299,7 @@
         <x:v>topics.summary</x:v>
       </x:c>
       <x:c r="C634" t="str">
-        <x:v>3倍速约15分钟 · 10次补给</x:v>
+        <x:v>15波挑战 · 10次补给</x:v>
       </x:c>
     </x:row>
     <x:row r="635">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R48479aa8aded4e8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R6a5008386a85467b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3380,7 +3380,7 @@
         <x:v>challenge.goal</x:v>
       </x:c>
       <x:c r="C278" s="16" t="str">
-        <x:v>守住15波怪潮</x:v>
+        <x:v>守住便利店，击败首领</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="58" customHeight="1">
@@ -3391,7 +3391,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="C279" s="16" t="str">
-        <x:v>首领来访</x:v>
+        <x:v>首领来袭，不能漏过</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="58" customHeight="1">
@@ -5407,7 +5407,7 @@
         <x:v>perk.S01.desc</x:v>
       </x:c>
       <x:c r="C462" t="str">
-        <x:v>豆包每第三轮攻击改为三连发，每发造成70%伤害。</x:v>
+        <x:v>每2轮发射3连弹，造成70%伤害；第6、11波各增加1发。</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -5451,7 +5451,7 @@
         <x:v>perk.S03.desc</x:v>
       </x:c>
       <x:c r="C466" t="str">
-        <x:v>布丁每第三轮攻击的爆点会在0.35秒后再爆一次，造成80%伤害。</x:v>
+        <x:v>每2轮追加一次更大范围的爆炸，造成90%攻击伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -5495,7 +5495,7 @@
         <x:v>perk.S05.desc</x:v>
       </x:c>
       <x:c r="C470" t="str">
-        <x:v>栗栗每第三轮攻击多放出一条电链，造成60%伤害。</x:v>
+        <x:v>每2轮追加电链，连接5名来客，伤害80%起并逐跳衰减；第6、11波各加1名。</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -5517,7 +5517,7 @@
         <x:v>perk.S06.desc</x:v>
       </x:c>
       <x:c r="C472" t="str">
-        <x:v>燃烧中的来客被击败时，对56范围内最多6名其他来客造成其每秒灼烧伤害120%的伤害。</x:v>
+        <x:v>击败燃烧来客，对72范围内最多8名造成灼烧伤害210%的余温。</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -5561,7 +5561,7 @@
         <x:v>perk.S08.desc</x:v>
       </x:c>
       <x:c r="C476" t="str">
-        <x:v>啾啾的每枚风弹命中后，弹向65范围内另一名来客，造成60%伤害。</x:v>
+        <x:v>额外攻击80范围内另一名来客，造成80%攻击伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
@@ -6650,7 +6650,7 @@
         <x:v>ui.redesign.supplyHint</x:v>
       </x:c>
       <x:c r="C575" t="str">
-        <x:v>请选择一份补给，助你轻松度过夜班！</x:v>
+        <x:v>专属强化会随夜班进度成长</x:v>
       </x:c>
     </x:row>
     <x:row r="576" ht="36" customHeight="1">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R6a5008386a85467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rc510eba70de1492d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2180,7 +2180,7 @@
         <x:v>ui.GameMenuView.006</x:v>
       </x:c>
       <x:c r="C169" s="13" t="str">
-        <x:v>共15波</x:v>
+        <x:v>共30波</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="58" hidden="0" customHeight="1">
@@ -7299,7 +7299,7 @@
         <x:v>topics.summary</x:v>
       </x:c>
       <x:c r="C634" t="str">
-        <x:v>15波挑战 · 10次补给</x:v>
+        <x:v>30波挑战 · 10次补给</x:v>
       </x:c>
     </x:row>
     <x:row r="635">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rc510eba70de1492d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R822b6d2be4644090"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3435,7 +3435,7 @@
         <x:v>challenge.enter</x:v>
       </x:c>
       <x:c r="C283" s="16" t="str">
-        <x:v>夜班加时赛</x:v>
+        <x:v>击退来客，攒满经验领取补给。</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="58" customHeight="1">
@@ -5407,7 +5407,7 @@
         <x:v>perk.S01.desc</x:v>
       </x:c>
       <x:c r="C462" t="str">
-        <x:v>每2轮发射3连弹，造成70%伤害；第6、11波各增加1发。</x:v>
+        <x:v>每2轮发射3连弹，造成48%伤害；第11、21波各增加1发。</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -5429,7 +5429,7 @@
         <x:v>perk.S02.desc</x:v>
       </x:c>
       <x:c r="C464" t="str">
-        <x:v>被减速的来客被击败时，将当前减速传给80范围内至多2名来客，持续1.5秒。</x:v>
+        <x:v>主目标附近70范围内额外2名敌人减速，持续1.1秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
@@ -5451,7 +5451,7 @@
         <x:v>perk.S03.desc</x:v>
       </x:c>
       <x:c r="C466" t="str">
-        <x:v>每2轮追加一次更大范围的爆炸，造成90%攻击伤害。</x:v>
+        <x:v>每2次攻击追加延时礼花，造成50%伤害，爆炸范围为原来的125%。</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -5473,7 +5473,7 @@
         <x:v>perk.S04.desc</x:v>
       </x:c>
       <x:c r="C468" t="str">
-        <x:v>咕咕离目标越远伤害越高，在原射程边缘达到额外35%。</x:v>
+        <x:v>目标距离越远伤害越高，最高额外20%。</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -5495,7 +5495,7 @@
         <x:v>perk.S05.desc</x:v>
       </x:c>
       <x:c r="C470" t="str">
-        <x:v>每2轮追加电链，连接5名来客，伤害80%起并逐跳衰减；第6、11波各加1名。</x:v>
+        <x:v>每2次攻击追加一次电链，造成50%伤害，最多连接4名敌人。</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -5517,7 +5517,7 @@
         <x:v>perk.S06.desc</x:v>
       </x:c>
       <x:c r="C472" t="str">
-        <x:v>击败燃烧来客，对72范围内最多8名造成灼烧伤害210%的余温。</x:v>
+        <x:v>灼烧击退触发64范围火爆，造成135%伤害，最多影响6名敌人。</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -5539,7 +5539,7 @@
         <x:v>perk.S07.desc</x:v>
       </x:c>
       <x:c r="C474" t="str">
-        <x:v>被标记的来客被击败后，将标记传给100范围内至多2名来客，持续2秒，最多传递3代。</x:v>
+        <x:v>标记击退向85范围内2名敌人传递，持续1.5秒，最多传2代。</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
@@ -5561,7 +5561,7 @@
         <x:v>perk.S08.desc</x:v>
       </x:c>
       <x:c r="C476" t="str">
-        <x:v>额外攻击80范围内另一名来客，造成80%攻击伤害。</x:v>
+        <x:v>散射击退触发70范围爆破，造成50%伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
@@ -5583,7 +5583,7 @@
         <x:v>perk.G01.desc</x:v>
       </x:c>
       <x:c r="C478" t="str">
-        <x:v>每波开始后的6秒内，全体攻击间隔缩短35%。</x:v>
+        <x:v>每波开头5秒，攻击间隔缩短22%。</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -5605,7 +5605,7 @@
         <x:v>perk.G02.desc</x:v>
       </x:c>
       <x:c r="C480" t="str">
-        <x:v>90范围内有其他种类店员时，伤害提高25%。</x:v>
+        <x:v>90范围内有其他种类店员时，伤害提高14%。</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -5627,7 +5627,7 @@
         <x:v>perk.G03.desc</x:v>
       </x:c>
       <x:c r="C482" t="str">
-        <x:v>90范围内没有其他店员时，伤害提高50%，射程缩短10%。</x:v>
+        <x:v>90范围内没有其他店员时，伤害提高28%，射程缩短10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
@@ -5649,7 +5649,7 @@
         <x:v>perk.G04.desc</x:v>
       </x:c>
       <x:c r="C484" t="str">
-        <x:v>每持有100金币，全体伤害提高2%，最多提高20%。</x:v>
+        <x:v>每持有100金币伤害提高1.2%，最高12%。</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -5671,7 +5671,7 @@
         <x:v>perk.G05.desc</x:v>
       </x:c>
       <x:c r="C486" t="str">
-        <x:v>上一波没有漏客时，本波伤害提高25%，射程提高15%。</x:v>
+        <x:v>上一波未漏怪时，本波伤害提高14%，射程提高8%。</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -5693,7 +5693,7 @@
         <x:v>perk.G06.desc</x:v>
       </x:c>
       <x:c r="C488" t="str">
-        <x:v>所选4种店员全部在场时，全体伤害提高35%。</x:v>
+        <x:v>四种出战店员都已建造时，全员伤害提高18%。</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
@@ -5715,7 +5715,7 @@
         <x:v>perk.E01.desc</x:v>
       </x:c>
       <x:c r="C490" t="str">
-        <x:v>立即获得200金币。</x:v>
+        <x:v>立即获得90金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
@@ -5737,7 +5737,7 @@
         <x:v>perk.E02.desc</x:v>
       </x:c>
       <x:c r="C492" t="str">
-        <x:v>接下来5次清波，按清波奖金到账前的金币获得15%利息，每次最多75金币。</x:v>
+        <x:v>接下来5次交班获得持币8%的利息，每次最多40金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -5759,7 +5759,7 @@
         <x:v>perk.E03.desc</x:v>
       </x:c>
       <x:c r="C494" t="str">
-        <x:v>接下来3次建造免费。免费投入不计入出售返还。</x:v>
+        <x:v>接下来2次建造免费，免费投入不计入出售返还。</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -5781,7 +5781,7 @@
         <x:v>perk.E04.desc</x:v>
       </x:c>
       <x:c r="C496" t="str">
-        <x:v>接下来2次进化免费。免费投入不计入出售返还。</x:v>
+        <x:v>接下来1次进化免费，免费投入不计入出售返还。</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
@@ -5803,7 +5803,7 @@
         <x:v>perk.E05.desc</x:v>
       </x:c>
       <x:c r="C498" t="str">
-        <x:v>立即获得60金币，此后每清除一件货物额外获得30金币。</x:v>
+        <x:v>立即获得40金币，之后每清除一处障碍额外获得16金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -5825,7 +5825,7 @@
         <x:v>perk.E06.desc</x:v>
       </x:c>
       <x:c r="C500" t="str">
-        <x:v>普通来客的基础金币奖励增加25%，向下取整。</x:v>
+        <x:v>普通怪击退收益额外提高12%，按战斗金币折算。</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
@@ -5847,7 +5847,7 @@
         <x:v>perk.X01.desc</x:v>
       </x:c>
       <x:c r="C502" t="str">
-        <x:v>每波第一名到达店门的普通来客返回路线30%处，保留生命与状态。</x:v>
+        <x:v>每波第一名漏网普通怪退回路线20%处。</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -5869,7 +5869,7 @@
         <x:v>perk.X02.desc</x:v>
       </x:c>
       <x:c r="C504" t="str">
-        <x:v>每波抵挡2点漏客伤害。</x:v>
+        <x:v>每波获得1层防漏护盾，抵消普通怪漏怪伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
@@ -5891,7 +5891,7 @@
         <x:v>perk.X03.desc</x:v>
       </x:c>
       <x:c r="C506" t="str">
-        <x:v>每波前3名进入最后20%路段的普通来客，移速降低60%，持续2秒。</x:v>
+        <x:v>每波最多2名走过路线80%的普通怪降至55%速度，持续2秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -5913,7 +5913,7 @@
         <x:v>perk.X04.desc</x:v>
       </x:c>
       <x:c r="C508" t="str">
-        <x:v>每累计收入100金币，全体攻击间隔缩短25%，持续4秒。出售收入不计入。</x:v>
+        <x:v>累计获得120金币后，攻击间隔缩短18%，持续3秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
@@ -5935,7 +5935,7 @@
         <x:v>perk.X05.desc</x:v>
       </x:c>
       <x:c r="C510" t="str">
-        <x:v>直接清除货物时，对100范围内其他货物造成其最大生命35%的伤害。</x:v>
+        <x:v>清障时对90范围内其他障碍造成20%最大耐久伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -5957,7 +5957,7 @@
         <x:v>perk.X06.desc</x:v>
       </x:c>
       <x:c r="C512" t="str">
-        <x:v>本波来客全部出现且只剩一名时，店员直击伤害提高40%。</x:v>
+        <x:v>路线最后一名在场敌人受到的伤害提高25%。</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
@@ -5979,7 +5979,7 @@
         <x:v>perk.F01.desc</x:v>
       </x:c>
       <x:c r="C514" t="str">
-        <x:v>每波随机一名最高等级店员变大，伤害提高80%，射程提高15%，攻击间隔增加20%。</x:v>
+        <x:v>每波一名最高级店员变大：伤害提高45%，射程提高8%，攻击间隔增加12%。</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -6001,7 +6001,7 @@
         <x:v>perk.F02.desc</x:v>
       </x:c>
       <x:c r="C516" t="str">
-        <x:v>全体店员变小，攻击间隔缩短25%，伤害降低10%。</x:v>
+        <x:v>全员变小：攻击间隔缩短18%，伤害降低10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
@@ -6023,7 +6023,7 @@
         <x:v>perk.F03.desc</x:v>
       </x:c>
       <x:c r="C518" t="str">
-        <x:v>每击败12名来客，随机获得20金币、一次100伤害爆炸或2秒减速。每波最多3次，额外攻击不计数。</x:v>
+        <x:v>每击退16名敌人掉落礼物，每波最多2个：获得8金币，70范围造成65伤害并降至55%速度2秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -6045,7 +6045,7 @@
         <x:v>perk.F04.desc</x:v>
       </x:c>
       <x:c r="C520" t="str">
-        <x:v>全队每完成24轮攻击，从店门滚出保龄球，沿路造成100伤害，最多命中8名来客，冷却8秒。</x:v>
+        <x:v>每击退30名敌人发出保龄球，每次70伤害，最多命中6名敌人，冷却10秒。</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -6067,7 +6067,7 @@
         <x:v>perk.F05.desc</x:v>
       </x:c>
       <x:c r="C522" t="str">
-        <x:v>每10秒在最靠近店门的3名来客处落下快递，0.6秒后对40范围造成80伤害。每次快递雨对同一来客只伤害一次。</x:v>
+        <x:v>每12秒向前排落下2颗糖果，每颗36范围造成55伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -6089,7 +6089,7 @@
         <x:v>perk.F06.desc</x:v>
       </x:c>
       <x:c r="C524" t="str">
-        <x:v>每波随机一名普通来客生命变为2倍，击败奖励变为4倍。</x:v>
+        <x:v>每波一名普通怪变成宝藏怪：生命翻倍，击退收益变为3倍。</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -7299,7 +7299,7 @@
         <x:v>topics.summary</x:v>
       </x:c>
       <x:c r="C634" t="str">
-        <x:v>30波挑战 · 10次补给</x:v>
+        <x:v>30波挑战 · 20次补给</x:v>
       </x:c>
     </x:row>
     <x:row r="635">
@@ -8467,6 +8467,721 @@
       </x:c>
       <x:c r="C740" t="str">
         <x:v>库存 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="741">
+      <x:c r="A741" s="15" t="n">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="B741" s="13" t="str">
+        <x:v>enemy.puff.name</x:v>
+      </x:c>
+      <x:c r="C741" s="13" t="str">
+        <x:v>泡芙团子</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="742">
+      <x:c r="A742" s="15" t="n">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c r="B742" s="13" t="str">
+        <x:v>collection.enemy-puff.category</x:v>
+      </x:c>
+      <x:c r="C742" s="13" t="str">
+        <x:v>普通来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="743">
+      <x:c r="A743" s="15" t="n">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c r="B743" s="13" t="str">
+        <x:v>collection.enemy-puff.traits</x:v>
+      </x:c>
+      <x:c r="C743" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="744">
+      <x:c r="A744" s="15" t="n">
+        <x:v>740</x:v>
+      </x:c>
+      <x:c r="B744" s="13" t="str">
+        <x:v>collection.enemy-puff.story</x:v>
+      </x:c>
+      <x:c r="C744" s="13" t="str">
+        <x:v>泡芙团子也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="745">
+      <x:c r="A745" s="15" t="n">
+        <x:v>741</x:v>
+      </x:c>
+      <x:c r="B745" s="13" t="str">
+        <x:v>enemy.pudding.name</x:v>
+      </x:c>
+      <x:c r="C745" s="13" t="str">
+        <x:v>焦糖布丁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="746">
+      <x:c r="A746" s="15" t="n">
+        <x:v>742</x:v>
+      </x:c>
+      <x:c r="B746" s="13" t="str">
+        <x:v>collection.enemy-pudding.category</x:v>
+      </x:c>
+      <x:c r="C746" s="13" t="str">
+        <x:v>普通来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="747">
+      <x:c r="A747" s="15" t="n">
+        <x:v>743</x:v>
+      </x:c>
+      <x:c r="B747" s="13" t="str">
+        <x:v>collection.enemy-pudding.traits</x:v>
+      </x:c>
+      <x:c r="C747" s="13" t="str">
+        <x:v>比同类更耐打但步伐稍慢。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="748">
+      <x:c r="A748" s="15" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="B748" s="13" t="str">
+        <x:v>collection.enemy-pudding.story</x:v>
+      </x:c>
+      <x:c r="C748" s="13" t="str">
+        <x:v>焦糖布丁也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="749">
+      <x:c r="A749" s="15" t="n">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="B749" s="13" t="str">
+        <x:v>enemy.biscuit.name</x:v>
+      </x:c>
+      <x:c r="C749" s="13" t="str">
+        <x:v>饼干小怪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="750">
+      <x:c r="A750" s="15" t="n">
+        <x:v>746</x:v>
+      </x:c>
+      <x:c r="B750" s="13" t="str">
+        <x:v>collection.enemy-biscuit.category</x:v>
+      </x:c>
+      <x:c r="C750" s="13" t="str">
+        <x:v>普通来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="751">
+      <x:c r="A751" s="15" t="n">
+        <x:v>747</x:v>
+      </x:c>
+      <x:c r="B751" s="13" t="str">
+        <x:v>collection.enemy-biscuit.traits</x:v>
+      </x:c>
+      <x:c r="C751" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="752">
+      <x:c r="A752" s="15" t="n">
+        <x:v>748</x:v>
+      </x:c>
+      <x:c r="B752" s="13" t="str">
+        <x:v>collection.enemy-biscuit.story</x:v>
+      </x:c>
+      <x:c r="C752" s="13" t="str">
+        <x:v>饼干小怪也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="753">
+      <x:c r="A753" s="15" t="n">
+        <x:v>749</x:v>
+      </x:c>
+      <x:c r="B753" s="13" t="str">
+        <x:v>enemy.soda.name</x:v>
+      </x:c>
+      <x:c r="C753" s="13" t="str">
+        <x:v>汽水蹦蹦</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="754">
+      <x:c r="A754" s="15" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="B754" s="13" t="str">
+        <x:v>collection.enemy-soda.category</x:v>
+      </x:c>
+      <x:c r="C754" s="13" t="str">
+        <x:v>快步来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="755">
+      <x:c r="A755" s="15" t="n">
+        <x:v>751</x:v>
+      </x:c>
+      <x:c r="B755" s="13" t="str">
+        <x:v>collection.enemy-soda.traits</x:v>
+      </x:c>
+      <x:c r="C755" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="756">
+      <x:c r="A756" s="15" t="n">
+        <x:v>752</x:v>
+      </x:c>
+      <x:c r="B756" s="13" t="str">
+        <x:v>collection.enemy-soda.story</x:v>
+      </x:c>
+      <x:c r="C756" s="13" t="str">
+        <x:v>汽水蹦蹦也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757">
+      <x:c r="A757" s="15" t="n">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="B757" s="13" t="str">
+        <x:v>enemy.coffee.name</x:v>
+      </x:c>
+      <x:c r="C757" s="13" t="str">
+        <x:v>咖啡急客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="758">
+      <x:c r="A758" s="15" t="n">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="B758" s="13" t="str">
+        <x:v>collection.enemy-coffee.category</x:v>
+      </x:c>
+      <x:c r="C758" s="13" t="str">
+        <x:v>快步来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="759">
+      <x:c r="A759" s="15" t="n">
+        <x:v>755</x:v>
+      </x:c>
+      <x:c r="B759" s="13" t="str">
+        <x:v>collection.enemy-coffee.traits</x:v>
+      </x:c>
+      <x:c r="C759" s="13" t="str">
+        <x:v>比同类更耐打，脚步也更急。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="760">
+      <x:c r="A760" s="15" t="n">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="B760" s="13" t="str">
+        <x:v>collection.enemy-coffee.story</x:v>
+      </x:c>
+      <x:c r="C760" s="13" t="str">
+        <x:v>咖啡急客也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="761">
+      <x:c r="A761" s="15" t="n">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="B761" s="13" t="str">
+        <x:v>enemy.tea.name</x:v>
+      </x:c>
+      <x:c r="C761" s="13" t="str">
+        <x:v>珍珠茶客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="762">
+      <x:c r="A762" s="15" t="n">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="B762" s="13" t="str">
+        <x:v>collection.enemy-tea.category</x:v>
+      </x:c>
+      <x:c r="C762" s="13" t="str">
+        <x:v>疾跑来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="763">
+      <x:c r="A763" s="15" t="n">
+        <x:v>759</x:v>
+      </x:c>
+      <x:c r="B763" s="13" t="str">
+        <x:v>collection.enemy-tea.traits</x:v>
+      </x:c>
+      <x:c r="C763" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="764">
+      <x:c r="A764" s="15" t="n">
+        <x:v>760</x:v>
+      </x:c>
+      <x:c r="B764" s="13" t="str">
+        <x:v>collection.enemy-tea.story</x:v>
+      </x:c>
+      <x:c r="C764" s="13" t="str">
+        <x:v>珍珠茶客也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="765">
+      <x:c r="A765" s="15" t="n">
+        <x:v>761</x:v>
+      </x:c>
+      <x:c r="B765" s="13" t="str">
+        <x:v>enemy.berrymilk.name</x:v>
+      </x:c>
+      <x:c r="C765" s="13" t="str">
+        <x:v>草莓奶客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="766">
+      <x:c r="A766" s="15" t="n">
+        <x:v>762</x:v>
+      </x:c>
+      <x:c r="B766" s="13" t="str">
+        <x:v>collection.enemy-berrymilk.category</x:v>
+      </x:c>
+      <x:c r="C766" s="13" t="str">
+        <x:v>疾跑来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="767">
+      <x:c r="A767" s="15" t="n">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c r="B767" s="13" t="str">
+        <x:v>collection.enemy-berrymilk.traits</x:v>
+      </x:c>
+      <x:c r="C767" s="13" t="str">
+        <x:v>比同类更耐打但步伐稍慢。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="768">
+      <x:c r="A768" s="15" t="n">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="B768" s="13" t="str">
+        <x:v>collection.enemy-berrymilk.story</x:v>
+      </x:c>
+      <x:c r="C768" s="13" t="str">
+        <x:v>草莓奶客也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769">
+      <x:c r="A769" s="15" t="n">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="B769" s="13" t="str">
+        <x:v>enemy.tin.name</x:v>
+      </x:c>
+      <x:c r="C769" s="13" t="str">
+        <x:v>铁罐卫士</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770">
+      <x:c r="A770" s="15" t="n">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="B770" s="13" t="str">
+        <x:v>collection.enemy-tin.category</x:v>
+      </x:c>
+      <x:c r="C770" s="13" t="str">
+        <x:v>护盾来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="771">
+      <x:c r="A771" s="15" t="n">
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="B771" s="13" t="str">
+        <x:v>collection.enemy-tin.traits</x:v>
+      </x:c>
+      <x:c r="C771" s="13" t="str">
+        <x:v>比同类更耐打但步伐稍慢。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772">
+      <x:c r="A772" s="15" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="B772" s="13" t="str">
+        <x:v>collection.enemy-tin.story</x:v>
+      </x:c>
+      <x:c r="C772" s="13" t="str">
+        <x:v>铁罐卫士也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773">
+      <x:c r="A773" s="15" t="n">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="B773" s="13" t="str">
+        <x:v>enemy.juice.name</x:v>
+      </x:c>
+      <x:c r="C773" s="13" t="str">
+        <x:v>果汁方方</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="774">
+      <x:c r="A774" s="15" t="n">
+        <x:v>770</x:v>
+      </x:c>
+      <x:c r="B774" s="13" t="str">
+        <x:v>collection.enemy-juice.category</x:v>
+      </x:c>
+      <x:c r="C774" s="13" t="str">
+        <x:v>护盾来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775">
+      <x:c r="A775" s="15" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="B775" s="13" t="str">
+        <x:v>collection.enemy-juice.traits</x:v>
+      </x:c>
+      <x:c r="C775" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776">
+      <x:c r="A776" s="15" t="n">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="B776" s="13" t="str">
+        <x:v>collection.enemy-juice.story</x:v>
+      </x:c>
+      <x:c r="C776" s="13" t="str">
+        <x:v>果汁方方也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="777">
+      <x:c r="A777" s="15" t="n">
+        <x:v>773</x:v>
+      </x:c>
+      <x:c r="B777" s="13" t="str">
+        <x:v>enemy.peach.name</x:v>
+      </x:c>
+      <x:c r="C777" s="13" t="str">
+        <x:v>蜜桃冻冻</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="778">
+      <x:c r="A778" s="15" t="n">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="B778" s="13" t="str">
+        <x:v>collection.enemy-peach.category</x:v>
+      </x:c>
+      <x:c r="C778" s="13" t="str">
+        <x:v>软糖来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779">
+      <x:c r="A779" s="15" t="n">
+        <x:v>775</x:v>
+      </x:c>
+      <x:c r="B779" s="13" t="str">
+        <x:v>collection.enemy-peach.traits</x:v>
+      </x:c>
+      <x:c r="C779" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780">
+      <x:c r="A780" s="15" t="n">
+        <x:v>776</x:v>
+      </x:c>
+      <x:c r="B780" s="13" t="str">
+        <x:v>collection.enemy-peach.story</x:v>
+      </x:c>
+      <x:c r="C780" s="13" t="str">
+        <x:v>蜜桃冻冻也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781">
+      <x:c r="A781" s="15" t="n">
+        <x:v>777</x:v>
+      </x:c>
+      <x:c r="B781" s="13" t="str">
+        <x:v>enemy.grape.name</x:v>
+      </x:c>
+      <x:c r="C781" s="13" t="str">
+        <x:v>葡萄冻冻</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782">
+      <x:c r="A782" s="15" t="n">
+        <x:v>778</x:v>
+      </x:c>
+      <x:c r="B782" s="13" t="str">
+        <x:v>collection.enemy-grape.category</x:v>
+      </x:c>
+      <x:c r="C782" s="13" t="str">
+        <x:v>软糖来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783">
+      <x:c r="A783" s="15" t="n">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="B783" s="13" t="str">
+        <x:v>collection.enemy-grape.traits</x:v>
+      </x:c>
+      <x:c r="C783" s="13" t="str">
+        <x:v>比同类更耐打但步伐稍慢。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784">
+      <x:c r="A784" s="15" t="n">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="B784" s="13" t="str">
+        <x:v>collection.enemy-grape.story</x:v>
+      </x:c>
+      <x:c r="C784" s="13" t="str">
+        <x:v>葡萄冻冻也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785">
+      <x:c r="A785" s="15" t="n">
+        <x:v>781</x:v>
+      </x:c>
+      <x:c r="B785" s="13" t="str">
+        <x:v>enemy.blue.name</x:v>
+      </x:c>
+      <x:c r="C785" s="13" t="str">
+        <x:v>蓝莓冻冻</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786">
+      <x:c r="A786" s="15" t="n">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="B786" s="13" t="str">
+        <x:v>collection.enemy-blue.category</x:v>
+      </x:c>
+      <x:c r="C786" s="13" t="str">
+        <x:v>软糖来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787">
+      <x:c r="A787" s="15" t="n">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="B787" s="13" t="str">
+        <x:v>collection.enemy-blue.traits</x:v>
+      </x:c>
+      <x:c r="C787" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788">
+      <x:c r="A788" s="15" t="n">
+        <x:v>784</x:v>
+      </x:c>
+      <x:c r="B788" s="13" t="str">
+        <x:v>collection.enemy-blue.story</x:v>
+      </x:c>
+      <x:c r="C788" s="13" t="str">
+        <x:v>蓝莓冻冻也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789">
+      <x:c r="A789" s="15" t="n">
+        <x:v>785</x:v>
+      </x:c>
+      <x:c r="B789" s="13" t="str">
+        <x:v>enemy.ricebox.name</x:v>
+      </x:c>
+      <x:c r="C789" s="13" t="str">
+        <x:v>饭盒壮壮</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790">
+      <x:c r="A790" s="15" t="n">
+        <x:v>786</x:v>
+      </x:c>
+      <x:c r="B790" s="13" t="str">
+        <x:v>collection.enemy-ricebox.category</x:v>
+      </x:c>
+      <x:c r="C790" s="13" t="str">
+        <x:v>厚血来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791">
+      <x:c r="A791" s="15" t="n">
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="B791" s="13" t="str">
+        <x:v>collection.enemy-ricebox.traits</x:v>
+      </x:c>
+      <x:c r="C791" s="13" t="str">
+        <x:v>比同类更耐打但步伐稍慢。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792">
+      <x:c r="A792" s="15" t="n">
+        <x:v>788</x:v>
+      </x:c>
+      <x:c r="B792" s="13" t="str">
+        <x:v>collection.enemy-ricebox.story</x:v>
+      </x:c>
+      <x:c r="C792" s="13" t="str">
+        <x:v>饭盒壮壮也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793">
+      <x:c r="A793" s="15" t="n">
+        <x:v>789</x:v>
+      </x:c>
+      <x:c r="B793" s="13" t="str">
+        <x:v>enemy.deliverybag.name</x:v>
+      </x:c>
+      <x:c r="C793" s="13" t="str">
+        <x:v>纸袋搬搬</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794">
+      <x:c r="A794" s="15" t="n">
+        <x:v>790</x:v>
+      </x:c>
+      <x:c r="B794" s="13" t="str">
+        <x:v>collection.enemy-deliverybag.category</x:v>
+      </x:c>
+      <x:c r="C794" s="13" t="str">
+        <x:v>厚血来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795">
+      <x:c r="A795" s="15" t="n">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="B795" s="13" t="str">
+        <x:v>collection.enemy-deliverybag.traits</x:v>
+      </x:c>
+      <x:c r="C795" s="13" t="str">
+        <x:v>沿用同类行动特点，留意它的新模样。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796">
+      <x:c r="A796" s="15" t="n">
+        <x:v>792</x:v>
+      </x:c>
+      <x:c r="B796" s="13" t="str">
+        <x:v>collection.enemy-deliverybag.story</x:v>
+      </x:c>
+      <x:c r="C796" s="13" t="str">
+        <x:v>纸袋搬搬也加入了夜班队伍。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797">
+      <x:c r="A797" s="15" t="n">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="B797" s="13" t="str">
+        <x:v>perk.R01.name</x:v>
+      </x:c>
+      <x:c r="C797" s="13" t="str">
+        <x:v>零用补给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798">
+      <x:c r="A798" s="15" t="n">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="B798" s="13" t="str">
+        <x:v>perk.R01.desc</x:v>
+      </x:c>
+      <x:c r="C798" s="13" t="str">
+        <x:v>立即获得40金币。可重复选择。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799">
+      <x:c r="A799" s="15" t="n">
+        <x:v>795</x:v>
+      </x:c>
+      <x:c r="B799" s="13" t="str">
+        <x:v>perk.R02.name</x:v>
+      </x:c>
+      <x:c r="C799" s="13" t="str">
+        <x:v>冷风补给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800">
+      <x:c r="A800" s="15" t="n">
+        <x:v>796</x:v>
+      </x:c>
+      <x:c r="B800" s="13" t="str">
+        <x:v>perk.R02.desc</x:v>
+      </x:c>
+      <x:c r="C800" s="13" t="str">
+        <x:v>释放2秒冷风，期间在场怪物降至20%速度；准备阶段留到下一波。可重复选择。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801">
+      <x:c r="A801" s="15" t="n">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="B801" s="13" t="str">
+        <x:v>perk.R03.name</x:v>
+      </x:c>
+      <x:c r="C801" s="13" t="str">
+        <x:v>门帘补给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802">
+      <x:c r="A802" s="15" t="n">
+        <x:v>798</x:v>
+      </x:c>
+      <x:c r="B802" s="13" t="str">
+        <x:v>perk.R03.desc</x:v>
+      </x:c>
+      <x:c r="C802" s="13" t="str">
+        <x:v>本波追加1层护盾，最多2层；准备阶段选择则留到下一波。可重复选择。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803">
+      <x:c r="A803" s="15" t="n">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="B803" s="13" t="str">
+        <x:v>challenge.xpProgress</x:v>
+      </x:c>
+      <x:c r="C803" s="13" t="str">
+        <x:v>补给 {p0}/{p1} · 还差{p2}经验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804">
+      <x:c r="A804" s="15" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="B804" s="13" t="str">
+        <x:v>challenge.xpReady</x:v>
+      </x:c>
+      <x:c r="C804" s="13" t="str">
+        <x:v>补给即将送达</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805">
+      <x:c r="A805" s="15" t="n">
+        <x:v>801</x:v>
+      </x:c>
+      <x:c r="B805" s="13" t="str">
+        <x:v>challenge.xpComplete</x:v>
+      </x:c>
+      <x:c r="C805" s="13" t="str">
+        <x:v>补给已满 {p0}/{p1}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R822b6d2be4644090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R82ed7412d9494133"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2841,7 +2841,7 @@
         <x:v>ui.GameRoot.030</x:v>
       </x:c>
       <x:c r="C229" s="13" t="str">
-        <x:v>第 {p0} 关{p1}</x:v>
+        <x:v>{p0}</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="58" hidden="0" customHeight="1">
@@ -9182,6 +9182,798 @@
       </x:c>
       <x:c r="C805" s="13" t="str">
         <x:v>补给已满 {p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806">
+      <x:c r="A806" s="15" t="n">
+        <x:v>802</x:v>
+      </x:c>
+      <x:c r="B806" s="13" t="str">
+        <x:v>enemy.mochi.name</x:v>
+      </x:c>
+      <x:c r="C806" s="13" t="str">
+        <x:v>麻薯团子</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807">
+      <x:c r="A807" s="15" t="n">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c r="B807" s="13" t="str">
+        <x:v>collection.enemy-mochi.category</x:v>
+      </x:c>
+      <x:c r="C807" s="13" t="str">
+        <x:v>软糯来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808">
+      <x:c r="A808" s="15" t="n">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="B808" s="13" t="str">
+        <x:v>collection.enemy-mochi.traits</x:v>
+      </x:c>
+      <x:c r="C808" s="13" t="str">
+        <x:v>生命适中，保持均衡火力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809">
+      <x:c r="A809" s="15" t="n">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c r="B809" s="13" t="str">
+        <x:v>collection.enemy-mochi.story</x:v>
+      </x:c>
+      <x:c r="C809" s="13" t="str">
+        <x:v>从甜品柜溜出来的小团子，最喜欢赶热闹。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810">
+      <x:c r="A810" s="15" t="n">
+        <x:v>806</x:v>
+      </x:c>
+      <x:c r="B810" s="13" t="str">
+        <x:v>enemy.popcorn.name</x:v>
+      </x:c>
+      <x:c r="C810" s="13" t="str">
+        <x:v>爆米花客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811">
+      <x:c r="A811" s="15" t="n">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="B811" s="13" t="str">
+        <x:v>collection.enemy-popcorn.category</x:v>
+      </x:c>
+      <x:c r="C811" s="13" t="str">
+        <x:v>轻快来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812">
+      <x:c r="A812" s="15" t="n">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="B812" s="13" t="str">
+        <x:v>collection.enemy-popcorn.traits</x:v>
+      </x:c>
+      <x:c r="C812" s="13" t="str">
+        <x:v>行动较快，注意补足路线后段火力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813">
+      <x:c r="A813" s="15" t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="B813" s="13" t="str">
+        <x:v>collection.enemy-popcorn.story</x:v>
+      </x:c>
+      <x:c r="C813" s="13" t="str">
+        <x:v>一听到叮咚门铃，头顶的爆米花就跳个不停。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814">
+      <x:c r="A814" s="15" t="n">
+        <x:v>810</x:v>
+      </x:c>
+      <x:c r="B814" s="13" t="str">
+        <x:v>enemy.noodlecup.name</x:v>
+      </x:c>
+      <x:c r="C814" s="13" t="str">
+        <x:v>泡面桶客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815">
+      <x:c r="A815" s="15" t="n">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="B815" s="13" t="str">
+        <x:v>collection.enemy-noodlecup.category</x:v>
+      </x:c>
+      <x:c r="C815" s="13" t="str">
+        <x:v>耐打来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816">
+      <x:c r="A816" s="15" t="n">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c r="B816" s="13" t="str">
+        <x:v>collection.enemy-noodlecup.traits</x:v>
+      </x:c>
+      <x:c r="C816" s="13" t="str">
+        <x:v>生命较高，清场道具伤害减半以上。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817">
+      <x:c r="A817" s="15" t="n">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c r="B817" s="13" t="str">
+        <x:v>collection.enemy-noodlecup.story</x:v>
+      </x:c>
+      <x:c r="C817" s="13" t="str">
+        <x:v>盖子永远掀开一角，说是怕错过夜宵。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818">
+      <x:c r="A818" s="15" t="n">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="B818" s="13" t="str">
+        <x:v>enemy.frostdonut.name</x:v>
+      </x:c>
+      <x:c r="C818" s="13" t="str">
+        <x:v>霜糖甜圈</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819">
+      <x:c r="A819" s="15" t="n">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="B819" s="13" t="str">
+        <x:v>collection.enemy-frostdonut.category</x:v>
+      </x:c>
+      <x:c r="C819" s="13" t="str">
+        <x:v>厚实来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820">
+      <x:c r="A820" s="15" t="n">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="B820" s="13" t="str">
+        <x:v>collection.enemy-frostdonut.traits</x:v>
+      </x:c>
+      <x:c r="C820" s="13" t="str">
+        <x:v>生命较高，减速配合集中火力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821">
+      <x:c r="A821" s="15" t="n">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c r="B821" s="13" t="str">
+        <x:v>collection.enemy-frostdonut.story</x:v>
+      </x:c>
+      <x:c r="C821" s="13" t="str">
+        <x:v>裹着一层厚厚糖霜，把夜班当成甜品巡游。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822">
+      <x:c r="A822" s="15" t="n">
+        <x:v>818</x:v>
+      </x:c>
+      <x:c r="B822" s="13" t="str">
+        <x:v>enemy.freezer.name</x:v>
+      </x:c>
+      <x:c r="C822" s="13" t="str">
+        <x:v>霜柜男爵</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823">
+      <x:c r="A823" s="15" t="n">
+        <x:v>819</x:v>
+      </x:c>
+      <x:c r="B823" s="13" t="str">
+        <x:v>collection.boss-freezer.category</x:v>
+      </x:c>
+      <x:c r="C823" s="13" t="str">
+        <x:v>冷柜首领</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824">
+      <x:c r="A824" s="15" t="n">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="B824" s="13" t="str">
+        <x:v>collection.boss-freezer.traits</x:v>
+      </x:c>
+      <x:c r="C824" s="13" t="str">
+        <x:v>高生命首领；漏过会造成大量损失。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825">
+      <x:c r="A825" s="15" t="n">
+        <x:v>821</x:v>
+      </x:c>
+      <x:c r="B825" s="13" t="str">
+        <x:v>collection.boss-freezer.story</x:v>
+      </x:c>
+      <x:c r="C825" s="13" t="str">
+        <x:v>自封冷柜男爵，披着冰蓝斗篷来检查夜班秩序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826">
+      <x:c r="A826" s="15" t="n">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c r="B826" s="13" t="str">
+        <x:v>enemy.vending.name</x:v>
+      </x:c>
+      <x:c r="C826" s="13" t="str">
+        <x:v>贩卖机大王</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827">
+      <x:c r="A827" s="15" t="n">
+        <x:v>823</x:v>
+      </x:c>
+      <x:c r="B827" s="13" t="str">
+        <x:v>collection.boss-vending.category</x:v>
+      </x:c>
+      <x:c r="C827" s="13" t="str">
+        <x:v>黎明首领</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828">
+      <x:c r="A828" s="15" t="n">
+        <x:v>824</x:v>
+      </x:c>
+      <x:c r="B828" s="13" t="str">
+        <x:v>collection.boss-vending.traits</x:v>
+      </x:c>
+      <x:c r="C828" s="13" t="str">
+        <x:v>极高生命的压轴首领；提前升级并集中火力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829">
+      <x:c r="A829" s="15" t="n">
+        <x:v>825</x:v>
+      </x:c>
+      <x:c r="B829" s="13" t="str">
+        <x:v>collection.boss-vending.story</x:v>
+      </x:c>
+      <x:c r="C829" s="13" t="str">
+        <x:v>在天亮前推开店门，坚持称自己为整条街的零食之王。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830">
+      <x:c r="A830" s="15" t="n">
+        <x:v>826</x:v>
+      </x:c>
+      <x:c r="B830" s="13" t="str">
+        <x:v>level.21.title</x:v>
+      </x:c>
+      <x:c r="C830" s="13" t="str">
+        <x:v>晨市开张</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831">
+      <x:c r="A831" s="15" t="n">
+        <x:v>827</x:v>
+      </x:c>
+      <x:c r="B831" s="13" t="str">
+        <x:v>level.21.goal</x:v>
+      </x:c>
+      <x:c r="C831" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832">
+      <x:c r="A832" s="15" t="n">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="B832" s="13" t="str">
+        <x:v>wave.21.opening</x:v>
+      </x:c>
+      <x:c r="C832" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833">
+      <x:c r="A833" s="15" t="n">
+        <x:v>829</x:v>
+      </x:c>
+      <x:c r="B833" s="13" t="str">
+        <x:v>wave.21.final</x:v>
+      </x:c>
+      <x:c r="C833" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834">
+      <x:c r="A834" s="15" t="n">
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="B834" s="13" t="str">
+        <x:v>level.22.title</x:v>
+      </x:c>
+      <x:c r="C834" s="13" t="str">
+        <x:v>街角热闹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835">
+      <x:c r="A835" s="15" t="n">
+        <x:v>831</x:v>
+      </x:c>
+      <x:c r="B835" s="13" t="str">
+        <x:v>level.22.goal</x:v>
+      </x:c>
+      <x:c r="C835" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836">
+      <x:c r="A836" s="15" t="n">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c r="B836" s="13" t="str">
+        <x:v>wave.22.opening</x:v>
+      </x:c>
+      <x:c r="C836" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="837">
+      <x:c r="A837" s="15" t="n">
+        <x:v>833</x:v>
+      </x:c>
+      <x:c r="B837" s="13" t="str">
+        <x:v>wave.22.final</x:v>
+      </x:c>
+      <x:c r="C837" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="838">
+      <x:c r="A838" s="15" t="n">
+        <x:v>834</x:v>
+      </x:c>
+      <x:c r="B838" s="13" t="str">
+        <x:v>level.23.title</x:v>
+      </x:c>
+      <x:c r="C838" s="13" t="str">
+        <x:v>甜品巷口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="839">
+      <x:c r="A839" s="15" t="n">
+        <x:v>835</x:v>
+      </x:c>
+      <x:c r="B839" s="13" t="str">
+        <x:v>level.23.goal</x:v>
+      </x:c>
+      <x:c r="C839" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="840">
+      <x:c r="A840" s="15" t="n">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="B840" s="13" t="str">
+        <x:v>wave.23.opening</x:v>
+      </x:c>
+      <x:c r="C840" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="841">
+      <x:c r="A841" s="15" t="n">
+        <x:v>837</x:v>
+      </x:c>
+      <x:c r="B841" s="13" t="str">
+        <x:v>wave.23.final</x:v>
+      </x:c>
+      <x:c r="C841" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="842">
+      <x:c r="A842" s="15" t="n">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c r="B842" s="13" t="str">
+        <x:v>level.24.title</x:v>
+      </x:c>
+      <x:c r="C842" s="13" t="str">
+        <x:v>补货高峰</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="843">
+      <x:c r="A843" s="15" t="n">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c r="B843" s="13" t="str">
+        <x:v>level.24.goal</x:v>
+      </x:c>
+      <x:c r="C843" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="844">
+      <x:c r="A844" s="15" t="n">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="B844" s="13" t="str">
+        <x:v>wave.24.opening</x:v>
+      </x:c>
+      <x:c r="C844" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="845">
+      <x:c r="A845" s="15" t="n">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="B845" s="13" t="str">
+        <x:v>wave.24.final</x:v>
+      </x:c>
+      <x:c r="C845" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="846">
+      <x:c r="A846" s="15" t="n">
+        <x:v>842</x:v>
+      </x:c>
+      <x:c r="B846" s="13" t="str">
+        <x:v>level.25.title</x:v>
+      </x:c>
+      <x:c r="C846" s="13" t="str">
+        <x:v>冷柜来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="847">
+      <x:c r="A847" s="15" t="n">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="B847" s="13" t="str">
+        <x:v>level.25.goal</x:v>
+      </x:c>
+      <x:c r="C847" s="13" t="str">
+        <x:v>守住冷柜男爵带领的20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="848">
+      <x:c r="A848" s="15" t="n">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="B848" s="13" t="str">
+        <x:v>wave.25.opening</x:v>
+      </x:c>
+      <x:c r="C848" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="849">
+      <x:c r="A849" s="15" t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="B849" s="13" t="str">
+        <x:v>wave.25.final</x:v>
+      </x:c>
+      <x:c r="C849" s="13" t="str">
+        <x:v>霜柜男爵到了！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="850">
+      <x:c r="A850" s="15" t="n">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="B850" s="13" t="str">
+        <x:v>level.26.title</x:v>
+      </x:c>
+      <x:c r="C850" s="13" t="str">
+        <x:v>夜宵集结</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="851">
+      <x:c r="A851" s="15" t="n">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="B851" s="13" t="str">
+        <x:v>level.26.goal</x:v>
+      </x:c>
+      <x:c r="C851" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="852">
+      <x:c r="A852" s="15" t="n">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="B852" s="13" t="str">
+        <x:v>wave.26.opening</x:v>
+      </x:c>
+      <x:c r="C852" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="853">
+      <x:c r="A853" s="15" t="n">
+        <x:v>849</x:v>
+      </x:c>
+      <x:c r="B853" s="13" t="str">
+        <x:v>wave.26.final</x:v>
+      </x:c>
+      <x:c r="C853" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="854">
+      <x:c r="A854" s="15" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="B854" s="13" t="str">
+        <x:v>level.27.title</x:v>
+      </x:c>
+      <x:c r="C854" s="13" t="str">
+        <x:v>糖霜街区</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="855">
+      <x:c r="A855" s="15" t="n">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="B855" s="13" t="str">
+        <x:v>level.27.goal</x:v>
+      </x:c>
+      <x:c r="C855" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="856">
+      <x:c r="A856" s="15" t="n">
+        <x:v>852</x:v>
+      </x:c>
+      <x:c r="B856" s="13" t="str">
+        <x:v>wave.27.opening</x:v>
+      </x:c>
+      <x:c r="C856" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="857">
+      <x:c r="A857" s="15" t="n">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="B857" s="13" t="str">
+        <x:v>wave.27.final</x:v>
+      </x:c>
+      <x:c r="C857" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="858">
+      <x:c r="A858" s="15" t="n">
+        <x:v>854</x:v>
+      </x:c>
+      <x:c r="B858" s="13" t="str">
+        <x:v>level.28.title</x:v>
+      </x:c>
+      <x:c r="C858" s="13" t="str">
+        <x:v>长夜巡店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="859">
+      <x:c r="A859" s="15" t="n">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="B859" s="13" t="str">
+        <x:v>level.28.goal</x:v>
+      </x:c>
+      <x:c r="C859" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="860">
+      <x:c r="A860" s="15" t="n">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="B860" s="13" t="str">
+        <x:v>wave.28.opening</x:v>
+      </x:c>
+      <x:c r="C860" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="861">
+      <x:c r="A861" s="15" t="n">
+        <x:v>857</x:v>
+      </x:c>
+      <x:c r="B861" s="13" t="str">
+        <x:v>wave.28.final</x:v>
+      </x:c>
+      <x:c r="C861" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="862">
+      <x:c r="A862" s="15" t="n">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="B862" s="13" t="str">
+        <x:v>level.29.title</x:v>
+      </x:c>
+      <x:c r="C862" s="13" t="str">
+        <x:v>最后的门铃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="863">
+      <x:c r="A863" s="15" t="n">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="B863" s="13" t="str">
+        <x:v>level.29.goal</x:v>
+      </x:c>
+      <x:c r="C863" s="13" t="str">
+        <x:v>交替布置火力，守住20波来客</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="864">
+      <x:c r="A864" s="15" t="n">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="B864" s="13" t="str">
+        <x:v>wave.29.opening</x:v>
+      </x:c>
+      <x:c r="C864" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="865">
+      <x:c r="A865" s="15" t="n">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c r="B865" s="13" t="str">
+        <x:v>wave.29.final</x:v>
+      </x:c>
+      <x:c r="C865" s="13" t="str">
+        <x:v>最后一波，坚持住！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="866">
+      <x:c r="A866" s="15" t="n">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c r="B866" s="13" t="str">
+        <x:v>level.30.title</x:v>
+      </x:c>
+      <x:c r="C866" s="13" t="str">
+        <x:v>黎明守店</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="867">
+      <x:c r="A867" s="15" t="n">
+        <x:v>863</x:v>
+      </x:c>
+      <x:c r="B867" s="13" t="str">
+        <x:v>level.30.goal</x:v>
+      </x:c>
+      <x:c r="C867" s="13" t="str">
+        <x:v>抵挡20波攻势，迎战贩卖机大王</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="868">
+      <x:c r="A868" s="15" t="n">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="B868" s="13" t="str">
+        <x:v>wave.30.opening</x:v>
+      </x:c>
+      <x:c r="C868" s="13" t="str">
+        <x:v>夜班开始，准备迎客！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="869">
+      <x:c r="A869" s="15" t="n">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="B869" s="13" t="str">
+        <x:v>wave.30.final</x:v>
+      </x:c>
+      <x:c r="C869" s="13" t="str">
+        <x:v>贩卖机大王来了！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="870">
+      <x:c r="A870" s="15" t="n">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="B870" s="13" t="str">
+        <x:v>topics.freezer.title</x:v>
+      </x:c>
+      <x:c r="C870" s="13" t="str">
+        <x:v>霜柜夜袭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="871">
+      <x:c r="A871" s="15" t="n">
+        <x:v>867</x:v>
+      </x:c>
+      <x:c r="B871" s="13" t="str">
+        <x:v>topics.freezer.rule</x:v>
+      </x:c>
+      <x:c r="C871" s="13" t="str">
+        <x:v>四种店员都到岗时，全员伤害提高18%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="872">
+      <x:c r="A872" s="15" t="n">
+        <x:v>868</x:v>
+      </x:c>
+      <x:c r="B872" s="13" t="str">
+        <x:v>topics.gifts.title</x:v>
+      </x:c>
+      <x:c r="C872" s="13" t="str">
+        <x:v>礼盒巡游</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="873">
+      <x:c r="A873" s="15" t="n">
+        <x:v>869</x:v>
+      </x:c>
+      <x:c r="B873" s="13" t="str">
+        <x:v>topics.gifts.rule</x:v>
+      </x:c>
+      <x:c r="C873" s="13" t="str">
+        <x:v>击退来客掉落礼物，补充金币并攻击附近敌人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="874">
+      <x:c r="A874" s="15" t="n">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c r="B874" s="13" t="str">
+        <x:v>topics.storm.title</x:v>
+      </x:c>
+      <x:c r="C874" s="13" t="str">
+        <x:v>糖雨风暴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="875">
+      <x:c r="A875" s="15" t="n">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="B875" s="13" t="str">
+        <x:v>topics.storm.rule</x:v>
+      </x:c>
+      <x:c r="C875" s="13" t="str">
+        <x:v>每12秒落下2颗糖果，攻击前排来客。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="876">
+      <x:c r="A876" s="15" t="n">
+        <x:v>872</x:v>
+      </x:c>
+      <x:c r="B876" s="13" t="str">
+        <x:v>topics.dawn.title</x:v>
+      </x:c>
+      <x:c r="C876" s="13" t="str">
+        <x:v>黎明决战</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="877">
+      <x:c r="A877" s="15" t="n">
+        <x:v>873</x:v>
+      </x:c>
+      <x:c r="B877" s="13" t="str">
+        <x:v>topics.dawn.rule</x:v>
+      </x:c>
+      <x:c r="C877" s="13" t="str">
+        <x:v>附近有其他种类店员时，伤害提高14%。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R82ed7412d9494133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rd958a4e0220e417f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9976,6 +9976,1502 @@
         <x:v>附近有其他种类店员时，伤害提高14%。</x:v>
       </x:c>
     </x:row>
+    <x:row r="878">
+      <x:c r="A878" s="15" t="n">
+        <x:v>874</x:v>
+      </x:c>
+      <x:c r="B878" s="13" t="str">
+        <x:v>tech.branch.sprout</x:v>
+      </x:c>
+      <x:c r="C878" s="13" t="str">
+        <x:v>豆包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="879">
+      <x:c r="A879" s="15" t="n">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="B879" s="13" t="str">
+        <x:v>tech.node.sprout_1.name</x:v>
+      </x:c>
+      <x:c r="C879" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="880">
+      <x:c r="A880" s="15" t="n">
+        <x:v>876</x:v>
+      </x:c>
+      <x:c r="B880" s="13" t="str">
+        <x:v>tech.node.sprout_1.desc</x:v>
+      </x:c>
+      <x:c r="C880" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="881">
+      <x:c r="A881" s="15" t="n">
+        <x:v>877</x:v>
+      </x:c>
+      <x:c r="B881" s="13" t="str">
+        <x:v>tech.node.sprout_2.name</x:v>
+      </x:c>
+      <x:c r="C881" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="882">
+      <x:c r="A882" s="15" t="n">
+        <x:v>878</x:v>
+      </x:c>
+      <x:c r="B882" s="13" t="str">
+        <x:v>tech.node.sprout_2.desc</x:v>
+      </x:c>
+      <x:c r="C882" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883">
+      <x:c r="A883" s="15" t="n">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="B883" s="13" t="str">
+        <x:v>tech.node.sprout_3.name</x:v>
+      </x:c>
+      <x:c r="C883" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="884">
+      <x:c r="A884" s="15" t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="B884" s="13" t="str">
+        <x:v>tech.node.sprout_3.desc</x:v>
+      </x:c>
+      <x:c r="C884" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="885">
+      <x:c r="A885" s="15" t="n">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c r="B885" s="13" t="str">
+        <x:v>tech.node.sprout_4.name</x:v>
+      </x:c>
+      <x:c r="C885" s="13" t="str">
+        <x:v>火力改良</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="886">
+      <x:c r="A886" s="15" t="n">
+        <x:v>882</x:v>
+      </x:c>
+      <x:c r="B886" s="13" t="str">
+        <x:v>tech.node.sprout_4.desc</x:v>
+      </x:c>
+      <x:c r="C886" s="13" t="str">
+        <x:v>直击伤害额外提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="887">
+      <x:c r="A887" s="15" t="n">
+        <x:v>883</x:v>
+      </x:c>
+      <x:c r="B887" s="13" t="str">
+        <x:v>tech.node.sprout_5.name</x:v>
+      </x:c>
+      <x:c r="C887" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="888">
+      <x:c r="A888" s="15" t="n">
+        <x:v>884</x:v>
+      </x:c>
+      <x:c r="B888" s="13" t="str">
+        <x:v>tech.node.sprout_5.desc</x:v>
+      </x:c>
+      <x:c r="C888" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="889">
+      <x:c r="A889" s="15" t="n">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c r="B889" s="13" t="str">
+        <x:v>tech.branch.frost</x:v>
+      </x:c>
+      <x:c r="C889" s="13" t="str">
+        <x:v>棉棉</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="890">
+      <x:c r="A890" s="15" t="n">
+        <x:v>886</x:v>
+      </x:c>
+      <x:c r="B890" s="13" t="str">
+        <x:v>tech.node.frost_1.name</x:v>
+      </x:c>
+      <x:c r="C890" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="891">
+      <x:c r="A891" s="15" t="n">
+        <x:v>887</x:v>
+      </x:c>
+      <x:c r="B891" s="13" t="str">
+        <x:v>tech.node.frost_1.desc</x:v>
+      </x:c>
+      <x:c r="C891" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="892">
+      <x:c r="A892" s="15" t="n">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="B892" s="13" t="str">
+        <x:v>tech.node.frost_2.name</x:v>
+      </x:c>
+      <x:c r="C892" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="893">
+      <x:c r="A893" s="15" t="n">
+        <x:v>889</x:v>
+      </x:c>
+      <x:c r="B893" s="13" t="str">
+        <x:v>tech.node.frost_2.desc</x:v>
+      </x:c>
+      <x:c r="C893" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="894">
+      <x:c r="A894" s="15" t="n">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="B894" s="13" t="str">
+        <x:v>tech.node.frost_3.name</x:v>
+      </x:c>
+      <x:c r="C894" s="13" t="str">
+        <x:v>冷气延续</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="895">
+      <x:c r="A895" s="15" t="n">
+        <x:v>891</x:v>
+      </x:c>
+      <x:c r="B895" s="13" t="str">
+        <x:v>tech.node.frost_3.desc</x:v>
+      </x:c>
+      <x:c r="C895" s="13" t="str">
+        <x:v>减速效果持续时间提高8%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="896">
+      <x:c r="A896" s="15" t="n">
+        <x:v>892</x:v>
+      </x:c>
+      <x:c r="B896" s="13" t="str">
+        <x:v>tech.node.frost_4.name</x:v>
+      </x:c>
+      <x:c r="C896" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="897">
+      <x:c r="A897" s="15" t="n">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="B897" s="13" t="str">
+        <x:v>tech.node.frost_4.desc</x:v>
+      </x:c>
+      <x:c r="C897" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="898">
+      <x:c r="A898" s="15" t="n">
+        <x:v>894</x:v>
+      </x:c>
+      <x:c r="B898" s="13" t="str">
+        <x:v>tech.node.frost_5.name</x:v>
+      </x:c>
+      <x:c r="C898" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="899">
+      <x:c r="A899" s="15" t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="B899" s="13" t="str">
+        <x:v>tech.node.frost_5.desc</x:v>
+      </x:c>
+      <x:c r="C899" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="900">
+      <x:c r="A900" s="15" t="n">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="B900" s="13" t="str">
+        <x:v>tech.branch.bloom</x:v>
+      </x:c>
+      <x:c r="C900" s="13" t="str">
+        <x:v>布丁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="901">
+      <x:c r="A901" s="15" t="n">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="B901" s="13" t="str">
+        <x:v>tech.node.bloom_1.name</x:v>
+      </x:c>
+      <x:c r="C901" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="902">
+      <x:c r="A902" s="15" t="n">
+        <x:v>898</x:v>
+      </x:c>
+      <x:c r="B902" s="13" t="str">
+        <x:v>tech.node.bloom_1.desc</x:v>
+      </x:c>
+      <x:c r="C902" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="903">
+      <x:c r="A903" s="15" t="n">
+        <x:v>899</x:v>
+      </x:c>
+      <x:c r="B903" s="13" t="str">
+        <x:v>tech.node.bloom_2.name</x:v>
+      </x:c>
+      <x:c r="C903" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="904">
+      <x:c r="A904" s="15" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="B904" s="13" t="str">
+        <x:v>tech.node.bloom_2.desc</x:v>
+      </x:c>
+      <x:c r="C904" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="905">
+      <x:c r="A905" s="15" t="n">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c r="B905" s="13" t="str">
+        <x:v>tech.node.bloom_3.name</x:v>
+      </x:c>
+      <x:c r="C905" s="13" t="str">
+        <x:v>礼花扩散</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="906">
+      <x:c r="A906" s="15" t="n">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c r="B906" s="13" t="str">
+        <x:v>tech.node.bloom_3.desc</x:v>
+      </x:c>
+      <x:c r="C906" s="13" t="str">
+        <x:v>爆炸范围提高6%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="907">
+      <x:c r="A907" s="15" t="n">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="B907" s="13" t="str">
+        <x:v>tech.node.bloom_4.name</x:v>
+      </x:c>
+      <x:c r="C907" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="908">
+      <x:c r="A908" s="15" t="n">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="B908" s="13" t="str">
+        <x:v>tech.node.bloom_4.desc</x:v>
+      </x:c>
+      <x:c r="C908" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="909">
+      <x:c r="A909" s="15" t="n">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="B909" s="13" t="str">
+        <x:v>tech.node.bloom_5.name</x:v>
+      </x:c>
+      <x:c r="C909" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="910">
+      <x:c r="A910" s="15" t="n">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c r="B910" s="13" t="str">
+        <x:v>tech.node.bloom_5.desc</x:v>
+      </x:c>
+      <x:c r="C910" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="911">
+      <x:c r="A911" s="15" t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="B911" s="13" t="str">
+        <x:v>tech.branch.scope</x:v>
+      </x:c>
+      <x:c r="C911" s="13" t="str">
+        <x:v>咕咕</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="912">
+      <x:c r="A912" s="15" t="n">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c r="B912" s="13" t="str">
+        <x:v>tech.node.scope_1.name</x:v>
+      </x:c>
+      <x:c r="C912" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="913">
+      <x:c r="A913" s="15" t="n">
+        <x:v>909</x:v>
+      </x:c>
+      <x:c r="B913" s="13" t="str">
+        <x:v>tech.node.scope_1.desc</x:v>
+      </x:c>
+      <x:c r="C913" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="914">
+      <x:c r="A914" s="15" t="n">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="B914" s="13" t="str">
+        <x:v>tech.node.scope_2.name</x:v>
+      </x:c>
+      <x:c r="C914" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="915">
+      <x:c r="A915" s="15" t="n">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="B915" s="13" t="str">
+        <x:v>tech.node.scope_2.desc</x:v>
+      </x:c>
+      <x:c r="C915" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="916">
+      <x:c r="A916" s="15" t="n">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="B916" s="13" t="str">
+        <x:v>tech.node.scope_3.name</x:v>
+      </x:c>
+      <x:c r="C916" s="13" t="str">
+        <x:v>贯穿训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="917">
+      <x:c r="A917" s="15" t="n">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="B917" s="13" t="str">
+        <x:v>tech.node.scope_3.desc</x:v>
+      </x:c>
+      <x:c r="C917" s="13" t="str">
+        <x:v>穿透长度提高6%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="918">
+      <x:c r="A918" s="15" t="n">
+        <x:v>914</x:v>
+      </x:c>
+      <x:c r="B918" s="13" t="str">
+        <x:v>tech.node.scope_4.name</x:v>
+      </x:c>
+      <x:c r="C918" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="919">
+      <x:c r="A919" s="15" t="n">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="B919" s="13" t="str">
+        <x:v>tech.node.scope_4.desc</x:v>
+      </x:c>
+      <x:c r="C919" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="920">
+      <x:c r="A920" s="15" t="n">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="B920" s="13" t="str">
+        <x:v>tech.node.scope_5.name</x:v>
+      </x:c>
+      <x:c r="C920" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="921">
+      <x:c r="A921" s="15" t="n">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="B921" s="13" t="str">
+        <x:v>tech.node.scope_5.desc</x:v>
+      </x:c>
+      <x:c r="C921" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="922">
+      <x:c r="A922" s="15" t="n">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="B922" s="13" t="str">
+        <x:v>tech.branch.spark</x:v>
+      </x:c>
+      <x:c r="C922" s="13" t="str">
+        <x:v>栗栗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="923">
+      <x:c r="A923" s="15" t="n">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="B923" s="13" t="str">
+        <x:v>tech.node.spark_1.name</x:v>
+      </x:c>
+      <x:c r="C923" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="924">
+      <x:c r="A924" s="15" t="n">
+        <x:v>920</x:v>
+      </x:c>
+      <x:c r="B924" s="13" t="str">
+        <x:v>tech.node.spark_1.desc</x:v>
+      </x:c>
+      <x:c r="C924" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="925">
+      <x:c r="A925" s="15" t="n">
+        <x:v>921</x:v>
+      </x:c>
+      <x:c r="B925" s="13" t="str">
+        <x:v>tech.node.spark_2.name</x:v>
+      </x:c>
+      <x:c r="C925" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="926">
+      <x:c r="A926" s="15" t="n">
+        <x:v>922</x:v>
+      </x:c>
+      <x:c r="B926" s="13" t="str">
+        <x:v>tech.node.spark_2.desc</x:v>
+      </x:c>
+      <x:c r="C926" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="927">
+      <x:c r="A927" s="15" t="n">
+        <x:v>923</x:v>
+      </x:c>
+      <x:c r="B927" s="13" t="str">
+        <x:v>tech.node.spark_3.name</x:v>
+      </x:c>
+      <x:c r="C927" s="13" t="str">
+        <x:v>电链精研</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="928">
+      <x:c r="A928" s="15" t="n">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="B928" s="13" t="str">
+        <x:v>tech.node.spark_3.desc</x:v>
+      </x:c>
+      <x:c r="C928" s="13" t="str">
+        <x:v>连锁每次传递的伤害保留系数提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="929">
+      <x:c r="A929" s="15" t="n">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="B929" s="13" t="str">
+        <x:v>tech.node.spark_4.name</x:v>
+      </x:c>
+      <x:c r="C929" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="930">
+      <x:c r="A930" s="15" t="n">
+        <x:v>926</x:v>
+      </x:c>
+      <x:c r="B930" s="13" t="str">
+        <x:v>tech.node.spark_4.desc</x:v>
+      </x:c>
+      <x:c r="C930" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="931">
+      <x:c r="A931" s="15" t="n">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="B931" s="13" t="str">
+        <x:v>tech.node.spark_5.name</x:v>
+      </x:c>
+      <x:c r="C931" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="932">
+      <x:c r="A932" s="15" t="n">
+        <x:v>928</x:v>
+      </x:c>
+      <x:c r="B932" s="13" t="str">
+        <x:v>tech.node.spark_5.desc</x:v>
+      </x:c>
+      <x:c r="C932" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="933">
+      <x:c r="A933" s="15" t="n">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="B933" s="13" t="str">
+        <x:v>tech.branch.ember</x:v>
+      </x:c>
+      <x:c r="C933" s="13" t="str">
+        <x:v>烘烘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="934">
+      <x:c r="A934" s="15" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="B934" s="13" t="str">
+        <x:v>tech.node.ember_1.name</x:v>
+      </x:c>
+      <x:c r="C934" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="935">
+      <x:c r="A935" s="15" t="n">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="B935" s="13" t="str">
+        <x:v>tech.node.ember_1.desc</x:v>
+      </x:c>
+      <x:c r="C935" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="936">
+      <x:c r="A936" s="15" t="n">
+        <x:v>932</x:v>
+      </x:c>
+      <x:c r="B936" s="13" t="str">
+        <x:v>tech.node.ember_2.name</x:v>
+      </x:c>
+      <x:c r="C936" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="937">
+      <x:c r="A937" s="15" t="n">
+        <x:v>933</x:v>
+      </x:c>
+      <x:c r="B937" s="13" t="str">
+        <x:v>tech.node.ember_2.desc</x:v>
+      </x:c>
+      <x:c r="C937" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="938">
+      <x:c r="A938" s="15" t="n">
+        <x:v>934</x:v>
+      </x:c>
+      <x:c r="B938" s="13" t="str">
+        <x:v>tech.node.ember_3.name</x:v>
+      </x:c>
+      <x:c r="C938" s="13" t="str">
+        <x:v>余火绵长</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="939">
+      <x:c r="A939" s="15" t="n">
+        <x:v>935</x:v>
+      </x:c>
+      <x:c r="B939" s="13" t="str">
+        <x:v>tech.node.ember_3.desc</x:v>
+      </x:c>
+      <x:c r="C939" s="13" t="str">
+        <x:v>灼烧持续时间提高8%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="940">
+      <x:c r="A940" s="15" t="n">
+        <x:v>936</x:v>
+      </x:c>
+      <x:c r="B940" s="13" t="str">
+        <x:v>tech.node.ember_4.name</x:v>
+      </x:c>
+      <x:c r="C940" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="941">
+      <x:c r="A941" s="15" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="B941" s="13" t="str">
+        <x:v>tech.node.ember_4.desc</x:v>
+      </x:c>
+      <x:c r="C941" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="942">
+      <x:c r="A942" s="15" t="n">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="B942" s="13" t="str">
+        <x:v>tech.node.ember_5.name</x:v>
+      </x:c>
+      <x:c r="C942" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="943">
+      <x:c r="A943" s="15" t="n">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="B943" s="13" t="str">
+        <x:v>tech.node.ember_5.desc</x:v>
+      </x:c>
+      <x:c r="C943" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="944">
+      <x:c r="A944" s="15" t="n">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="B944" s="13" t="str">
+        <x:v>tech.branch.mint</x:v>
+      </x:c>
+      <x:c r="C944" s="13" t="str">
+        <x:v>薄荷</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="945">
+      <x:c r="A945" s="15" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="B945" s="13" t="str">
+        <x:v>tech.node.mint_1.name</x:v>
+      </x:c>
+      <x:c r="C945" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="946">
+      <x:c r="A946" s="15" t="n">
+        <x:v>942</x:v>
+      </x:c>
+      <x:c r="B946" s="13" t="str">
+        <x:v>tech.node.mint_1.desc</x:v>
+      </x:c>
+      <x:c r="C946" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="947">
+      <x:c r="A947" s="15" t="n">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="B947" s="13" t="str">
+        <x:v>tech.node.mint_2.name</x:v>
+      </x:c>
+      <x:c r="C947" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="948">
+      <x:c r="A948" s="15" t="n">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="B948" s="13" t="str">
+        <x:v>tech.node.mint_2.desc</x:v>
+      </x:c>
+      <x:c r="C948" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="949">
+      <x:c r="A949" s="15" t="n">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="B949" s="13" t="str">
+        <x:v>tech.node.mint_3.name</x:v>
+      </x:c>
+      <x:c r="C949" s="13" t="str">
+        <x:v>标记延续</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="950">
+      <x:c r="A950" s="15" t="n">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="B950" s="13" t="str">
+        <x:v>tech.node.mint_3.desc</x:v>
+      </x:c>
+      <x:c r="C950" s="13" t="str">
+        <x:v>标记持续时间提高8%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="951">
+      <x:c r="A951" s="15" t="n">
+        <x:v>947</x:v>
+      </x:c>
+      <x:c r="B951" s="13" t="str">
+        <x:v>tech.node.mint_4.name</x:v>
+      </x:c>
+      <x:c r="C951" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="952">
+      <x:c r="A952" s="15" t="n">
+        <x:v>948</x:v>
+      </x:c>
+      <x:c r="B952" s="13" t="str">
+        <x:v>tech.node.mint_4.desc</x:v>
+      </x:c>
+      <x:c r="C952" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="953">
+      <x:c r="A953" s="15" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="B953" s="13" t="str">
+        <x:v>tech.node.mint_5.name</x:v>
+      </x:c>
+      <x:c r="C953" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="954">
+      <x:c r="A954" s="15" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="B954" s="13" t="str">
+        <x:v>tech.node.mint_5.desc</x:v>
+      </x:c>
+      <x:c r="C954" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="955">
+      <x:c r="A955" s="15" t="n">
+        <x:v>951</x:v>
+      </x:c>
+      <x:c r="B955" s="13" t="str">
+        <x:v>tech.branch.fan</x:v>
+      </x:c>
+      <x:c r="C955" s="13" t="str">
+        <x:v>啾啾</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="956">
+      <x:c r="A956" s="15" t="n">
+        <x:v>952</x:v>
+      </x:c>
+      <x:c r="B956" s="13" t="str">
+        <x:v>tech.node.fan_1.name</x:v>
+      </x:c>
+      <x:c r="C956" s="13" t="str">
+        <x:v>扎实训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="957">
+      <x:c r="A957" s="15" t="n">
+        <x:v>953</x:v>
+      </x:c>
+      <x:c r="B957" s="13" t="str">
+        <x:v>tech.node.fan_1.desc</x:v>
+      </x:c>
+      <x:c r="C957" s="13" t="str">
+        <x:v>直击伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="958">
+      <x:c r="A958" s="15" t="n">
+        <x:v>954</x:v>
+      </x:c>
+      <x:c r="B958" s="13" t="str">
+        <x:v>tech.node.fan_2.name</x:v>
+      </x:c>
+      <x:c r="C958" s="13" t="str">
+        <x:v>站位练习</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="959">
+      <x:c r="A959" s="15" t="n">
+        <x:v>955</x:v>
+      </x:c>
+      <x:c r="B959" s="13" t="str">
+        <x:v>tech.node.fan_2.desc</x:v>
+      </x:c>
+      <x:c r="C959" s="13" t="str">
+        <x:v>射程提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="960">
+      <x:c r="A960" s="15" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="B960" s="13" t="str">
+        <x:v>tech.node.fan_3.name</x:v>
+      </x:c>
+      <x:c r="C960" s="13" t="str">
+        <x:v>熟练手法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="961">
+      <x:c r="A961" s="15" t="n">
+        <x:v>957</x:v>
+      </x:c>
+      <x:c r="B961" s="13" t="str">
+        <x:v>tech.node.fan_3.desc</x:v>
+      </x:c>
+      <x:c r="C961" s="13" t="str">
+        <x:v>攻击间隔缩短4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="962">
+      <x:c r="A962" s="15" t="n">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c r="B962" s="13" t="str">
+        <x:v>tech.node.fan_4.name</x:v>
+      </x:c>
+      <x:c r="C962" s="13" t="str">
+        <x:v>火力改良</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="963">
+      <x:c r="A963" s="15" t="n">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="B963" s="13" t="str">
+        <x:v>tech.node.fan_4.desc</x:v>
+      </x:c>
+      <x:c r="C963" s="13" t="str">
+        <x:v>直击伤害额外提高4%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="964">
+      <x:c r="A964" s="15" t="n">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="B964" s="13" t="str">
+        <x:v>tech.node.fan_5.name</x:v>
+      </x:c>
+      <x:c r="C964" s="13" t="str">
+        <x:v>夜班专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="965">
+      <x:c r="A965" s="15" t="n">
+        <x:v>961</x:v>
+      </x:c>
+      <x:c r="B965" s="13" t="str">
+        <x:v>tech.node.fan_5.desc</x:v>
+      </x:c>
+      <x:c r="C965" s="13" t="str">
+        <x:v>直击伤害额外提高5%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="966">
+      <x:c r="A966" s="15" t="n">
+        <x:v>962</x:v>
+      </x:c>
+      <x:c r="B966" s="13" t="str">
+        <x:v>tech.branch.logistics</x:v>
+      </x:c>
+      <x:c r="C966" s="13" t="str">
+        <x:v>后勤</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="967">
+      <x:c r="A967" s="15" t="n">
+        <x:v>963</x:v>
+      </x:c>
+      <x:c r="B967" s="13" t="str">
+        <x:v>tech.node.logistics_1.name</x:v>
+      </x:c>
+      <x:c r="C967" s="13" t="str">
+        <x:v>备料有方</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="968">
+      <x:c r="A968" s="15" t="n">
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="B968" s="13" t="str">
+        <x:v>tech.node.logistics_1.desc</x:v>
+      </x:c>
+      <x:c r="C968" s="13" t="str">
+        <x:v>建造店员费用降低2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="969">
+      <x:c r="A969" s="15" t="n">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="B969" s="13" t="str">
+        <x:v>tech.node.logistics_2.name</x:v>
+      </x:c>
+      <x:c r="C969" s="13" t="str">
+        <x:v>工具维护</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="970">
+      <x:c r="A970" s="15" t="n">
+        <x:v>966</x:v>
+      </x:c>
+      <x:c r="B970" s="13" t="str">
+        <x:v>tech.node.logistics_2.desc</x:v>
+      </x:c>
+      <x:c r="C970" s="13" t="str">
+        <x:v>升级和进化费用降低3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="971">
+      <x:c r="A971" s="15" t="n">
+        <x:v>967</x:v>
+      </x:c>
+      <x:c r="B971" s="13" t="str">
+        <x:v>tech.node.logistics_3.name</x:v>
+      </x:c>
+      <x:c r="C971" s="13" t="str">
+        <x:v>精打细算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="972">
+      <x:c r="A972" s="15" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="B972" s="13" t="str">
+        <x:v>tech.node.logistics_3.desc</x:v>
+      </x:c>
+      <x:c r="C972" s="13" t="str">
+        <x:v>建造费用再降低2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="973">
+      <x:c r="A973" s="15" t="n">
+        <x:v>969</x:v>
+      </x:c>
+      <x:c r="B973" s="13" t="str">
+        <x:v>tech.node.logistics_4.name</x:v>
+      </x:c>
+      <x:c r="C973" s="13" t="str">
+        <x:v>熟练交接</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="974">
+      <x:c r="A974" s="15" t="n">
+        <x:v>970</x:v>
+      </x:c>
+      <x:c r="B974" s="13" t="str">
+        <x:v>tech.node.logistics_4.desc</x:v>
+      </x:c>
+      <x:c r="C974" s="13" t="str">
+        <x:v>升级和进化费用再降低3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975">
+      <x:c r="A975" s="15" t="n">
+        <x:v>971</x:v>
+      </x:c>
+      <x:c r="B975" s="13" t="str">
+        <x:v>tech.node.logistics_5.name</x:v>
+      </x:c>
+      <x:c r="C975" s="13" t="str">
+        <x:v>开门备用金</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="976">
+      <x:c r="A976" s="15" t="n">
+        <x:v>972</x:v>
+      </x:c>
+      <x:c r="B976" s="13" t="str">
+        <x:v>tech.node.logistics_5.desc</x:v>
+      </x:c>
+      <x:c r="C976" s="13" t="str">
+        <x:v>每局初始战斗金币增加15。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="977">
+      <x:c r="A977" s="15" t="n">
+        <x:v>973</x:v>
+      </x:c>
+      <x:c r="B977" s="13" t="str">
+        <x:v>tech.branch.props</x:v>
+      </x:c>
+      <x:c r="C977" s="13" t="str">
+        <x:v>道具</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="978">
+      <x:c r="A978" s="15" t="n">
+        <x:v>974</x:v>
+      </x:c>
+      <x:c r="B978" s="13" t="str">
+        <x:v>tech.node.props_1.name</x:v>
+      </x:c>
+      <x:c r="C978" s="13" t="str">
+        <x:v>冷风加时</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="979">
+      <x:c r="A979" s="15" t="n">
+        <x:v>975</x:v>
+      </x:c>
+      <x:c r="B979" s="13" t="str">
+        <x:v>tech.node.props_1.desc</x:v>
+      </x:c>
+      <x:c r="C979" s="13" t="str">
+        <x:v>冻结道具持续时间增加0.4秒。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="980">
+      <x:c r="A980" s="15" t="n">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="B980" s="13" t="str">
+        <x:v>tech.node.props_2.name</x:v>
+      </x:c>
+      <x:c r="C980" s="13" t="str">
+        <x:v>零钱补包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="981">
+      <x:c r="A981" s="15" t="n">
+        <x:v>977</x:v>
+      </x:c>
+      <x:c r="B981" s="13" t="str">
+        <x:v>tech.node.props_2.desc</x:v>
+      </x:c>
+      <x:c r="C981" s="13" t="str">
+        <x:v>金币道具每次多提供8战斗金币。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="982">
+      <x:c r="A982" s="15" t="n">
+        <x:v>978</x:v>
+      </x:c>
+      <x:c r="B982" s="13" t="str">
+        <x:v>tech.node.props_3.name</x:v>
+      </x:c>
+      <x:c r="C982" s="13" t="str">
+        <x:v>冷风延续</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="983">
+      <x:c r="A983" s="15" t="n">
+        <x:v>979</x:v>
+      </x:c>
+      <x:c r="B983" s="13" t="str">
+        <x:v>tech.node.props_3.desc</x:v>
+      </x:c>
+      <x:c r="C983" s="13" t="str">
+        <x:v>冻结道具再延长0.4秒。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="984">
+      <x:c r="A984" s="15" t="n">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="B984" s="13" t="str">
+        <x:v>tech.node.props_4.name</x:v>
+      </x:c>
+      <x:c r="C984" s="13" t="str">
+        <x:v>备用零钱</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="985">
+      <x:c r="A985" s="15" t="n">
+        <x:v>981</x:v>
+      </x:c>
+      <x:c r="B985" s="13" t="str">
+        <x:v>tech.node.props_4.desc</x:v>
+      </x:c>
+      <x:c r="C985" s="13" t="str">
+        <x:v>金币道具再多提供8战斗金币。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="986">
+      <x:c r="A986" s="15" t="n">
+        <x:v>982</x:v>
+      </x:c>
+      <x:c r="B986" s="13" t="str">
+        <x:v>tech.node.props_5.name</x:v>
+      </x:c>
+      <x:c r="C986" s="13" t="str">
+        <x:v>长效冷风</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="987">
+      <x:c r="A987" s="15" t="n">
+        <x:v>983</x:v>
+      </x:c>
+      <x:c r="B987" s="13" t="str">
+        <x:v>tech.node.props_5.desc</x:v>
+      </x:c>
+      <x:c r="C987" s="13" t="str">
+        <x:v>冻结道具再延长0.6秒。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="988">
+      <x:c r="A988" s="15" t="n">
+        <x:v>984</x:v>
+      </x:c>
+      <x:c r="B988" s="13" t="str">
+        <x:v>tech.title</x:v>
+      </x:c>
+      <x:c r="C988" s="13" t="str">
+        <x:v>科技研究</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="989">
+      <x:c r="A989" s="15" t="n">
+        <x:v>985</x:v>
+      </x:c>
+      <x:c r="B989" s="13" t="str">
+        <x:v>tech.summary</x:v>
+      </x:c>
+      <x:c r="C989" s="13" t="str">
+        <x:v>已研究 {p0}/{p1} 项 · 冒险与挑战生效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="990">
+      <x:c r="A990" s="15" t="n">
+        <x:v>986</x:v>
+      </x:c>
+      <x:c r="B990" s="13" t="str">
+        <x:v>tech.balance</x:v>
+      </x:c>
+      <x:c r="C990" s="13" t="str">
+        <x:v>便利店金币 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="991">
+      <x:c r="A991" s="15" t="n">
+        <x:v>987</x:v>
+      </x:c>
+      <x:c r="B991" s="13" t="str">
+        <x:v>tech.back</x:v>
+      </x:c>
+      <x:c r="C991" s="13" t="str">
+        <x:v>返回</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="992">
+      <x:c r="A992" s="15" t="n">
+        <x:v>988</x:v>
+      </x:c>
+      <x:c r="B992" s="13" t="str">
+        <x:v>tech.page</x:v>
+      </x:c>
+      <x:c r="C992" s="13" t="str">
+        <x:v>{p0}/{p1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="993">
+      <x:c r="A993" s="15" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="B993" s="13" t="str">
+        <x:v>tech.previous</x:v>
+      </x:c>
+      <x:c r="C993" s="13" t="str">
+        <x:v>上一页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="994">
+      <x:c r="A994" s="15" t="n">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="B994" s="13" t="str">
+        <x:v>tech.next</x:v>
+      </x:c>
+      <x:c r="C994" s="13" t="str">
+        <x:v>下一页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="995">
+      <x:c r="A995" s="15" t="n">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="B995" s="13" t="str">
+        <x:v>tech.legacy</x:v>
+      </x:c>
+      <x:c r="C995" s="13" t="str">
+        <x:v>商品研发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="996">
+      <x:c r="A996" s="15" t="n">
+        <x:v>992</x:v>
+      </x:c>
+      <x:c r="B996" s="13" t="str">
+        <x:v>tech.owned</x:v>
+      </x:c>
+      <x:c r="C996" s="13" t="str">
+        <x:v>已研究</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="997">
+      <x:c r="A997" s="15" t="n">
+        <x:v>993</x:v>
+      </x:c>
+      <x:c r="B997" s="13" t="str">
+        <x:v>tech.available</x:v>
+      </x:c>
+      <x:c r="C997" s="13" t="str">
+        <x:v>可研究</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="998">
+      <x:c r="A998" s="15" t="n">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="B998" s="13" t="str">
+        <x:v>tech.locked</x:v>
+      </x:c>
+      <x:c r="C998" s="13" t="str">
+        <x:v>未开放</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="999">
+      <x:c r="A999" s="15" t="n">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="B999" s="13" t="str">
+        <x:v>tech.buy</x:v>
+      </x:c>
+      <x:c r="C999" s="13" t="str">
+        <x:v>研究 {p0} 金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1000">
+      <x:c r="A1000" s="15" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="B1000" s="13" t="str">
+        <x:v>tech.done</x:v>
+      </x:c>
+      <x:c r="C1000" s="13" t="str">
+        <x:v>已完成研究</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001">
+      <x:c r="A1001" s="15" t="n">
+        <x:v>997</x:v>
+      </x:c>
+      <x:c r="B1001" s="13" t="str">
+        <x:v>tech.needPrevious</x:v>
+      </x:c>
+      <x:c r="C1001" s="13" t="str">
+        <x:v>先研究「{p0}」</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1002">
+      <x:c r="A1002" s="15" t="n">
+        <x:v>998</x:v>
+      </x:c>
+      <x:c r="B1002" s="13" t="str">
+        <x:v>tech.needLevel</x:v>
+      </x:c>
+      <x:c r="C1002" s="13" t="str">
+        <x:v>通关冒险第{p0}关后开放</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1003">
+      <x:c r="A1003" s="15" t="n">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="B1003" s="13" t="str">
+        <x:v>tech.needCoins</x:v>
+      </x:c>
+      <x:c r="C1003" s="13" t="str">
+        <x:v>金币不足，还差{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1004">
+      <x:c r="A1004" s="15" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="B1004" s="13" t="str">
+        <x:v>tech.ready</x:v>
+      </x:c>
+      <x:c r="C1004" s="13" t="str">
+        <x:v>购买后在下一局生效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1005">
+      <x:c r="A1005" s="15" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="B1005" s="13" t="str">
+        <x:v>tech.bought</x:v>
+      </x:c>
+      <x:c r="C1005" s="13" t="str">
+        <x:v>研究完成，之后的战斗持续生效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1006">
+      <x:c r="A1006" s="15" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="B1006" s="13" t="str">
+        <x:v>tech.failed</x:v>
+      </x:c>
+      <x:c r="C1006" s="13" t="str">
+        <x:v>条件已变化，请重新选择</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1007">
+      <x:c r="A1007" s="15" t="n">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="B1007" s="13" t="str">
+        <x:v>tech.reset</x:v>
+      </x:c>
+      <x:c r="C1007" s="13" t="str">
+        <x:v>重置研究</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008">
+      <x:c r="A1008" s="15" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="B1008" s="13" t="str">
+        <x:v>tech.confirmReset</x:v>
+      </x:c>
+      <x:c r="C1008" s="13" t="str">
+        <x:v>确认返还 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1009">
+      <x:c r="A1009" s="15" t="n">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="B1009" s="13" t="str">
+        <x:v>tech.refundHint</x:v>
+      </x:c>
+      <x:c r="C1009" s="13" t="str">
+        <x:v>再次点击重置，返还已投入的{p0}金币。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1010">
+      <x:c r="A1010" s="15" t="n">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="B1010" s="13" t="str">
+        <x:v>tech.refunded</x:v>
+      </x:c>
+      <x:c r="C1010" s="13" t="str">
+        <x:v>研究已重置，返还{p0}金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1011">
+      <x:c r="A1011" s="15" t="n">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="B1011" s="13" t="str">
+        <x:v>tech.empty</x:v>
+      </x:c>
+      <x:c r="C1011" s="13" t="str">
+        <x:v>尚未投入研究金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1012">
+      <x:c r="A1012" s="15" t="n">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="B1012" s="13" t="str">
+        <x:v>tech.rank</x:v>
+      </x:c>
+      <x:c r="C1012" s="13" t="str">
+        <x:v>{p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1013">
+      <x:c r="A1013" s="15" t="n">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="B1013" s="13" t="str">
+        <x:v>shop.technology</x:v>
+      </x:c>
+      <x:c r="C1013" s="13" t="str">
+        <x:v>科技</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rd958a4e0220e417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rab2870c0276744e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11205,7 +11205,7 @@
         <x:v>tech.summary</x:v>
       </x:c>
       <x:c r="C989" s="13" t="str">
-        <x:v>已研究 {p0}/{p1} 项 · 冒险与挑战生效</x:v>
+        <x:v>已研究 {p0}/{p1} 项 · 永久成长</x:v>
       </x:c>
     </x:row>
     <x:row r="990">
@@ -11370,7 +11370,7 @@
         <x:v>tech.ready</x:v>
       </x:c>
       <x:c r="C1004" s="13" t="str">
-        <x:v>购买后在下一局生效</x:v>
+        <x:v>永久研究 · 下局生效</x:v>
       </x:c>
     </x:row>
     <x:row r="1005">
@@ -11381,7 +11381,7 @@
         <x:v>tech.bought</x:v>
       </x:c>
       <x:c r="C1005" s="13" t="str">
-        <x:v>研究完成，之后的战斗持续生效</x:v>
+        <x:v>研究完成，下局开始生效</x:v>
       </x:c>
     </x:row>
     <x:row r="1006">
@@ -11397,79 +11397,1512 @@
     </x:row>
     <x:row r="1007">
       <x:c r="A1007" s="15" t="n">
-        <x:v>1003</x:v>
+        <x:v>1008</x:v>
       </x:c>
       <x:c r="B1007" s="13" t="str">
-        <x:v>tech.reset</x:v>
+        <x:v>tech.rank</x:v>
       </x:c>
       <x:c r="C1007" s="13" t="str">
-        <x:v>重置研究</x:v>
+        <x:v>{p0}</x:v>
       </x:c>
     </x:row>
     <x:row r="1008">
       <x:c r="A1008" s="15" t="n">
-        <x:v>1004</x:v>
+        <x:v>1009</x:v>
       </x:c>
       <x:c r="B1008" s="13" t="str">
-        <x:v>tech.confirmReset</x:v>
+        <x:v>shop.technology</x:v>
       </x:c>
       <x:c r="C1008" s="13" t="str">
-        <x:v>确认返还 {p0}</x:v>
+        <x:v>科技</x:v>
       </x:c>
     </x:row>
     <x:row r="1009">
       <x:c r="A1009" s="15" t="n">
-        <x:v>1005</x:v>
+        <x:v>1010</x:v>
       </x:c>
       <x:c r="B1009" s="13" t="str">
-        <x:v>tech.refundHint</x:v>
+        <x:v>tech.branch.sprout.summary</x:v>
       </x:c>
       <x:c r="C1009" s="13" t="str">
-        <x:v>再次点击重置，返还已投入的{p0}金币。</x:v>
+        <x:v>稳定直击
+扎实输出</x:v>
       </x:c>
     </x:row>
     <x:row r="1010">
       <x:c r="A1010" s="15" t="n">
-        <x:v>1006</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="B1010" s="13" t="str">
-        <x:v>tech.refunded</x:v>
+        <x:v>tech.branch.frost.summary</x:v>
       </x:c>
       <x:c r="C1010" s="13" t="str">
-        <x:v>研究已重置，返还{p0}金币</x:v>
+        <x:v>冰霜延续
+减速控场</x:v>
       </x:c>
     </x:row>
     <x:row r="1011">
       <x:c r="A1011" s="15" t="n">
-        <x:v>1007</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="B1011" s="13" t="str">
-        <x:v>tech.empty</x:v>
+        <x:v>tech.branch.bloom.summary</x:v>
       </x:c>
       <x:c r="C1011" s="13" t="str">
-        <x:v>尚未投入研究金币</x:v>
+        <x:v>礼花绽放
+范围清敌</x:v>
       </x:c>
     </x:row>
     <x:row r="1012">
       <x:c r="A1012" s="15" t="n">
-        <x:v>1008</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="B1012" s="13" t="str">
-        <x:v>tech.rank</x:v>
+        <x:v>tech.branch.scope.summary</x:v>
       </x:c>
       <x:c r="C1012" s="13" t="str">
-        <x:v>{p0}</x:v>
+        <x:v>贯穿长线
+远程狙击</x:v>
       </x:c>
     </x:row>
     <x:row r="1013">
       <x:c r="A1013" s="15" t="n">
-        <x:v>1009</x:v>
+        <x:v>1014</x:v>
       </x:c>
       <x:c r="B1013" s="13" t="str">
-        <x:v>shop.technology</x:v>
+        <x:v>tech.branch.spark.summary</x:v>
       </x:c>
       <x:c r="C1013" s="13" t="str">
-        <x:v>科技</x:v>
+        <x:v>电链传递
+连锁制敌</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014">
+      <x:c r="A1014" s="15" t="n">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="B1014" s="13" t="str">
+        <x:v>tech.branch.ember.summary</x:v>
+      </x:c>
+      <x:c r="C1014" s="13" t="str">
+        <x:v>余火延续
+持续灼烧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015">
+      <x:c r="A1015" s="15" t="n">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="B1015" s="13" t="str">
+        <x:v>tech.branch.mint.summary</x:v>
+      </x:c>
+      <x:c r="C1015" s="13" t="str">
+        <x:v>标记延续
+协同集火</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016">
+      <x:c r="A1016" s="15" t="n">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="B1016" s="13" t="str">
+        <x:v>tech.branch.fan.summary</x:v>
+      </x:c>
+      <x:c r="C1016" s="13" t="str">
+        <x:v>扇风加速
+密集打击</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017">
+      <x:c r="A1017" s="15" t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="B1017" s="13" t="str">
+        <x:v>tech.branch.logistics.summary</x:v>
+      </x:c>
+      <x:c r="C1017" s="13" t="str">
+        <x:v>节省费用
+开局储备</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018">
+      <x:c r="A1018" s="15" t="n">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="B1018" s="13" t="str">
+        <x:v>tech.branch.props.summary</x:v>
+      </x:c>
+      <x:c r="C1018" s="13" t="str">
+        <x:v>强化道具
+从容应急</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019">
+      <x:c r="A1019" s="15" t="n">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="B1019" s="13" t="str">
+        <x:v>tech.branch.boss</x:v>
+      </x:c>
+      <x:c r="C1019" s="13" t="str">
+        <x:v>首领克制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020">
+      <x:c r="A1020" s="15" t="n">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="B1020" s="13" t="str">
+        <x:v>tech.branch.boss.summary</x:v>
+      </x:c>
+      <x:c r="C1020" s="13" t="str">
+        <x:v>直击首领
+提高效率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021">
+      <x:c r="A1021" s="15" t="n">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="B1021" s="13" t="str">
+        <x:v>tech.node.boss_1.name</x:v>
+      </x:c>
+      <x:c r="C1021" s="13" t="str">
+        <x:v>识破弱点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022">
+      <x:c r="A1022" s="15" t="n">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="B1022" s="13" t="str">
+        <x:v>tech.node.boss_1.desc</x:v>
+      </x:c>
+      <x:c r="C1022" s="13" t="str">
+        <x:v>店员直击首领伤害提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023">
+      <x:c r="A1023" s="15" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="B1023" s="13" t="str">
+        <x:v>tech.node.boss_2.name</x:v>
+      </x:c>
+      <x:c r="C1023" s="13" t="str">
+        <x:v>精准压制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024">
+      <x:c r="A1024" s="15" t="n">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="B1024" s="13" t="str">
+        <x:v>tech.node.boss_2.desc</x:v>
+      </x:c>
+      <x:c r="C1024" s="13" t="str">
+        <x:v>店员直击首领伤害提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025">
+      <x:c r="A1025" s="15" t="n">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="B1025" s="13" t="str">
+        <x:v>tech.node.boss_3.name</x:v>
+      </x:c>
+      <x:c r="C1025" s="13" t="str">
+        <x:v>重点集火</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026">
+      <x:c r="A1026" s="15" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="B1026" s="13" t="str">
+        <x:v>tech.node.boss_3.desc</x:v>
+      </x:c>
+      <x:c r="C1026" s="13" t="str">
+        <x:v>店员直击首领伤害提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027">
+      <x:c r="A1027" s="15" t="n">
+        <x:v>1028</x:v>
+      </x:c>
+      <x:c r="B1027" s="13" t="str">
+        <x:v>tech.node.boss_4.name</x:v>
+      </x:c>
+      <x:c r="C1027" s="13" t="str">
+        <x:v>破绽追击</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028">
+      <x:c r="A1028" s="15" t="n">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="B1028" s="13" t="str">
+        <x:v>tech.node.boss_4.desc</x:v>
+      </x:c>
+      <x:c r="C1028" s="13" t="str">
+        <x:v>店员直击首领伤害提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029">
+      <x:c r="A1029" s="15" t="n">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="B1029" s="13" t="str">
+        <x:v>tech.node.boss_5.name</x:v>
+      </x:c>
+      <x:c r="C1029" s="13" t="str">
+        <x:v>首领专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030">
+      <x:c r="A1030" s="15" t="n">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c r="B1030" s="13" t="str">
+        <x:v>tech.node.boss_5.desc</x:v>
+      </x:c>
+      <x:c r="C1030" s="13" t="str">
+        <x:v>店员直击首领伤害提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031">
+      <x:c r="A1031" s="15" t="n">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="B1031" s="13" t="str">
+        <x:v>tech.branch.clearing</x:v>
+      </x:c>
+      <x:c r="C1031" s="13" t="str">
+        <x:v>清障技巧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032">
+      <x:c r="A1032" s="15" t="n">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="B1032" s="13" t="str">
+        <x:v>tech.branch.clearing.summary</x:v>
+      </x:c>
+      <x:c r="C1032" s="13" t="str">
+        <x:v>加快清障
+腾出阵地</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1033">
+      <x:c r="A1033" s="15" t="n">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="B1033" s="13" t="str">
+        <x:v>tech.node.clearing_1.name</x:v>
+      </x:c>
+      <x:c r="C1033" s="13" t="str">
+        <x:v>清障入门</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1034">
+      <x:c r="A1034" s="15" t="n">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="B1034" s="13" t="str">
+        <x:v>tech.node.clearing_1.desc</x:v>
+      </x:c>
+      <x:c r="C1034" s="13" t="str">
+        <x:v>店员攻击障碍伤害提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1035">
+      <x:c r="A1035" s="15" t="n">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="B1035" s="13" t="str">
+        <x:v>tech.node.clearing_2.name</x:v>
+      </x:c>
+      <x:c r="C1035" s="13" t="str">
+        <x:v>工具保养</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1036">
+      <x:c r="A1036" s="15" t="n">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="B1036" s="13" t="str">
+        <x:v>tech.node.clearing_2.desc</x:v>
+      </x:c>
+      <x:c r="C1036" s="13" t="str">
+        <x:v>店员攻击障碍伤害提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1037">
+      <x:c r="A1037" s="15" t="n">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="B1037" s="13" t="str">
+        <x:v>tech.node.clearing_3.name</x:v>
+      </x:c>
+      <x:c r="C1037" s="13" t="str">
+        <x:v>拆解训练</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1038">
+      <x:c r="A1038" s="15" t="n">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="B1038" s="13" t="str">
+        <x:v>tech.node.clearing_3.desc</x:v>
+      </x:c>
+      <x:c r="C1038" s="13" t="str">
+        <x:v>店员攻击障碍伤害提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1039">
+      <x:c r="A1039" s="15" t="n">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="B1039" s="13" t="str">
+        <x:v>tech.node.clearing_4.name</x:v>
+      </x:c>
+      <x:c r="C1039" s="13" t="str">
+        <x:v>精准拆除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1040">
+      <x:c r="A1040" s="15" t="n">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="B1040" s="13" t="str">
+        <x:v>tech.node.clearing_4.desc</x:v>
+      </x:c>
+      <x:c r="C1040" s="13" t="str">
+        <x:v>店员攻击障碍伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1041">
+      <x:c r="A1041" s="15" t="n">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="B1041" s="13" t="str">
+        <x:v>tech.node.clearing_5.name</x:v>
+      </x:c>
+      <x:c r="C1041" s="13" t="str">
+        <x:v>清障专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1042">
+      <x:c r="A1042" s="15" t="n">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="B1042" s="13" t="str">
+        <x:v>tech.node.clearing_5.desc</x:v>
+      </x:c>
+      <x:c r="C1042" s="13" t="str">
+        <x:v>店员攻击障碍伤害提高3%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1043">
+      <x:c r="A1043" s="15" t="n">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="B1043" s="13" t="str">
+        <x:v>tech.branch.salvage</x:v>
+      </x:c>
+      <x:c r="C1043" s="13" t="str">
+        <x:v>残骸回收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1044">
+      <x:c r="A1044" s="15" t="n">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="B1044" s="13" t="str">
+        <x:v>tech.branch.salvage.summary</x:v>
+      </x:c>
+      <x:c r="C1044" s="13" t="str">
+        <x:v>回收残骸
+积攒金币</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1045">
+      <x:c r="A1045" s="15" t="n">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="B1045" s="13" t="str">
+        <x:v>tech.node.salvage_1.name</x:v>
+      </x:c>
+      <x:c r="C1045" s="13" t="str">
+        <x:v>随手回收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1046">
+      <x:c r="A1046" s="15" t="n">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="B1046" s="13" t="str">
+        <x:v>tech.node.salvage_1.desc</x:v>
+      </x:c>
+      <x:c r="C1046" s="13" t="str">
+        <x:v>清除障碍的基础战斗金币提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1047">
+      <x:c r="A1047" s="15" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="B1047" s="13" t="str">
+        <x:v>tech.node.salvage_2.name</x:v>
+      </x:c>
+      <x:c r="C1047" s="13" t="str">
+        <x:v>分类整理</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1048">
+      <x:c r="A1048" s="15" t="n">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="B1048" s="13" t="str">
+        <x:v>tech.node.salvage_2.desc</x:v>
+      </x:c>
+      <x:c r="C1048" s="13" t="str">
+        <x:v>清除障碍的基础战斗金币提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1049">
+      <x:c r="A1049" s="15" t="n">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="B1049" s="13" t="str">
+        <x:v>tech.node.salvage_3.name</x:v>
+      </x:c>
+      <x:c r="C1049" s="13" t="str">
+        <x:v>材料识别</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1050">
+      <x:c r="A1050" s="15" t="n">
+        <x:v>1051</x:v>
+      </x:c>
+      <x:c r="B1050" s="13" t="str">
+        <x:v>tech.node.salvage_3.desc</x:v>
+      </x:c>
+      <x:c r="C1050" s="13" t="str">
+        <x:v>清除障碍的基础战斗金币提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1051">
+      <x:c r="A1051" s="15" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="B1051" s="13" t="str">
+        <x:v>tech.node.salvage_4.name</x:v>
+      </x:c>
+      <x:c r="C1051" s="13" t="str">
+        <x:v>精细拆解</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1052">
+      <x:c r="A1052" s="15" t="n">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="B1052" s="13" t="str">
+        <x:v>tech.node.salvage_4.desc</x:v>
+      </x:c>
+      <x:c r="C1052" s="13" t="str">
+        <x:v>清除障碍的基础战斗金币提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1053">
+      <x:c r="A1053" s="15" t="n">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="B1053" s="13" t="str">
+        <x:v>tech.node.salvage_5.name</x:v>
+      </x:c>
+      <x:c r="C1053" s="13" t="str">
+        <x:v>回收专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1054">
+      <x:c r="A1054" s="15" t="n">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="B1054" s="13" t="str">
+        <x:v>tech.node.salvage_5.desc</x:v>
+      </x:c>
+      <x:c r="C1054" s="13" t="str">
+        <x:v>清除障碍的基础战斗金币提高2%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1055">
+      <x:c r="A1055" s="15" t="n">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="B1055" s="13" t="str">
+        <x:v>tech.branch.supply</x:v>
+      </x:c>
+      <x:c r="C1055" s="13" t="str">
+        <x:v>补给调度</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1056">
+      <x:c r="A1056" s="15" t="n">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="B1056" s="13" t="str">
+        <x:v>tech.branch.supply.summary</x:v>
+      </x:c>
+      <x:c r="C1056" s="13" t="str">
+        <x:v>积累经验
+加快补给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1057">
+      <x:c r="A1057" s="15" t="n">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="B1057" s="13" t="str">
+        <x:v>tech.node.supply_1.name</x:v>
+      </x:c>
+      <x:c r="C1057" s="13" t="str">
+        <x:v>夜班登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1058">
+      <x:c r="A1058" s="15" t="n">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="B1058" s="13" t="str">
+        <x:v>tech.node.supply_1.desc</x:v>
+      </x:c>
+      <x:c r="C1058" s="13" t="str">
+        <x:v>挑战击退怪物获得经验提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1059">
+      <x:c r="A1059" s="15" t="n">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="B1059" s="13" t="str">
+        <x:v>tech.node.supply_2.name</x:v>
+      </x:c>
+      <x:c r="C1059" s="13" t="str">
+        <x:v>物资统筹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1060">
+      <x:c r="A1060" s="15" t="n">
+        <x:v>1061</x:v>
+      </x:c>
+      <x:c r="B1060" s="13" t="str">
+        <x:v>tech.node.supply_2.desc</x:v>
+      </x:c>
+      <x:c r="C1060" s="13" t="str">
+        <x:v>挑战击退怪物获得经验提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1061">
+      <x:c r="A1061" s="15" t="n">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="B1061" s="13" t="str">
+        <x:v>tech.node.supply_3.name</x:v>
+      </x:c>
+      <x:c r="C1061" s="13" t="str">
+        <x:v>及时补包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1062">
+      <x:c r="A1062" s="15" t="n">
+        <x:v>1063</x:v>
+      </x:c>
+      <x:c r="B1062" s="13" t="str">
+        <x:v>tech.node.supply_3.desc</x:v>
+      </x:c>
+      <x:c r="C1062" s="13" t="str">
+        <x:v>挑战击退怪物获得经验提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1063">
+      <x:c r="A1063" s="15" t="n">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c r="B1063" s="13" t="str">
+        <x:v>tech.node.supply_4.name</x:v>
+      </x:c>
+      <x:c r="C1063" s="13" t="str">
+        <x:v>高效交接</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1064">
+      <x:c r="A1064" s="15" t="n">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="B1064" s="13" t="str">
+        <x:v>tech.node.supply_4.desc</x:v>
+      </x:c>
+      <x:c r="C1064" s="13" t="str">
+        <x:v>挑战击退怪物获得经验提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1065">
+      <x:c r="A1065" s="15" t="n">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="B1065" s="13" t="str">
+        <x:v>tech.node.supply_5.name</x:v>
+      </x:c>
+      <x:c r="C1065" s="13" t="str">
+        <x:v>调度专精</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1066">
+      <x:c r="A1066" s="15" t="n">
+        <x:v>1067</x:v>
+      </x:c>
+      <x:c r="B1066" s="13" t="str">
+        <x:v>tech.node.supply_5.desc</x:v>
+      </x:c>
+      <x:c r="C1066" s="13" t="str">
+        <x:v>挑战击退怪物获得经验提高1%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1067">
+      <x:c r="A1067" s="15" t="n">
+        <x:v>1068</x:v>
+      </x:c>
+      <x:c r="B1067" s="13" t="str">
+        <x:v>tech.node.sprout_1.brief</x:v>
+      </x:c>
+      <x:c r="C1067" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1068">
+      <x:c r="A1068" s="15" t="n">
+        <x:v>1069</x:v>
+      </x:c>
+      <x:c r="B1068" s="13" t="str">
+        <x:v>tech.node.sprout_2.brief</x:v>
+      </x:c>
+      <x:c r="C1068" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1069">
+      <x:c r="A1069" s="15" t="n">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="B1069" s="13" t="str">
+        <x:v>tech.node.sprout_3.brief</x:v>
+      </x:c>
+      <x:c r="C1069" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1070">
+      <x:c r="A1070" s="15" t="n">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="B1070" s="13" t="str">
+        <x:v>tech.node.sprout_4.brief</x:v>
+      </x:c>
+      <x:c r="C1070" s="13" t="str">
+        <x:v>直击伤害 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1071">
+      <x:c r="A1071" s="15" t="n">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c r="B1071" s="13" t="str">
+        <x:v>tech.node.sprout_5.brief</x:v>
+      </x:c>
+      <x:c r="C1071" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1072">
+      <x:c r="A1072" s="15" t="n">
+        <x:v>1073</x:v>
+      </x:c>
+      <x:c r="B1072" s="13" t="str">
+        <x:v>tech.node.frost_1.brief</x:v>
+      </x:c>
+      <x:c r="C1072" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1073">
+      <x:c r="A1073" s="15" t="n">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="B1073" s="13" t="str">
+        <x:v>tech.node.frost_2.brief</x:v>
+      </x:c>
+      <x:c r="C1073" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1074">
+      <x:c r="A1074" s="15" t="n">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="B1074" s="13" t="str">
+        <x:v>tech.node.frost_3.brief</x:v>
+      </x:c>
+      <x:c r="C1074" s="13" t="str">
+        <x:v>减速时长 +8%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1075">
+      <x:c r="A1075" s="15" t="n">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="B1075" s="13" t="str">
+        <x:v>tech.node.frost_4.brief</x:v>
+      </x:c>
+      <x:c r="C1075" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1076">
+      <x:c r="A1076" s="15" t="n">
+        <x:v>1077</x:v>
+      </x:c>
+      <x:c r="B1076" s="13" t="str">
+        <x:v>tech.node.frost_5.brief</x:v>
+      </x:c>
+      <x:c r="C1076" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1077">
+      <x:c r="A1077" s="15" t="n">
+        <x:v>1078</x:v>
+      </x:c>
+      <x:c r="B1077" s="13" t="str">
+        <x:v>tech.node.bloom_1.brief</x:v>
+      </x:c>
+      <x:c r="C1077" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1078">
+      <x:c r="A1078" s="15" t="n">
+        <x:v>1079</x:v>
+      </x:c>
+      <x:c r="B1078" s="13" t="str">
+        <x:v>tech.node.bloom_2.brief</x:v>
+      </x:c>
+      <x:c r="C1078" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1079">
+      <x:c r="A1079" s="15" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="B1079" s="13" t="str">
+        <x:v>tech.node.bloom_3.brief</x:v>
+      </x:c>
+      <x:c r="C1079" s="13" t="str">
+        <x:v>爆炸范围 +6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1080">
+      <x:c r="A1080" s="15" t="n">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="B1080" s="13" t="str">
+        <x:v>tech.node.bloom_4.brief</x:v>
+      </x:c>
+      <x:c r="C1080" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1081">
+      <x:c r="A1081" s="15" t="n">
+        <x:v>1082</x:v>
+      </x:c>
+      <x:c r="B1081" s="13" t="str">
+        <x:v>tech.node.bloom_5.brief</x:v>
+      </x:c>
+      <x:c r="C1081" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1082">
+      <x:c r="A1082" s="15" t="n">
+        <x:v>1083</x:v>
+      </x:c>
+      <x:c r="B1082" s="13" t="str">
+        <x:v>tech.node.scope_1.brief</x:v>
+      </x:c>
+      <x:c r="C1082" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1083">
+      <x:c r="A1083" s="15" t="n">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="B1083" s="13" t="str">
+        <x:v>tech.node.scope_2.brief</x:v>
+      </x:c>
+      <x:c r="C1083" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1084">
+      <x:c r="A1084" s="15" t="n">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="B1084" s="13" t="str">
+        <x:v>tech.node.scope_3.brief</x:v>
+      </x:c>
+      <x:c r="C1084" s="13" t="str">
+        <x:v>贯穿长度 +6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1085">
+      <x:c r="A1085" s="15" t="n">
+        <x:v>1086</x:v>
+      </x:c>
+      <x:c r="B1085" s="13" t="str">
+        <x:v>tech.node.scope_4.brief</x:v>
+      </x:c>
+      <x:c r="C1085" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1086">
+      <x:c r="A1086" s="15" t="n">
+        <x:v>1087</x:v>
+      </x:c>
+      <x:c r="B1086" s="13" t="str">
+        <x:v>tech.node.scope_5.brief</x:v>
+      </x:c>
+      <x:c r="C1086" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1087">
+      <x:c r="A1087" s="15" t="n">
+        <x:v>1088</x:v>
+      </x:c>
+      <x:c r="B1087" s="13" t="str">
+        <x:v>tech.node.spark_1.brief</x:v>
+      </x:c>
+      <x:c r="C1087" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1088">
+      <x:c r="A1088" s="15" t="n">
+        <x:v>1089</x:v>
+      </x:c>
+      <x:c r="B1088" s="13" t="str">
+        <x:v>tech.node.spark_2.brief</x:v>
+      </x:c>
+      <x:c r="C1088" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1089">
+      <x:c r="A1089" s="15" t="n">
+        <x:v>1090</x:v>
+      </x:c>
+      <x:c r="B1089" s="13" t="str">
+        <x:v>tech.node.spark_3.brief</x:v>
+      </x:c>
+      <x:c r="C1089" s="13" t="str">
+        <x:v>电链系数 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1090">
+      <x:c r="A1090" s="15" t="n">
+        <x:v>1091</x:v>
+      </x:c>
+      <x:c r="B1090" s="13" t="str">
+        <x:v>tech.node.spark_4.brief</x:v>
+      </x:c>
+      <x:c r="C1090" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1091">
+      <x:c r="A1091" s="15" t="n">
+        <x:v>1092</x:v>
+      </x:c>
+      <x:c r="B1091" s="13" t="str">
+        <x:v>tech.node.spark_5.brief</x:v>
+      </x:c>
+      <x:c r="C1091" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1092">
+      <x:c r="A1092" s="15" t="n">
+        <x:v>1093</x:v>
+      </x:c>
+      <x:c r="B1092" s="13" t="str">
+        <x:v>tech.node.ember_1.brief</x:v>
+      </x:c>
+      <x:c r="C1092" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1093">
+      <x:c r="A1093" s="15" t="n">
+        <x:v>1094</x:v>
+      </x:c>
+      <x:c r="B1093" s="13" t="str">
+        <x:v>tech.node.ember_2.brief</x:v>
+      </x:c>
+      <x:c r="C1093" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1094">
+      <x:c r="A1094" s="15" t="n">
+        <x:v>1095</x:v>
+      </x:c>
+      <x:c r="B1094" s="13" t="str">
+        <x:v>tech.node.ember_3.brief</x:v>
+      </x:c>
+      <x:c r="C1094" s="13" t="str">
+        <x:v>灼烧时长 +8%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1095">
+      <x:c r="A1095" s="15" t="n">
+        <x:v>1096</x:v>
+      </x:c>
+      <x:c r="B1095" s="13" t="str">
+        <x:v>tech.node.ember_4.brief</x:v>
+      </x:c>
+      <x:c r="C1095" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1096">
+      <x:c r="A1096" s="15" t="n">
+        <x:v>1097</x:v>
+      </x:c>
+      <x:c r="B1096" s="13" t="str">
+        <x:v>tech.node.ember_5.brief</x:v>
+      </x:c>
+      <x:c r="C1096" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1097">
+      <x:c r="A1097" s="15" t="n">
+        <x:v>1098</x:v>
+      </x:c>
+      <x:c r="B1097" s="13" t="str">
+        <x:v>tech.node.mint_1.brief</x:v>
+      </x:c>
+      <x:c r="C1097" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1098">
+      <x:c r="A1098" s="15" t="n">
+        <x:v>1099</x:v>
+      </x:c>
+      <x:c r="B1098" s="13" t="str">
+        <x:v>tech.node.mint_2.brief</x:v>
+      </x:c>
+      <x:c r="C1098" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1099">
+      <x:c r="A1099" s="15" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="B1099" s="13" t="str">
+        <x:v>tech.node.mint_3.brief</x:v>
+      </x:c>
+      <x:c r="C1099" s="13" t="str">
+        <x:v>标记时长 +8%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1100">
+      <x:c r="A1100" s="15" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="B1100" s="13" t="str">
+        <x:v>tech.node.mint_4.brief</x:v>
+      </x:c>
+      <x:c r="C1100" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1101">
+      <x:c r="A1101" s="15" t="n">
+        <x:v>1102</x:v>
+      </x:c>
+      <x:c r="B1101" s="13" t="str">
+        <x:v>tech.node.mint_5.brief</x:v>
+      </x:c>
+      <x:c r="C1101" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1102">
+      <x:c r="A1102" s="15" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="B1102" s="13" t="str">
+        <x:v>tech.node.fan_1.brief</x:v>
+      </x:c>
+      <x:c r="C1102" s="13" t="str">
+        <x:v>直击伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1103">
+      <x:c r="A1103" s="15" t="n">
+        <x:v>1104</x:v>
+      </x:c>
+      <x:c r="B1103" s="13" t="str">
+        <x:v>tech.node.fan_2.brief</x:v>
+      </x:c>
+      <x:c r="C1103" s="13" t="str">
+        <x:v>射程 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1104">
+      <x:c r="A1104" s="15" t="n">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="B1104" s="13" t="str">
+        <x:v>tech.node.fan_3.brief</x:v>
+      </x:c>
+      <x:c r="C1104" s="13" t="str">
+        <x:v>攻击间隔 −4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1105">
+      <x:c r="A1105" s="15" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="B1105" s="13" t="str">
+        <x:v>tech.node.fan_4.brief</x:v>
+      </x:c>
+      <x:c r="C1105" s="13" t="str">
+        <x:v>直击伤害 +4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1106">
+      <x:c r="A1106" s="15" t="n">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c r="B1106" s="13" t="str">
+        <x:v>tech.node.fan_5.brief</x:v>
+      </x:c>
+      <x:c r="C1106" s="13" t="str">
+        <x:v>直击伤害 +5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1107">
+      <x:c r="A1107" s="15" t="n">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c r="B1107" s="13" t="str">
+        <x:v>tech.node.logistics_1.brief</x:v>
+      </x:c>
+      <x:c r="C1107" s="13" t="str">
+        <x:v>建造费用 −2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1108">
+      <x:c r="A1108" s="15" t="n">
+        <x:v>1109</x:v>
+      </x:c>
+      <x:c r="B1108" s="13" t="str">
+        <x:v>tech.node.logistics_2.brief</x:v>
+      </x:c>
+      <x:c r="C1108" s="13" t="str">
+        <x:v>升级费用 −3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1109">
+      <x:c r="A1109" s="15" t="n">
+        <x:v>1110</x:v>
+      </x:c>
+      <x:c r="B1109" s="13" t="str">
+        <x:v>tech.node.logistics_3.brief</x:v>
+      </x:c>
+      <x:c r="C1109" s="13" t="str">
+        <x:v>建造费用 −2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1110">
+      <x:c r="A1110" s="15" t="n">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="B1110" s="13" t="str">
+        <x:v>tech.node.logistics_4.brief</x:v>
+      </x:c>
+      <x:c r="C1110" s="13" t="str">
+        <x:v>升级费用 −3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1111">
+      <x:c r="A1111" s="15" t="n">
+        <x:v>1112</x:v>
+      </x:c>
+      <x:c r="B1111" s="13" t="str">
+        <x:v>tech.node.logistics_5.brief</x:v>
+      </x:c>
+      <x:c r="C1111" s="13" t="str">
+        <x:v>开局金币 +15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1112">
+      <x:c r="A1112" s="15" t="n">
+        <x:v>1113</x:v>
+      </x:c>
+      <x:c r="B1112" s="13" t="str">
+        <x:v>tech.node.props_1.brief</x:v>
+      </x:c>
+      <x:c r="C1112" s="13" t="str">
+        <x:v>冻结时长 +0.4秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1113">
+      <x:c r="A1113" s="15" t="n">
+        <x:v>1114</x:v>
+      </x:c>
+      <x:c r="B1113" s="13" t="str">
+        <x:v>tech.node.props_2.brief</x:v>
+      </x:c>
+      <x:c r="C1113" s="13" t="str">
+        <x:v>道具金币 +8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1114">
+      <x:c r="A1114" s="15" t="n">
+        <x:v>1115</x:v>
+      </x:c>
+      <x:c r="B1114" s="13" t="str">
+        <x:v>tech.node.props_3.brief</x:v>
+      </x:c>
+      <x:c r="C1114" s="13" t="str">
+        <x:v>冻结时长 +0.4秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1115">
+      <x:c r="A1115" s="15" t="n">
+        <x:v>1116</x:v>
+      </x:c>
+      <x:c r="B1115" s="13" t="str">
+        <x:v>tech.node.props_4.brief</x:v>
+      </x:c>
+      <x:c r="C1115" s="13" t="str">
+        <x:v>道具金币 +8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1116">
+      <x:c r="A1116" s="15" t="n">
+        <x:v>1117</x:v>
+      </x:c>
+      <x:c r="B1116" s="13" t="str">
+        <x:v>tech.node.props_5.brief</x:v>
+      </x:c>
+      <x:c r="C1116" s="13" t="str">
+        <x:v>冻结时长 +0.6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1117">
+      <x:c r="A1117" s="15" t="n">
+        <x:v>1118</x:v>
+      </x:c>
+      <x:c r="B1117" s="13" t="str">
+        <x:v>tech.node.boss_1.brief</x:v>
+      </x:c>
+      <x:c r="C1117" s="13" t="str">
+        <x:v>首领直击 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1118">
+      <x:c r="A1118" s="15" t="n">
+        <x:v>1119</x:v>
+      </x:c>
+      <x:c r="B1118" s="13" t="str">
+        <x:v>tech.node.boss_2.brief</x:v>
+      </x:c>
+      <x:c r="C1118" s="13" t="str">
+        <x:v>首领直击 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1119">
+      <x:c r="A1119" s="15" t="n">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="B1119" s="13" t="str">
+        <x:v>tech.node.boss_3.brief</x:v>
+      </x:c>
+      <x:c r="C1119" s="13" t="str">
+        <x:v>首领直击 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1120">
+      <x:c r="A1120" s="15" t="n">
+        <x:v>1121</x:v>
+      </x:c>
+      <x:c r="B1120" s="13" t="str">
+        <x:v>tech.node.boss_4.brief</x:v>
+      </x:c>
+      <x:c r="C1120" s="13" t="str">
+        <x:v>首领直击 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1121">
+      <x:c r="A1121" s="15" t="n">
+        <x:v>1122</x:v>
+      </x:c>
+      <x:c r="B1121" s="13" t="str">
+        <x:v>tech.node.boss_5.brief</x:v>
+      </x:c>
+      <x:c r="C1121" s="13" t="str">
+        <x:v>首领直击 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1122">
+      <x:c r="A1122" s="15" t="n">
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c r="B1122" s="13" t="str">
+        <x:v>tech.node.clearing_1.brief</x:v>
+      </x:c>
+      <x:c r="C1122" s="13" t="str">
+        <x:v>清障伤害 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1123">
+      <x:c r="A1123" s="15" t="n">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="B1123" s="13" t="str">
+        <x:v>tech.node.clearing_2.brief</x:v>
+      </x:c>
+      <x:c r="C1123" s="13" t="str">
+        <x:v>清障伤害 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1124">
+      <x:c r="A1124" s="15" t="n">
+        <x:v>1125</x:v>
+      </x:c>
+      <x:c r="B1124" s="13" t="str">
+        <x:v>tech.node.clearing_3.brief</x:v>
+      </x:c>
+      <x:c r="C1124" s="13" t="str">
+        <x:v>清障伤害 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1125">
+      <x:c r="A1125" s="15" t="n">
+        <x:v>1126</x:v>
+      </x:c>
+      <x:c r="B1125" s="13" t="str">
+        <x:v>tech.node.clearing_4.brief</x:v>
+      </x:c>
+      <x:c r="C1125" s="13" t="str">
+        <x:v>清障伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1126">
+      <x:c r="A1126" s="15" t="n">
+        <x:v>1127</x:v>
+      </x:c>
+      <x:c r="B1126" s="13" t="str">
+        <x:v>tech.node.clearing_5.brief</x:v>
+      </x:c>
+      <x:c r="C1126" s="13" t="str">
+        <x:v>清障伤害 +3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1127">
+      <x:c r="A1127" s="15" t="n">
+        <x:v>1128</x:v>
+      </x:c>
+      <x:c r="B1127" s="13" t="str">
+        <x:v>tech.node.salvage_1.brief</x:v>
+      </x:c>
+      <x:c r="C1127" s="13" t="str">
+        <x:v>残骸金币 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1128">
+      <x:c r="A1128" s="15" t="n">
+        <x:v>1129</x:v>
+      </x:c>
+      <x:c r="B1128" s="13" t="str">
+        <x:v>tech.node.salvage_2.brief</x:v>
+      </x:c>
+      <x:c r="C1128" s="13" t="str">
+        <x:v>残骸金币 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1129">
+      <x:c r="A1129" s="15" t="n">
+        <x:v>1130</x:v>
+      </x:c>
+      <x:c r="B1129" s="13" t="str">
+        <x:v>tech.node.salvage_3.brief</x:v>
+      </x:c>
+      <x:c r="C1129" s="13" t="str">
+        <x:v>残骸金币 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1130">
+      <x:c r="A1130" s="15" t="n">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="B1130" s="13" t="str">
+        <x:v>tech.node.salvage_4.brief</x:v>
+      </x:c>
+      <x:c r="C1130" s="13" t="str">
+        <x:v>残骸金币 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1131">
+      <x:c r="A1131" s="15" t="n">
+        <x:v>1132</x:v>
+      </x:c>
+      <x:c r="B1131" s="13" t="str">
+        <x:v>tech.node.salvage_5.brief</x:v>
+      </x:c>
+      <x:c r="C1131" s="13" t="str">
+        <x:v>残骸金币 +2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1132">
+      <x:c r="A1132" s="15" t="n">
+        <x:v>1133</x:v>
+      </x:c>
+      <x:c r="B1132" s="13" t="str">
+        <x:v>tech.node.supply_1.brief</x:v>
+      </x:c>
+      <x:c r="C1132" s="13" t="str">
+        <x:v>击退经验 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1133">
+      <x:c r="A1133" s="15" t="n">
+        <x:v>1134</x:v>
+      </x:c>
+      <x:c r="B1133" s="13" t="str">
+        <x:v>tech.node.supply_2.brief</x:v>
+      </x:c>
+      <x:c r="C1133" s="13" t="str">
+        <x:v>击退经验 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1134">
+      <x:c r="A1134" s="15" t="n">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="B1134" s="13" t="str">
+        <x:v>tech.node.supply_3.brief</x:v>
+      </x:c>
+      <x:c r="C1134" s="13" t="str">
+        <x:v>击退经验 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1135">
+      <x:c r="A1135" s="15" t="n">
+        <x:v>1136</x:v>
+      </x:c>
+      <x:c r="B1135" s="13" t="str">
+        <x:v>tech.node.supply_4.brief</x:v>
+      </x:c>
+      <x:c r="C1135" s="13" t="str">
+        <x:v>击退经验 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1136">
+      <x:c r="A1136" s="15" t="n">
+        <x:v>1137</x:v>
+      </x:c>
+      <x:c r="B1136" s="13" t="str">
+        <x:v>tech.node.supply_5.brief</x:v>
+      </x:c>
+      <x:c r="C1136" s="13" t="str">
+        <x:v>击退经验 +1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1137">
+      <x:c r="A1137" s="15" t="n">
+        <x:v>1138</x:v>
+      </x:c>
+      <x:c r="B1137" s="13" t="str">
+        <x:v>tech.branchProgress</x:v>
+      </x:c>
+      <x:c r="C1137" s="13" t="str">
+        <x:v>{p0} · 已研究 {p1}/{p2}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1138">
+      <x:c r="A1138" s="15" t="n">
+        <x:v>1139</x:v>
+      </x:c>
+      <x:c r="B1138" s="13" t="str">
+        <x:v>tech.cardCost</x:v>
+      </x:c>
+      <x:c r="C1138" s="13" t="str">
+        <x:v>下一项 {p0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1139">
+      <x:c r="A1139" s="15" t="n">
+        <x:v>1140</x:v>
+      </x:c>
+      <x:c r="B1139" s="13" t="str">
+        <x:v>tech.cardDone</x:v>
+      </x:c>
+      <x:c r="C1139" s="13" t="str">
+        <x:v>已全部研究</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1140">
+      <x:c r="A1140" s="15" t="n">
+        <x:v>1141</x:v>
+      </x:c>
+      <x:c r="B1140" s="13" t="str">
+        <x:v>tech.cardGate</x:v>
+      </x:c>
+      <x:c r="C1140" s="13" t="str">
+        <x:v>通关第{p0}关开放</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1141">
+      <x:c r="A1141" s="15" t="n">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="B1141" s="13" t="str">
+        <x:v>tech.backOverview</x:v>
+      </x:c>
+      <x:c r="C1141" s="13" t="str">
+        <x:v>总览</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1142">
+      <x:c r="A1142" s="15" t="n">
+        <x:v>1143</x:v>
+      </x:c>
+      <x:c r="B1142" s="13" t="str">
+        <x:v>tech.detailProgress</x:v>
+      </x:c>
+      <x:c r="C1142" s="13" t="str">
+        <x:v>已研究 {p0}/{p1} 项 · 逐级开放</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rab2870c0276744e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R05c342be09e94204"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11425,8 +11425,7 @@
         <x:v>tech.branch.sprout.summary</x:v>
       </x:c>
       <x:c r="C1009" s="13" t="str">
-        <x:v>稳定直击
-扎实输出</x:v>
+        <x:v>稳定直击，扎实输出</x:v>
       </x:c>
     </x:row>
     <x:row r="1010">
@@ -11437,8 +11436,7 @@
         <x:v>tech.branch.frost.summary</x:v>
       </x:c>
       <x:c r="C1010" s="13" t="str">
-        <x:v>冰霜延续
-减速控场</x:v>
+        <x:v>冰霜延续，减速控场</x:v>
       </x:c>
     </x:row>
     <x:row r="1011">
@@ -11449,8 +11447,7 @@
         <x:v>tech.branch.bloom.summary</x:v>
       </x:c>
       <x:c r="C1011" s="13" t="str">
-        <x:v>礼花绽放
-范围清敌</x:v>
+        <x:v>礼花绽放，范围清敌</x:v>
       </x:c>
     </x:row>
     <x:row r="1012">
@@ -11461,8 +11458,7 @@
         <x:v>tech.branch.scope.summary</x:v>
       </x:c>
       <x:c r="C1012" s="13" t="str">
-        <x:v>贯穿长线
-远程狙击</x:v>
+        <x:v>贯穿长线，远程狙击</x:v>
       </x:c>
     </x:row>
     <x:row r="1013">
@@ -11473,8 +11469,7 @@
         <x:v>tech.branch.spark.summary</x:v>
       </x:c>
       <x:c r="C1013" s="13" t="str">
-        <x:v>电链传递
-连锁制敌</x:v>
+        <x:v>电链传递，连锁制敌</x:v>
       </x:c>
     </x:row>
     <x:row r="1014">
@@ -11485,8 +11480,7 @@
         <x:v>tech.branch.ember.summary</x:v>
       </x:c>
       <x:c r="C1014" s="13" t="str">
-        <x:v>余火延续
-持续灼烧</x:v>
+        <x:v>余火延续，持续灼烧</x:v>
       </x:c>
     </x:row>
     <x:row r="1015">
@@ -11497,8 +11491,7 @@
         <x:v>tech.branch.mint.summary</x:v>
       </x:c>
       <x:c r="C1015" s="13" t="str">
-        <x:v>标记延续
-协同集火</x:v>
+        <x:v>标记延续，协同集火</x:v>
       </x:c>
     </x:row>
     <x:row r="1016">
@@ -11509,8 +11502,7 @@
         <x:v>tech.branch.fan.summary</x:v>
       </x:c>
       <x:c r="C1016" s="13" t="str">
-        <x:v>扇风加速
-密集打击</x:v>
+        <x:v>扇风加速，密集打击</x:v>
       </x:c>
     </x:row>
     <x:row r="1017">
@@ -11521,8 +11513,7 @@
         <x:v>tech.branch.logistics.summary</x:v>
       </x:c>
       <x:c r="C1017" s="13" t="str">
-        <x:v>节省费用
-开局储备</x:v>
+        <x:v>节省费用，开局储备</x:v>
       </x:c>
     </x:row>
     <x:row r="1018">
@@ -11533,8 +11524,7 @@
         <x:v>tech.branch.props.summary</x:v>
       </x:c>
       <x:c r="C1018" s="13" t="str">
-        <x:v>强化道具
-从容应急</x:v>
+        <x:v>强化道具，从容应急</x:v>
       </x:c>
     </x:row>
     <x:row r="1019">
@@ -11556,8 +11546,7 @@
         <x:v>tech.branch.boss.summary</x:v>
       </x:c>
       <x:c r="C1020" s="13" t="str">
-        <x:v>直击首领
-提高效率</x:v>
+        <x:v>直击首领，提高效率</x:v>
       </x:c>
     </x:row>
     <x:row r="1021">
@@ -11689,8 +11678,7 @@
         <x:v>tech.branch.clearing.summary</x:v>
       </x:c>
       <x:c r="C1032" s="13" t="str">
-        <x:v>加快清障
-腾出阵地</x:v>
+        <x:v>加快清障，腾出阵地</x:v>
       </x:c>
     </x:row>
     <x:row r="1033">
@@ -11822,8 +11810,7 @@
         <x:v>tech.branch.salvage.summary</x:v>
       </x:c>
       <x:c r="C1044" s="13" t="str">
-        <x:v>回收残骸
-积攒金币</x:v>
+        <x:v>回收残骸，积攒金币</x:v>
       </x:c>
     </x:row>
     <x:row r="1045">
@@ -11955,8 +11942,7 @@
         <x:v>tech.branch.supply.summary</x:v>
       </x:c>
       <x:c r="C1056" s="13" t="str">
-        <x:v>积累经验
-加快补给</x:v>
+        <x:v>积累经验，加快补给</x:v>
       </x:c>
     </x:row>
     <x:row r="1057">
@@ -12858,7 +12844,7 @@
         <x:v>tech.cardCost</x:v>
       </x:c>
       <x:c r="C1138" s="13" t="str">
-        <x:v>下一项 {p0}</x:v>
+        <x:v>{p0}金币</x:v>
       </x:c>
     </x:row>
     <x:row r="1139">
@@ -12869,7 +12855,7 @@
         <x:v>tech.cardDone</x:v>
       </x:c>
       <x:c r="C1139" s="13" t="str">
-        <x:v>已全部研究</x:v>
+        <x:v>全部完成</x:v>
       </x:c>
     </x:row>
     <x:row r="1140">
@@ -12880,7 +12866,8 @@
         <x:v>tech.cardGate</x:v>
       </x:c>
       <x:c r="C1140" s="13" t="str">
-        <x:v>通关第{p0}关开放</x:v>
+        <x:v>通关{p0}关
+开放</x:v>
       </x:c>
     </x:row>
     <x:row r="1141">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="R05c342be09e94204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rcd7698b7bb66467c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2719,7 +2719,7 @@
         <x:v>ui.GameRoot.019</x:v>
       </x:c>
       <x:c r="C218" s="13" t="str">
-        <x:v>二十夜守护完成！</x:v>
+        <x:v>{p0}夜守护完成！</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="58" hidden="0" customHeight="1">
@@ -3832,7 +3832,7 @@
         <x:v>result.complete</x:v>
       </x:c>
       <x:c r="C319" s="16" t="str">
-        <x:v>二十关全部完成</x:v>
+        <x:v>{p0}关全部完成</x:v>
       </x:c>
     </x:row>
     <x:row r="320" ht="58" customHeight="1">

--- a/design/tables/I18.xlsx
+++ b/design/tables/I18.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Rcd7698b7bb66467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18" sheetId="1" r:id="Raae180969b7044af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6650,7 +6650,7 @@
         <x:v>ui.redesign.supplyHint</x:v>
       </x:c>
       <x:c r="C575" t="str">
-        <x:v>专属强化会随夜班进度成长</x:v>
+        <x:v>请选择一份补给，助你轻松渡过夜班！</x:v>
       </x:c>
     </x:row>
     <x:row r="576" ht="36" customHeight="1">
